--- a/セリフ編集/キャラタイプ別/蠱惑×強気.xlsx
+++ b/セリフ編集/キャラタイプ別/蠱惑×強気.xlsx
@@ -306,7 +306,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H280"/>
+  <dimension ref="A1:H315"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -2693,7 +2693,7 @@
       </c>
       <c r="F74" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">引き分け? 私は納得してないわよ。</t>
+          <t xml:space="preserve">決着つかず? 私は納得してないわよ。</t>
         </is>
       </c>
     </row>
@@ -2892,7 +2892,7 @@
     <row r="81" ht="40" customHeight="1">
       <c r="A81" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.default.bold.seductive[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B81" t="inlineStr" s="2">
@@ -2902,12 +2902,12 @@
       </c>
       <c r="C81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETAIN_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D81" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">default.bold.seductive[1]</t>
+          <t xml:space="preserve">accepted.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E81" t="inlineStr" s="2">
@@ -2917,14 +2917,14 @@
       </c>
       <c r="F81" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ終わりじゃないわ</t>
+          <t xml:space="preserve">もっと大きな舞台で証明してみせるわ。…見ていて</t>
         </is>
       </c>
     </row>
     <row r="82" ht="40" customHeight="1">
       <c r="A82" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.former_champ.bold.seductive[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.bold.seductive[2]</t>
         </is>
       </c>
       <c r="B82" t="inlineStr" s="2">
@@ -2934,12 +2934,12 @@
       </c>
       <c r="C82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETAIN_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D82" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">former_champ.bold.seductive[1]</t>
+          <t xml:space="preserve">accepted.bold.seductive[2]</t>
         </is>
       </c>
       <c r="E82" t="inlineStr" s="2">
@@ -2949,14 +2949,14 @@
       </c>
       <c r="F82" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう一シーズンだけ。結果を出すわ</t>
+          <t xml:space="preserve">行かせてもらうわ。世話になったわね</t>
         </is>
       </c>
     </row>
     <row r="83" ht="40" customHeight="1">
       <c r="A83" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.heel.bold.seductive[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B83" t="inlineStr" s="2">
@@ -2966,12 +2966,12 @@
       </c>
       <c r="C83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETAIN_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D83" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heel.bold.seductive[1]</t>
+          <t xml:space="preserve">defended.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E83" t="inlineStr" s="2">
@@ -2981,14 +2981,14 @@
       </c>
       <c r="F83" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">引き留めるの？ …悪くない判断ね</t>
+          <t xml:space="preserve">そこまで言うなら、残ってあげるわ</t>
         </is>
       </c>
     </row>
     <row r="84" ht="40" customHeight="1">
       <c r="A84" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.high_trust.bold.seductive[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.bold.seductive[2]</t>
         </is>
       </c>
       <c r="B84" t="inlineStr" s="2">
@@ -2998,12 +2998,12 @@
       </c>
       <c r="C84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETAIN_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D84" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">high_trust.bold.seductive[1]</t>
+          <t xml:space="preserve">defended.bold.seductive[2]</t>
         </is>
       </c>
       <c r="E84" t="inlineStr" s="2">
@@ -3013,14 +3013,14 @@
       </c>
       <c r="F84" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">信じてくれるの？ …もう少し付き合うわ</t>
+          <t xml:space="preserve">ふふ…簡単には手放さないのね。…悪い気はしないの</t>
         </is>
       </c>
     </row>
     <row r="85" ht="40" customHeight="1">
       <c r="A85" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_former_champ.bold.seductive[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B85" t="inlineStr" s="2">
@@ -3030,12 +3030,12 @@
       </c>
       <c r="C85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D85" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_former_champ.bold.seductive[1]</t>
+          <t xml:space="preserve">defense_failed.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E85" t="inlineStr" s="2">
@@ -3045,14 +3045,14 @@
       </c>
       <c r="F85" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最後に…もう一回輝かせてくれる？</t>
+          <t xml:space="preserve">…ごめんなさいね。でも、わたしの決意は固いの</t>
         </is>
       </c>
     </row>
     <row r="86" ht="40" customHeight="1">
       <c r="A86" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_heel.bold.seductive[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.bold.seductive[2]</t>
         </is>
       </c>
       <c r="B86" t="inlineStr" s="2">
@@ -3062,12 +3062,12 @@
       </c>
       <c r="C86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D86" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_heel.bold.seductive[1]</t>
+          <t xml:space="preserve">defense_failed.bold.seductive[2]</t>
         </is>
       </c>
       <c r="E86" t="inlineStr" s="2">
@@ -3077,14 +3077,14 @@
       </c>
       <c r="F86" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いいわよ。最後くらい大人しくしてあげる</t>
+          <t xml:space="preserve">止められても止まらないわ。じゃあね</t>
         </is>
       </c>
     </row>
     <row r="87" ht="40" customHeight="1">
       <c r="A87" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_no_title.bold.seductive[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.default.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B87" t="inlineStr" s="2">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="C87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
+          <t xml:space="preserve">RETAIN_LINES</t>
         </is>
       </c>
       <c r="D87" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_no_title.bold.seductive[1]</t>
+          <t xml:space="preserve">default.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E87" t="inlineStr" s="2">
@@ -3109,14 +3109,14 @@
       </c>
       <c r="F87" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんな終わり方なのね…わかったわ</t>
+          <t xml:space="preserve">まだ終わりじゃないわ</t>
         </is>
       </c>
     </row>
     <row r="88" ht="40" customHeight="1">
       <c r="A88" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.bold.seductive[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.former_champ.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B88" t="inlineStr" s="2">
@@ -3126,12 +3126,12 @@
       </c>
       <c r="C88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
+          <t xml:space="preserve">RETAIN_LINES</t>
         </is>
       </c>
       <c r="D88" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_terminal.bold.seductive[1]</t>
+          <t xml:space="preserve">former_champ.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E88" t="inlineStr" s="2">
@@ -3141,14 +3141,14 @@
       </c>
       <c r="F88" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…認めるわ。もう限界なの</t>
+          <t xml:space="preserve">もう一シーズンだけ。結果を出すわ</t>
         </is>
       </c>
     </row>
     <row r="89" ht="40" customHeight="1">
       <c r="A89" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_winless.bold.seductive[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.heel.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B89" t="inlineStr" s="2">
@@ -3158,12 +3158,12 @@
       </c>
       <c r="C89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
+          <t xml:space="preserve">RETAIN_LINES</t>
         </is>
       </c>
       <c r="D89" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_winless.bold.seductive[1]</t>
+          <t xml:space="preserve">heel.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E89" t="inlineStr" s="2">
@@ -3173,14 +3173,14 @@
       </c>
       <c r="F89" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">認めたくないけど…結果が全てよね</t>
+          <t xml:space="preserve">引き留めるの？ …悪くない判断ね</t>
         </is>
       </c>
     </row>
     <row r="90" ht="40" customHeight="1">
       <c r="A90" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.bold.seductive[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.high_trust.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B90" t="inlineStr" s="2">
@@ -3190,12 +3190,12 @@
       </c>
       <c r="C90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
+          <t xml:space="preserve">RETAIN_LINES</t>
         </is>
       </c>
       <c r="D90" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_champ.bold.seductive[1]</t>
+          <t xml:space="preserve">high_trust.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E90" t="inlineStr" s="2">
@@ -3205,14 +3205,14 @@
       </c>
       <c r="F90" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">王者を辞めさせる？ 100年早いわよ</t>
+          <t xml:space="preserve">信じてくれるの？ …もう少し付き合うわ</t>
         </is>
       </c>
     </row>
     <row r="91" ht="40" customHeight="1">
       <c r="A91" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_distrust.bold.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_former_champ.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B91" t="inlineStr" s="2">
@@ -3222,12 +3222,12 @@
       </c>
       <c r="C91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
         </is>
       </c>
       <c r="D91" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_distrust.bold.seductive[1]</t>
+          <t xml:space="preserve">accept_former_champ.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E91" t="inlineStr" s="2">
@@ -3237,14 +3237,14 @@
       </c>
       <c r="F91" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私が邪魔なの？ はっきり言ってくれる？</t>
+          <t xml:space="preserve">最後に…もう一回輝かせてくれる？</t>
         </is>
       </c>
     </row>
     <row r="92" ht="40" customHeight="1">
       <c r="A92" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_fighting.bold.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_heel.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B92" t="inlineStr" s="2">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="C92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
         </is>
       </c>
       <c r="D92" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_fighting.bold.seductive[1]</t>
+          <t xml:space="preserve">accept_heel.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E92" t="inlineStr" s="2">
@@ -3269,14 +3269,14 @@
       </c>
       <c r="F92" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">諦めるのはまだ早いわ。見ていて</t>
+          <t xml:space="preserve">…いいわよ。最後くらい大人しくしてあげる</t>
         </is>
       </c>
     </row>
     <row r="93" ht="40" customHeight="1">
       <c r="A93" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_heel.bold.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_no_title.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B93" t="inlineStr" s="2">
@@ -3286,12 +3286,12 @@
       </c>
       <c r="C93" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
         </is>
       </c>
       <c r="D93" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_heel.bold.seductive[1]</t>
+          <t xml:space="preserve">accept_no_title.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E93" t="inlineStr" s="2">
@@ -3301,14 +3301,14 @@
       </c>
       <c r="F93" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私がいなくなったら…この団体、終わるわよ？</t>
+          <t xml:space="preserve">こんな終わり方なのね…わかったわ</t>
         </is>
       </c>
     </row>
     <row r="94" ht="40" customHeight="1">
       <c r="A94" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.bold.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B94" t="inlineStr" s="2">
@@ -3318,12 +3318,12 @@
       </c>
       <c r="C94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
         </is>
       </c>
       <c r="D94" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A1_champion.bold.seductive[1]</t>
+          <t xml:space="preserve">accept_terminal.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E94" t="inlineStr" s="2">
@@ -3333,14 +3333,14 @@
       </c>
       <c r="F94" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最後まで背負い切ったわ。最高の景色だった</t>
+          <t xml:space="preserve">…認めるわ。もう限界なの</t>
         </is>
       </c>
     </row>
     <row r="95" ht="40" customHeight="1">
       <c r="A95" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.bold.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_winless.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B95" t="inlineStr" s="2">
@@ -3350,12 +3350,12 @@
       </c>
       <c r="C95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
         </is>
       </c>
       <c r="D95" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A2_uncrowned.bold.seductive[1]</t>
+          <t xml:space="preserve">accept_winless.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E95" t="inlineStr" s="2">
@@ -3365,14 +3365,14 @@
       </c>
       <c r="F95" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">逃げなかったわ。それだけは誇りに思ってる</t>
+          <t xml:space="preserve">認めたくないけど…結果が全てよね</t>
         </is>
       </c>
     </row>
     <row r="96" ht="40" customHeight="1">
       <c r="A96" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.bold.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B96" t="inlineStr" s="2">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="C96" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
         </is>
       </c>
       <c r="D96" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A3_heel.bold.seductive[1]</t>
+          <t xml:space="preserve">refuse_champ.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E96" t="inlineStr" s="2">
@@ -3397,14 +3397,14 @@
       </c>
       <c r="F96" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最後まで嫌われ者…ふふ、最高だったわ</t>
+          <t xml:space="preserve">王者を辞めさせる？ 100年早いわよ</t>
         </is>
       </c>
     </row>
     <row r="97" ht="40" customHeight="1">
       <c r="A97" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.bold.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_distrust.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B97" t="inlineStr" s="2">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="C97" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
         </is>
       </c>
       <c r="D97" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A4_veteran.bold.seductive[1]</t>
+          <t xml:space="preserve">refuse_distrust.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E97" t="inlineStr" s="2">
@@ -3429,14 +3429,14 @@
       </c>
       <c r="F97" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あっという間だったわ。悔いはないの</t>
+          <t xml:space="preserve">私が邪魔なの？ はっきり言ってくれる？</t>
         </is>
       </c>
     </row>
     <row r="98" ht="40" customHeight="1">
       <c r="A98" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B1_young.bold.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_fighting.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B98" t="inlineStr" s="2">
@@ -3446,12 +3446,12 @@
       </c>
       <c r="C98" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
         </is>
       </c>
       <c r="D98" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1_young.bold.seductive[1]</t>
+          <t xml:space="preserve">refuse_fighting.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E98" t="inlineStr" s="2">
@@ -3461,14 +3461,14 @@
       </c>
       <c r="F98" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">嘘…まだ始まったばかりじゃない…</t>
+          <t xml:space="preserve">諦めるのはまだ早いわ。見ていて</t>
         </is>
       </c>
     </row>
     <row r="99" ht="40" customHeight="1">
       <c r="A99" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.bold.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_heel.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B99" t="inlineStr" s="2">
@@ -3478,12 +3478,12 @@
       </c>
       <c r="C99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
         </is>
       </c>
       <c r="D99" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_prime.bold.seductive[1]</t>
+          <t xml:space="preserve">refuse_heel.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E99" t="inlineStr" s="2">
@@ -3493,14 +3493,14 @@
       </c>
       <c r="F99" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだやれると信じてたのに…</t>
+          <t xml:space="preserve">私がいなくなったら…この団体、終わるわよ？</t>
         </is>
       </c>
     </row>
     <row r="100" ht="40" customHeight="1">
       <c r="A100" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B3_older.bold.seductive[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B100" t="inlineStr" s="2">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="D100" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B3_older.bold.seductive[1]</t>
+          <t xml:space="preserve">A1_champion.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E100" t="inlineStr" s="2">
@@ -3525,14 +3525,14 @@
       </c>
       <c r="F100" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">体は限界だけど…心はまだ燃えてるわ</t>
+          <t xml:space="preserve">最後まで背負い切ったわ。最高の景色だった</t>
         </is>
       </c>
     </row>
     <row r="101" ht="40" customHeight="1">
       <c r="A101" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.bold.seductive[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B101" t="inlineStr" s="2">
@@ -3547,7 +3547,7 @@
       </c>
       <c r="D101" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_champion_injury.bold.seductive[1]</t>
+          <t xml:space="preserve">A2_uncrowned.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E101" t="inlineStr" s="2">
@@ -3557,14 +3557,14 @@
       </c>
       <c r="F101" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオンのまま終わるなんて…残酷ね</t>
+          <t xml:space="preserve">逃げなかったわ。それだけは誇りに思ってる</t>
         </is>
       </c>
     </row>
     <row r="102" ht="40" customHeight="1">
       <c r="A102" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VOLUNTARY_STAY_LINES.bold.seductive[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B102" t="inlineStr" s="2">
@@ -3574,12 +3574,12 @@
       </c>
       <c r="C102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">VOLUNTARY_STAY_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D102" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[1]</t>
+          <t xml:space="preserve">A3_heel.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E102" t="inlineStr" s="2">
@@ -3589,14 +3589,14 @@
       </c>
       <c r="F102" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">残るわ。ここで一番になるって決めたの</t>
+          <t xml:space="preserve">最後まで嫌われ者…ふふ、最高だったわ</t>
         </is>
       </c>
     </row>
     <row r="103" ht="40" customHeight="1">
       <c r="A103" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.bold.seductive[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B103" t="inlineStr" s="2">
@@ -3606,29 +3606,29 @@
       </c>
       <c r="C103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D103" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_accept.bold.seductive[1]</t>
+          <t xml:space="preserve">A4_veteran.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F103" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、分かってくれるじゃない♡ 期待しててね。</t>
+          <t xml:space="preserve">あっという間だったわ。悔いはないの</t>
         </is>
       </c>
     </row>
     <row r="104" ht="40" customHeight="1">
       <c r="A104" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.bold.seductive[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B1_young.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B104" t="inlineStr" s="2">
@@ -3638,29 +3638,29 @@
       </c>
       <c r="C104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D104" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_accept.bold.seductive[1]</t>
+          <t xml:space="preserve">B1_young.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F104" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……まあ、少しは考えてくれたのね。次はもっと期待してるわよ♡</t>
+          <t xml:space="preserve">嘘…まだ始まったばかりじゃない…</t>
         </is>
       </c>
     </row>
     <row r="105" ht="40" customHeight="1">
       <c r="A105" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.bold.seductive[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B105" t="inlineStr" s="2">
@@ -3670,29 +3670,29 @@
       </c>
       <c r="C105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D105" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_refuse.bold.seductive[1]</t>
+          <t xml:space="preserve">B2_prime.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F105" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ふうん。まあいいわ。でもね、次はないからね？</t>
+          <t xml:space="preserve">まだやれると信じてたのに…</t>
         </is>
       </c>
     </row>
     <row r="106" ht="40" customHeight="1">
       <c r="A106" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.bold.seductive[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B3_older.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B106" t="inlineStr" s="2">
@@ -3702,29 +3702,29 @@
       </c>
       <c r="C106" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D106" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.bold.seductive[1]</t>
+          <t xml:space="preserve">B3_older.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E106" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F106" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ねえ社長。{tenure}もうちょっと私のこと大事にしてくれてもいいんじゃない？ {record}</t>
+          <t xml:space="preserve">体は限界だけど…心はまだ燃えてるわ</t>
         </is>
       </c>
     </row>
     <row r="107" ht="40" customHeight="1">
       <c r="A107" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.bold.seductive[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B107" t="inlineStr" s="2">
@@ -3734,29 +3734,29 @@
       </c>
       <c r="C107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D107" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_refuse.bold.seductive[1]</t>
+          <t xml:space="preserve">B4_champion_injury.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F107" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ふうん。まあいいけど、我慢にも限度があるからね？</t>
+          <t xml:space="preserve">チャンピオンのまま終わるなんて…残酷ね</t>
         </is>
       </c>
     </row>
     <row r="108" ht="40" customHeight="1">
       <c r="A108" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.bold.seductive[1]</t>
+          <t xml:space="preserve">VOLUNTARY_STAY_LINES.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B108" t="inlineStr" s="2">
@@ -3766,29 +3766,29 @@
       </c>
       <c r="C108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">VOLUNTARY_STAY_LINES</t>
         </is>
       </c>
       <c r="D108" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_listen.bold.seductive[1]</t>
+          <t xml:space="preserve">bold.seductive[1]</t>
         </is>
       </c>
       <c r="E108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F108" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……聞いてくれるの。{record}正直ね、もっと大きな舞台が見たいの。</t>
+          <t xml:space="preserve">残るわ。ここで一番になるって決めたの</t>
         </is>
       </c>
     </row>
     <row r="109" ht="40" customHeight="1">
       <c r="A109" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.bold.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B109" t="inlineStr" s="2">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="D109" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.bold.seductive[1]</t>
+          <t xml:space="preserve">raise_accept.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E109" t="inlineStr" s="2">
@@ -3813,14 +3813,14 @@
       </c>
       <c r="F109" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長。{tenure}もう決めたの。…ここを出るわ。</t>
+          <t xml:space="preserve">ふふ、分かってくれるじゃない♡ 期待しててね。</t>
         </is>
       </c>
     </row>
     <row r="110" ht="40" customHeight="1">
       <c r="A110" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.bold.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B110" t="inlineStr" s="2">
@@ -3835,7 +3835,7 @@
       </c>
       <c r="D110" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_release.bold.seductive[1]</t>
+          <t xml:space="preserve">raise_negotiate_accept.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E110" t="inlineStr" s="2">
@@ -3845,14 +3845,14 @@
       </c>
       <c r="F110" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ふふ、予想通りね。{rivalry}じゃあね、社長。</t>
+          <t xml:space="preserve">……まあ、少しは考えてくれたのね。次はもっと期待してるわよ♡</t>
         </is>
       </c>
     </row>
     <row r="111" ht="40" customHeight="1">
       <c r="A111" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.bold.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B111" t="inlineStr" s="2">
@@ -3867,7 +3867,7 @@
       </c>
       <c r="D111" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_fail.bold.seductive[1]</t>
+          <t xml:space="preserve">raise_negotiate_refuse.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E111" t="inlineStr" s="2">
@@ -3877,14 +3877,14 @@
       </c>
       <c r="F111" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……悪いけど、もう決めたの。…引き止めても無駄よ。</t>
+          <t xml:space="preserve">……ふうん。まあいいわ。でもね、次はないからね？</t>
         </is>
       </c>
     </row>
     <row r="112" ht="40" customHeight="1">
       <c r="A112" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.bold.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B112" t="inlineStr" s="2">
@@ -3899,7 +3899,7 @@
       </c>
       <c r="D112" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_success.bold.seductive[1]</t>
+          <t xml:space="preserve">raise_open.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E112" t="inlineStr" s="2">
@@ -3909,402 +3909,402 @@
       </c>
       <c r="F112" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……仕方ないわね。そこまで言うなら、もう少しだけ付き合ってあげる。</t>
+          <t xml:space="preserve">ねえ社長。{tenure}もうちょっと私のこと大事にしてくれてもいいんじゃない？ {record}</t>
         </is>
       </c>
     </row>
     <row r="113" ht="40" customHeight="1">
       <c r="A113" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.bold.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">raise_refuse.bold.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……ふうん。まあいいけど、我慢にも限度があるからね？</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="40" customHeight="1">
+      <c r="A114" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.bold.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">sudden_departure.bold.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">社長、もう無理よ。お世話になりました……って言いたいところだけど、正直そんな気にもなれないの。</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="40" customHeight="1">
+      <c r="A115" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.bold.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">sudden_departure.bold.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">もう決めたの。これ以上ここにいる理由がないもの。……じゃあね。</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="40" customHeight="1">
+      <c r="A116" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.bold.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_listen.bold.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……聞いてくれるの。{record}正直ね、もっと大きな舞台が見たいの。</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="40" customHeight="1">
+      <c r="A117" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.bold.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_open.bold.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">社長。{tenure}もう決めたの。…ここを出るわ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="40" customHeight="1">
+      <c r="A118" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.bold.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_release.bold.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……ふふ、予想通りね。{rivalry}じゃあね、社長。</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="40" customHeight="1">
+      <c r="A119" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.bold.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_retain_fail.bold.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……悪いけど、もう決めたの。…引き止めても無駄よ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="40" customHeight="1">
+      <c r="A120" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.bold.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_retain_success.bold.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……仕方ないわね。そこまで言うなら、もう少しだけ付き合ってあげる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="40" customHeight="1">
+      <c r="A121" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">NEGOTIATE_LINES.blocked.bold.seductive[1]</t>
         </is>
       </c>
-      <c r="B113" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr" s="2">
+      <c r="B121" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr" s="12">
+      <c r="D121" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">blocked.bold.seductive[1]</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr" s="2">
+      <c r="E121" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F113" t="inlineStr" s="3">
+      <c r="F121" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">ふふ…買いかぶってくれてありがとう。
 でも今の仲間を裏切るつもりは毛頭ないわ</t>
         </is>
       </c>
     </row>
-    <row r="114" ht="40" customHeight="1">
-      <c r="A114" t="inlineStr" s="15">
+    <row r="122" ht="40" customHeight="1">
+      <c r="A122" t="inlineStr" s="15">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES.fail.bold.seductive[1]</t>
         </is>
       </c>
-      <c r="B114" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr" s="2">
+      <c r="B122" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr" s="12">
+      <c r="D122" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">fail.bold.seductive[1]</t>
         </is>
       </c>
-      <c r="E114" t="inlineStr" s="2">
+      <c r="E122" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F114" t="inlineStr" s="3">
+      <c r="F122" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">ここが私の居場所なの。
 出直してきて</t>
         </is>
       </c>
     </row>
-    <row r="115" ht="40" customHeight="1">
-      <c r="A115" t="inlineStr" s="15">
+    <row r="123" ht="40" customHeight="1">
+      <c r="A123" t="inlineStr" s="15">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES.start.bold.seductive[1]</t>
         </is>
       </c>
-      <c r="B115" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr" s="2">
+      <c r="B123" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr" s="12">
+      <c r="D123" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">start.bold.seductive[1]</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr" s="2">
+      <c r="E123" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F115" t="inlineStr" s="3">
+      <c r="F123" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">私を引き抜こうだなんて…
 ふふ、面白い度胸してるわね</t>
         </is>
       </c>
     </row>
-    <row r="116" ht="40" customHeight="1">
-      <c r="A116" t="inlineStr" s="15">
+    <row r="124" ht="40" customHeight="1">
+      <c r="A124" t="inlineStr" s="15">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES.success.bold.seductive[1]</t>
         </is>
       </c>
-      <c r="B116" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr" s="2">
+      <c r="B124" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr" s="12">
+      <c r="D124" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">success.bold.seductive[1]</t>
         </is>
       </c>
-      <c r="E116" t="inlineStr" s="2">
+      <c r="E124" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F116" t="inlineStr" s="3">
+      <c r="F124" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">認めてあげるわ。
 格の違いを見せてあげる</t>
         </is>
       </c>
     </row>
-    <row r="117" ht="40" customHeight="1">
-      <c r="A117" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_ABSTRACT.seductive.bold[1]</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_ABSTRACT.seductive.bold[1]</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">社長、私たちのこと、もう少し気にかけて。寂しくなっちゃうから。</t>
-        </is>
-      </c>
-    </row>
-    <row r="118" ht="40" customHeight="1">
-      <c r="A118" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MAIN.seductive.bold[1]</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_MAIN.seductive.bold[1]</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">社長、次のメイン、私に任せてくれない? 必ず客を沸かすから。</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="40" customHeight="1">
-      <c r="A119" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MONEY.seductive.bold[1]</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_MONEY.seductive.bold[1]</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">社長、私たちの給料の話、ちょっと聞いてくれない?</t>
-        </is>
-      </c>
-    </row>
-    <row r="120" ht="40" customHeight="1">
-      <c r="A120" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_RECOGNITION.seductive.bold[1]</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_RECOGNITION.seductive.bold[1]</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">社長、私の貢献、ちゃんと見てくれてる? 確かめさせて。</t>
-        </is>
-      </c>
-    </row>
-    <row r="121" ht="40" customHeight="1">
-      <c r="A121" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.A.seductive.bold[1]</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.A.seductive.bold[1]</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">ありがとう社長、嬉しい。ちゃんと届いてたんだね。</t>
-        </is>
-      </c>
-    </row>
-    <row r="122" ht="40" customHeight="1">
-      <c r="A122" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.B.seductive.bold[1]</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.B.seductive.bold[1]</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">…そう。じゃあ、忘れて。</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" ht="40" customHeight="1">
-      <c r="A123" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.C.seductive.bold[1]</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.C.seductive.bold[1]</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">…そう、別ルートね。それも嬉しい、ありがとう。</t>
-        </is>
-      </c>
-    </row>
-    <row r="124" ht="40" customHeight="1">
-      <c r="A124" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.A.seductive.bold[1]</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.A.seductive.bold[1]</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">ありがとう、社長。期待してて、ちゃんと魅せるから。</t>
-        </is>
-      </c>
-    </row>
     <row r="125" ht="40" customHeight="1">
       <c r="A125" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.B.seductive.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_ABSTRACT.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B125" t="inlineStr" s="2">
@@ -4319,7 +4319,7 @@
       </c>
       <c r="D125" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.B.seductive.bold[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_ABSTRACT.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E125" t="inlineStr" s="2">
@@ -4329,14 +4329,14 @@
       </c>
       <c r="F125" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そう。じゃあ、覚えておくね。</t>
+          <t xml:space="preserve">社長、私たちのこと、もう少し気にかけて。寂しくなっちゃうから。</t>
         </is>
       </c>
     </row>
     <row r="126" ht="40" customHeight="1">
       <c r="A126" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.C.seductive.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MAIN.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B126" t="inlineStr" s="2">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="D126" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.C.seductive.bold[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_MAIN.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E126" t="inlineStr" s="2">
@@ -4361,14 +4361,14 @@
       </c>
       <c r="F126" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そう。それも悪くないかもね。ありがとう。</t>
+          <t xml:space="preserve">社長、次のメイン、私に任せてくれない? 必ず客を沸かすから。</t>
         </is>
       </c>
     </row>
     <row r="127" ht="40" customHeight="1">
       <c r="A127" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.A.seductive.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MONEY.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B127" t="inlineStr" s="2">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="D127" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.A.seductive.bold[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_MONEY.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E127" t="inlineStr" s="2">
@@ -4393,14 +4393,14 @@
       </c>
       <c r="F127" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとう社長、嬉しい。みんなにも伝えるね。</t>
+          <t xml:space="preserve">社長、私たちの給料の話、ちょっと聞いてくれない?</t>
         </is>
       </c>
     </row>
     <row r="128" ht="40" customHeight="1">
       <c r="A128" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.B.seductive.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_RECOGNITION.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B128" t="inlineStr" s="2">
@@ -4415,7 +4415,7 @@
       </c>
       <c r="D128" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.B.seductive.bold[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_RECOGNITION.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E128" t="inlineStr" s="2">
@@ -4425,14 +4425,14 @@
       </c>
       <c r="F128" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そう。わかった、また話そうね。</t>
+          <t xml:space="preserve">社長、私の貢献、ちゃんと見てくれてる? 確かめさせて。</t>
         </is>
       </c>
     </row>
     <row r="129" ht="40" customHeight="1">
       <c r="A129" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.C.seductive.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.A.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B129" t="inlineStr" s="2">
@@ -4447,7 +4447,7 @@
       </c>
       <c r="D129" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.C.seductive.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.A.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E129" t="inlineStr" s="2">
@@ -4457,14 +4457,14 @@
       </c>
       <c r="F129" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ふぅん、お金じゃないんだ。まあ、それも嬉しいよ。</t>
+          <t xml:space="preserve">ありがとう社長、嬉しい。ちゃんと届いてたんだね。</t>
         </is>
       </c>
     </row>
     <row r="130" ht="40" customHeight="1">
       <c r="A130" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.A.seductive.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.B.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B130" t="inlineStr" s="2">
@@ -4479,7 +4479,7 @@
       </c>
       <c r="D130" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.A.seductive.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.B.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E130" t="inlineStr" s="2">
@@ -4489,14 +4489,14 @@
       </c>
       <c r="F130" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとう社長、嬉しい。ちゃんと見ててくれたんだね。</t>
+          <t xml:space="preserve">…そう。じゃあ、忘れて。</t>
         </is>
       </c>
     </row>
     <row r="131" ht="40" customHeight="1">
       <c r="A131" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.B.seductive.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.C.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B131" t="inlineStr" s="2">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="D131" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.B.seductive.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.C.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E131" t="inlineStr" s="2">
@@ -4521,14 +4521,14 @@
       </c>
       <c r="F131" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そう。じゃあ忘れて。</t>
+          <t xml:space="preserve">…そう、別ルートね。それも嬉しい、ありがとう。</t>
         </is>
       </c>
     </row>
     <row r="132" ht="40" customHeight="1">
       <c r="A132" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.C.seductive.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.A.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B132" t="inlineStr" s="2">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="D132" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.C.seductive.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.A.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E132" t="inlineStr" s="2">
@@ -4553,14 +4553,14 @@
       </c>
       <c r="F132" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そう、別の形ね。それも嬉しい、ありがとう。</t>
+          <t xml:space="preserve">ありがとう、社長。期待してて、ちゃんと魅せるから。</t>
         </is>
       </c>
     </row>
     <row r="133" ht="40" customHeight="1">
       <c r="A133" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.A.seductive.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.B.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B133" t="inlineStr" s="2">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="D133" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.A.seductive.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.B.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E133" t="inlineStr" s="2">
@@ -4585,14 +4585,14 @@
       </c>
       <c r="F133" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そう、次は声かけるね。ごめんなさい。</t>
+          <t xml:space="preserve">…そう。じゃあ、覚えておくね。</t>
         </is>
       </c>
     </row>
     <row r="134" ht="40" customHeight="1">
       <c r="A134" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.B.seductive.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.C.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B134" t="inlineStr" s="2">
@@ -4607,7 +4607,7 @@
       </c>
       <c r="D134" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.B.seductive.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.C.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E134" t="inlineStr" s="2">
@@ -4617,14 +4617,14 @@
       </c>
       <c r="F134" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとう。仲間内の付き合いも、大事だからね。</t>
+          <t xml:space="preserve">…そう。それも悪くないかもね。ありがとう。</t>
         </is>
       </c>
     </row>
     <row r="135" ht="40" customHeight="1">
       <c r="A135" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.A.seductive.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.A.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B135" t="inlineStr" s="2">
@@ -4639,7 +4639,7 @@
       </c>
       <c r="D135" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.A.seductive.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.A.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E135" t="inlineStr" s="2">
@@ -4649,14 +4649,14 @@
       </c>
       <c r="F135" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そう、気をつけるね。</t>
+          <t xml:space="preserve">ありがとう社長、嬉しい。みんなにも伝えるね。</t>
         </is>
       </c>
     </row>
     <row r="136" ht="40" customHeight="1">
       <c r="A136" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.B.seductive.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.B.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B136" t="inlineStr" s="2">
@@ -4671,7 +4671,7 @@
       </c>
       <c r="D136" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.B.seductive.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.B.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E136" t="inlineStr" s="2">
@@ -4681,14 +4681,14 @@
       </c>
       <c r="F136" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとう、社長。</t>
+          <t xml:space="preserve">…そう。わかった、また話そうね。</t>
         </is>
       </c>
     </row>
     <row r="137" ht="40" customHeight="1">
       <c r="A137" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.A.seductive.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.C.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B137" t="inlineStr" s="2">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="D137" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.A.seductive.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.C.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E137" t="inlineStr" s="2">
@@ -4713,14 +4713,14 @@
       </c>
       <c r="F137" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そう、線を引くね。客はノッてたんだけど。</t>
+          <t xml:space="preserve">…ふぅん、お金じゃないんだ。まあ、それも嬉しいよ。</t>
         </is>
       </c>
     </row>
     <row r="138" ht="40" customHeight="1">
       <c r="A138" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.B.seductive.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.A.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B138" t="inlineStr" s="2">
@@ -4735,7 +4735,7 @@
       </c>
       <c r="D138" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.B.seductive.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.A.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E138" t="inlineStr" s="2">
@@ -4745,14 +4745,14 @@
       </c>
       <c r="F138" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとう、社長。これも仕事だからね。</t>
+          <t xml:space="preserve">ありがとう社長、嬉しい。ちゃんと見ててくれたんだね。</t>
         </is>
       </c>
     </row>
     <row r="139" ht="40" customHeight="1">
       <c r="A139" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.A.seductive.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.B.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B139" t="inlineStr" s="2">
@@ -4767,7 +4767,7 @@
       </c>
       <c r="D139" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.A.seductive.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.B.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E139" t="inlineStr" s="2">
@@ -4777,14 +4777,14 @@
       </c>
       <c r="F139" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ごめん、社長。明日から、ちゃんと出るね。</t>
+          <t xml:space="preserve">…そう。じゃあ忘れて。</t>
         </is>
       </c>
     </row>
     <row r="140" ht="40" customHeight="1">
       <c r="A140" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.B.seductive.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.C.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B140" t="inlineStr" s="2">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="D140" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.B.seductive.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.C.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E140" t="inlineStr" s="2">
@@ -4809,14 +4809,14 @@
       </c>
       <c r="F140" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとう、社長。お返しは、ちゃんとするから。</t>
+          <t xml:space="preserve">…そう、別の形ね。それも嬉しい、ありがとう。</t>
         </is>
       </c>
     </row>
     <row r="141" ht="40" customHeight="1">
       <c r="A141" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.C.seductive.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.A.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B141" t="inlineStr" s="2">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="D141" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.C.seductive.bold[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.A.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E141" t="inlineStr" s="2">
@@ -4841,14 +4841,14 @@
       </c>
       <c r="F141" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そう、メンバー優先ね。ありがとう。</t>
+          <t xml:space="preserve">…そう、次は声かけるね。ごめんなさい。</t>
         </is>
       </c>
     </row>
     <row r="142" ht="40" customHeight="1">
       <c r="A142" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.A.seductive.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.B.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B142" t="inlineStr" s="2">
@@ -4863,7 +4863,7 @@
       </c>
       <c r="D142" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.A.seductive.bold[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.B.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E142" t="inlineStr" s="2">
@@ -4873,14 +4873,14 @@
       </c>
       <c r="F142" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとう、社長。ちょっと休むね。</t>
+          <t xml:space="preserve">…ありがとう。仲間内の付き合いも、大事だからね。</t>
         </is>
       </c>
     </row>
     <row r="143" ht="40" customHeight="1">
       <c r="A143" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.B.seductive.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.A.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B143" t="inlineStr" s="2">
@@ -4895,7 +4895,7 @@
       </c>
       <c r="D143" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.B.seductive.bold[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.A.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E143" t="inlineStr" s="2">
@@ -4905,14 +4905,14 @@
       </c>
       <c r="F143" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…大丈夫、まだ平気だよ。</t>
+          <t xml:space="preserve">…そう、気をつけるね。</t>
         </is>
       </c>
     </row>
     <row r="144" ht="40" customHeight="1">
       <c r="A144" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.C.seductive.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.B.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B144" t="inlineStr" s="2">
@@ -4927,7 +4927,7 @@
       </c>
       <c r="D144" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.C.seductive.bold[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.B.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E144" t="inlineStr" s="2">
@@ -4937,14 +4937,14 @@
       </c>
       <c r="F144" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そう、メンバーケアね。私も助かる、ありがとう。</t>
+          <t xml:space="preserve">…ありがとう、社長。</t>
         </is>
       </c>
     </row>
     <row r="145" ht="40" customHeight="1">
       <c r="A145" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.A.seductive.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.A.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B145" t="inlineStr" s="2">
@@ -4959,7 +4959,7 @@
       </c>
       <c r="D145" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.A.seductive.bold[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.A.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E145" t="inlineStr" s="2">
@@ -4969,14 +4969,14 @@
       </c>
       <c r="F145" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そう。私から皆に話すね。</t>
+          <t xml:space="preserve">…そう、線を引くね。客はノッてたんだけど。</t>
         </is>
       </c>
     </row>
     <row r="146" ht="40" customHeight="1">
       <c r="A146" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.B.seductive.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.B.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B146" t="inlineStr" s="2">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="D146" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.B.seductive.bold[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.B.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E146" t="inlineStr" s="2">
@@ -5001,14 +5001,14 @@
       </c>
       <c r="F146" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとう、社長。穏便にね。</t>
+          <t xml:space="preserve">…ありがとう、社長。これも仕事だからね。</t>
         </is>
       </c>
     </row>
     <row r="147" ht="40" customHeight="1">
       <c r="A147" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.C.seductive.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.A.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B147" t="inlineStr" s="2">
@@ -5023,7 +5023,7 @@
       </c>
       <c r="D147" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.C.seductive.bold[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.A.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E147" t="inlineStr" s="2">
@@ -5033,14 +5033,14 @@
       </c>
       <c r="F147" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そう、下の子のケアね。ありがとう。</t>
+          <t xml:space="preserve">…ごめん、社長。明日から、ちゃんと出るね。</t>
         </is>
       </c>
     </row>
     <row r="148" ht="40" customHeight="1">
       <c r="A148" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.A.seductive.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.B.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B148" t="inlineStr" s="2">
@@ -5055,7 +5055,7 @@
       </c>
       <c r="D148" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.A.seductive.bold[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.B.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E148" t="inlineStr" s="2">
@@ -5065,14 +5065,14 @@
       </c>
       <c r="F148" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そう。気をつけるね。</t>
+          <t xml:space="preserve">…ありがとう、社長。お返しは、ちゃんとするから。</t>
         </is>
       </c>
     </row>
     <row r="149" ht="40" customHeight="1">
       <c r="A149" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.B.seductive.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.C.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B149" t="inlineStr" s="2">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="D149" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.B.seductive.bold[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.C.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E149" t="inlineStr" s="2">
@@ -5097,14 +5097,14 @@
       </c>
       <c r="F149" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（小さく息を吐いて、視線を逸らした）</t>
+          <t xml:space="preserve">…そう、メンバー優先ね。ありがとう。</t>
         </is>
       </c>
     </row>
     <row r="150" ht="40" customHeight="1">
       <c r="A150" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.C.seductive.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.A.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B150" t="inlineStr" s="2">
@@ -5119,7 +5119,7 @@
       </c>
       <c r="D150" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.C.seductive.bold[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.A.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E150" t="inlineStr" s="2">
@@ -5129,14 +5129,14 @@
       </c>
       <c r="F150" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そう、別ルートね。ありがとう。</t>
+          <t xml:space="preserve">…ありがとう、社長。ちょっと休むね。</t>
         </is>
       </c>
     </row>
     <row r="151" ht="40" customHeight="1">
       <c r="A151" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.A.seductive.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.B.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="2">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="D151" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.A.seductive.bold[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.B.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E151" t="inlineStr" s="2">
@@ -5161,14 +5161,14 @@
       </c>
       <c r="F151" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そうね、緩めるね。怪我させたくないし。</t>
+          <t xml:space="preserve">…大丈夫、まだ平気だよ。</t>
         </is>
       </c>
     </row>
     <row r="152" ht="40" customHeight="1">
       <c r="A152" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.B.seductive.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.C.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B152" t="inlineStr" s="2">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="D152" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.B.seductive.bold[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.C.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E152" t="inlineStr" s="2">
@@ -5193,14 +5193,14 @@
       </c>
       <c r="F152" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとう、社長。このまま続けるね。</t>
+          <t xml:space="preserve">…そう、メンバーケアね。私も助かる、ありがとう。</t>
         </is>
       </c>
     </row>
     <row r="153" ht="40" customHeight="1">
       <c r="A153" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.C.seductive.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.A.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="2">
@@ -5215,7 +5215,7 @@
       </c>
       <c r="D153" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.C.seductive.bold[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.A.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E153" t="inlineStr" s="2">
@@ -5225,14 +5225,14 @@
       </c>
       <c r="F153" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そう、子たち優先ね。ありがとう。</t>
+          <t xml:space="preserve">…そう。私から皆に話すね。</t>
         </is>
       </c>
     </row>
     <row r="154" ht="40" customHeight="1">
       <c r="A154" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES.bold.attack.seductive</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.B.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B154" t="inlineStr" s="2">
@@ -5242,12 +5242,12 @@
       </c>
       <c r="C154" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D154" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.attack.seductive</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.B.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E154" t="inlineStr" s="2">
@@ -5257,14 +5257,14 @@
       </c>
       <c r="F154" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう、隣には立てないわ</t>
+          <t xml:space="preserve">…ありがとう、社長。穏便にね。</t>
         </is>
       </c>
     </row>
     <row r="155" ht="40" customHeight="1">
       <c r="A155" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES.bold.defend.seductive</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.C.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="2">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="C155" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D155" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.defend.seductive</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.C.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E155" t="inlineStr" s="2">
@@ -5289,29 +5289,29 @@
       </c>
       <c r="F155" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">上等よ。受けて立つわ</t>
+          <t xml:space="preserve">…そう、下の子のケアね。ありがとう。</t>
         </is>
       </c>
     </row>
     <row r="156" ht="40" customHeight="1">
       <c r="A156" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F04_TARGET_LINES.bold.seductive[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.A.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F04_TARGET_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D156" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.A.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E156" t="inlineStr" s="2">
@@ -5321,14 +5321,14 @@
       </c>
       <c r="F156" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ……今、一番息ができるのは、あの人たちの隣なの。</t>
+          <t xml:space="preserve">…そう。気をつけるね。</t>
         </is>
       </c>
     </row>
     <row r="157" ht="40" customHeight="1">
       <c r="A157" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES.bold.seductive[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.B.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="2">
@@ -5338,29 +5338,29 @@
       </c>
       <c r="C157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D157" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.B.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F157" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">当然よ。まだまだこんなものじゃないわ</t>
+          <t xml:space="preserve">（小さく息を吐いて、視線を逸らした）</t>
         </is>
       </c>
     </row>
     <row r="158" ht="40" customHeight="1">
       <c r="A158" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES.bold.seductive[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.C.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B158" t="inlineStr" s="2">
@@ -5370,29 +5370,29 @@
       </c>
       <c r="C158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D158" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.C.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F158" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう少し…あと少しで何かが掴めそうなの</t>
+          <t xml:space="preserve">…そう、別ルートね。ありがとう。</t>
         </is>
       </c>
     </row>
     <row r="159" ht="40" customHeight="1">
       <c r="A159" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES.bold.seductive[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.A.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="2">
@@ -5402,29 +5402,29 @@
       </c>
       <c r="C159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D159" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.A.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F159" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">燃えないの…何をしても、火がつかないわ</t>
+          <t xml:space="preserve">…そうね、緩めるね。怪我させたくないし。</t>
         </is>
       </c>
     </row>
     <row r="160" ht="40" customHeight="1">
       <c r="A160" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.bold.seductive[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.B.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="2">
@@ -5434,29 +5434,29 @@
       </c>
       <c r="C160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D160" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.B.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F160" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">目が覚めたわ。ここで終わるなんて、つまらないもの</t>
+          <t xml:space="preserve">…ありがとう、社長。このまま続けるね。</t>
         </is>
       </c>
     </row>
     <row r="161" ht="40" customHeight="1">
       <c r="A161" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES.bold.seductive[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.C.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
@@ -5466,29 +5466,29 @@
       </c>
       <c r="C161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D161" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.C.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F161" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お待たせ。ここからが本番よ</t>
+          <t xml:space="preserve">…そう、子たち優先ね。ありがとう。</t>
         </is>
       </c>
     </row>
     <row r="162" ht="40" customHeight="1">
       <c r="A162" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.defeat.bold.seductive[1]</t>
+          <t xml:space="preserve">FACTION_F02_LINES.bold.attack.seductive</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
@@ -5498,29 +5498,29 @@
       </c>
       <c r="C162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
         </is>
       </c>
       <c r="D162" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defeat.bold.seductive[1]</t>
+          <t xml:space="preserve">bold.attack.seductive</t>
         </is>
       </c>
       <c r="E162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F162" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら…おかしいわね、こんなはずじゃ</t>
+          <t xml:space="preserve">もう、隣には立てないわ</t>
         </is>
       </c>
     </row>
     <row r="163" ht="40" customHeight="1">
       <c r="A163" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.bold.seductive[1]</t>
+          <t xml:space="preserve">FACTION_F02_LINES.bold.defend.seductive</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
@@ -5530,61 +5530,61 @@
       </c>
       <c r="C163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
         </is>
       </c>
       <c r="D163" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_moderate_recovery.bold.seductive[1]</t>
+          <t xml:space="preserve">bold.defend.seductive</t>
         </is>
       </c>
       <c r="E163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F163" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">治ったはずなのに…おかしいわね</t>
+          <t xml:space="preserve">上等よ。受けて立つわ</t>
         </is>
       </c>
     </row>
     <row r="164" ht="40" customHeight="1">
       <c r="A164" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.bold.seductive[1]</t>
+          <t xml:space="preserve">FACTION_F04_TARGET_LINES.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
         </is>
       </c>
       <c r="C164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">FACTION_F04_TARGET_LINES</t>
         </is>
       </c>
       <c r="D164" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_severe_recovery.bold.seductive[1]</t>
+          <t xml:space="preserve">bold.seductive[1]</t>
         </is>
       </c>
       <c r="E164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F164" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私が…怯えてる？ 嘘でしょう</t>
+          <t xml:space="preserve">ふふ……今、一番息ができるのは、あの人たちの隣なの。</t>
         </is>
       </c>
     </row>
     <row r="165" ht="40" customHeight="1">
       <c r="A165" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.bold.seductive[1]</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="C165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
         </is>
       </c>
       <c r="D165" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">penalty_end.bold.seductive[1]</t>
+          <t xml:space="preserve">bold.seductive[1]</t>
         </is>
       </c>
       <c r="E165" t="inlineStr" s="2">
@@ -5609,14 +5609,14 @@
       </c>
       <c r="F165" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">体は万全なのに…気持ちがついてこないの</t>
+          <t xml:space="preserve">当然よ。まだまだこんなものじゃないわ</t>
         </is>
       </c>
     </row>
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.bold.seductive[1]</t>
+          <t xml:space="preserve">BT_HINT_LINES.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -5626,29 +5626,29 @@
       </c>
       <c r="C166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">BT_HINT_LINES</t>
         </is>
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.bold.seductive[1]</t>
+          <t xml:space="preserve">bold.seductive[1]</t>
         </is>
       </c>
       <c r="E166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F166" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全力を引き出してくれた相手に感謝。…次はもっと激しくいくわよ？</t>
+          <t xml:space="preserve">もう少し…あと少しで何かが掴めそうなの</t>
         </is>
       </c>
     </row>
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.bold.seductive[1]</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -5658,29 +5658,29 @@
       </c>
       <c r="C167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
         </is>
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.bold.seductive[1]</t>
+          <t xml:space="preserve">bold.seductive[1]</t>
         </is>
       </c>
       <c r="E167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F167" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頂点からの景色は最高よ。…あなたには見せてあげないけど</t>
+          <t xml:space="preserve">燃えないの…何をしても、火がつかないわ</t>
         </is>
       </c>
     </row>
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.bold.seductive[1]</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
@@ -5690,29 +5690,29 @@
       </c>
       <c r="C168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
         </is>
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.bold.seductive[1]</t>
+          <t xml:space="preserve">bold.seductive[1]</t>
         </is>
       </c>
       <c r="E168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F168" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高の舞台で、最高の人生だった。…最後まで美しかったでしょう？</t>
+          <t xml:space="preserve">目が覚めたわ。ここで終わるなんて、つまらないもの</t>
         </is>
       </c>
     </row>
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.bold.seductive[1]</t>
+          <t xml:space="preserve">SLUMP_END_LINES.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -5722,29 +5722,29 @@
       </c>
       <c r="C169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_END_LINES</t>
         </is>
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.bold.seductive[1]</t>
+          <t xml:space="preserve">bold.seductive[1]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F169" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一番になるべくしてなった。当然でしょう？ …でも、まだ満足してないわ</t>
+          <t xml:space="preserve">お待たせ。ここからが本番よ</t>
         </is>
       </c>
     </row>
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.bold.seductive[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.defeat.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
@@ -5754,29 +5754,29 @@
       </c>
       <c r="C170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.bold.seductive[1]</t>
+          <t xml:space="preserve">defeat.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F170" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">嬉しい？ ええ、嬉しいわ。でもこの程度で満足する女じゃないの</t>
+          <t xml:space="preserve">あら…おかしいわね、こんなはずじゃ</t>
         </is>
       </c>
     </row>
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.bold.seductive[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5786,29 +5786,29 @@
       </c>
       <c r="C171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[1]</t>
+          <t xml:space="preserve">injury_moderate_recovery.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F171" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ドームで…本気の私、見せてあげる</t>
+          <t xml:space="preserve">治ったはずなのに…おかしいわね</t>
         </is>
       </c>
     </row>
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.bold.seductive[2]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5818,29 +5818,29 @@
       </c>
       <c r="C172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[2]</t>
+          <t xml:space="preserve">injury_severe_recovery.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F172" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この大舞台、たっぷり熱くしてあげるわよ</t>
+          <t xml:space="preserve">私が…怯えてる？ 嘘でしょう</t>
         </is>
       </c>
     </row>
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.bold.seductive[3]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5850,29 +5850,29 @@
       </c>
       <c r="C173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[3]</t>
+          <t xml:space="preserve">penalty_end.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F173" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うふふ、今夜は容赦しないわよ</t>
+          <t xml:space="preserve">体は万全なのに…気持ちがついてこないの</t>
         </is>
       </c>
     </row>
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.bold.seductive[1]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -5882,12 +5882,12 @@
       </c>
       <c r="C174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[1]</t>
+          <t xml:space="preserve">bestMatch.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E174" t="inlineStr" s="2">
@@ -5897,14 +5897,14 @@
       </c>
       <c r="F174" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">満員…最高の演出になったわね</t>
+          <t xml:space="preserve">全力を引き出してくれた相手に感謝。…次はもっと激しくいくわよ？</t>
         </is>
       </c>
     </row>
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.bold.seductive[2]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -5914,12 +5914,12 @@
       </c>
       <c r="C175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[2]</t>
+          <t xml:space="preserve">champion.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E175" t="inlineStr" s="2">
@@ -5929,14 +5929,14 @@
       </c>
       <c r="F175" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この熱量、また必ず味わいたい</t>
+          <t xml:space="preserve">頂点からの景色は最高よ。…あなたには見せてあげないけど</t>
         </is>
       </c>
     </row>
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.bold.seductive[3]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -5946,12 +5946,12 @@
       </c>
       <c r="C176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[3]</t>
+          <t xml:space="preserve">hallOfFame.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
@@ -5961,14 +5961,14 @@
       </c>
       <c r="F176" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うふふ、皆様を虜にしてやったわ</t>
+          <t xml:space="preserve">最高の舞台で、最高の人生だった。…最後まで美しかったでしょう？</t>
         </is>
       </c>
     </row>
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.bold.seductive[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -5978,29 +5978,29 @@
       </c>
       <c r="C177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.bold.seductive[1]</t>
+          <t xml:space="preserve">mvp.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F177" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ足りないわ。もっと強くなれる気がするの</t>
+          <t xml:space="preserve">一番になるべくしてなった。当然でしょう？ …でも、まだ満足してないわ</t>
         </is>
       </c>
     </row>
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.bold.seductive[1]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -6010,29 +6010,29 @@
       </c>
       <c r="C178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.bold.seductive[1]</t>
+          <t xml:space="preserve">rookie.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F178" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仲間がいるって、いいものね</t>
+          <t xml:space="preserve">嬉しい？ ええ、嬉しいわ。でもこの程度で満足する女じゃないの</t>
         </is>
       </c>
     </row>
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.bold.seductive[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -6042,29 +6042,29 @@
       </c>
       <c r="C179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.bold.seductive[1]</t>
+          <t xml:space="preserve">bold.seductive[1]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F179" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この程度で止まるつもりはないわ</t>
+          <t xml:space="preserve">ドームで…本気の私、見せてあげる</t>
         </is>
       </c>
     </row>
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.bold.seductive[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.bold.seductive[2]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -6074,29 +6074,29 @@
       </c>
       <c r="C180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.bold.seductive[1]</t>
+          <t xml:space="preserve">bold.seductive[2]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F180" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この人気、活かさない手はないわね</t>
+          <t xml:space="preserve">この大舞台、たっぷり熱くしてあげるわよ</t>
         </is>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.bold.seductive[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.bold.seductive[3]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -6106,29 +6106,29 @@
       </c>
       <c r="C181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.bold.seductive[1]</t>
+          <t xml:space="preserve">bold.seductive[3]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F181" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ここにいて、私の夢は叶うのかしら</t>
+          <t xml:space="preserve">うふふ、今夜は容赦しないわよ</t>
         </is>
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.bold.seductive[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -6138,29 +6138,29 @@
       </c>
       <c r="C182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_warning.bold.seductive[1]</t>
+          <t xml:space="preserve">bold.seductive[1]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F182" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…このままでいいのかなって、ふと思うの</t>
+          <t xml:space="preserve">満員…最高の演出になったわね</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.bold.seductive[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.bold.seductive[2]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6170,29 +6170,29 @@
       </c>
       <c r="C183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.bold.seductive[1]</t>
+          <t xml:space="preserve">bold.seductive[2]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F183" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">嬉しいわ。実力で返させてもらうわね</t>
+          <t xml:space="preserve">この熱量、また必ず味わいたい</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.bold.seductive[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.bold.seductive[3]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6202,29 +6202,29 @@
       </c>
       <c r="C184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.bold.seductive[1]</t>
+          <t xml:space="preserve">bold.seductive[3]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">帰る頃には一回り強くなってるわよ</t>
+          <t xml:space="preserve">うふふ、皆様を虜にしてやったわ</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.bold.seductive[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6234,29 +6234,29 @@
       </c>
       <c r="C185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage_high_trust.bold.seductive[1]</t>
+          <t xml:space="preserve">N1.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あなたが信じてくれるなら…絶対応えるわ</t>
+          <t xml:space="preserve">まだ足りないわ。もっと強くなれる気がするの</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.bold.seductive[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6266,29 +6266,29 @@
       </c>
       <c r="C186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.bold.seductive[1]</t>
+          <t xml:space="preserve">N2.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">止まるつもりはないわ。見ていてね</t>
+          <t xml:space="preserve">仲間がいるって、いいものね</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.bold.seductive[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6298,29 +6298,29 @@
       </c>
       <c r="C187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.bold.seductive[1]</t>
+          <t xml:space="preserve">N3.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F187" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">注目される場って好きよ。任せて</t>
+          <t xml:space="preserve">この程度で止まるつもりはないわ</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.bold.seductive[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6330,29 +6330,29 @@
       </c>
       <c r="C188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.bold.seductive[1]</t>
+          <t xml:space="preserve">N4.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F188" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい雰囲気ね。チームが成長してる証拠だわ</t>
+          <t xml:space="preserve">この人気、活かさない手はないわね</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.bold.seductive[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6362,29 +6362,29 @@
       </c>
       <c r="C189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.bold.seductive[1]</t>
+          <t xml:space="preserve">N5_low.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F189" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">リフレッシュしてくるわ。戻ったらもっと輝くから</t>
+          <t xml:space="preserve">…ここにいて、私の夢は叶うのかしら</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.bold.seductive[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6394,29 +6394,29 @@
       </c>
       <c r="C190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.bold.seductive[1]</t>
+          <t xml:space="preserve">N5_warning.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F190" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この環境、無駄にしないわ。見ていてね</t>
+          <t xml:space="preserve">…このままでいいのかなって、ふと思うの</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.bold.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="C191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.bold.seductive[1]</t>
+          <t xml:space="preserve">bonus.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
@@ -6441,14 +6441,14 @@
       </c>
       <c r="F191" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">注目される場は好きよ。もちろんやるわ</t>
+          <t xml:space="preserve">嬉しいわ。実力で返させてもらうわね</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.bold.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6458,12 +6458,12 @@
       </c>
       <c r="C192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.bold.seductive[1]</t>
+          <t xml:space="preserve">camp.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
@@ -6473,14 +6473,14 @@
       </c>
       <c r="F192" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">他所からいい話が来てるの。正直、迷ってるわ</t>
+          <t xml:space="preserve">帰る頃には一回り強くなってるわよ</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.bold.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="C193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.bold.seductive[1]</t>
+          <t xml:space="preserve">encourage_high_trust.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
@@ -6505,14 +6505,14 @@
       </c>
       <c r="F193" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ベルトが欲しいの。組んでもらえる？</t>
+          <t xml:space="preserve">あなたが信じてくれるなら…絶対応えるわ</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.bold.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6522,12 +6522,12 @@
       </c>
       <c r="C194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.bold.seductive[1]</t>
+          <t xml:space="preserve">encourage.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
@@ -6537,14 +6537,14 @@
       </c>
       <c r="F194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの人と決着をつけたいの。組んでもらえる？</t>
+          <t xml:space="preserve">止まるつもりはないわ。見ていてね</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.bold.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6554,12 +6554,12 @@
       </c>
       <c r="C195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.bold.seductive[1]</t>
+          <t xml:space="preserve">faction_decree.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
@@ -6569,14 +6569,14 @@
       </c>
       <c r="F195" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…体が限界なの。少し休ませて</t>
+          <t xml:space="preserve">いいわ、畳みましょう。……でも、覚えておいて</t>
         </is>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.bold.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="C196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.bold.seductive[1]</t>
+          <t xml:space="preserve">media.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
@@ -6601,14 +6601,14 @@
       </c>
       <c r="F196" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このままじゃ我慢の限界よ。考え直してもらえない？</t>
+          <t xml:space="preserve">注目される場って好きよ。任せて</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.bold.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="C197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.bold.seductive[1]</t>
+          <t xml:space="preserve">party.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
@@ -6633,14 +6633,14 @@
       </c>
       <c r="F197" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もっと強くなりたいの。特訓させてもらえる？</t>
+          <t xml:space="preserve">いい雰囲気ね。チームが成長してる証拠だわ</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.bold.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6650,12 +6650,12 @@
       </c>
       <c r="C198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.bold.seductive[1]</t>
+          <t xml:space="preserve">refresh_leave.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
@@ -6665,14 +6665,14 @@
       </c>
       <c r="F198" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">後輩の面倒、見させてもらえるかしら？</t>
+          <t xml:space="preserve">リフレッシュしてくるわ。戻ったらもっと輝くから</t>
         </is>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.bold.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="C199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.bold.seductive[1]</t>
+          <t xml:space="preserve">special_treatment.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
@@ -6697,14 +6697,14 @@
       </c>
       <c r="F199" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんなところで止まるつもりはないわ…すぐ戻る</t>
+          <t xml:space="preserve">早く戻りたいの…待っていてね</t>
         </is>
       </c>
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.bold.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6714,12 +6714,12 @@
       </c>
       <c r="C200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.bold.seductive[1]</t>
+          <t xml:space="preserve">trainer.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
@@ -6729,14 +6729,14 @@
       </c>
       <c r="F200" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの人の態度、もう我慢できないの</t>
+          <t xml:space="preserve">この環境、無駄にしないわ。見ていてね</t>
         </is>
       </c>
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.bold.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6746,12 +6746,12 @@
       </c>
       <c r="C201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.bold.seductive[1]</t>
+          <t xml:space="preserve">E1.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
@@ -6761,14 +6761,14 @@
       </c>
       <c r="F201" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">黙ってるつもりはないわ。向こうが悪いんだから</t>
+          <t xml:space="preserve">注目される場は好きよ。もちろんやるわ</t>
         </is>
       </c>
     </row>
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.bold.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6778,12 +6778,12 @@
       </c>
       <c r="C202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.bold.seductive[1]</t>
+          <t xml:space="preserve">E6.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
@@ -6793,14 +6793,14 @@
       </c>
       <c r="F202" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私とブランドの組み合わせ…最高じゃない♡</t>
+          <t xml:space="preserve">他所からいい話が来てるの。正直、迷ってるわ</t>
         </is>
       </c>
     </row>
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.bold.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="C203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.bold.seductive[1]</t>
+          <t xml:space="preserve">S_boycott.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
@@ -6825,14 +6825,14 @@
       </c>
       <c r="F203" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全国に私を見てもらえるのね。楽しみだわ♡</t>
+          <t xml:space="preserve">練習？ 出してもくれないのに、意味があるのかしら</t>
         </is>
       </c>
     </row>
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.bold.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.bold.seductive[2]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6842,12 +6842,12 @@
       </c>
       <c r="C204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.bold.seductive[1]</t>
+          <t xml:space="preserve">S_boycott.bold.seductive[2]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
@@ -6857,14 +6857,14 @@
       </c>
       <c r="F204" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ファンを喜ばせるのは得意よ。任せて♡</t>
+          <t xml:space="preserve">リングに上がれないなら、やっても同じでしょう？</t>
         </is>
       </c>
     </row>
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.bold.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="C205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.bold.seductive[1]</t>
+          <t xml:space="preserve">S_grumble.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
@@ -6889,14 +6889,14 @@
       </c>
       <c r="F205" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ランウェイ、私のためにあるようなものよ♡</t>
+          <t xml:space="preserve">（「わたしたち、ずいぶん軽く見られてるのね」と笑みを崩さずに言い放っている）</t>
         </is>
       </c>
     </row>
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.bold.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6906,12 +6906,12 @@
       </c>
       <c r="C206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.bold.seductive[1]</t>
+          <t xml:space="preserve">S_sns.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
@@ -6921,14 +6921,14 @@
       </c>
       <c r="F206" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私の本気の魅力、たっぷり撮ってもらうわ♡</t>
+          <t xml:space="preserve">（SNSに「このまま終わるつもりはないの。楽しみにしてて」と投稿）</t>
         </is>
       </c>
     </row>
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.bold.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6938,12 +6938,12 @@
       </c>
       <c r="C207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.bold.seductive[1]</t>
+          <t xml:space="preserve">S1.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
@@ -6953,14 +6953,14 @@
       </c>
       <c r="F207" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">バラエティでも私のペースで話すわ♡</t>
+          <t xml:space="preserve">ベルトが欲しいの。組んでもらえる？</t>
         </is>
       </c>
     </row>
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.bold.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -6970,12 +6970,12 @@
       </c>
       <c r="C208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.bold.seductive[1]</t>
+          <t xml:space="preserve">S2.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
@@ -6985,14 +6985,14 @@
       </c>
       <c r="F208" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全国に見てもらえるのね。楽しみだわ</t>
+          <t xml:space="preserve">あの人と決着をつけたいの。組んでもらえる？</t>
         </is>
       </c>
     </row>
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.bold.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -7002,29 +7002,29 @@
       </c>
       <c r="C209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[1]</t>
+          <t xml:space="preserve">S3.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F209" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私を選んで。後悔はさせないわ</t>
+          <t xml:space="preserve">…体が限界なの。少し休ませて</t>
         </is>
       </c>
     </row>
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.bold.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -7034,29 +7034,29 @@
       </c>
       <c r="C210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[1]</t>
+          <t xml:space="preserve">S4_direct.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F210" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオン、獲りに来たの。覚悟してて</t>
+          <t xml:space="preserve">このままじゃ我慢の限界よ。考え直してもらえない？</t>
         </is>
       </c>
     </row>
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.bold.seductive[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7066,29 +7066,29 @@
       </c>
       <c r="C211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[2]</t>
+          <t xml:space="preserve">S4_silent.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F211" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この団体、私が盛り上げてあげる</t>
+          <t xml:space="preserve">…………（笑みは崩さないまま、指先だけが強く握られている）</t>
         </is>
       </c>
     </row>
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.bold.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7098,29 +7098,29 @@
       </c>
       <c r="C212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[1]</t>
+          <t xml:space="preserve">S5.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F212" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">てっぺん獲りに来たの。一緒に頂点に立ちましょう</t>
+          <t xml:space="preserve">もっと強くなりたいの。特訓させてもらえる？</t>
         </is>
       </c>
     </row>
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.bold.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7130,29 +7130,29 @@
       </c>
       <c r="C213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[1]</t>
+          <t xml:space="preserve">S6.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F213" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頂点まで一直線よ。見ていてね</t>
+          <t xml:space="preserve">後輩の面倒、見させてもらえるかしら？</t>
         </is>
       </c>
     </row>
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.bold.seductive[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7162,29 +7162,29 @@
       </c>
       <c r="C214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[1]</t>
+          <t xml:space="preserve">B1.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F214" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんなことで止まると思ってる？ 甘いわ</t>
+          <t xml:space="preserve">こんなところで止まるつもりはないわ…すぐ戻る</t>
         </is>
       </c>
     </row>
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.bold.seductive[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7194,29 +7194,29 @@
       </c>
       <c r="C215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[2]</t>
+          <t xml:space="preserve">B2_fighter1.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F215" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">すぐ戻るわ。覚悟してなさい</t>
+          <t xml:space="preserve">あの人の態度、もう我慢できないの</t>
         </is>
       </c>
     </row>
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.bold.seductive[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7226,29 +7226,29 @@
       </c>
       <c r="C216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.bold.seductive[1]</t>
+          <t xml:space="preserve">B2_fighter2.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F216" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私を選んで。後悔はさせないわ</t>
+          <t xml:space="preserve">黙ってるつもりはないわ。向こうが悪いんだから</t>
         </is>
       </c>
     </row>
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.bold.seductive[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7258,29 +7258,29 @@
       </c>
       <c r="C217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.bold.seductive[1]</t>
+          <t xml:space="preserve">B4_brand.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F217" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオン、獲りに来たの。覚悟してて</t>
+          <t xml:space="preserve">私とブランドの組み合わせ…最高じゃない♡</t>
         </is>
       </c>
     </row>
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.bold.seductive[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7290,29 +7290,29 @@
       </c>
       <c r="C218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.bold.seductive[2]</t>
+          <t xml:space="preserve">B4_cm.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F218" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この団体、私が盛り上げてあげる</t>
+          <t xml:space="preserve">全国に私を見てもらえるのね。楽しみだわ♡</t>
         </is>
       </c>
     </row>
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.bold.seductive[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7322,29 +7322,29 @@
       </c>
       <c r="C219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.bold.seductive[1]</t>
+          <t xml:space="preserve">B4_fan.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F219" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">てっぺん獲りに来たの。一緒に頂点に立ちましょう</t>
+          <t xml:space="preserve">ファンを喜ばせるのは得意よ。任せて♡</t>
         </is>
       </c>
     </row>
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.bold.seductive[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7354,29 +7354,29 @@
       </c>
       <c r="C220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.bold.seductive[1]</t>
+          <t xml:space="preserve">B4_fashion.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頂点まで一直線よ。見ていてね</t>
+          <t xml:space="preserve">ランウェイ、私のためにあるようなものよ♡</t>
         </is>
       </c>
     </row>
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.bold.seductive[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7386,29 +7386,29 @@
       </c>
       <c r="C221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.bold.seductive[1]</t>
+          <t xml:space="preserve">B4_gravure.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F221" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんなことで止まると思ってる？ 甘いわ</t>
+          <t xml:space="preserve">私の本気の魅力、たっぷり撮ってもらうわ♡</t>
         </is>
       </c>
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.bold.seductive[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7418,29 +7418,29 @@
       </c>
       <c r="C222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.bold.seductive[2]</t>
+          <t xml:space="preserve">B4_variety.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">すぐ戻るわ。覚悟してなさい</t>
+          <t xml:space="preserve">バラエティでも私のペースで話すわ♡</t>
         </is>
       </c>
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.bold.seductive[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7450,29 +7450,29 @@
       </c>
       <c r="C223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.bold.seductive[1]</t>
+          <t xml:space="preserve">B4.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F223" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しいわ…でも、いつか必ず戻ってくる</t>
+          <t xml:space="preserve">全国に見てもらえるのね。楽しみだわ</t>
         </is>
       </c>
     </row>
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.bold.seductive[2]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7482,12 +7482,12 @@
       </c>
       <c r="C224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.bold.seductive[2]</t>
+          <t xml:space="preserve">bold.seductive[1]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
@@ -7497,14 +7497,14 @@
       </c>
       <c r="F224" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この借り、いつか返しに来るから</t>
+          <t xml:space="preserve">私を選んで。後悔はさせないわ</t>
         </is>
       </c>
     </row>
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.bold.seductive[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7514,12 +7514,12 @@
       </c>
       <c r="C225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.bold.seductive[1]</t>
+          <t xml:space="preserve">bold.seductive[1]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
@@ -7529,14 +7529,14 @@
       </c>
       <c r="F225" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">レンタルでも全力よ。見ていてね</t>
+          <t xml:space="preserve">チャンピオン、獲りに来たの。覚悟してて</t>
         </is>
       </c>
     </row>
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.bold.seductive[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.bold.seductive[2]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7546,12 +7546,12 @@
       </c>
       <c r="C226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.bold.seductive[1]</t>
+          <t xml:space="preserve">bold.seductive[2]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
@@ -7561,14 +7561,14 @@
       </c>
       <c r="F226" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…今日は認めるわ。でもこの借り、必ず返す</t>
+          <t xml:space="preserve">この団体、私が盛り上げてあげる</t>
         </is>
       </c>
     </row>
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.bold.seductive[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7578,12 +7578,12 @@
       </c>
       <c r="C227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.bold.seductive[1]</t>
+          <t xml:space="preserve">bold.seductive[1]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
@@ -7593,14 +7593,14 @@
       </c>
       <c r="F227" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ誰も私を超えられないわね。当然でしょう</t>
+          <t xml:space="preserve">てっぺん獲りに来たの。一緒に頂点に立ちましょう</t>
         </is>
       </c>
     </row>
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.bold.seductive[1]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7610,12 +7610,12 @@
       </c>
       <c r="C228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.bold.seductive[1]</t>
+          <t xml:space="preserve">bold.seductive[1]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
@@ -7625,14 +7625,14 @@
       </c>
       <c r="F228" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…覚えておきなさい。すぐに返してもらうわ</t>
+          <t xml:space="preserve">頂点まで一直線よ。見ていてね</t>
         </is>
       </c>
     </row>
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.bold.seductive[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7642,12 +7642,12 @@
       </c>
       <c r="C229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.bold.seductive[1]</t>
+          <t xml:space="preserve">bold.seductive[1]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
@@ -7657,14 +7657,14 @@
       </c>
       <c r="F229" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">これが始まりよ。このベルトで時代を作る</t>
+          <t xml:space="preserve">こんなことで止まると思ってる？ 甘いわ</t>
         </is>
       </c>
     </row>
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.bold.seductive[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.bold.seductive[2]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7674,12 +7674,12 @@
       </c>
       <c r="C230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[1]</t>
+          <t xml:space="preserve">bold.seductive[2]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
@@ -7689,14 +7689,14 @@
       </c>
       <c r="F230" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しいわ…でも、いつか必ず戻ってくる</t>
+          <t xml:space="preserve">すぐ戻るわ。覚悟してなさい</t>
         </is>
       </c>
     </row>
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.bold.seductive[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7706,12 +7706,12 @@
       </c>
       <c r="C231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[2]</t>
+          <t xml:space="preserve">draftInterest.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
@@ -7721,14 +7721,14 @@
       </c>
       <c r="F231" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この借り、いつか返しに来るから</t>
+          <t xml:space="preserve">私を選んで。後悔はさせないわ</t>
         </is>
       </c>
     </row>
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.bold.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="C232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[1]</t>
+          <t xml:space="preserve">draftJoin.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
@@ -7753,14 +7753,14 @@
       </c>
       <c r="F232" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">レンタルでも全力よ。見ていてね</t>
+          <t xml:space="preserve">チャンピオン、獲りに来たの。覚悟してて</t>
         </is>
       </c>
     </row>
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.bold.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.bold.seductive[2]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="C233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[1]</t>
+          <t xml:space="preserve">draftJoin.bold.seductive[2]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
@@ -7785,14 +7785,14 @@
       </c>
       <c r="F233" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…今日は認めるわ。でもこの借り、必ず返す</t>
+          <t xml:space="preserve">この団体、私が盛り上げてあげる</t>
         </is>
       </c>
     </row>
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.bold.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7802,12 +7802,12 @@
       </c>
       <c r="C234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[1]</t>
+          <t xml:space="preserve">faGreeting.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
@@ -7817,14 +7817,14 @@
       </c>
       <c r="F234" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ誰も私を超えられないわね。当然でしょう</t>
+          <t xml:space="preserve">拾った目利きは正解よ。…すぐに分かるわ</t>
         </is>
       </c>
     </row>
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.bold.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7834,12 +7834,12 @@
       </c>
       <c r="C235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[1]</t>
+          <t xml:space="preserve">faSigning.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
@@ -7849,14 +7849,14 @@
       </c>
       <c r="F235" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…覚えておきなさい。すぐに返してもらうわ</t>
+          <t xml:space="preserve">てっぺん獲りに来たの。一緒に頂点に立ちましょう</t>
         </is>
       </c>
     </row>
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.bold.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="C236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[1]</t>
+          <t xml:space="preserve">faWelcome.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
@@ -7881,14 +7881,14 @@
       </c>
       <c r="F236" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">これが始まりよ。このベルトで時代を作る</t>
+          <t xml:space="preserve">頂点まで一直線よ。見ていてね</t>
         </is>
       </c>
     </row>
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.bold.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -7898,29 +7898,29 @@
       </c>
       <c r="C237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.bold.seductive[1]</t>
+          <t xml:space="preserve">injury.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F237" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">気に入ったわ。なかなか味のある人ね</t>
+          <t xml:space="preserve">こんなことで止まると思ってる？ 甘いわ</t>
         </is>
       </c>
     </row>
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.bold.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.bold.seductive[2]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -7930,29 +7930,29 @@
       </c>
       <c r="C238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.bold.seductive[1]</t>
+          <t xml:space="preserve">injury.bold.seductive[2]</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F238" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高のコンビネーションよ、私たち</t>
+          <t xml:space="preserve">すぐ戻るわ。覚悟してなさい</t>
         </is>
       </c>
     </row>
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.bold.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -7962,29 +7962,29 @@
       </c>
       <c r="C239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.bold.seductive[1]</t>
+          <t xml:space="preserve">release.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F239" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">なかなかの逸材ね。ふふ、楽しみ</t>
+          <t xml:space="preserve">悔しいわ…でも、いつか必ず戻ってくる</t>
         </is>
       </c>
     </row>
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.bold.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.bold.seductive[2]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -7994,29 +7994,29 @@
       </c>
       <c r="C240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[1]</t>
+          <t xml:space="preserve">release.bold.seductive[2]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F240" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、あの輝きは一時的だったみたいね。でもいい夢だったわ</t>
+          <t xml:space="preserve">この借り、いつか返しに来るから</t>
         </is>
       </c>
     </row>
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.bold.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -8026,29 +8026,29 @@
       </c>
       <c r="C241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.bold.seductive[1]</t>
+          <t xml:space="preserve">rentalGreeting.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F241" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">満身創痍の私、悪くないでしょ? この傷ごと、最後を飾るわ</t>
+          <t xml:space="preserve">レンタルでも全力よ。見ていてね</t>
         </is>
       </c>
     </row>
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.bold.seductive[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8058,29 +8058,29 @@
       </c>
       <c r="C242" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.bold.seductive[2]</t>
+          <t xml:space="preserve">scoutGreeting.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F242" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで残ったんだもの。一番いいところ、見せてあげる</t>
+          <t xml:space="preserve">わたしに声をかけた責任は、取ってちょうだいね</t>
         </is>
       </c>
     </row>
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.bold.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -8090,29 +8090,29 @@
       </c>
       <c r="C243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.bold.seductive[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F243" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">相手は誰? 何人来ても…最後まで残るのは、こっちよ</t>
+          <t xml:space="preserve">…今日は認めるわ。でもこの借り、必ず返す</t>
         </is>
       </c>
     </row>
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.bold.seductive[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8122,29 +8122,29 @@
       </c>
       <c r="C244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.bold.seductive[2]</t>
+          <t xml:space="preserve">titleDefense.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F244" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もっと骨のあるのを出してきて。全部相手にしてあげる</t>
+          <t xml:space="preserve">まだ誰も私を超えられないわね。当然でしょう</t>
         </is>
       </c>
     </row>
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.bold.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8154,29 +8154,29 @@
       </c>
       <c r="C245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.bold.seductive[1]</t>
+          <t xml:space="preserve">titleLoss.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F245" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人、落としたわ。…でも、まだ足りないの。次、早く出してよ</t>
+          <t xml:space="preserve">…覚えておきなさい。すぐに返してもらうわ</t>
         </is>
       </c>
     </row>
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.bold.seductive[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8186,29 +8186,29 @@
       </c>
       <c r="C246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.bold.seductive[2]</t>
+          <t xml:space="preserve">titleWin.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F246" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ立ってるの、見える? 次の子、こっちにいらっしゃい。全部相手にしてあげる</t>
+          <t xml:space="preserve">これが始まりよ。このベルトで時代を作る</t>
         </is>
       </c>
     </row>
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.bold.seductive[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8218,29 +8218,29 @@
       </c>
       <c r="C247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.bold.seductive[1]</t>
+          <t xml:space="preserve">bold.seductive[1]</t>
         </is>
       </c>
       <c r="E247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F247" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この三人が最強だった。美しい勝利でしょ？</t>
+          <t xml:space="preserve">悔しいわ…でも、いつか必ず戻ってくる</t>
         </is>
       </c>
     </row>
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.bold.seductive[2]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.bold.seductive[2]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8250,29 +8250,29 @@
       </c>
       <c r="C248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.bold.seductive[2]</t>
+          <t xml:space="preserve">bold.seductive[2]</t>
         </is>
       </c>
       <c r="E248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F248" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仲間が繋いでくれた勝ちを、最後に飾ったの。良いチームだったわ</t>
+          <t xml:space="preserve">この借り、いつか返しに来るから</t>
         </is>
       </c>
     </row>
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.bold.seductive[1]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8282,29 +8282,29 @@
       </c>
       <c r="C249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.bold.seductive[1]</t>
+          <t xml:space="preserve">bold.seductive[1]</t>
         </is>
       </c>
       <c r="E249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F249" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">賞はもらっておくわ。でも次は……もっと大きなものを奪いに行くから</t>
+          <t xml:space="preserve">レンタルでも全力よ。見ていてね</t>
         </is>
       </c>
     </row>
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.bold.seductive[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8314,29 +8314,29 @@
       </c>
       <c r="C250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.bold.seductive[2]</t>
+          <t xml:space="preserve">bold.seductive[1]</t>
         </is>
       </c>
       <c r="E250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F250" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この程度じゃ満たされない。次は全部、こっちのものにするわ</t>
+          <t xml:space="preserve">…今日は認めるわ。でもこの借り、必ず返す</t>
         </is>
       </c>
     </row>
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.bold.seductive[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8346,29 +8346,29 @@
       </c>
       <c r="C251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.bold.seductive[1]</t>
+          <t xml:space="preserve">bold.seductive[1]</t>
         </is>
       </c>
       <c r="E251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F251" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何人でもいいわよ？ 最後にこの場所に立つのは、いつだって私だもの</t>
+          <t xml:space="preserve">まだ誰も私を超えられないわね。当然でしょう</t>
         </is>
       </c>
     </row>
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.bold.seductive[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8378,29 +8378,29 @@
       </c>
       <c r="C252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.bold.seductive[2]</t>
+          <t xml:space="preserve">bold.seductive[1]</t>
         </is>
       </c>
       <c r="E252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F252" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全員倒してきたの。まだ物足りないくらい</t>
+          <t xml:space="preserve">…覚えておきなさい。すぐに返してもらうわ</t>
         </is>
       </c>
     </row>
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.bold.seductive[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8410,29 +8410,29 @@
       </c>
       <c r="C253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.bold.seductive[1]</t>
+          <t xml:space="preserve">bold.seductive[1]</t>
         </is>
       </c>
       <c r="E253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F253" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、優勝しちゃったわ。当然だけどね</t>
+          <t xml:space="preserve">これが始まりよ。このベルトで時代を作る</t>
         </is>
       </c>
     </row>
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.bold.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8442,29 +8442,29 @@
       </c>
       <c r="C254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.bold.seductive[2]</t>
+          <t xml:space="preserve">bond_39_down.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F254" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたしが一番。それが証明されたわね</t>
+          <t xml:space="preserve">合わないわ。どうしても合わないの</t>
         </is>
       </c>
     </row>
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.bold.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.bold.seductive[2]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8474,29 +8474,29 @@
       </c>
       <c r="C255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D255" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.bold.seductive[1]</t>
+          <t xml:space="preserve">bond_39_down.bold.seductive[2]</t>
         </is>
       </c>
       <c r="E255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F255" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悔しいわ。でも、わたしはここで終わらない</t>
+          <t xml:space="preserve">これ以上は無理ね。それだけよ</t>
         </is>
       </c>
     </row>
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.bold.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8506,29 +8506,29 @@
       </c>
       <c r="C256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.bold.seductive[2]</t>
+          <t xml:space="preserve">bond_59_down.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F256" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次は必ず勝つわ</t>
+          <t xml:space="preserve">壁を作ってない？ 気に入らないわ</t>
         </is>
       </c>
     </row>
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.bold.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.bold.seductive[2]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8538,29 +8538,29 @@
       </c>
       <c r="C257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D257" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.bold.seductive[1]</t>
+          <t xml:space="preserve">bond_59_down.bold.seductive[2]</t>
         </is>
       </c>
       <c r="E257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F257" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、もう終わり？ 物足りないわね</t>
+          <t xml:space="preserve">前はもっと話してくれたのに。…どうしたのかしら</t>
         </is>
       </c>
     </row>
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.bold.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8570,29 +8570,29 @@
       </c>
       <c r="C258" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D258" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.bold.seductive[2]</t>
+          <t xml:space="preserve">bond_60_up.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E258" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F258" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、予定通りよ。次の相手が楽しみ</t>
+          <t xml:space="preserve">気に入ったわ。なかなか味のある人ね</t>
         </is>
       </c>
     </row>
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.bold.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8602,29 +8602,29 @@
       </c>
       <c r="C259" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.bold.seductive[1]</t>
+          <t xml:space="preserve">bond_80_up.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E259" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F259" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ足りないわね。もっと上に行くわ</t>
+          <t xml:space="preserve">最高のコンビネーションよ、私たち</t>
         </is>
       </c>
     </row>
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.bold.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8634,29 +8634,29 @@
       </c>
       <c r="C260" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.bold.seductive[2]</t>
+          <t xml:space="preserve">rivalry_29_down.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E260" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F260" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい舞台だったわ。でも、わたしはもっと上を目指す</t>
+          <t xml:space="preserve">……もう終わったことよ</t>
         </is>
       </c>
     </row>
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.bold.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.bold.seductive[2]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8666,29 +8666,29 @@
       </c>
       <c r="C261" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.bold.seductive[1]</t>
+          <t xml:space="preserve">rivalry_29_down.bold.seductive[2]</t>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F261" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、最後のお相手ね。たっぷり楽しませてあげるわ</t>
+          <t xml:space="preserve">決着はついたわ。次に進むの</t>
         </is>
       </c>
     </row>
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.bold.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8698,29 +8698,29 @@
       </c>
       <c r="C262" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.bold.seductive[2]</t>
+          <t xml:space="preserve">rivalry_30_up.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E262" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F262" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">優勝はわたしのもの。決まっていることよ</t>
+          <t xml:space="preserve">なかなかの逸材ね。ふふ、楽しみ</t>
         </is>
       </c>
     </row>
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.bold.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8730,29 +8730,29 @@
       </c>
       <c r="C263" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.bold.seductive[1]</t>
+          <t xml:space="preserve">rivalry_50_up.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E263" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F263" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、可愛い相手ね。すぐ終わらせてあげるわ</t>
+          <t xml:space="preserve">全力を出せる相手。最高の敵ね、ふふ</t>
         </is>
       </c>
     </row>
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.bold.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.bold.seductive[2]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8762,29 +8762,29 @@
       </c>
       <c r="C264" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.bold.seductive[2]</t>
+          <t xml:space="preserve">rivalry_50_up.bold.seductive[2]</t>
         </is>
       </c>
       <c r="E264" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F264" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたしに勝てるつもり？ 甘いわね</t>
+          <t xml:space="preserve">超える。それが今の私の全てよ</t>
         </is>
       </c>
     </row>
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.bold.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8794,29 +8794,29 @@
       </c>
       <c r="C265" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.bold.seductive[1]</t>
+          <t xml:space="preserve">rivalry_70_up.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E265" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F265" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、指名してくれたの？ 嬉しいわ</t>
+          <t xml:space="preserve">あの人がいたから強くなれたの。感謝してる…でも負けないわ</t>
         </is>
       </c>
     </row>
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.bold.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.bold.seductive[2]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -8826,29 +8826,29 @@
       </c>
       <c r="C266" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.bold.seductive[2]</t>
+          <t xml:space="preserve">rivalry_70_up.bold.seductive[2]</t>
         </is>
       </c>
       <c r="E266" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F266" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたしの舞台が増えるのね。楽しみ</t>
+          <t xml:space="preserve">この戦いに終わりはない。…望むところね</t>
         </is>
       </c>
     </row>
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.bold.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -8858,29 +8858,29 @@
       </c>
       <c r="C267" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D267" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[1]</t>
+          <t xml:space="preserve">trust_above_75.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E267" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F267" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">容赦しないわよ。覚悟してね</t>
+          <t xml:space="preserve">ここが最高の場所。私がもっと強くしてみせるわ</t>
         </is>
       </c>
     </row>
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.bold.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.bold.seductive[2]</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -8890,29 +8890,29 @@
       </c>
       <c r="C268" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D268" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[1]</t>
+          <t xml:space="preserve">trust_above_75.bold.seductive[2]</t>
         </is>
       </c>
       <c r="E268" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F268" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ずっと待ってたのよ、この瞬間を……!ふふ、最高の気分ね</t>
+          <t xml:space="preserve">この団体を背負っていく覚悟はできてるの</t>
         </is>
       </c>
     </row>
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.bold.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -8922,29 +8922,29 @@
       </c>
       <c r="C269" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D269" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[1]</t>
+          <t xml:space="preserve">trust_below_20.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E269" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F269" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら…随分と自信がおありのようね。壊してあげるわ</t>
+          <t xml:space="preserve">ふざけないで。私の価値がわからないなら、もう付き合いきれないわ</t>
         </is>
       </c>
     </row>
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.bold.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.bold.seductive[2]</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -8954,29 +8954,29 @@
       </c>
       <c r="C270" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D270" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[2]</t>
+          <t xml:space="preserve">trust_below_20.bold.seductive[2]</t>
         </is>
       </c>
       <c r="E270" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F270" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">可哀想だけど…手加減はしないわよ</t>
+          <t xml:space="preserve">この扱い、許すつもりはないの。忘れないことね</t>
         </is>
       </c>
     </row>
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.bold.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -8986,29 +8986,29 @@
       </c>
       <c r="C271" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D271" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[1]</t>
+          <t xml:space="preserve">trust_below_35.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E271" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F271" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、残念。もっと遊びたかったのに</t>
+          <t xml:space="preserve">この扱いは何かしら。私の実力、わかってるの？</t>
         </is>
       </c>
     </row>
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.bold.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.bold.seductive[2]</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -9018,29 +9018,29 @@
       </c>
       <c r="C272" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D272" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[2]</t>
+          <t xml:space="preserve">trust_below_35.bold.seductive[2]</t>
         </is>
       </c>
       <c r="E272" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F272" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">逃げちゃうの？ …つまらない団体ね</t>
+          <t xml:space="preserve">ここにいていいのか…考え直す時期かもね</t>
         </is>
       </c>
     </row>
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.bold.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -9050,29 +9050,29 @@
       </c>
       <c r="C273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.bold.seductive[1]</t>
+          <t xml:space="preserve">bold.seductive[1]</t>
         </is>
       </c>
       <c r="E273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F273" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら…やられちゃったわ。……許さないけど</t>
+          <t xml:space="preserve">ふふ、あの輝きは一時的だったみたいね。でもいい夢だったわ</t>
         </is>
       </c>
     </row>
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.bold.seductive[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="C274" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.bold.seductive[2]</t>
+          <t xml:space="preserve">preFinal.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E274" t="inlineStr" s="2">
@@ -9097,14 +9097,14 @@
       </c>
       <c r="F274" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日は譲ってあげるわ。次は…ないけどね</t>
+          <t xml:space="preserve">満身創痍の私、悪くないでしょ? この傷ごと、最後を飾るわ</t>
         </is>
       </c>
     </row>
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.bold.seductive[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.bold.seductive[2]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -9114,12 +9114,12 @@
       </c>
       <c r="C275" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.bold.seductive[1]</t>
+          <t xml:space="preserve">preFinal.bold.seductive[2]</t>
         </is>
       </c>
       <c r="E275" t="inlineStr" s="2">
@@ -9129,14 +9129,14 @@
       </c>
       <c r="F275" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、もう終わり？ もっと楽しみたかったのに</t>
+          <t xml:space="preserve">ここまで残ったんだもの。一番いいところ、見せてあげる</t>
         </is>
       </c>
     </row>
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.bold.seductive[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -9146,12 +9146,12 @@
       </c>
       <c r="C276" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.bold.seductive[2]</t>
+          <t xml:space="preserve">preMatch.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E276" t="inlineStr" s="2">
@@ -9161,14 +9161,14 @@
       </c>
       <c r="F276" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">予想通りの結果ね。つまらないわ</t>
+          <t xml:space="preserve">相手は誰? 何人来ても…最後まで残るのは、こっちよ</t>
         </is>
       </c>
     </row>
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.bold.seductive[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.bold.seductive[2]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -9178,12 +9178,12 @@
       </c>
       <c r="C277" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[1]</t>
+          <t xml:space="preserve">preMatch.bold.seductive[2]</t>
         </is>
       </c>
       <c r="E277" t="inlineStr" s="2">
@@ -9193,14 +9193,14 @@
       </c>
       <c r="F277" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">当然よ。うちの団体を甘く見ないことね</t>
+          <t xml:space="preserve">もっと骨のあるのを出してきて。全部相手にしてあげる</t>
         </is>
       </c>
     </row>
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.bold.seductive[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -9210,12 +9210,12 @@
       </c>
       <c r="C278" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[2]</t>
+          <t xml:space="preserve">survivor.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E278" t="inlineStr" s="2">
@@ -9225,14 +9225,14 @@
       </c>
       <c r="F278" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ物足りないわね。もっと強い相手はいないの？</t>
+          <t xml:space="preserve">一人、落としたわ。…でも、まだ足りないの。次、早く出してよ</t>
         </is>
       </c>
     </row>
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.bold.seductive[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.bold.seductive[2]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="C279" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[3]</t>
+          <t xml:space="preserve">survivor.bold.seductive[2]</t>
         </is>
       </c>
       <c r="E279" t="inlineStr" s="2">
@@ -9257,44 +9257,1164 @@
       </c>
       <c r="F279" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">当然の結果よ。うちを甘く見ないことね</t>
+          <t xml:space="preserve">まだ立ってるの、見える? 次の子、こっちにいらっしゃい。全部相手にしてあげる</t>
         </is>
       </c>
     </row>
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.bold.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">champion.bold.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">この三人が最強だった。美しい勝利でしょ？</t>
+        </is>
+      </c>
+    </row>
+    <row r="281" ht="40" customHeight="1">
+      <c r="A281" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.bold.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">champion.bold.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">仲間が繋いでくれた勝ちを、最後に飾ったの。良いチームだったわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="282" ht="40" customHeight="1">
+      <c r="A282" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.bold.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">defiant.bold.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">賞はもらっておくわ。でも次は……もっと大きなものを奪いに行くから</t>
+        </is>
+      </c>
+    </row>
+    <row r="283" ht="40" customHeight="1">
+      <c r="A283" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.bold.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">defiant.bold.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">この程度じゃ満たされない。次は全部、こっちのものにするわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="284" ht="40" customHeight="1">
+      <c r="A284" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.bold.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">gauntlet.bold.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">何人でもいいわよ？ 最後にこの場所に立つのは、いつだって私だもの</t>
+        </is>
+      </c>
+    </row>
+    <row r="285" ht="40" customHeight="1">
+      <c r="A285" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.bold.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">gauntlet.bold.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">全員倒してきたの。まだ物足りないくらい</t>
+        </is>
+      </c>
+    </row>
+    <row r="286" ht="40" customHeight="1">
+      <c r="A286" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.bold.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">champion.bold.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あら、優勝しちゃったわ。当然だけどね</t>
+        </is>
+      </c>
+    </row>
+    <row r="287" ht="40" customHeight="1">
+      <c r="A287" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.bold.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">champion.bold.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">わたしが一番。それが証明されたわね</t>
+        </is>
+      </c>
+    </row>
+    <row r="288" ht="40" customHeight="1">
+      <c r="A288" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.bold.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">postLose.bold.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…悔しいわ。でも、わたしはここで終わらない</t>
+        </is>
+      </c>
+    </row>
+    <row r="289" ht="40" customHeight="1">
+      <c r="A289" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.bold.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">postLose.bold.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">次は必ず勝つわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="290" ht="40" customHeight="1">
+      <c r="A290" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.bold.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">postMatchWin.bold.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あら、もう終わり？ 物足りないわね</t>
+        </is>
+      </c>
+    </row>
+    <row r="291" ht="40" customHeight="1">
+      <c r="A291" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.bold.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">postMatchWin.bold.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ふふ、予定通りよ。次の相手が楽しみ</t>
+        </is>
+      </c>
+    </row>
+    <row r="292" ht="40" customHeight="1">
+      <c r="A292" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.bold.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">postWin.bold.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">まだ足りないわね。もっと上に行くわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="293" ht="40" customHeight="1">
+      <c r="A293" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.bold.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">postWin.bold.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">いい舞台だったわ。でも、わたしはもっと上を目指す</t>
+        </is>
+      </c>
+    </row>
+    <row r="294" ht="40" customHeight="1">
+      <c r="A294" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.bold.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preFinal.bold.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あら、最後のお相手ね。たっぷり楽しませてあげるわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="295" ht="40" customHeight="1">
+      <c r="A295" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.bold.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preFinal.bold.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">優勝はわたしのもの。決まっていることよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="296" ht="40" customHeight="1">
+      <c r="A296" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.bold.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preMatch.bold.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あら、可愛い相手ね。すぐ終わらせてあげるわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="297" ht="40" customHeight="1">
+      <c r="A297" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.bold.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preMatch.bold.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">わたしに勝てるつもり？ 甘いわね</t>
+        </is>
+      </c>
+    </row>
+    <row r="298" ht="40" customHeight="1">
+      <c r="A298" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.bold.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">summon.bold.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あら、指名してくれたの？ 嬉しいわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="299" ht="40" customHeight="1">
+      <c r="A299" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.bold.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">summon.bold.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">わたしの舞台が増えるのね。楽しみ</t>
+        </is>
+      </c>
+    </row>
+    <row r="300" ht="40" customHeight="1">
+      <c r="A300" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.bold.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bold.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">容赦しないわよ。覚悟してね</t>
+        </is>
+      </c>
+    </row>
+    <row r="301" ht="40" customHeight="1">
+      <c r="A301" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.bold.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bold.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ずっと待ってたのよ、この瞬間を……!ふふ、最高の気分ね</t>
+        </is>
+      </c>
+    </row>
+    <row r="302" ht="40" customHeight="1">
+      <c r="A302" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.bold.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bold.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あら…随分と自信がおありのようね。壊してあげるわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="303" ht="40" customHeight="1">
+      <c r="A303" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.bold.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bold.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">可哀想だけど…手加減はしないわよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="304" ht="40" customHeight="1">
+      <c r="A304" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.bold.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bold.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あら、残念。もっと遊びたかったのに</t>
+        </is>
+      </c>
+    </row>
+    <row r="305" ht="40" customHeight="1">
+      <c r="A305" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.bold.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bold.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">逃げちゃうの？ …つまらない団体ね</t>
+        </is>
+      </c>
+    </row>
+    <row r="306" ht="40" customHeight="1">
+      <c r="A306" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.bold.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_lose.bold.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あら…やられちゃったわ。……許さないけど</t>
+        </is>
+      </c>
+    </row>
+    <row r="307" ht="40" customHeight="1">
+      <c r="A307" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.bold.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_lose.bold.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">今日は譲ってあげるわ。次は…ないけどね</t>
+        </is>
+      </c>
+    </row>
+    <row r="308" ht="40" customHeight="1">
+      <c r="A308" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.bold.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_win.bold.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あら、もう終わり？ もっと楽しみたかったのに</t>
+        </is>
+      </c>
+    </row>
+    <row r="309" ht="40" customHeight="1">
+      <c r="A309" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.bold.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_win.bold.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">予想通りの結果ね。つまらないわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="310" ht="40" customHeight="1">
+      <c r="A310" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.bold.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bold.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">当然よ。うちの団体を甘く見ないことね</t>
+        </is>
+      </c>
+    </row>
+    <row r="311" ht="40" customHeight="1">
+      <c r="A311" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.bold.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bold.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">まだ物足りないわね。もっと強い相手はいないの？</t>
+        </is>
+      </c>
+    </row>
+    <row r="312" ht="40" customHeight="1">
+      <c r="A312" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.bold.seductive[3]</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bold.seductive[3]</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">当然の結果よ。うちを甘く見ないことね</t>
+        </is>
+      </c>
+    </row>
+    <row r="313" ht="40" customHeight="1">
+      <c r="A313" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">ENDING_LINES.fighter.bold.seductive[1]</t>
         </is>
       </c>
-      <c r="B280" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C280" t="inlineStr" s="2">
+      <c r="B313" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">ENDING_LINES</t>
         </is>
       </c>
-      <c r="D280" t="inlineStr" s="12">
+      <c r="D313" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">fighter.bold.seductive[1]</t>
         </is>
       </c>
-      <c r="E280" t="inlineStr" s="2">
+      <c r="E313" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">18 経営危機・エンディング</t>
         </is>
       </c>
-      <c r="F280" t="inlineStr" s="3">
+      <c r="F313" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">頂点に立ったわ。でもまだ先があるみたいね</t>
         </is>
       </c>
     </row>
+    <row r="314" ht="40" customHeight="1">
+      <c r="A314" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.bold.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bold.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">拾った目利きは正解よ。…すぐに分かるわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="315" ht="40" customHeight="1">
+      <c r="A315" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES.bold.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bold.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">わたしに声をかけた責任は、取ってちょうだいね</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H280"/>
+  <autoFilter ref="A1:H315"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/蠱惑×強気.xlsx
+++ b/セリフ編集/キャラタイプ別/蠱惑×強気.xlsx
@@ -306,7 +306,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H315"/>
+  <dimension ref="A1:H314"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -364,7 +364,7 @@
     <row r="2" ht="40" customHeight="1">
       <c r="A2" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.bold.seductive[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr" s="2">
@@ -379,7 +379,7 @@
       </c>
       <c r="D2" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.bold.seductive[1]</t>
+          <t xml:space="preserve">atk.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E2" t="inlineStr" s="2">
@@ -396,7 +396,7 @@
     <row r="3" ht="40" customHeight="1">
       <c r="A3" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.bold.seductive[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr" s="2">
@@ -411,7 +411,7 @@
       </c>
       <c r="D3" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.bold.seductive[2]</t>
+          <t xml:space="preserve">atk.seductive.bold[2]</t>
         </is>
       </c>
       <c r="E3" t="inlineStr" s="2">
@@ -428,7 +428,7 @@
     <row r="4" ht="40" customHeight="1">
       <c r="A4" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.bold.seductive[3]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.seductive.bold[3]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr" s="2">
@@ -443,7 +443,7 @@
       </c>
       <c r="D4" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.bold.seductive[3]</t>
+          <t xml:space="preserve">atk.seductive.bold[3]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr" s="2">
@@ -460,7 +460,7 @@
     <row r="5" ht="40" customHeight="1">
       <c r="A5" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.bold.seductive[4]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.seductive.bold[4]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr" s="2">
@@ -475,7 +475,7 @@
       </c>
       <c r="D5" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.bold.seductive[4]</t>
+          <t xml:space="preserve">atk.seductive.bold[4]</t>
         </is>
       </c>
       <c r="E5" t="inlineStr" s="2">
@@ -492,7 +492,7 @@
     <row r="6" ht="40" customHeight="1">
       <c r="A6" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.bold.seductive[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr" s="2">
@@ -507,7 +507,7 @@
       </c>
       <c r="D6" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.bold.seductive[1]</t>
+          <t xml:space="preserve">bigmove.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E6" t="inlineStr" s="2">
@@ -524,7 +524,7 @@
     <row r="7" ht="40" customHeight="1">
       <c r="A7" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.bold.seductive[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr" s="2">
@@ -539,7 +539,7 @@
       </c>
       <c r="D7" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.bold.seductive[2]</t>
+          <t xml:space="preserve">bigmove.seductive.bold[2]</t>
         </is>
       </c>
       <c r="E7" t="inlineStr" s="2">
@@ -556,7 +556,7 @@
     <row r="8" ht="40" customHeight="1">
       <c r="A8" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.bold.seductive[3]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.seductive.bold[3]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr" s="2">
@@ -571,7 +571,7 @@
       </c>
       <c r="D8" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.bold.seductive[3]</t>
+          <t xml:space="preserve">bigmove.seductive.bold[3]</t>
         </is>
       </c>
       <c r="E8" t="inlineStr" s="2">
@@ -588,7 +588,7 @@
     <row r="9" ht="40" customHeight="1">
       <c r="A9" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.climax.bold.seductive[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.climax.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr" s="2">
@@ -603,7 +603,7 @@
       </c>
       <c r="D9" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">climax.bold.seductive[1]</t>
+          <t xml:space="preserve">climax.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E9" t="inlineStr" s="2">
@@ -620,7 +620,7 @@
     <row r="10" ht="40" customHeight="1">
       <c r="A10" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.climax.bold.seductive[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.climax.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr" s="2">
@@ -635,7 +635,7 @@
       </c>
       <c r="D10" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">climax.bold.seductive[2]</t>
+          <t xml:space="preserve">climax.seductive.bold[2]</t>
         </is>
       </c>
       <c r="E10" t="inlineStr" s="2">
@@ -652,7 +652,7 @@
     <row r="11" ht="40" customHeight="1">
       <c r="A11" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES.bold.seductive[1]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr" s="2">
@@ -667,7 +667,7 @@
       </c>
       <c r="D11" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[1]</t>
+          <t xml:space="preserve">seductive.bold[1]</t>
         </is>
       </c>
       <c r="E11" t="inlineStr" s="2">
@@ -684,7 +684,7 @@
     <row r="12" ht="40" customHeight="1">
       <c r="A12" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES.bold.seductive[2]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr" s="2">
@@ -699,7 +699,7 @@
       </c>
       <c r="D12" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[2]</t>
+          <t xml:space="preserve">seductive.bold[2]</t>
         </is>
       </c>
       <c r="E12" t="inlineStr" s="2">
@@ -716,7 +716,7 @@
     <row r="13" ht="40" customHeight="1">
       <c r="A13" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES.bold.seductive[3]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.seductive.bold[3]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr" s="2">
@@ -731,7 +731,7 @@
       </c>
       <c r="D13" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[3]</t>
+          <t xml:space="preserve">seductive.bold[3]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr" s="2">
@@ -748,7 +748,7 @@
     <row r="14" ht="40" customHeight="1">
       <c r="A14" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner.bold.seductive[1]</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr" s="2">
@@ -763,7 +763,7 @@
       </c>
       <c r="D14" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">badWinner.bold.seductive[1]</t>
+          <t xml:space="preserve">badWinner.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E14" t="inlineStr" s="2">
@@ -780,7 +780,7 @@
     <row r="15" ht="40" customHeight="1">
       <c r="A15" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner.bold.seductive[1]</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr" s="2">
@@ -795,7 +795,7 @@
       </c>
       <c r="D15" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">goodWinner.bold.seductive[1]</t>
+          <t xml:space="preserve">goodWinner.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E15" t="inlineStr" s="2">
@@ -812,7 +812,7 @@
     <row r="16" ht="40" customHeight="1">
       <c r="A16" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.bold.seductive[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr" s="2">
@@ -827,7 +827,7 @@
       </c>
       <c r="D16" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">competition_won.bold.seductive[1]</t>
+          <t xml:space="preserve">competition_won.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E16" t="inlineStr" s="2">
@@ -844,7 +844,7 @@
     <row r="17" ht="40" customHeight="1">
       <c r="A17" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.bold.seductive[2]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B17" t="inlineStr" s="2">
@@ -859,7 +859,7 @@
       </c>
       <c r="D17" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">competition_won.bold.seductive[2]</t>
+          <t xml:space="preserve">competition_won.seductive.bold[2]</t>
         </is>
       </c>
       <c r="E17" t="inlineStr" s="2">
@@ -876,7 +876,7 @@
     <row r="18" ht="40" customHeight="1">
       <c r="A18" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.bold.seductive[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr" s="2">
@@ -891,7 +891,7 @@
       </c>
       <c r="D18" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">direct.bold.seductive[1]</t>
+          <t xml:space="preserve">direct.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E18" t="inlineStr" s="2">
@@ -908,7 +908,7 @@
     <row r="19" ht="40" customHeight="1">
       <c r="A19" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.bold.seductive[2]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B19" t="inlineStr" s="2">
@@ -923,7 +923,7 @@
       </c>
       <c r="D19" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">direct.bold.seductive[2]</t>
+          <t xml:space="preserve">direct.seductive.bold[2]</t>
         </is>
       </c>
       <c r="E19" t="inlineStr" s="2">
@@ -940,7 +940,7 @@
     <row r="20" ht="40" customHeight="1">
       <c r="A20" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing.bold.seductive[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B20" t="inlineStr" s="2">
@@ -955,7 +955,7 @@
       </c>
       <c r="D20" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fa_signing.bold.seductive[1]</t>
+          <t xml:space="preserve">fa_signing.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E20" t="inlineStr" s="2">
@@ -972,7 +972,7 @@
     <row r="21" ht="40" customHeight="1">
       <c r="A21" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing.bold.seductive[2]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B21" t="inlineStr" s="2">
@@ -987,7 +987,7 @@
       </c>
       <c r="D21" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fa_signing.bold.seductive[2]</t>
+          <t xml:space="preserve">fa_signing.seductive.bold[2]</t>
         </is>
       </c>
       <c r="E21" t="inlineStr" s="2">
@@ -1004,7 +1004,7 @@
     <row r="22" ht="40" customHeight="1">
       <c r="A22" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.bold.seductive.hit[1]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.seductive.bold.hit[1]</t>
         </is>
       </c>
       <c r="B22" t="inlineStr" s="2">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="D22" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive.hit[1]</t>
+          <t xml:space="preserve">seductive.bold.hit[1]</t>
         </is>
       </c>
       <c r="E22" t="inlineStr" s="2">
@@ -1036,7 +1036,7 @@
     <row r="23" ht="40" customHeight="1">
       <c r="A23" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.bold.seductive.hit[2]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.seductive.bold.hit[2]</t>
         </is>
       </c>
       <c r="B23" t="inlineStr" s="2">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="D23" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive.hit[2]</t>
+          <t xml:space="preserve">seductive.bold.hit[2]</t>
         </is>
       </c>
       <c r="E23" t="inlineStr" s="2">
@@ -1068,7 +1068,7 @@
     <row r="24" ht="40" customHeight="1">
       <c r="A24" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.bold.seductive.win[1]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.seductive.bold.win[1]</t>
         </is>
       </c>
       <c r="B24" t="inlineStr" s="2">
@@ -1083,7 +1083,7 @@
       </c>
       <c r="D24" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive.win[1]</t>
+          <t xml:space="preserve">seductive.bold.win[1]</t>
         </is>
       </c>
       <c r="E24" t="inlineStr" s="2">
@@ -1100,7 +1100,7 @@
     <row r="25" ht="40" customHeight="1">
       <c r="A25" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.bold.seductive.win[2]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.seductive.bold.win[2]</t>
         </is>
       </c>
       <c r="B25" t="inlineStr" s="2">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="D25" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive.win[2]</t>
+          <t xml:space="preserve">seductive.bold.win[2]</t>
         </is>
       </c>
       <c r="E25" t="inlineStr" s="2">
@@ -1132,7 +1132,7 @@
     <row r="26" ht="40" customHeight="1">
       <c r="A26" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BETRAYAL_LINES.bold.seductive[1]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B26" t="inlineStr" s="2">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="D26" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[1]</t>
+          <t xml:space="preserve">seductive.bold[1]</t>
         </is>
       </c>
       <c r="E26" t="inlineStr" s="2">
@@ -1164,7 +1164,7 @@
     <row r="27" ht="40" customHeight="1">
       <c r="A27" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BETRAYAL_LINES.bold.seductive[2]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B27" t="inlineStr" s="2">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="D27" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[2]</t>
+          <t xml:space="preserve">seductive.bold[2]</t>
         </is>
       </c>
       <c r="E27" t="inlineStr" s="2">
@@ -1196,7 +1196,7 @@
     <row r="28" ht="40" customHeight="1">
       <c r="A28" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BETRAYAL_LINES.bold.seductive[3]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.seductive.bold[3]</t>
         </is>
       </c>
       <c r="B28" t="inlineStr" s="2">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="D28" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[3]</t>
+          <t xml:space="preserve">seductive.bold[3]</t>
         </is>
       </c>
       <c r="E28" t="inlineStr" s="2">
@@ -1228,7 +1228,7 @@
     <row r="29" ht="40" customHeight="1">
       <c r="A29" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_SAVE_LINES.bold.seductive[1]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B29" t="inlineStr" s="2">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="D29" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[1]</t>
+          <t xml:space="preserve">seductive.bold[1]</t>
         </is>
       </c>
       <c r="E29" t="inlineStr" s="2">
@@ -1260,7 +1260,7 @@
     <row r="30" ht="40" customHeight="1">
       <c r="A30" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_SAVE_LINES.bold.seductive[2]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B30" t="inlineStr" s="2">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="D30" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[2]</t>
+          <t xml:space="preserve">seductive.bold[2]</t>
         </is>
       </c>
       <c r="E30" t="inlineStr" s="2">
@@ -1292,7 +1292,7 @@
     <row r="31" ht="40" customHeight="1">
       <c r="A31" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_SAVE_LINES.bold.seductive[3]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.seductive.bold[3]</t>
         </is>
       </c>
       <c r="B31" t="inlineStr" s="2">
@@ -1307,7 +1307,7 @@
       </c>
       <c r="D31" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[3]</t>
+          <t xml:space="preserve">seductive.bold[3]</t>
         </is>
       </c>
       <c r="E31" t="inlineStr" s="2">
@@ -1324,7 +1324,7 @@
     <row r="32" ht="40" customHeight="1">
       <c r="A32" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_LINES.bold.seductive[1]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B32" t="inlineStr" s="2">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="D32" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[1]</t>
+          <t xml:space="preserve">seductive.bold[1]</t>
         </is>
       </c>
       <c r="E32" t="inlineStr" s="2">
@@ -1356,7 +1356,7 @@
     <row r="33" ht="40" customHeight="1">
       <c r="A33" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_LINES.bold.seductive[2]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B33" t="inlineStr" s="2">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="D33" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[2]</t>
+          <t xml:space="preserve">seductive.bold[2]</t>
         </is>
       </c>
       <c r="E33" t="inlineStr" s="2">
@@ -1388,7 +1388,7 @@
     <row r="34" ht="40" customHeight="1">
       <c r="A34" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_LINES.bold.seductive[3]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.seductive.bold[3]</t>
         </is>
       </c>
       <c r="B34" t="inlineStr" s="2">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="D34" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[3]</t>
+          <t xml:space="preserve">seductive.bold[3]</t>
         </is>
       </c>
       <c r="E34" t="inlineStr" s="2">
@@ -1420,7 +1420,7 @@
     <row r="35" ht="40" customHeight="1">
       <c r="A35" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HOT_TAG_LINES.bold.seductive[1]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B35" t="inlineStr" s="2">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="D35" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[1]</t>
+          <t xml:space="preserve">seductive.bold[1]</t>
         </is>
       </c>
       <c r="E35" t="inlineStr" s="2">
@@ -1452,7 +1452,7 @@
     <row r="36" ht="40" customHeight="1">
       <c r="A36" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HOT_TAG_LINES.bold.seductive[2]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B36" t="inlineStr" s="2">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="D36" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[2]</t>
+          <t xml:space="preserve">seductive.bold[2]</t>
         </is>
       </c>
       <c r="E36" t="inlineStr" s="2">
@@ -1484,7 +1484,7 @@
     <row r="37" ht="40" customHeight="1">
       <c r="A37" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HOT_TAG_LINES.bold.seductive[3]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.seductive.bold[3]</t>
         </is>
       </c>
       <c r="B37" t="inlineStr" s="2">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="D37" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[3]</t>
+          <t xml:space="preserve">seductive.bold[3]</t>
         </is>
       </c>
       <c r="E37" t="inlineStr" s="2">
@@ -1516,7 +1516,7 @@
     <row r="38" ht="40" customHeight="1">
       <c r="A38" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.bold.seductive[1]</t>
+          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B38" t="inlineStr" s="2">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="D38" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[1]</t>
+          <t xml:space="preserve">seductive.bold[1]</t>
         </is>
       </c>
       <c r="E38" t="inlineStr" s="2">
@@ -1548,7 +1548,7 @@
     <row r="39" ht="40" customHeight="1">
       <c r="A39" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.bold.seductive[2]</t>
+          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B39" t="inlineStr" s="2">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="D39" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[2]</t>
+          <t xml:space="preserve">seductive.bold[2]</t>
         </is>
       </c>
       <c r="E39" t="inlineStr" s="2">
@@ -1580,7 +1580,7 @@
     <row r="40" ht="40" customHeight="1">
       <c r="A40" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_WIN_LINES.bold.seductive[1]</t>
+          <t xml:space="preserve">TAG_MATCH_WIN_LINES.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B40" t="inlineStr" s="2">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="D40" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[1]</t>
+          <t xml:space="preserve">seductive.bold[1]</t>
         </is>
       </c>
       <c r="E40" t="inlineStr" s="2">
@@ -1612,7 +1612,7 @@
     <row r="41" ht="40" customHeight="1">
       <c r="A41" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_WIN_LINES.bold.seductive[2]</t>
+          <t xml:space="preserve">TAG_MATCH_WIN_LINES.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B41" t="inlineStr" s="2">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="D41" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[2]</t>
+          <t xml:space="preserve">seductive.bold[2]</t>
         </is>
       </c>
       <c r="E41" t="inlineStr" s="2">
@@ -1644,7 +1644,7 @@
     <row r="42" ht="40" customHeight="1">
       <c r="A42" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser.bold.seductive[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B42" t="inlineStr" s="2">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="D42" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.bold.seductive[1]</t>
+          <t xml:space="preserve">loser.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E42" t="inlineStr" s="2">
@@ -1676,7 +1676,7 @@
     <row r="43" ht="40" customHeight="1">
       <c r="A43" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner.bold.seductive[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B43" t="inlineStr" s="2">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="D43" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.bold.seductive[1]</t>
+          <t xml:space="preserve">winner.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E43" t="inlineStr" s="2">
@@ -1708,7 +1708,7 @@
     <row r="44" ht="40" customHeight="1">
       <c r="A44" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.loser.bold.seductive[1]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.loser.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B44" t="inlineStr" s="2">
@@ -1723,7 +1723,7 @@
       </c>
       <c r="D44" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.bold.seductive[1]</t>
+          <t xml:space="preserve">loser.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E44" t="inlineStr" s="2">
@@ -1740,7 +1740,7 @@
     <row r="45" ht="40" customHeight="1">
       <c r="A45" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.bold.seductive[1]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B45" t="inlineStr" s="2">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="D45" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.bold.seductive[1]</t>
+          <t xml:space="preserve">winner.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E45" t="inlineStr" s="2">
@@ -1772,7 +1772,7 @@
     <row r="46" ht="40" customHeight="1">
       <c r="A46" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.bold.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B46" t="inlineStr" s="2">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="D46" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.bold.seductive[1]</t>
+          <t xml:space="preserve">attacker.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E46" t="inlineStr" s="2">
@@ -1804,7 +1804,7 @@
     <row r="47" ht="40" customHeight="1">
       <c r="A47" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.bold.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B47" t="inlineStr" s="2">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="D47" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.bold.seductive[1]</t>
+          <t xml:space="preserve">defender.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E47" t="inlineStr" s="2">
@@ -1836,7 +1836,7 @@
     <row r="48" ht="40" customHeight="1">
       <c r="A48" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker.bold.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B48" t="inlineStr" s="2">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="D48" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.bold.seductive[1]</t>
+          <t xml:space="preserve">attacker.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E48" t="inlineStr" s="2">
@@ -1868,7 +1868,7 @@
     <row r="49" ht="40" customHeight="1">
       <c r="A49" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender.bold.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B49" t="inlineStr" s="2">
@@ -1883,7 +1883,7 @@
       </c>
       <c r="D49" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.bold.seductive[1]</t>
+          <t xml:space="preserve">defender.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E49" t="inlineStr" s="2">
@@ -1900,7 +1900,7 @@
     <row r="50" ht="40" customHeight="1">
       <c r="A50" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.bold.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B50" t="inlineStr" s="2">
@@ -1915,7 +1915,7 @@
       </c>
       <c r="D50" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.bold.seductive[1]</t>
+          <t xml:space="preserve">attacker.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E50" t="inlineStr" s="2">
@@ -1932,7 +1932,7 @@
     <row r="51" ht="40" customHeight="1">
       <c r="A51" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.bold.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B51" t="inlineStr" s="2">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="D51" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.bold.seductive[1]</t>
+          <t xml:space="preserve">loserLines.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E51" t="inlineStr" s="2">
@@ -1964,7 +1964,7 @@
     <row r="52" ht="40" customHeight="1">
       <c r="A52" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.bold.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B52" t="inlineStr" s="2">
@@ -1979,7 +1979,7 @@
       </c>
       <c r="D52" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.bold.seductive[1]</t>
+          <t xml:space="preserve">winnerLines.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E52" t="inlineStr" s="2">
@@ -1996,7 +1996,7 @@
     <row r="53" ht="40" customHeight="1">
       <c r="A53" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.bold.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B53" t="inlineStr" s="2">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="D53" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.bold.seductive[1]</t>
+          <t xml:space="preserve">loser.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E53" t="inlineStr" s="2">
@@ -2028,7 +2028,7 @@
     <row r="54" ht="40" customHeight="1">
       <c r="A54" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.bold.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B54" t="inlineStr" s="2">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="D54" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.bold.seductive[1]</t>
+          <t xml:space="preserve">winner.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E54" t="inlineStr" s="2">
@@ -2060,7 +2060,7 @@
     <row r="55" ht="40" customHeight="1">
       <c r="A55" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.bold.seductive[1]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B55" t="inlineStr" s="2">
@@ -2075,7 +2075,7 @@
       </c>
       <c r="D55" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.bold.seductive[1]</t>
+          <t xml:space="preserve">loserLines.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E55" t="inlineStr" s="2">
@@ -2092,7 +2092,7 @@
     <row r="56" ht="40" customHeight="1">
       <c r="A56" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.bold.seductive[1]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B56" t="inlineStr" s="2">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="D56" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.bold.seductive[1]</t>
+          <t xml:space="preserve">winnerLines.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E56" t="inlineStr" s="2">
@@ -2892,7 +2892,7 @@
     <row r="81" ht="40" customHeight="1">
       <c r="A81" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.bold.seductive[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B81" t="inlineStr" s="2">
@@ -2907,7 +2907,7 @@
       </c>
       <c r="D81" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accepted.bold.seductive[1]</t>
+          <t xml:space="preserve">accepted.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E81" t="inlineStr" s="2">
@@ -2924,7 +2924,7 @@
     <row r="82" ht="40" customHeight="1">
       <c r="A82" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.bold.seductive[2]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B82" t="inlineStr" s="2">
@@ -2939,7 +2939,7 @@
       </c>
       <c r="D82" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accepted.bold.seductive[2]</t>
+          <t xml:space="preserve">accepted.seductive.bold[2]</t>
         </is>
       </c>
       <c r="E82" t="inlineStr" s="2">
@@ -2956,7 +2956,7 @@
     <row r="83" ht="40" customHeight="1">
       <c r="A83" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.bold.seductive[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B83" t="inlineStr" s="2">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="D83" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defended.bold.seductive[1]</t>
+          <t xml:space="preserve">defended.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E83" t="inlineStr" s="2">
@@ -2988,7 +2988,7 @@
     <row r="84" ht="40" customHeight="1">
       <c r="A84" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.bold.seductive[2]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B84" t="inlineStr" s="2">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="D84" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defended.bold.seductive[2]</t>
+          <t xml:space="preserve">defended.seductive.bold[2]</t>
         </is>
       </c>
       <c r="E84" t="inlineStr" s="2">
@@ -3020,7 +3020,7 @@
     <row r="85" ht="40" customHeight="1">
       <c r="A85" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.bold.seductive[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B85" t="inlineStr" s="2">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="D85" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defense_failed.bold.seductive[1]</t>
+          <t xml:space="preserve">defense_failed.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E85" t="inlineStr" s="2">
@@ -3052,7 +3052,7 @@
     <row r="86" ht="40" customHeight="1">
       <c r="A86" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.bold.seductive[2]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B86" t="inlineStr" s="2">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="D86" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defense_failed.bold.seductive[2]</t>
+          <t xml:space="preserve">defense_failed.seductive.bold[2]</t>
         </is>
       </c>
       <c r="E86" t="inlineStr" s="2">
@@ -3084,7 +3084,7 @@
     <row r="87" ht="40" customHeight="1">
       <c r="A87" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.default.bold.seductive[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.default.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B87" t="inlineStr" s="2">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="D87" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">default.bold.seductive[1]</t>
+          <t xml:space="preserve">default.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E87" t="inlineStr" s="2">
@@ -3116,7 +3116,7 @@
     <row r="88" ht="40" customHeight="1">
       <c r="A88" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.former_champ.bold.seductive[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.former_champ.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B88" t="inlineStr" s="2">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="D88" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">former_champ.bold.seductive[1]</t>
+          <t xml:space="preserve">former_champ.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E88" t="inlineStr" s="2">
@@ -3148,7 +3148,7 @@
     <row r="89" ht="40" customHeight="1">
       <c r="A89" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.heel.bold.seductive[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.heel.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B89" t="inlineStr" s="2">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="D89" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heel.bold.seductive[1]</t>
+          <t xml:space="preserve">heel.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E89" t="inlineStr" s="2">
@@ -3180,7 +3180,7 @@
     <row r="90" ht="40" customHeight="1">
       <c r="A90" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.high_trust.bold.seductive[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.high_trust.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B90" t="inlineStr" s="2">
@@ -3195,7 +3195,7 @@
       </c>
       <c r="D90" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">high_trust.bold.seductive[1]</t>
+          <t xml:space="preserve">high_trust.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E90" t="inlineStr" s="2">
@@ -3212,7 +3212,7 @@
     <row r="91" ht="40" customHeight="1">
       <c r="A91" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_former_champ.bold.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_former_champ.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B91" t="inlineStr" s="2">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="D91" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_former_champ.bold.seductive[1]</t>
+          <t xml:space="preserve">accept_former_champ.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E91" t="inlineStr" s="2">
@@ -3244,7 +3244,7 @@
     <row r="92" ht="40" customHeight="1">
       <c r="A92" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_heel.bold.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_heel.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B92" t="inlineStr" s="2">
@@ -3259,7 +3259,7 @@
       </c>
       <c r="D92" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_heel.bold.seductive[1]</t>
+          <t xml:space="preserve">accept_heel.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E92" t="inlineStr" s="2">
@@ -3276,7 +3276,7 @@
     <row r="93" ht="40" customHeight="1">
       <c r="A93" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_no_title.bold.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_no_title.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B93" t="inlineStr" s="2">
@@ -3291,7 +3291,7 @@
       </c>
       <c r="D93" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_no_title.bold.seductive[1]</t>
+          <t xml:space="preserve">accept_no_title.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E93" t="inlineStr" s="2">
@@ -3308,7 +3308,7 @@
     <row r="94" ht="40" customHeight="1">
       <c r="A94" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.bold.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B94" t="inlineStr" s="2">
@@ -3323,7 +3323,7 @@
       </c>
       <c r="D94" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_terminal.bold.seductive[1]</t>
+          <t xml:space="preserve">accept_terminal.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E94" t="inlineStr" s="2">
@@ -3340,7 +3340,7 @@
     <row r="95" ht="40" customHeight="1">
       <c r="A95" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_winless.bold.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_winless.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B95" t="inlineStr" s="2">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="D95" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_winless.bold.seductive[1]</t>
+          <t xml:space="preserve">accept_winless.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E95" t="inlineStr" s="2">
@@ -3372,7 +3372,7 @@
     <row r="96" ht="40" customHeight="1">
       <c r="A96" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.bold.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B96" t="inlineStr" s="2">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="D96" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_champ.bold.seductive[1]</t>
+          <t xml:space="preserve">refuse_champ.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E96" t="inlineStr" s="2">
@@ -3404,7 +3404,7 @@
     <row r="97" ht="40" customHeight="1">
       <c r="A97" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_distrust.bold.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_distrust.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B97" t="inlineStr" s="2">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="D97" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_distrust.bold.seductive[1]</t>
+          <t xml:space="preserve">refuse_distrust.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E97" t="inlineStr" s="2">
@@ -3436,7 +3436,7 @@
     <row r="98" ht="40" customHeight="1">
       <c r="A98" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_fighting.bold.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_fighting.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B98" t="inlineStr" s="2">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="D98" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_fighting.bold.seductive[1]</t>
+          <t xml:space="preserve">refuse_fighting.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E98" t="inlineStr" s="2">
@@ -3468,7 +3468,7 @@
     <row r="99" ht="40" customHeight="1">
       <c r="A99" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_heel.bold.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_heel.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B99" t="inlineStr" s="2">
@@ -3483,7 +3483,7 @@
       </c>
       <c r="D99" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_heel.bold.seductive[1]</t>
+          <t xml:space="preserve">refuse_heel.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E99" t="inlineStr" s="2">
@@ -3500,7 +3500,7 @@
     <row r="100" ht="40" customHeight="1">
       <c r="A100" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.bold.seductive[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B100" t="inlineStr" s="2">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="D100" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A1_champion.bold.seductive[1]</t>
+          <t xml:space="preserve">A1_champion.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E100" t="inlineStr" s="2">
@@ -3532,7 +3532,7 @@
     <row r="101" ht="40" customHeight="1">
       <c r="A101" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.bold.seductive[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B101" t="inlineStr" s="2">
@@ -3547,7 +3547,7 @@
       </c>
       <c r="D101" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A2_uncrowned.bold.seductive[1]</t>
+          <t xml:space="preserve">A2_uncrowned.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E101" t="inlineStr" s="2">
@@ -3564,7 +3564,7 @@
     <row r="102" ht="40" customHeight="1">
       <c r="A102" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.bold.seductive[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B102" t="inlineStr" s="2">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="D102" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A3_heel.bold.seductive[1]</t>
+          <t xml:space="preserve">A3_heel.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E102" t="inlineStr" s="2">
@@ -3596,7 +3596,7 @@
     <row r="103" ht="40" customHeight="1">
       <c r="A103" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.bold.seductive[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B103" t="inlineStr" s="2">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="D103" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A4_veteran.bold.seductive[1]</t>
+          <t xml:space="preserve">A4_veteran.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E103" t="inlineStr" s="2">
@@ -3628,7 +3628,7 @@
     <row r="104" ht="40" customHeight="1">
       <c r="A104" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B1_young.bold.seductive[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B1_young.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B104" t="inlineStr" s="2">
@@ -3643,7 +3643,7 @@
       </c>
       <c r="D104" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1_young.bold.seductive[1]</t>
+          <t xml:space="preserve">B1_young.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E104" t="inlineStr" s="2">
@@ -3660,7 +3660,7 @@
     <row r="105" ht="40" customHeight="1">
       <c r="A105" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.bold.seductive[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B105" t="inlineStr" s="2">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="D105" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_prime.bold.seductive[1]</t>
+          <t xml:space="preserve">B2_prime.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E105" t="inlineStr" s="2">
@@ -3692,7 +3692,7 @@
     <row r="106" ht="40" customHeight="1">
       <c r="A106" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B3_older.bold.seductive[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B3_older.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B106" t="inlineStr" s="2">
@@ -3707,7 +3707,7 @@
       </c>
       <c r="D106" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B3_older.bold.seductive[1]</t>
+          <t xml:space="preserve">B3_older.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E106" t="inlineStr" s="2">
@@ -3724,7 +3724,7 @@
     <row r="107" ht="40" customHeight="1">
       <c r="A107" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.bold.seductive[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B107" t="inlineStr" s="2">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="D107" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_champion_injury.bold.seductive[1]</t>
+          <t xml:space="preserve">B4_champion_injury.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E107" t="inlineStr" s="2">
@@ -3756,7 +3756,7 @@
     <row r="108" ht="40" customHeight="1">
       <c r="A108" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VOLUNTARY_STAY_LINES.bold.seductive[1]</t>
+          <t xml:space="preserve">VOLUNTARY_STAY_LINES.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B108" t="inlineStr" s="2">
@@ -3771,7 +3771,7 @@
       </c>
       <c r="D108" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[1]</t>
+          <t xml:space="preserve">seductive.bold[1]</t>
         </is>
       </c>
       <c r="E108" t="inlineStr" s="2">
@@ -3788,7 +3788,7 @@
     <row r="109" ht="40" customHeight="1">
       <c r="A109" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.bold.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B109" t="inlineStr" s="2">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="D109" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_accept.bold.seductive[1]</t>
+          <t xml:space="preserve">raise_accept.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E109" t="inlineStr" s="2">
@@ -3820,7 +3820,7 @@
     <row r="110" ht="40" customHeight="1">
       <c r="A110" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.bold.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B110" t="inlineStr" s="2">
@@ -3835,7 +3835,7 @@
       </c>
       <c r="D110" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_accept.bold.seductive[1]</t>
+          <t xml:space="preserve">raise_negotiate_accept.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E110" t="inlineStr" s="2">
@@ -3852,7 +3852,7 @@
     <row r="111" ht="40" customHeight="1">
       <c r="A111" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.bold.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B111" t="inlineStr" s="2">
@@ -3867,7 +3867,7 @@
       </c>
       <c r="D111" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_refuse.bold.seductive[1]</t>
+          <t xml:space="preserve">raise_negotiate_refuse.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E111" t="inlineStr" s="2">
@@ -3884,7 +3884,7 @@
     <row r="112" ht="40" customHeight="1">
       <c r="A112" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.bold.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B112" t="inlineStr" s="2">
@@ -3899,7 +3899,7 @@
       </c>
       <c r="D112" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.bold.seductive[1]</t>
+          <t xml:space="preserve">raise_open.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E112" t="inlineStr" s="2">
@@ -3916,7 +3916,7 @@
     <row r="113" ht="40" customHeight="1">
       <c r="A113" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.bold.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B113" t="inlineStr" s="2">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="D113" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_refuse.bold.seductive[1]</t>
+          <t xml:space="preserve">raise_refuse.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E113" t="inlineStr" s="2">
@@ -3948,7 +3948,7 @@
     <row r="114" ht="40" customHeight="1">
       <c r="A114" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.bold.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B114" t="inlineStr" s="2">
@@ -3963,7 +3963,7 @@
       </c>
       <c r="D114" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.bold.seductive[1]</t>
+          <t xml:space="preserve">sudden_departure.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E114" t="inlineStr" s="2">
@@ -3980,7 +3980,7 @@
     <row r="115" ht="40" customHeight="1">
       <c r="A115" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.bold.seductive[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B115" t="inlineStr" s="2">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="D115" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.bold.seductive[2]</t>
+          <t xml:space="preserve">sudden_departure.seductive.bold[2]</t>
         </is>
       </c>
       <c r="E115" t="inlineStr" s="2">
@@ -4012,7 +4012,7 @@
     <row r="116" ht="40" customHeight="1">
       <c r="A116" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.bold.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B116" t="inlineStr" s="2">
@@ -4027,7 +4027,7 @@
       </c>
       <c r="D116" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_listen.bold.seductive[1]</t>
+          <t xml:space="preserve">transfer_listen.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E116" t="inlineStr" s="2">
@@ -4044,7 +4044,7 @@
     <row r="117" ht="40" customHeight="1">
       <c r="A117" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.bold.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B117" t="inlineStr" s="2">
@@ -4059,7 +4059,7 @@
       </c>
       <c r="D117" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.bold.seductive[1]</t>
+          <t xml:space="preserve">transfer_open.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E117" t="inlineStr" s="2">
@@ -4076,7 +4076,7 @@
     <row r="118" ht="40" customHeight="1">
       <c r="A118" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.bold.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B118" t="inlineStr" s="2">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="D118" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_release.bold.seductive[1]</t>
+          <t xml:space="preserve">transfer_release.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E118" t="inlineStr" s="2">
@@ -4108,7 +4108,7 @@
     <row r="119" ht="40" customHeight="1">
       <c r="A119" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.bold.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B119" t="inlineStr" s="2">
@@ -4123,7 +4123,7 @@
       </c>
       <c r="D119" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_fail.bold.seductive[1]</t>
+          <t xml:space="preserve">transfer_retain_fail.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E119" t="inlineStr" s="2">
@@ -4140,7 +4140,7 @@
     <row r="120" ht="40" customHeight="1">
       <c r="A120" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.bold.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B120" t="inlineStr" s="2">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="D120" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_success.bold.seductive[1]</t>
+          <t xml:space="preserve">transfer_retain_success.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E120" t="inlineStr" s="2">
@@ -4172,7 +4172,7 @@
     <row r="121" ht="40" customHeight="1">
       <c r="A121" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.blocked.bold.seductive[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.blocked.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B121" t="inlineStr" s="2">
@@ -4187,7 +4187,7 @@
       </c>
       <c r="D121" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">blocked.bold.seductive[1]</t>
+          <t xml:space="preserve">blocked.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E121" t="inlineStr" s="2">
@@ -4205,7 +4205,7 @@
     <row r="122" ht="40" customHeight="1">
       <c r="A122" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.fail.bold.seductive[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.fail.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B122" t="inlineStr" s="2">
@@ -4220,7 +4220,7 @@
       </c>
       <c r="D122" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fail.bold.seductive[1]</t>
+          <t xml:space="preserve">fail.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E122" t="inlineStr" s="2">
@@ -4238,7 +4238,7 @@
     <row r="123" ht="40" customHeight="1">
       <c r="A123" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.start.bold.seductive[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.start.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B123" t="inlineStr" s="2">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="D123" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">start.bold.seductive[1]</t>
+          <t xml:space="preserve">start.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E123" t="inlineStr" s="2">
@@ -4271,7 +4271,7 @@
     <row r="124" ht="40" customHeight="1">
       <c r="A124" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.success.bold.seductive[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.success.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B124" t="inlineStr" s="2">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="D124" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">success.bold.seductive[1]</t>
+          <t xml:space="preserve">success.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E124" t="inlineStr" s="2">
@@ -5552,39 +5552,39 @@
     <row r="164" ht="40" customHeight="1">
       <c r="A164" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F04_TARGET_LINES.bold.seductive[1]</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F04_TARGET_LINES</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
         </is>
       </c>
       <c r="D164" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[1]</t>
+          <t xml:space="preserve">seductive.bold[1]</t>
         </is>
       </c>
       <c r="E164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F164" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ……今、一番息ができるのは、あの人たちの隣なの。</t>
+          <t xml:space="preserve">当然よ。まだまだこんなものじゃないわ</t>
         </is>
       </c>
     </row>
     <row r="165" ht="40" customHeight="1">
       <c r="A165" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES.bold.seductive[1]</t>
+          <t xml:space="preserve">BT_HINT_LINES.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="C165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
+          <t xml:space="preserve">BT_HINT_LINES</t>
         </is>
       </c>
       <c r="D165" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[1]</t>
+          <t xml:space="preserve">seductive.bold[1]</t>
         </is>
       </c>
       <c r="E165" t="inlineStr" s="2">
@@ -5609,14 +5609,14 @@
       </c>
       <c r="F165" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">当然よ。まだまだこんなものじゃないわ</t>
+          <t xml:space="preserve">もう少し…あと少しで何かが掴めそうなの</t>
         </is>
       </c>
     </row>
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES.bold.seductive[1]</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="C166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
         </is>
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[1]</t>
+          <t xml:space="preserve">seductive.bold[1]</t>
         </is>
       </c>
       <c r="E166" t="inlineStr" s="2">
@@ -5641,14 +5641,14 @@
       </c>
       <c r="F166" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう少し…あと少しで何かが掴めそうなの</t>
+          <t xml:space="preserve">燃えないの…何をしても、火がつかないわ</t>
         </is>
       </c>
     </row>
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES.bold.seductive[1]</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -5658,12 +5658,12 @@
       </c>
       <c r="C167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
         </is>
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[1]</t>
+          <t xml:space="preserve">seductive.bold[1]</t>
         </is>
       </c>
       <c r="E167" t="inlineStr" s="2">
@@ -5673,14 +5673,14 @@
       </c>
       <c r="F167" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">燃えないの…何をしても、火がつかないわ</t>
+          <t xml:space="preserve">目が覚めたわ。ここで終わるなんて、つまらないもの</t>
         </is>
       </c>
     </row>
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.bold.seductive[1]</t>
+          <t xml:space="preserve">SLUMP_END_LINES.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="C168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
+          <t xml:space="preserve">SLUMP_END_LINES</t>
         </is>
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[1]</t>
+          <t xml:space="preserve">seductive.bold[1]</t>
         </is>
       </c>
       <c r="E168" t="inlineStr" s="2">
@@ -5705,14 +5705,14 @@
       </c>
       <c r="F168" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">目が覚めたわ。ここで終わるなんて、つまらないもの</t>
+          <t xml:space="preserve">お待たせ。ここからが本番よ</t>
         </is>
       </c>
     </row>
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES.bold.seductive[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.defeat.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -5722,12 +5722,12 @@
       </c>
       <c r="C169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[1]</t>
+          <t xml:space="preserve">defeat.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr" s="2">
@@ -5737,14 +5737,14 @@
       </c>
       <c r="F169" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お待たせ。ここからが本番よ</t>
+          <t xml:space="preserve">あら…おかしいわね、こんなはずじゃ</t>
         </is>
       </c>
     </row>
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.defeat.bold.seductive[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
@@ -5759,7 +5759,7 @@
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defeat.bold.seductive[1]</t>
+          <t xml:space="preserve">injury_moderate_recovery.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E170" t="inlineStr" s="2">
@@ -5769,14 +5769,14 @@
       </c>
       <c r="F170" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら…おかしいわね、こんなはずじゃ</t>
+          <t xml:space="preserve">治ったはずなのに…おかしいわね</t>
         </is>
       </c>
     </row>
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.bold.seductive[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_moderate_recovery.bold.seductive[1]</t>
+          <t xml:space="preserve">injury_severe_recovery.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E171" t="inlineStr" s="2">
@@ -5801,14 +5801,14 @@
       </c>
       <c r="F171" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">治ったはずなのに…おかしいわね</t>
+          <t xml:space="preserve">私が…怯えてる？ 嘘でしょう</t>
         </is>
       </c>
     </row>
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.bold.seductive[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5823,7 +5823,7 @@
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_severe_recovery.bold.seductive[1]</t>
+          <t xml:space="preserve">penalty_end.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E172" t="inlineStr" s="2">
@@ -5833,14 +5833,14 @@
       </c>
       <c r="F172" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私が…怯えてる？ 嘘でしょう</t>
+          <t xml:space="preserve">体は万全なのに…気持ちがついてこないの</t>
         </is>
       </c>
     </row>
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.bold.seductive[1]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5850,29 +5850,29 @@
       </c>
       <c r="C173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">penalty_end.bold.seductive[1]</t>
+          <t xml:space="preserve">bestMatch.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F173" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">体は万全なのに…気持ちがついてこないの</t>
+          <t xml:space="preserve">全力を引き出してくれた相手に感謝。…次はもっと激しくいくわよ？</t>
         </is>
       </c>
     </row>
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.bold.seductive[1]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -5887,7 +5887,7 @@
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.bold.seductive[1]</t>
+          <t xml:space="preserve">champion.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E174" t="inlineStr" s="2">
@@ -5897,14 +5897,14 @@
       </c>
       <c r="F174" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全力を引き出してくれた相手に感謝。…次はもっと激しくいくわよ？</t>
+          <t xml:space="preserve">頂点からの景色は最高よ。…あなたには見せてあげないけど</t>
         </is>
       </c>
     </row>
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.bold.seductive[1]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -5919,7 +5919,7 @@
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.bold.seductive[1]</t>
+          <t xml:space="preserve">hallOfFame.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E175" t="inlineStr" s="2">
@@ -5929,14 +5929,14 @@
       </c>
       <c r="F175" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頂点からの景色は最高よ。…あなたには見せてあげないけど</t>
+          <t xml:space="preserve">最高の舞台で、最高の人生だった。…最後まで美しかったでしょう？</t>
         </is>
       </c>
     </row>
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.bold.seductive[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -5951,7 +5951,7 @@
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.bold.seductive[1]</t>
+          <t xml:space="preserve">mvp.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
@@ -5961,14 +5961,14 @@
       </c>
       <c r="F176" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高の舞台で、最高の人生だった。…最後まで美しかったでしょう？</t>
+          <t xml:space="preserve">一番になるべくしてなった。当然でしょう？ …でも、まだ満足してないわ</t>
         </is>
       </c>
     </row>
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.bold.seductive[1]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -5983,7 +5983,7 @@
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.bold.seductive[1]</t>
+          <t xml:space="preserve">rookie.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
@@ -5993,14 +5993,14 @@
       </c>
       <c r="F177" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一番になるべくしてなった。当然でしょう？ …でも、まだ満足してないわ</t>
+          <t xml:space="preserve">嬉しい？ ええ、嬉しいわ。でもこの程度で満足する女じゃないの</t>
         </is>
       </c>
     </row>
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.bold.seductive[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -6010,12 +6010,12 @@
       </c>
       <c r="C178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.bold.seductive[1]</t>
+          <t xml:space="preserve">seductive.bold[1]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr" s="2">
@@ -6025,14 +6025,14 @@
       </c>
       <c r="F178" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">嬉しい？ ええ、嬉しいわ。でもこの程度で満足する女じゃないの</t>
+          <t xml:space="preserve">ドームで…本気の私、見せてあげる</t>
         </is>
       </c>
     </row>
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.bold.seductive[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -6047,7 +6047,7 @@
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[1]</t>
+          <t xml:space="preserve">seductive.bold[2]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr" s="2">
@@ -6057,14 +6057,14 @@
       </c>
       <c r="F179" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ドームで…本気の私、見せてあげる</t>
+          <t xml:space="preserve">この大舞台、たっぷり熱くしてあげるわよ</t>
         </is>
       </c>
     </row>
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.bold.seductive[2]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.seductive.bold[3]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -6079,7 +6079,7 @@
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[2]</t>
+          <t xml:space="preserve">seductive.bold[3]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
@@ -6089,14 +6089,14 @@
       </c>
       <c r="F180" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この大舞台、たっぷり熱くしてあげるわよ</t>
+          <t xml:space="preserve">うふふ、今夜は容赦しないわよ</t>
         </is>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.bold.seductive[3]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -6106,12 +6106,12 @@
       </c>
       <c r="C181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[3]</t>
+          <t xml:space="preserve">seductive.bold[1]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
@@ -6121,14 +6121,14 @@
       </c>
       <c r="F181" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うふふ、今夜は容赦しないわよ</t>
+          <t xml:space="preserve">満員…最高の演出になったわね</t>
         </is>
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.bold.seductive[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[1]</t>
+          <t xml:space="preserve">seductive.bold[2]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
@@ -6153,14 +6153,14 @@
       </c>
       <c r="F182" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">満員…最高の演出になったわね</t>
+          <t xml:space="preserve">この熱量、また必ず味わいたい</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.bold.seductive[2]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.seductive.bold[3]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6175,7 +6175,7 @@
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[2]</t>
+          <t xml:space="preserve">seductive.bold[3]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
@@ -6185,14 +6185,14 @@
       </c>
       <c r="F183" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この熱量、また必ず味わいたい</t>
+          <t xml:space="preserve">うふふ、皆様を虜にしてやったわ</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.bold.seductive[3]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6202,29 +6202,29 @@
       </c>
       <c r="C184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[3]</t>
+          <t xml:space="preserve">N1.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うふふ、皆様を虜にしてやったわ</t>
+          <t xml:space="preserve">まだ足りないわ。もっと強くなれる気がするの</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.bold.seductive[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6239,7 +6239,7 @@
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.bold.seductive[1]</t>
+          <t xml:space="preserve">N2.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
@@ -6249,14 +6249,14 @@
       </c>
       <c r="F185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ足りないわ。もっと強くなれる気がするの</t>
+          <t xml:space="preserve">仲間がいるって、いいものね</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.bold.seductive[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.bold.seductive[1]</t>
+          <t xml:space="preserve">N3.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
@@ -6281,14 +6281,14 @@
       </c>
       <c r="F186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仲間がいるって、いいものね</t>
+          <t xml:space="preserve">この程度で止まるつもりはないわ</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.bold.seductive[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6303,7 +6303,7 @@
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.bold.seductive[1]</t>
+          <t xml:space="preserve">N4.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
@@ -6313,14 +6313,14 @@
       </c>
       <c r="F187" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この程度で止まるつもりはないわ</t>
+          <t xml:space="preserve">この人気、活かさない手はないわね</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.bold.seductive[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.bold.seductive[1]</t>
+          <t xml:space="preserve">N5_low.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
@@ -6345,14 +6345,14 @@
       </c>
       <c r="F188" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この人気、活かさない手はないわね</t>
+          <t xml:space="preserve">…ここにいて、私の夢は叶うのかしら</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.bold.seductive[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6367,7 +6367,7 @@
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.bold.seductive[1]</t>
+          <t xml:space="preserve">N5_warning.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
@@ -6377,14 +6377,14 @@
       </c>
       <c r="F189" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ここにいて、私の夢は叶うのかしら</t>
+          <t xml:space="preserve">…このままでいいのかなって、ふと思うの</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.bold.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6394,29 +6394,29 @@
       </c>
       <c r="C190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_warning.bold.seductive[1]</t>
+          <t xml:space="preserve">bonus.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F190" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…このままでいいのかなって、ふと思うの</t>
+          <t xml:space="preserve">嬉しいわ。実力で返させてもらうわね</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.bold.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6431,7 +6431,7 @@
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.bold.seductive[1]</t>
+          <t xml:space="preserve">camp.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
@@ -6441,14 +6441,14 @@
       </c>
       <c r="F191" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">嬉しいわ。実力で返させてもらうわね</t>
+          <t xml:space="preserve">帰る頃には一回り強くなってるわよ</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.bold.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6463,7 +6463,7 @@
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.bold.seductive[1]</t>
+          <t xml:space="preserve">encourage_high_trust.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
@@ -6473,14 +6473,14 @@
       </c>
       <c r="F192" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">帰る頃には一回り強くなってるわよ</t>
+          <t xml:space="preserve">あなたが信じてくれるなら…絶対応えるわ</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.bold.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6495,7 +6495,7 @@
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage_high_trust.bold.seductive[1]</t>
+          <t xml:space="preserve">encourage.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
@@ -6505,14 +6505,14 @@
       </c>
       <c r="F193" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あなたが信じてくれるなら…絶対応えるわ</t>
+          <t xml:space="preserve">止まるつもりはないわ。見ていてね</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.bold.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6527,7 +6527,7 @@
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.bold.seductive[1]</t>
+          <t xml:space="preserve">faction_decree.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
@@ -6537,14 +6537,14 @@
       </c>
       <c r="F194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">止まるつもりはないわ。見ていてね</t>
+          <t xml:space="preserve">いいわ、畳みましょう。……でも、覚えておいて</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.bold.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6559,7 +6559,7 @@
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faction_decree.bold.seductive[1]</t>
+          <t xml:space="preserve">media.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
@@ -6569,14 +6569,14 @@
       </c>
       <c r="F195" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いいわ、畳みましょう。……でも、覚えておいて</t>
+          <t xml:space="preserve">注目される場って好きよ。任せて</t>
         </is>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.bold.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6591,7 +6591,7 @@
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.bold.seductive[1]</t>
+          <t xml:space="preserve">party.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
@@ -6601,14 +6601,14 @@
       </c>
       <c r="F196" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">注目される場って好きよ。任せて</t>
+          <t xml:space="preserve">いい雰囲気ね。チームが成長してる証拠だわ</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.bold.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6623,7 +6623,7 @@
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.bold.seductive[1]</t>
+          <t xml:space="preserve">refresh_leave.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
@@ -6633,14 +6633,14 @@
       </c>
       <c r="F197" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい雰囲気ね。チームが成長してる証拠だわ</t>
+          <t xml:space="preserve">リフレッシュしてくるわ。戻ったらもっと輝くから</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.bold.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6655,7 +6655,7 @@
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.bold.seductive[1]</t>
+          <t xml:space="preserve">special_treatment.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
@@ -6665,14 +6665,14 @@
       </c>
       <c r="F198" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">リフレッシュしてくるわ。戻ったらもっと輝くから</t>
+          <t xml:space="preserve">早く戻りたいの…待っていてね</t>
         </is>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.bold.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6687,7 +6687,7 @@
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">special_treatment.bold.seductive[1]</t>
+          <t xml:space="preserve">trainer.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
@@ -6697,14 +6697,14 @@
       </c>
       <c r="F199" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">早く戻りたいの…待っていてね</t>
+          <t xml:space="preserve">この環境、無駄にしないわ。見ていてね</t>
         </is>
       </c>
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.bold.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6714,12 +6714,12 @@
       </c>
       <c r="C200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.bold.seductive[1]</t>
+          <t xml:space="preserve">E1.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
@@ -6729,14 +6729,14 @@
       </c>
       <c r="F200" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この環境、無駄にしないわ。見ていてね</t>
+          <t xml:space="preserve">注目される場は好きよ。もちろんやるわ</t>
         </is>
       </c>
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.bold.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.bold.seductive[1]</t>
+          <t xml:space="preserve">E6.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
@@ -6761,14 +6761,14 @@
       </c>
       <c r="F201" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">注目される場は好きよ。もちろんやるわ</t>
+          <t xml:space="preserve">他所からいい話が来てるの。正直、迷ってるわ</t>
         </is>
       </c>
     </row>
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.bold.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6783,7 +6783,7 @@
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.bold.seductive[1]</t>
+          <t xml:space="preserve">S_boycott.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
@@ -6793,14 +6793,14 @@
       </c>
       <c r="F202" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">他所からいい話が来てるの。正直、迷ってるわ</t>
+          <t xml:space="preserve">練習？ 出してもくれないのに、意味があるのかしら</t>
         </is>
       </c>
     </row>
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.bold.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6815,7 +6815,7 @@
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.bold.seductive[1]</t>
+          <t xml:space="preserve">S_boycott.seductive.bold[2]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
@@ -6825,14 +6825,14 @@
       </c>
       <c r="F203" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">練習？ 出してもくれないのに、意味があるのかしら</t>
+          <t xml:space="preserve">リングに上がれないなら、やっても同じでしょう？</t>
         </is>
       </c>
     </row>
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.bold.seductive[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6847,7 +6847,7 @@
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.bold.seductive[2]</t>
+          <t xml:space="preserve">S_grumble.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
@@ -6857,14 +6857,14 @@
       </c>
       <c r="F204" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">リングに上がれないなら、やっても同じでしょう？</t>
+          <t xml:space="preserve">（「わたしたち、ずいぶん軽く見られてるのね」と笑みを崩さずに言い放っている）</t>
         </is>
       </c>
     </row>
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.bold.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6879,7 +6879,7 @@
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_grumble.bold.seductive[1]</t>
+          <t xml:space="preserve">S_sns.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
@@ -6889,14 +6889,14 @@
       </c>
       <c r="F205" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（「わたしたち、ずいぶん軽く見られてるのね」と笑みを崩さずに言い放っている）</t>
+          <t xml:space="preserve">（SNSに「このまま終わるつもりはないの。楽しみにしてて」と投稿）</t>
         </is>
       </c>
     </row>
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.bold.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6911,7 +6911,7 @@
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_sns.bold.seductive[1]</t>
+          <t xml:space="preserve">S1.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
@@ -6921,14 +6921,14 @@
       </c>
       <c r="F206" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（SNSに「このまま終わるつもりはないの。楽しみにしてて」と投稿）</t>
+          <t xml:space="preserve">ベルトが欲しいの。組んでもらえる？</t>
         </is>
       </c>
     </row>
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.bold.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6943,7 +6943,7 @@
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.bold.seductive[1]</t>
+          <t xml:space="preserve">S2.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
@@ -6953,14 +6953,14 @@
       </c>
       <c r="F207" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ベルトが欲しいの。組んでもらえる？</t>
+          <t xml:space="preserve">あの人と決着をつけたいの。組んでもらえる？</t>
         </is>
       </c>
     </row>
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.bold.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -6975,7 +6975,7 @@
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.bold.seductive[1]</t>
+          <t xml:space="preserve">S3.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
@@ -6985,14 +6985,14 @@
       </c>
       <c r="F208" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの人と決着をつけたいの。組んでもらえる？</t>
+          <t xml:space="preserve">…体が限界なの。少し休ませて</t>
         </is>
       </c>
     </row>
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.bold.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -7007,7 +7007,7 @@
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.bold.seductive[1]</t>
+          <t xml:space="preserve">S4_direct.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
@@ -7017,14 +7017,14 @@
       </c>
       <c r="F209" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…体が限界なの。少し休ませて</t>
+          <t xml:space="preserve">このままじゃ我慢の限界よ。考え直してもらえない？</t>
         </is>
       </c>
     </row>
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.bold.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -7039,7 +7039,7 @@
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.bold.seductive[1]</t>
+          <t xml:space="preserve">S4_silent.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
@@ -7049,14 +7049,14 @@
       </c>
       <c r="F210" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このままじゃ我慢の限界よ。考え直してもらえない？</t>
+          <t xml:space="preserve">…………（笑みは崩さないまま、指先だけが強く握られている）</t>
         </is>
       </c>
     </row>
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.bold.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7071,7 +7071,7 @@
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_silent.bold.seductive[1]</t>
+          <t xml:space="preserve">S5.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
@@ -7081,14 +7081,14 @@
       </c>
       <c r="F211" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…………（笑みは崩さないまま、指先だけが強く握られている）</t>
+          <t xml:space="preserve">もっと強くなりたいの。特訓させてもらえる？</t>
         </is>
       </c>
     </row>
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.bold.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7103,7 +7103,7 @@
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.bold.seductive[1]</t>
+          <t xml:space="preserve">S6.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
@@ -7113,14 +7113,14 @@
       </c>
       <c r="F212" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もっと強くなりたいの。特訓させてもらえる？</t>
+          <t xml:space="preserve">後輩の面倒、見させてもらえるかしら？</t>
         </is>
       </c>
     </row>
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.bold.seductive[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7130,12 +7130,12 @@
       </c>
       <c r="C213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.bold.seductive[1]</t>
+          <t xml:space="preserve">B1.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
@@ -7145,14 +7145,14 @@
       </c>
       <c r="F213" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">後輩の面倒、見させてもらえるかしら？</t>
+          <t xml:space="preserve">こんなところで止まるつもりはないわ…すぐ戻る</t>
         </is>
       </c>
     </row>
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.bold.seductive[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7167,7 +7167,7 @@
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.bold.seductive[1]</t>
+          <t xml:space="preserve">B2_fighter1.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
@@ -7177,14 +7177,14 @@
       </c>
       <c r="F214" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんなところで止まるつもりはないわ…すぐ戻る</t>
+          <t xml:space="preserve">あの人の態度、もう我慢できないの</t>
         </is>
       </c>
     </row>
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.bold.seductive[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7199,7 +7199,7 @@
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.bold.seductive[1]</t>
+          <t xml:space="preserve">B2_fighter2.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
@@ -7209,14 +7209,14 @@
       </c>
       <c r="F215" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの人の態度、もう我慢できないの</t>
+          <t xml:space="preserve">黙ってるつもりはないわ。向こうが悪いんだから</t>
         </is>
       </c>
     </row>
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.bold.seductive[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.bold.seductive[1]</t>
+          <t xml:space="preserve">B4_brand.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
@@ -7241,14 +7241,14 @@
       </c>
       <c r="F216" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">黙ってるつもりはないわ。向こうが悪いんだから</t>
+          <t xml:space="preserve">私とブランドの組み合わせ…最高じゃない♡</t>
         </is>
       </c>
     </row>
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.bold.seductive[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7263,7 +7263,7 @@
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.bold.seductive[1]</t>
+          <t xml:space="preserve">B4_cm.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
@@ -7273,14 +7273,14 @@
       </c>
       <c r="F217" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私とブランドの組み合わせ…最高じゃない♡</t>
+          <t xml:space="preserve">全国に私を見てもらえるのね。楽しみだわ♡</t>
         </is>
       </c>
     </row>
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.bold.seductive[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7295,7 +7295,7 @@
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.bold.seductive[1]</t>
+          <t xml:space="preserve">B4_fan.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
@@ -7305,14 +7305,14 @@
       </c>
       <c r="F218" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全国に私を見てもらえるのね。楽しみだわ♡</t>
+          <t xml:space="preserve">ファンを喜ばせるのは得意よ。任せて♡</t>
         </is>
       </c>
     </row>
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.bold.seductive[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7327,7 +7327,7 @@
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.bold.seductive[1]</t>
+          <t xml:space="preserve">B4_fashion.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
@@ -7337,14 +7337,14 @@
       </c>
       <c r="F219" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ファンを喜ばせるのは得意よ。任せて♡</t>
+          <t xml:space="preserve">ランウェイ、私のためにあるようなものよ♡</t>
         </is>
       </c>
     </row>
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.bold.seductive[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7359,7 +7359,7 @@
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.bold.seductive[1]</t>
+          <t xml:space="preserve">B4_gravure.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
@@ -7369,14 +7369,14 @@
       </c>
       <c r="F220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ランウェイ、私のためにあるようなものよ♡</t>
+          <t xml:space="preserve">私の本気の魅力、たっぷり撮ってもらうわ♡</t>
         </is>
       </c>
     </row>
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.bold.seductive[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.bold.seductive[1]</t>
+          <t xml:space="preserve">B4_variety.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
@@ -7401,14 +7401,14 @@
       </c>
       <c r="F221" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私の本気の魅力、たっぷり撮ってもらうわ♡</t>
+          <t xml:space="preserve">バラエティでも私のペースで話すわ♡</t>
         </is>
       </c>
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.bold.seductive[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7423,7 +7423,7 @@
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.bold.seductive[1]</t>
+          <t xml:space="preserve">B4.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
@@ -7433,14 +7433,14 @@
       </c>
       <c r="F222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">バラエティでも私のペースで話すわ♡</t>
+          <t xml:space="preserve">全国に見てもらえるのね。楽しみだわ</t>
         </is>
       </c>
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.bold.seductive[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7450,29 +7450,29 @@
       </c>
       <c r="C223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.bold.seductive[1]</t>
+          <t xml:space="preserve">seductive.bold[1]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F223" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全国に見てもらえるのね。楽しみだわ</t>
+          <t xml:space="preserve">私を選んで。後悔はさせないわ</t>
         </is>
       </c>
     </row>
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.bold.seductive[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7482,12 +7482,12 @@
       </c>
       <c r="C224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[1]</t>
+          <t xml:space="preserve">seductive.bold[1]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
@@ -7497,14 +7497,14 @@
       </c>
       <c r="F224" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私を選んで。後悔はさせないわ</t>
+          <t xml:space="preserve">チャンピオン、獲りに来たの。覚悟してて</t>
         </is>
       </c>
     </row>
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.bold.seductive[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7519,7 +7519,7 @@
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[1]</t>
+          <t xml:space="preserve">seductive.bold[2]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
@@ -7529,14 +7529,14 @@
       </c>
       <c r="F225" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオン、獲りに来たの。覚悟してて</t>
+          <t xml:space="preserve">この団体、私が盛り上げてあげる</t>
         </is>
       </c>
     </row>
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.bold.seductive[2]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7546,12 +7546,12 @@
       </c>
       <c r="C226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[2]</t>
+          <t xml:space="preserve">seductive.bold[1]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
@@ -7561,14 +7561,14 @@
       </c>
       <c r="F226" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この団体、私が盛り上げてあげる</t>
+          <t xml:space="preserve">てっぺん獲りに来たの。一緒に頂点に立ちましょう</t>
         </is>
       </c>
     </row>
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.bold.seductive[1]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7578,12 +7578,12 @@
       </c>
       <c r="C227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[1]</t>
+          <t xml:space="preserve">seductive.bold[1]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
@@ -7593,14 +7593,14 @@
       </c>
       <c r="F227" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">てっぺん獲りに来たの。一緒に頂点に立ちましょう</t>
+          <t xml:space="preserve">頂点まで一直線よ。見ていてね</t>
         </is>
       </c>
     </row>
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.bold.seductive[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7610,12 +7610,12 @@
       </c>
       <c r="C228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[1]</t>
+          <t xml:space="preserve">seductive.bold[1]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
@@ -7625,14 +7625,14 @@
       </c>
       <c r="F228" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頂点まで一直線よ。見ていてね</t>
+          <t xml:space="preserve">こんなことで止まると思ってる？ 甘いわ</t>
         </is>
       </c>
     </row>
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.bold.seductive[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7647,7 +7647,7 @@
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[1]</t>
+          <t xml:space="preserve">seductive.bold[2]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
@@ -7657,14 +7657,14 @@
       </c>
       <c r="F229" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんなことで止まると思ってる？ 甘いわ</t>
+          <t xml:space="preserve">すぐ戻るわ。覚悟してなさい</t>
         </is>
       </c>
     </row>
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.bold.seductive[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7674,12 +7674,12 @@
       </c>
       <c r="C230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[2]</t>
+          <t xml:space="preserve">draftInterest.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
@@ -7689,14 +7689,14 @@
       </c>
       <c r="F230" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">すぐ戻るわ。覚悟してなさい</t>
+          <t xml:space="preserve">私を選んで。後悔はさせないわ</t>
         </is>
       </c>
     </row>
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.bold.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7711,7 +7711,7 @@
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.bold.seductive[1]</t>
+          <t xml:space="preserve">draftJoin.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
@@ -7721,14 +7721,14 @@
       </c>
       <c r="F231" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私を選んで。後悔はさせないわ</t>
+          <t xml:space="preserve">チャンピオン、獲りに来たの。覚悟してて</t>
         </is>
       </c>
     </row>
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.bold.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7743,7 +7743,7 @@
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.bold.seductive[1]</t>
+          <t xml:space="preserve">draftJoin.seductive.bold[2]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
@@ -7753,14 +7753,14 @@
       </c>
       <c r="F232" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオン、獲りに来たの。覚悟してて</t>
+          <t xml:space="preserve">この団体、私が盛り上げてあげる</t>
         </is>
       </c>
     </row>
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.bold.seductive[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7775,7 +7775,7 @@
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.bold.seductive[2]</t>
+          <t xml:space="preserve">faGreeting.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
@@ -7785,14 +7785,14 @@
       </c>
       <c r="F233" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この団体、私が盛り上げてあげる</t>
+          <t xml:space="preserve">拾った目利きは正解よ。…すぐに分かるわ</t>
         </is>
       </c>
     </row>
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.bold.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7807,7 +7807,7 @@
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.bold.seductive[1]</t>
+          <t xml:space="preserve">faSigning.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
@@ -7817,14 +7817,14 @@
       </c>
       <c r="F234" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">拾った目利きは正解よ。…すぐに分かるわ</t>
+          <t xml:space="preserve">てっぺん獲りに来たの。一緒に頂点に立ちましょう</t>
         </is>
       </c>
     </row>
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.bold.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7839,7 +7839,7 @@
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.bold.seductive[1]</t>
+          <t xml:space="preserve">faWelcome.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
@@ -7849,14 +7849,14 @@
       </c>
       <c r="F235" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">てっぺん獲りに来たの。一緒に頂点に立ちましょう</t>
+          <t xml:space="preserve">頂点まで一直線よ。見ていてね</t>
         </is>
       </c>
     </row>
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.bold.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7871,7 +7871,7 @@
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.bold.seductive[1]</t>
+          <t xml:space="preserve">injury.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
@@ -7881,14 +7881,14 @@
       </c>
       <c r="F236" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頂点まで一直線よ。見ていてね</t>
+          <t xml:space="preserve">こんなことで止まると思ってる？ 甘いわ</t>
         </is>
       </c>
     </row>
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.bold.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -7903,7 +7903,7 @@
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.bold.seductive[1]</t>
+          <t xml:space="preserve">injury.seductive.bold[2]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
@@ -7913,14 +7913,14 @@
       </c>
       <c r="F237" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんなことで止まると思ってる？ 甘いわ</t>
+          <t xml:space="preserve">すぐ戻るわ。覚悟してなさい</t>
         </is>
       </c>
     </row>
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.bold.seductive[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -7935,7 +7935,7 @@
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.bold.seductive[2]</t>
+          <t xml:space="preserve">release.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
@@ -7945,14 +7945,14 @@
       </c>
       <c r="F238" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">すぐ戻るわ。覚悟してなさい</t>
+          <t xml:space="preserve">悔しいわ…でも、いつか必ず戻ってくる</t>
         </is>
       </c>
     </row>
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.bold.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -7967,7 +7967,7 @@
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.bold.seductive[1]</t>
+          <t xml:space="preserve">release.seductive.bold[2]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
@@ -7977,14 +7977,14 @@
       </c>
       <c r="F239" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しいわ…でも、いつか必ず戻ってくる</t>
+          <t xml:space="preserve">この借り、いつか返しに来るから</t>
         </is>
       </c>
     </row>
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.bold.seductive[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -7999,7 +7999,7 @@
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.bold.seductive[2]</t>
+          <t xml:space="preserve">rentalGreeting.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
@@ -8009,14 +8009,14 @@
       </c>
       <c r="F240" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この借り、いつか返しに来るから</t>
+          <t xml:space="preserve">レンタルでも全力よ。見ていてね</t>
         </is>
       </c>
     </row>
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.bold.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -8031,7 +8031,7 @@
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.bold.seductive[1]</t>
+          <t xml:space="preserve">scoutGreeting.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
@@ -8041,14 +8041,14 @@
       </c>
       <c r="F241" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">レンタルでも全力よ。見ていてね</t>
+          <t xml:space="preserve">わたしに声をかけた責任は、取ってちょうだいね</t>
         </is>
       </c>
     </row>
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.bold.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8063,7 +8063,7 @@
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.bold.seductive[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
@@ -8073,14 +8073,14 @@
       </c>
       <c r="F242" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたしに声をかけた責任は、取ってちょうだいね</t>
+          <t xml:space="preserve">…今日は認めるわ。でもこの借り、必ず返す</t>
         </is>
       </c>
     </row>
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.bold.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -8095,7 +8095,7 @@
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.bold.seductive[1]</t>
+          <t xml:space="preserve">titleDefense.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E243" t="inlineStr" s="2">
@@ -8105,14 +8105,14 @@
       </c>
       <c r="F243" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…今日は認めるわ。でもこの借り、必ず返す</t>
+          <t xml:space="preserve">まだ誰も私を超えられないわね。当然でしょう</t>
         </is>
       </c>
     </row>
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.bold.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8127,7 +8127,7 @@
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.bold.seductive[1]</t>
+          <t xml:space="preserve">titleLoss.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
@@ -8137,14 +8137,14 @@
       </c>
       <c r="F244" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ誰も私を超えられないわね。当然でしょう</t>
+          <t xml:space="preserve">…覚えておきなさい。すぐに返してもらうわ</t>
         </is>
       </c>
     </row>
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.bold.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8159,7 +8159,7 @@
       </c>
       <c r="D245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.bold.seductive[1]</t>
+          <t xml:space="preserve">titleWin.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
@@ -8169,14 +8169,14 @@
       </c>
       <c r="F245" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…覚えておきなさい。すぐに返してもらうわ</t>
+          <t xml:space="preserve">これが始まりよ。このベルトで時代を作る</t>
         </is>
       </c>
     </row>
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.bold.seductive[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8186,12 +8186,12 @@
       </c>
       <c r="C246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.bold.seductive[1]</t>
+          <t xml:space="preserve">seductive.bold[1]</t>
         </is>
       </c>
       <c r="E246" t="inlineStr" s="2">
@@ -8201,14 +8201,14 @@
       </c>
       <c r="F246" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">これが始まりよ。このベルトで時代を作る</t>
+          <t xml:space="preserve">悔しいわ…でも、いつか必ず戻ってくる</t>
         </is>
       </c>
     </row>
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.bold.seductive[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8223,7 +8223,7 @@
       </c>
       <c r="D247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[1]</t>
+          <t xml:space="preserve">seductive.bold[2]</t>
         </is>
       </c>
       <c r="E247" t="inlineStr" s="2">
@@ -8233,14 +8233,14 @@
       </c>
       <c r="F247" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しいわ…でも、いつか必ず戻ってくる</t>
+          <t xml:space="preserve">この借り、いつか返しに来るから</t>
         </is>
       </c>
     </row>
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.bold.seductive[2]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8250,12 +8250,12 @@
       </c>
       <c r="C248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[2]</t>
+          <t xml:space="preserve">seductive.bold[1]</t>
         </is>
       </c>
       <c r="E248" t="inlineStr" s="2">
@@ -8265,14 +8265,14 @@
       </c>
       <c r="F248" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この借り、いつか返しに来るから</t>
+          <t xml:space="preserve">レンタルでも全力よ。見ていてね</t>
         </is>
       </c>
     </row>
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.bold.seductive[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8282,12 +8282,12 @@
       </c>
       <c r="C249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[1]</t>
+          <t xml:space="preserve">seductive.bold[1]</t>
         </is>
       </c>
       <c r="E249" t="inlineStr" s="2">
@@ -8297,14 +8297,14 @@
       </c>
       <c r="F249" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">レンタルでも全力よ。見ていてね</t>
+          <t xml:space="preserve">…今日は認めるわ。でもこの借り、必ず返す</t>
         </is>
       </c>
     </row>
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.bold.seductive[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8314,12 +8314,12 @@
       </c>
       <c r="C250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[1]</t>
+          <t xml:space="preserve">seductive.bold[1]</t>
         </is>
       </c>
       <c r="E250" t="inlineStr" s="2">
@@ -8329,14 +8329,14 @@
       </c>
       <c r="F250" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…今日は認めるわ。でもこの借り、必ず返す</t>
+          <t xml:space="preserve">まだ誰も私を超えられないわね。当然でしょう</t>
         </is>
       </c>
     </row>
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.bold.seductive[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8346,12 +8346,12 @@
       </c>
       <c r="C251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[1]</t>
+          <t xml:space="preserve">seductive.bold[1]</t>
         </is>
       </c>
       <c r="E251" t="inlineStr" s="2">
@@ -8361,14 +8361,14 @@
       </c>
       <c r="F251" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ誰も私を超えられないわね。当然でしょう</t>
+          <t xml:space="preserve">…覚えておきなさい。すぐに返してもらうわ</t>
         </is>
       </c>
     </row>
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.bold.seductive[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8378,12 +8378,12 @@
       </c>
       <c r="C252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[1]</t>
+          <t xml:space="preserve">seductive.bold[1]</t>
         </is>
       </c>
       <c r="E252" t="inlineStr" s="2">
@@ -8393,14 +8393,14 @@
       </c>
       <c r="F252" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…覚えておきなさい。すぐに返してもらうわ</t>
+          <t xml:space="preserve">これが始まりよ。このベルトで時代を作る</t>
         </is>
       </c>
     </row>
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.bold.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8410,29 +8410,29 @@
       </c>
       <c r="C253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[1]</t>
+          <t xml:space="preserve">bond_39_down.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F253" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">これが始まりよ。このベルトで時代を作る</t>
+          <t xml:space="preserve">合わないわ。どうしても合わないの</t>
         </is>
       </c>
     </row>
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.bold.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.bold.seductive[2]</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8447,7 +8447,7 @@
       </c>
       <c r="D254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.bold.seductive[1]</t>
+          <t xml:space="preserve">bond_39_down.bold.seductive[2]</t>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="2">
@@ -8457,14 +8457,14 @@
       </c>
       <c r="F254" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">合わないわ。どうしても合わないの</t>
+          <t xml:space="preserve">これ以上は無理ね。それだけよ</t>
         </is>
       </c>
     </row>
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.bold.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8479,7 +8479,7 @@
       </c>
       <c r="D255" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.bold.seductive[2]</t>
+          <t xml:space="preserve">bond_59_down.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E255" t="inlineStr" s="2">
@@ -8489,14 +8489,14 @@
       </c>
       <c r="F255" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">これ以上は無理ね。それだけよ</t>
+          <t xml:space="preserve">壁を作ってない？ 気に入らないわ</t>
         </is>
       </c>
     </row>
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.bold.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.bold.seductive[2]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="D256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.bold.seductive[1]</t>
+          <t xml:space="preserve">bond_59_down.bold.seductive[2]</t>
         </is>
       </c>
       <c r="E256" t="inlineStr" s="2">
@@ -8521,14 +8521,14 @@
       </c>
       <c r="F256" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">壁を作ってない？ 気に入らないわ</t>
+          <t xml:space="preserve">前はもっと話してくれたのに。…どうしたのかしら</t>
         </is>
       </c>
     </row>
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.bold.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8543,7 +8543,7 @@
       </c>
       <c r="D257" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.bold.seductive[2]</t>
+          <t xml:space="preserve">bond_60_up.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E257" t="inlineStr" s="2">
@@ -8553,14 +8553,14 @@
       </c>
       <c r="F257" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">前はもっと話してくれたのに。…どうしたのかしら</t>
+          <t xml:space="preserve">気に入ったわ。なかなか味のある人ね</t>
         </is>
       </c>
     </row>
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.bold.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8575,7 +8575,7 @@
       </c>
       <c r="D258" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.bold.seductive[1]</t>
+          <t xml:space="preserve">bond_80_up.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E258" t="inlineStr" s="2">
@@ -8585,14 +8585,14 @@
       </c>
       <c r="F258" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">気に入ったわ。なかなか味のある人ね</t>
+          <t xml:space="preserve">最高のコンビネーションよ、私たち</t>
         </is>
       </c>
     </row>
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.bold.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8607,7 +8607,7 @@
       </c>
       <c r="D259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.bold.seductive[1]</t>
+          <t xml:space="preserve">rivalry_29_down.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E259" t="inlineStr" s="2">
@@ -8617,14 +8617,14 @@
       </c>
       <c r="F259" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高のコンビネーションよ、私たち</t>
+          <t xml:space="preserve">……もう終わったことよ</t>
         </is>
       </c>
     </row>
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.bold.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.bold.seductive[2]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8639,7 +8639,7 @@
       </c>
       <c r="D260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.bold.seductive[1]</t>
+          <t xml:space="preserve">rivalry_29_down.bold.seductive[2]</t>
         </is>
       </c>
       <c r="E260" t="inlineStr" s="2">
@@ -8649,14 +8649,14 @@
       </c>
       <c r="F260" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……もう終わったことよ</t>
+          <t xml:space="preserve">決着はついたわ。次に進むの</t>
         </is>
       </c>
     </row>
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.bold.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8671,7 +8671,7 @@
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.bold.seductive[2]</t>
+          <t xml:space="preserve">rivalry_30_up.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
@@ -8681,14 +8681,14 @@
       </c>
       <c r="F261" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決着はついたわ。次に進むの</t>
+          <t xml:space="preserve">なかなかの逸材ね。ふふ、楽しみ</t>
         </is>
       </c>
     </row>
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.bold.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8703,7 +8703,7 @@
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.bold.seductive[1]</t>
+          <t xml:space="preserve">rivalry_50_up.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E262" t="inlineStr" s="2">
@@ -8713,14 +8713,14 @@
       </c>
       <c r="F262" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">なかなかの逸材ね。ふふ、楽しみ</t>
+          <t xml:space="preserve">全力を出せる相手。最高の敵ね、ふふ</t>
         </is>
       </c>
     </row>
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.bold.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.bold.seductive[2]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8735,7 +8735,7 @@
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.bold.seductive[1]</t>
+          <t xml:space="preserve">rivalry_50_up.bold.seductive[2]</t>
         </is>
       </c>
       <c r="E263" t="inlineStr" s="2">
@@ -8745,14 +8745,14 @@
       </c>
       <c r="F263" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全力を出せる相手。最高の敵ね、ふふ</t>
+          <t xml:space="preserve">超える。それが今の私の全てよ</t>
         </is>
       </c>
     </row>
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.bold.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8767,7 +8767,7 @@
       </c>
       <c r="D264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.bold.seductive[2]</t>
+          <t xml:space="preserve">rivalry_70_up.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E264" t="inlineStr" s="2">
@@ -8777,14 +8777,14 @@
       </c>
       <c r="F264" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">超える。それが今の私の全てよ</t>
+          <t xml:space="preserve">あの人がいたから強くなれたの。感謝してる…でも負けないわ</t>
         </is>
       </c>
     </row>
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.bold.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.bold.seductive[2]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8799,7 +8799,7 @@
       </c>
       <c r="D265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.bold.seductive[1]</t>
+          <t xml:space="preserve">rivalry_70_up.bold.seductive[2]</t>
         </is>
       </c>
       <c r="E265" t="inlineStr" s="2">
@@ -8809,14 +8809,14 @@
       </c>
       <c r="F265" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの人がいたから強くなれたの。感謝してる…でも負けないわ</t>
+          <t xml:space="preserve">この戦いに終わりはない。…望むところね</t>
         </is>
       </c>
     </row>
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.bold.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="D266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.bold.seductive[2]</t>
+          <t xml:space="preserve">trust_above_75.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E266" t="inlineStr" s="2">
@@ -8841,14 +8841,14 @@
       </c>
       <c r="F266" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この戦いに終わりはない。…望むところね</t>
+          <t xml:space="preserve">ここが最高の場所。私がもっと強くしてみせるわ</t>
         </is>
       </c>
     </row>
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.bold.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.bold.seductive[2]</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -8863,7 +8863,7 @@
       </c>
       <c r="D267" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.bold.seductive[1]</t>
+          <t xml:space="preserve">trust_above_75.bold.seductive[2]</t>
         </is>
       </c>
       <c r="E267" t="inlineStr" s="2">
@@ -8873,14 +8873,14 @@
       </c>
       <c r="F267" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここが最高の場所。私がもっと強くしてみせるわ</t>
+          <t xml:space="preserve">この団体を背負っていく覚悟はできてるの</t>
         </is>
       </c>
     </row>
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.bold.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -8895,7 +8895,7 @@
       </c>
       <c r="D268" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.bold.seductive[2]</t>
+          <t xml:space="preserve">trust_below_20.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E268" t="inlineStr" s="2">
@@ -8905,14 +8905,14 @@
       </c>
       <c r="F268" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この団体を背負っていく覚悟はできてるの</t>
+          <t xml:space="preserve">ふざけないで。私の価値がわからないなら、もう付き合いきれないわ</t>
         </is>
       </c>
     </row>
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.bold.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.bold.seductive[2]</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -8927,7 +8927,7 @@
       </c>
       <c r="D269" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.bold.seductive[1]</t>
+          <t xml:space="preserve">trust_below_20.bold.seductive[2]</t>
         </is>
       </c>
       <c r="E269" t="inlineStr" s="2">
@@ -8937,14 +8937,14 @@
       </c>
       <c r="F269" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふざけないで。私の価値がわからないなら、もう付き合いきれないわ</t>
+          <t xml:space="preserve">この扱い、許すつもりはないの。忘れないことね</t>
         </is>
       </c>
     </row>
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.bold.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -8959,7 +8959,7 @@
       </c>
       <c r="D270" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.bold.seductive[2]</t>
+          <t xml:space="preserve">trust_below_35.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E270" t="inlineStr" s="2">
@@ -8969,14 +8969,14 @@
       </c>
       <c r="F270" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この扱い、許すつもりはないの。忘れないことね</t>
+          <t xml:space="preserve">この扱いは何かしら。私の実力、わかってるの？</t>
         </is>
       </c>
     </row>
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.bold.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.bold.seductive[2]</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -8991,7 +8991,7 @@
       </c>
       <c r="D271" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.bold.seductive[1]</t>
+          <t xml:space="preserve">trust_below_35.bold.seductive[2]</t>
         </is>
       </c>
       <c r="E271" t="inlineStr" s="2">
@@ -9001,14 +9001,14 @@
       </c>
       <c r="F271" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この扱いは何かしら。私の実力、わかってるの？</t>
+          <t xml:space="preserve">ここにいていいのか…考え直す時期かもね</t>
         </is>
       </c>
     </row>
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.bold.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -9018,12 +9018,12 @@
       </c>
       <c r="C272" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D272" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.bold.seductive[2]</t>
+          <t xml:space="preserve">seductive.bold[1]</t>
         </is>
       </c>
       <c r="E272" t="inlineStr" s="2">
@@ -9033,14 +9033,14 @@
       </c>
       <c r="F272" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここにいていいのか…考え直す時期かもね</t>
+          <t xml:space="preserve">ふふ、あの輝きは一時的だったみたいね。でもいい夢だったわ</t>
         </is>
       </c>
     </row>
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.bold.seductive[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -9050,29 +9050,29 @@
       </c>
       <c r="C273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[1]</t>
+          <t xml:space="preserve">preFinal.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F273" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、あの輝きは一時的だったみたいね。でもいい夢だったわ</t>
+          <t xml:space="preserve">満身創痍の私、悪くないでしょ? この傷ごと、最後を飾るわ</t>
         </is>
       </c>
     </row>
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.bold.seductive[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -9087,7 +9087,7 @@
       </c>
       <c r="D274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.bold.seductive[1]</t>
+          <t xml:space="preserve">preFinal.seductive.bold[2]</t>
         </is>
       </c>
       <c r="E274" t="inlineStr" s="2">
@@ -9097,14 +9097,14 @@
       </c>
       <c r="F274" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">満身創痍の私、悪くないでしょ? この傷ごと、最後を飾るわ</t>
+          <t xml:space="preserve">ここまで残ったんだもの。一番いいところ、見せてあげる</t>
         </is>
       </c>
     </row>
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.bold.seductive[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -9119,7 +9119,7 @@
       </c>
       <c r="D275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.bold.seductive[2]</t>
+          <t xml:space="preserve">preMatch.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E275" t="inlineStr" s="2">
@@ -9129,14 +9129,14 @@
       </c>
       <c r="F275" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで残ったんだもの。一番いいところ、見せてあげる</t>
+          <t xml:space="preserve">相手は誰? 何人来ても…最後まで残るのは、こっちよ</t>
         </is>
       </c>
     </row>
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.bold.seductive[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -9151,7 +9151,7 @@
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.bold.seductive[1]</t>
+          <t xml:space="preserve">preMatch.seductive.bold[2]</t>
         </is>
       </c>
       <c r="E276" t="inlineStr" s="2">
@@ -9161,14 +9161,14 @@
       </c>
       <c r="F276" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">相手は誰? 何人来ても…最後まで残るのは、こっちよ</t>
+          <t xml:space="preserve">もっと骨のあるのを出してきて。全部相手にしてあげる</t>
         </is>
       </c>
     </row>
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.bold.seductive[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -9183,7 +9183,7 @@
       </c>
       <c r="D277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.bold.seductive[2]</t>
+          <t xml:space="preserve">survivor.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E277" t="inlineStr" s="2">
@@ -9193,14 +9193,14 @@
       </c>
       <c r="F277" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もっと骨のあるのを出してきて。全部相手にしてあげる</t>
+          <t xml:space="preserve">一人、落としたわ。…でも、まだ足りないの。次、早く出してよ</t>
         </is>
       </c>
     </row>
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.bold.seductive[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -9215,7 +9215,7 @@
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.bold.seductive[1]</t>
+          <t xml:space="preserve">survivor.seductive.bold[2]</t>
         </is>
       </c>
       <c r="E278" t="inlineStr" s="2">
@@ -9225,14 +9225,14 @@
       </c>
       <c r="F278" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人、落としたわ。…でも、まだ足りないの。次、早く出してよ</t>
+          <t xml:space="preserve">まだ立ってるの、見える? 次の子、こっちにいらっしゃい。全部相手にしてあげる</t>
         </is>
       </c>
     </row>
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.bold.seductive[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="C279" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.bold.seductive[2]</t>
+          <t xml:space="preserve">champion.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E279" t="inlineStr" s="2">
@@ -9257,14 +9257,14 @@
       </c>
       <c r="F279" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ立ってるの、見える? 次の子、こっちにいらっしゃい。全部相手にしてあげる</t>
+          <t xml:space="preserve">この三人が最強だった。美しい勝利でしょ？</t>
         </is>
       </c>
     </row>
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.bold.seductive[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -9279,7 +9279,7 @@
       </c>
       <c r="D280" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.bold.seductive[1]</t>
+          <t xml:space="preserve">champion.seductive.bold[2]</t>
         </is>
       </c>
       <c r="E280" t="inlineStr" s="2">
@@ -9289,14 +9289,14 @@
       </c>
       <c r="F280" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この三人が最強だった。美しい勝利でしょ？</t>
+          <t xml:space="preserve">仲間が繋いでくれた勝ちを、最後に飾ったの。良いチームだったわ</t>
         </is>
       </c>
     </row>
     <row r="281" ht="40" customHeight="1">
       <c r="A281" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.bold.seductive[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -9311,7 +9311,7 @@
       </c>
       <c r="D281" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.bold.seductive[2]</t>
+          <t xml:space="preserve">defiant.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E281" t="inlineStr" s="2">
@@ -9321,14 +9321,14 @@
       </c>
       <c r="F281" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仲間が繋いでくれた勝ちを、最後に飾ったの。良いチームだったわ</t>
+          <t xml:space="preserve">賞はもらっておくわ。でも次は……もっと大きなものを奪いに行くから</t>
         </is>
       </c>
     </row>
     <row r="282" ht="40" customHeight="1">
       <c r="A282" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.bold.seductive[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -9343,7 +9343,7 @@
       </c>
       <c r="D282" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.bold.seductive[1]</t>
+          <t xml:space="preserve">defiant.seductive.bold[2]</t>
         </is>
       </c>
       <c r="E282" t="inlineStr" s="2">
@@ -9353,14 +9353,14 @@
       </c>
       <c r="F282" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">賞はもらっておくわ。でも次は……もっと大きなものを奪いに行くから</t>
+          <t xml:space="preserve">この程度じゃ満たされない。次は全部、こっちのものにするわ</t>
         </is>
       </c>
     </row>
     <row r="283" ht="40" customHeight="1">
       <c r="A283" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.bold.seductive[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -9375,7 +9375,7 @@
       </c>
       <c r="D283" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.bold.seductive[2]</t>
+          <t xml:space="preserve">gauntlet.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E283" t="inlineStr" s="2">
@@ -9385,14 +9385,14 @@
       </c>
       <c r="F283" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この程度じゃ満たされない。次は全部、こっちのものにするわ</t>
+          <t xml:space="preserve">何人でもいいわよ？ 最後にこの場所に立つのは、いつだって私だもの</t>
         </is>
       </c>
     </row>
     <row r="284" ht="40" customHeight="1">
       <c r="A284" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.bold.seductive[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -9407,7 +9407,7 @@
       </c>
       <c r="D284" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.bold.seductive[1]</t>
+          <t xml:space="preserve">gauntlet.seductive.bold[2]</t>
         </is>
       </c>
       <c r="E284" t="inlineStr" s="2">
@@ -9417,14 +9417,14 @@
       </c>
       <c r="F284" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何人でもいいわよ？ 最後にこの場所に立つのは、いつだって私だもの</t>
+          <t xml:space="preserve">全員倒してきたの。まだ物足りないくらい</t>
         </is>
       </c>
     </row>
     <row r="285" ht="40" customHeight="1">
       <c r="A285" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.bold.seductive[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
@@ -9434,12 +9434,12 @@
       </c>
       <c r="C285" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D285" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.bold.seductive[2]</t>
+          <t xml:space="preserve">champion.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E285" t="inlineStr" s="2">
@@ -9449,14 +9449,14 @@
       </c>
       <c r="F285" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全員倒してきたの。まだ物足りないくらい</t>
+          <t xml:space="preserve">あら、優勝しちゃったわ。当然だけどね</t>
         </is>
       </c>
     </row>
     <row r="286" ht="40" customHeight="1">
       <c r="A286" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.bold.seductive[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
@@ -9471,7 +9471,7 @@
       </c>
       <c r="D286" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.bold.seductive[1]</t>
+          <t xml:space="preserve">champion.seductive.bold[2]</t>
         </is>
       </c>
       <c r="E286" t="inlineStr" s="2">
@@ -9481,14 +9481,14 @@
       </c>
       <c r="F286" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、優勝しちゃったわ。当然だけどね</t>
+          <t xml:space="preserve">わたしが一番。それが証明されたわね</t>
         </is>
       </c>
     </row>
     <row r="287" ht="40" customHeight="1">
       <c r="A287" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.bold.seductive[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
@@ -9503,7 +9503,7 @@
       </c>
       <c r="D287" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.bold.seductive[2]</t>
+          <t xml:space="preserve">postLose.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E287" t="inlineStr" s="2">
@@ -9513,14 +9513,14 @@
       </c>
       <c r="F287" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたしが一番。それが証明されたわね</t>
+          <t xml:space="preserve">…悔しいわ。でも、わたしはここで終わらない</t>
         </is>
       </c>
     </row>
     <row r="288" ht="40" customHeight="1">
       <c r="A288" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.bold.seductive[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
@@ -9535,7 +9535,7 @@
       </c>
       <c r="D288" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.bold.seductive[1]</t>
+          <t xml:space="preserve">postLose.seductive.bold[2]</t>
         </is>
       </c>
       <c r="E288" t="inlineStr" s="2">
@@ -9545,14 +9545,14 @@
       </c>
       <c r="F288" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悔しいわ。でも、わたしはここで終わらない</t>
+          <t xml:space="preserve">次は必ず勝つわ</t>
         </is>
       </c>
     </row>
     <row r="289" ht="40" customHeight="1">
       <c r="A289" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.bold.seductive[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
@@ -9567,7 +9567,7 @@
       </c>
       <c r="D289" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.bold.seductive[2]</t>
+          <t xml:space="preserve">postMatchWin.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E289" t="inlineStr" s="2">
@@ -9577,14 +9577,14 @@
       </c>
       <c r="F289" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次は必ず勝つわ</t>
+          <t xml:space="preserve">あら、もう終わり？ 物足りないわね</t>
         </is>
       </c>
     </row>
     <row r="290" ht="40" customHeight="1">
       <c r="A290" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.bold.seductive[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="2">
@@ -9599,7 +9599,7 @@
       </c>
       <c r="D290" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.bold.seductive[1]</t>
+          <t xml:space="preserve">postMatchWin.seductive.bold[2]</t>
         </is>
       </c>
       <c r="E290" t="inlineStr" s="2">
@@ -9609,14 +9609,14 @@
       </c>
       <c r="F290" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、もう終わり？ 物足りないわね</t>
+          <t xml:space="preserve">ふふ、予定通りよ。次の相手が楽しみ</t>
         </is>
       </c>
     </row>
     <row r="291" ht="40" customHeight="1">
       <c r="A291" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.bold.seductive[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="2">
@@ -9631,7 +9631,7 @@
       </c>
       <c r="D291" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.bold.seductive[2]</t>
+          <t xml:space="preserve">postWin.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E291" t="inlineStr" s="2">
@@ -9641,14 +9641,14 @@
       </c>
       <c r="F291" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、予定通りよ。次の相手が楽しみ</t>
+          <t xml:space="preserve">まだ足りないわね。もっと上に行くわ</t>
         </is>
       </c>
     </row>
     <row r="292" ht="40" customHeight="1">
       <c r="A292" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.bold.seductive[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="2">
@@ -9663,7 +9663,7 @@
       </c>
       <c r="D292" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.bold.seductive[1]</t>
+          <t xml:space="preserve">postWin.seductive.bold[2]</t>
         </is>
       </c>
       <c r="E292" t="inlineStr" s="2">
@@ -9673,14 +9673,14 @@
       </c>
       <c r="F292" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ足りないわね。もっと上に行くわ</t>
+          <t xml:space="preserve">いい舞台だったわ。でも、わたしはもっと上を目指す</t>
         </is>
       </c>
     </row>
     <row r="293" ht="40" customHeight="1">
       <c r="A293" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.bold.seductive[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="2">
@@ -9695,7 +9695,7 @@
       </c>
       <c r="D293" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.bold.seductive[2]</t>
+          <t xml:space="preserve">preFinal.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E293" t="inlineStr" s="2">
@@ -9705,14 +9705,14 @@
       </c>
       <c r="F293" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい舞台だったわ。でも、わたしはもっと上を目指す</t>
+          <t xml:space="preserve">あら、最後のお相手ね。たっぷり楽しませてあげるわ</t>
         </is>
       </c>
     </row>
     <row r="294" ht="40" customHeight="1">
       <c r="A294" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.bold.seductive[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B294" t="inlineStr" s="2">
@@ -9727,7 +9727,7 @@
       </c>
       <c r="D294" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.bold.seductive[1]</t>
+          <t xml:space="preserve">preFinal.seductive.bold[2]</t>
         </is>
       </c>
       <c r="E294" t="inlineStr" s="2">
@@ -9737,14 +9737,14 @@
       </c>
       <c r="F294" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、最後のお相手ね。たっぷり楽しませてあげるわ</t>
+          <t xml:space="preserve">優勝はわたしのもの。決まっていることよ</t>
         </is>
       </c>
     </row>
     <row r="295" ht="40" customHeight="1">
       <c r="A295" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.bold.seductive[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B295" t="inlineStr" s="2">
@@ -9759,7 +9759,7 @@
       </c>
       <c r="D295" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.bold.seductive[2]</t>
+          <t xml:space="preserve">preMatch.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E295" t="inlineStr" s="2">
@@ -9769,14 +9769,14 @@
       </c>
       <c r="F295" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">優勝はわたしのもの。決まっていることよ</t>
+          <t xml:space="preserve">あら、可愛い相手ね。すぐ終わらせてあげるわ</t>
         </is>
       </c>
     </row>
     <row r="296" ht="40" customHeight="1">
       <c r="A296" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.bold.seductive[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B296" t="inlineStr" s="2">
@@ -9791,7 +9791,7 @@
       </c>
       <c r="D296" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.bold.seductive[1]</t>
+          <t xml:space="preserve">preMatch.seductive.bold[2]</t>
         </is>
       </c>
       <c r="E296" t="inlineStr" s="2">
@@ -9801,14 +9801,14 @@
       </c>
       <c r="F296" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、可愛い相手ね。すぐ終わらせてあげるわ</t>
+          <t xml:space="preserve">わたしに勝てるつもり？ 甘いわね</t>
         </is>
       </c>
     </row>
     <row r="297" ht="40" customHeight="1">
       <c r="A297" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.bold.seductive[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B297" t="inlineStr" s="2">
@@ -9823,7 +9823,7 @@
       </c>
       <c r="D297" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.bold.seductive[2]</t>
+          <t xml:space="preserve">summon.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E297" t="inlineStr" s="2">
@@ -9833,14 +9833,14 @@
       </c>
       <c r="F297" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたしに勝てるつもり？ 甘いわね</t>
+          <t xml:space="preserve">あら、指名してくれたの？ 嬉しいわ</t>
         </is>
       </c>
     </row>
     <row r="298" ht="40" customHeight="1">
       <c r="A298" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.bold.seductive[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B298" t="inlineStr" s="2">
@@ -9855,7 +9855,7 @@
       </c>
       <c r="D298" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.bold.seductive[1]</t>
+          <t xml:space="preserve">summon.seductive.bold[2]</t>
         </is>
       </c>
       <c r="E298" t="inlineStr" s="2">
@@ -9865,14 +9865,14 @@
       </c>
       <c r="F298" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、指名してくれたの？ 嬉しいわ</t>
+          <t xml:space="preserve">わたしの舞台が増えるのね。楽しみ</t>
         </is>
       </c>
     </row>
     <row r="299" ht="40" customHeight="1">
       <c r="A299" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.bold.seductive[2]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B299" t="inlineStr" s="2">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="C299" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D299" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.bold.seductive[2]</t>
+          <t xml:space="preserve">seductive.bold[1]</t>
         </is>
       </c>
       <c r="E299" t="inlineStr" s="2">
@@ -9897,14 +9897,14 @@
       </c>
       <c r="F299" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたしの舞台が増えるのね。楽しみ</t>
+          <t xml:space="preserve">容赦しないわよ。覚悟してね</t>
         </is>
       </c>
     </row>
     <row r="300" ht="40" customHeight="1">
       <c r="A300" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.bold.seductive[1]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B300" t="inlineStr" s="2">
@@ -9914,12 +9914,12 @@
       </c>
       <c r="C300" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D300" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[1]</t>
+          <t xml:space="preserve">seductive.bold[1]</t>
         </is>
       </c>
       <c r="E300" t="inlineStr" s="2">
@@ -9929,14 +9929,14 @@
       </c>
       <c r="F300" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">容赦しないわよ。覚悟してね</t>
+          <t xml:space="preserve">ずっと待ってたのよ、この瞬間を……!ふふ、最高の気分ね</t>
         </is>
       </c>
     </row>
     <row r="301" ht="40" customHeight="1">
       <c r="A301" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.bold.seductive[1]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B301" t="inlineStr" s="2">
@@ -9946,12 +9946,12 @@
       </c>
       <c r="C301" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D301" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[1]</t>
+          <t xml:space="preserve">seductive.bold[1]</t>
         </is>
       </c>
       <c r="E301" t="inlineStr" s="2">
@@ -9961,14 +9961,14 @@
       </c>
       <c r="F301" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ずっと待ってたのよ、この瞬間を……!ふふ、最高の気分ね</t>
+          <t xml:space="preserve">あら…随分と自信がおありのようね。壊してあげるわ</t>
         </is>
       </c>
     </row>
     <row r="302" ht="40" customHeight="1">
       <c r="A302" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.bold.seductive[1]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B302" t="inlineStr" s="2">
@@ -9983,7 +9983,7 @@
       </c>
       <c r="D302" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[1]</t>
+          <t xml:space="preserve">seductive.bold[2]</t>
         </is>
       </c>
       <c r="E302" t="inlineStr" s="2">
@@ -9993,14 +9993,14 @@
       </c>
       <c r="F302" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら…随分と自信がおありのようね。壊してあげるわ</t>
+          <t xml:space="preserve">可哀想だけど…手加減はしないわよ</t>
         </is>
       </c>
     </row>
     <row r="303" ht="40" customHeight="1">
       <c r="A303" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.bold.seductive[2]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B303" t="inlineStr" s="2">
@@ -10010,12 +10010,12 @@
       </c>
       <c r="C303" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D303" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[2]</t>
+          <t xml:space="preserve">seductive.bold[1]</t>
         </is>
       </c>
       <c r="E303" t="inlineStr" s="2">
@@ -10025,14 +10025,14 @@
       </c>
       <c r="F303" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">可哀想だけど…手加減はしないわよ</t>
+          <t xml:space="preserve">あら、残念。もっと遊びたかったのに</t>
         </is>
       </c>
     </row>
     <row r="304" ht="40" customHeight="1">
       <c r="A304" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.bold.seductive[1]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B304" t="inlineStr" s="2">
@@ -10047,7 +10047,7 @@
       </c>
       <c r="D304" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[1]</t>
+          <t xml:space="preserve">seductive.bold[2]</t>
         </is>
       </c>
       <c r="E304" t="inlineStr" s="2">
@@ -10057,14 +10057,14 @@
       </c>
       <c r="F304" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、残念。もっと遊びたかったのに</t>
+          <t xml:space="preserve">逃げちゃうの？ …つまらない団体ね</t>
         </is>
       </c>
     </row>
     <row r="305" ht="40" customHeight="1">
       <c r="A305" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.bold.seductive[2]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B305" t="inlineStr" s="2">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="C305" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D305" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[2]</t>
+          <t xml:space="preserve">result_lose.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E305" t="inlineStr" s="2">
@@ -10089,14 +10089,14 @@
       </c>
       <c r="F305" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">逃げちゃうの？ …つまらない団体ね</t>
+          <t xml:space="preserve">あら…やられちゃったわ。……許さないけど</t>
         </is>
       </c>
     </row>
     <row r="306" ht="40" customHeight="1">
       <c r="A306" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.bold.seductive[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B306" t="inlineStr" s="2">
@@ -10111,7 +10111,7 @@
       </c>
       <c r="D306" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.bold.seductive[1]</t>
+          <t xml:space="preserve">result_lose.seductive.bold[2]</t>
         </is>
       </c>
       <c r="E306" t="inlineStr" s="2">
@@ -10121,14 +10121,14 @@
       </c>
       <c r="F306" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら…やられちゃったわ。……許さないけど</t>
+          <t xml:space="preserve">今日は譲ってあげるわ。次は…ないけどね</t>
         </is>
       </c>
     </row>
     <row r="307" ht="40" customHeight="1">
       <c r="A307" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.bold.seductive[2]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B307" t="inlineStr" s="2">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="D307" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.bold.seductive[2]</t>
+          <t xml:space="preserve">result_win.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E307" t="inlineStr" s="2">
@@ -10153,14 +10153,14 @@
       </c>
       <c r="F307" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日は譲ってあげるわ。次は…ないけどね</t>
+          <t xml:space="preserve">あら、もう終わり？ もっと楽しみたかったのに</t>
         </is>
       </c>
     </row>
     <row r="308" ht="40" customHeight="1">
       <c r="A308" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.bold.seductive[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B308" t="inlineStr" s="2">
@@ -10175,7 +10175,7 @@
       </c>
       <c r="D308" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.bold.seductive[1]</t>
+          <t xml:space="preserve">result_win.seductive.bold[2]</t>
         </is>
       </c>
       <c r="E308" t="inlineStr" s="2">
@@ -10185,14 +10185,14 @@
       </c>
       <c r="F308" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、もう終わり？ もっと楽しみたかったのに</t>
+          <t xml:space="preserve">予想通りの結果ね。つまらないわ</t>
         </is>
       </c>
     </row>
     <row r="309" ht="40" customHeight="1">
       <c r="A309" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.bold.seductive[2]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B309" t="inlineStr" s="2">
@@ -10202,12 +10202,12 @@
       </c>
       <c r="C309" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D309" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.bold.seductive[2]</t>
+          <t xml:space="preserve">seductive.bold[1]</t>
         </is>
       </c>
       <c r="E309" t="inlineStr" s="2">
@@ -10217,14 +10217,14 @@
       </c>
       <c r="F309" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">予想通りの結果ね。つまらないわ</t>
+          <t xml:space="preserve">当然よ。うちの団体を甘く見ないことね</t>
         </is>
       </c>
     </row>
     <row r="310" ht="40" customHeight="1">
       <c r="A310" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.bold.seductive[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B310" t="inlineStr" s="2">
@@ -10239,7 +10239,7 @@
       </c>
       <c r="D310" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[1]</t>
+          <t xml:space="preserve">seductive.bold[2]</t>
         </is>
       </c>
       <c r="E310" t="inlineStr" s="2">
@@ -10249,14 +10249,14 @@
       </c>
       <c r="F310" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">当然よ。うちの団体を甘く見ないことね</t>
+          <t xml:space="preserve">まだ物足りないわね。もっと強い相手はいないの？</t>
         </is>
       </c>
     </row>
     <row r="311" ht="40" customHeight="1">
       <c r="A311" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.bold.seductive[2]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.seductive.bold[3]</t>
         </is>
       </c>
       <c r="B311" t="inlineStr" s="2">
@@ -10271,7 +10271,7 @@
       </c>
       <c r="D311" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[2]</t>
+          <t xml:space="preserve">seductive.bold[3]</t>
         </is>
       </c>
       <c r="E311" t="inlineStr" s="2">
@@ -10281,14 +10281,14 @@
       </c>
       <c r="F311" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ物足りないわね。もっと強い相手はいないの？</t>
+          <t xml:space="preserve">当然の結果よ。うちを甘く見ないことね</t>
         </is>
       </c>
     </row>
     <row r="312" ht="40" customHeight="1">
       <c r="A312" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.bold.seductive[3]</t>
+          <t xml:space="preserve">ENDING_LINES.fighter.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B312" t="inlineStr" s="2">
@@ -10298,29 +10298,29 @@
       </c>
       <c r="C312" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">ENDING_LINES</t>
         </is>
       </c>
       <c r="D312" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[3]</t>
+          <t xml:space="preserve">fighter.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E312" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
         </is>
       </c>
       <c r="F312" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">当然の結果よ。うちを甘く見ないことね</t>
+          <t xml:space="preserve">頂点に立ったわ。でもまだ先があるみたいね</t>
         </is>
       </c>
     </row>
     <row r="313" ht="40" customHeight="1">
       <c r="A313" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.bold.seductive[1]</t>
+          <t xml:space="preserve">FA_GREETING_LINES.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B313" t="inlineStr" s="2">
@@ -10330,29 +10330,29 @@
       </c>
       <c r="C313" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
         </is>
       </c>
       <c r="D313" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.bold.seductive[1]</t>
+          <t xml:space="preserve">seductive.bold[1]</t>
         </is>
       </c>
       <c r="E313" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
       <c r="F313" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頂点に立ったわ。でもまだ先があるみたいね</t>
+          <t xml:space="preserve">拾った目利きは正解よ。…すぐに分かるわ</t>
         </is>
       </c>
     </row>
     <row r="314" ht="40" customHeight="1">
       <c r="A314" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.bold.seductive[1]</t>
+          <t xml:space="preserve">SCOUT_GREETING_LINES.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B314" t="inlineStr" s="2">
@@ -10362,12 +10362,12 @@
       </c>
       <c r="C314" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
       <c r="D314" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.seductive[1]</t>
+          <t xml:space="preserve">seductive.bold[1]</t>
         </is>
       </c>
       <c r="E314" t="inlineStr" s="2">
@@ -10377,44 +10377,12 @@
       </c>
       <c r="F314" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">拾った目利きは正解よ。…すぐに分かるわ</t>
-        </is>
-      </c>
-    </row>
-    <row r="315" ht="40" customHeight="1">
-      <c r="A315" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES.bold.seductive[1]</t>
-        </is>
-      </c>
-      <c r="B315" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C315" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
-        </is>
-      </c>
-      <c r="D315" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">bold.seductive[1]</t>
-        </is>
-      </c>
-      <c r="E315" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
-        </is>
-      </c>
-      <c r="F315" t="inlineStr" s="3">
-        <is>
           <t xml:space="preserve">わたしに声をかけた責任は、取ってちょうだいね</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H315"/>
+  <autoFilter ref="A1:H314"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/蠱惑×強気.xlsx
+++ b/セリフ編集/キャラタイプ別/蠱惑×強気.xlsx
@@ -306,7 +306,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H314"/>
+  <dimension ref="A1:H316"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -485,7 +485,7 @@
       </c>
       <c r="F5" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたしの全部、受け止めなさい</t>
+          <t xml:space="preserve">私の全部、受け止めなさい</t>
         </is>
       </c>
     </row>
@@ -613,7 +613,7 @@
       </c>
       <c r="F9" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（ここからよ…わたしの時間が、始まるの）</t>
+          <t xml:space="preserve">（ここからよ…私の時間が、始まるの）</t>
         </is>
       </c>
     </row>
@@ -805,7 +805,7 @@
       </c>
       <c r="F15" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けられない試合だったわ。…ふふ、応えられて満足</t>
+          <t xml:space="preserve">負けられない試合だったわ。…ふふ、応えたまでよ</t>
         </is>
       </c>
     </row>
@@ -837,7 +837,7 @@
       </c>
       <c r="F16" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">高い買い物だったでしょ？ …元は取らせてあげる♡</t>
+          <t xml:space="preserve">高い買い物だったでしょ？ …元は取らせてあげる</t>
         </is>
       </c>
     </row>
@@ -869,7 +869,7 @@
       </c>
       <c r="F17" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私をめぐって争奪戦…ふふ、気分いいわ♡</t>
+          <t xml:space="preserve">私をめぐって争奪戦…ふふ、気分いいわ</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
       </c>
       <c r="F18" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">契約してあげてもいいわよ？ …ふふ、冗談♡</t>
+          <t xml:space="preserve">契約してあげてもいいわよ？ …ふふ、冗談</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="F20" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">フリーで磨いた牙…ここで見せてあげる♡</t>
+          <t xml:space="preserve">フリーで磨いた牙…ここで見せてあげる</t>
         </is>
       </c>
     </row>
@@ -997,7 +997,7 @@
       </c>
       <c r="F21" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ようやくいい団体が見つかったわ。楽しませてね♡</t>
+          <t xml:space="preserve">ようやくいい団体が見つかったわ。楽しませてね</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="F27" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ちっ…間に合わないわ</t>
+          <t xml:space="preserve">くっ…間に合わないわ</t>
         </is>
       </c>
     </row>
@@ -1413,7 +1413,7 @@
       </c>
       <c r="F34" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">逃がさないわ、そっち任せた</t>
+          <t xml:space="preserve">逃がさないわ、そっちは任せたわ</t>
         </is>
       </c>
     </row>
@@ -1477,7 +1477,7 @@
       </c>
       <c r="F36" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたしの番よ</t>
+          <t xml:space="preserve">私の番よ</t>
         </is>
       </c>
     </row>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="F38" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたしのミスよ、{partner}…悪いわね。でも次は絶対、返すわ。</t>
+          <t xml:space="preserve">私のミスよ、{partner}…悪いわね。でも次は絶対、返すわ。</t>
         </is>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="F41" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">見た？ これが{partner}とわたしのタッグよ。</t>
+          <t xml:space="preserve">見た？ これが{partner}と私のタッグよ。</t>
         </is>
       </c>
     </row>
@@ -2309,7 +2309,7 @@
       </c>
       <c r="F62" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">身の程を教えてあげたい相手がいるの。組んでくれる?</t>
+          <t xml:space="preserve">身の程を教えてあげたい相手がいるの。組んでくれる？</t>
         </is>
       </c>
     </row>
@@ -2437,7 +2437,7 @@
       </c>
       <c r="F66" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ったわ。当然でしょ? ……ありがと、社長。</t>
+          <t xml:space="preserve">勝ったわ。当然でしょ？ ……ありがと、社長。</t>
         </is>
       </c>
     </row>
@@ -2533,7 +2533,7 @@
       </c>
       <c r="F69" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">へえ、私に噛みつくの? …いい度胸ね。</t>
+          <t xml:space="preserve">へえ、私に噛みつくの？ …いい度胸ね。</t>
         </is>
       </c>
     </row>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="F71" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">後悔しても知らないわよ? ふふ。</t>
+          <t xml:space="preserve">後悔しても知らないわよ？ ふふ。</t>
         </is>
       </c>
     </row>
@@ -2629,7 +2629,7 @@
       </c>
       <c r="F72" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決めさせてくれないの? 生意気ね。</t>
+          <t xml:space="preserve">決めさせてくれないの？ 生意気ね。</t>
         </is>
       </c>
     </row>
@@ -2693,7 +2693,7 @@
       </c>
       <c r="F74" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決着つかず? 私は納得してないわよ。</t>
+          <t xml:space="preserve">決着つかず？ 私は納得してないわよ。</t>
         </is>
       </c>
     </row>
@@ -2885,7 +2885,7 @@
       </c>
       <c r="F80" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう一度来る? …今度は容赦しない。</t>
+          <t xml:space="preserve">もう一度来る？ …今度は容赦しない。</t>
         </is>
       </c>
     </row>
@@ -3045,7 +3045,7 @@
       </c>
       <c r="F85" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ごめんなさいね。でも、わたしの決意は固いの</t>
+          <t xml:space="preserve">…ごめんなさいね。でも、私の決意は固いの</t>
         </is>
       </c>
     </row>
@@ -3813,7 +3813,7 @@
       </c>
       <c r="F109" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、分かってくれるじゃない♡ 期待しててね。</t>
+          <t xml:space="preserve">ふふ、分かってくれるじゃない 期待しててね。</t>
         </is>
       </c>
     </row>
@@ -3845,7 +3845,7 @@
       </c>
       <c r="F110" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……まあ、少しは考えてくれたのね。次はもっと期待してるわよ♡</t>
+          <t xml:space="preserve">……まあ、少しは考えてくれたのね。次はもっと期待してるわよ</t>
         </is>
       </c>
     </row>
@@ -4361,7 +4361,7 @@
       </c>
       <c r="F126" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、次のメイン、私に任せてくれない? 必ず客を沸かすから。</t>
+          <t xml:space="preserve">社長、次のメイン、私に任せてくれない？ 必ず客を沸かすから。</t>
         </is>
       </c>
     </row>
@@ -4393,7 +4393,7 @@
       </c>
       <c r="F127" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、私たちの給料の話、ちょっと聞いてくれない?</t>
+          <t xml:space="preserve">社長、私たちの給料の話、ちょっと聞いてくれない？</t>
         </is>
       </c>
     </row>
@@ -4425,7 +4425,7 @@
       </c>
       <c r="F128" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、私の貢献、ちゃんと見てくれてる? 確かめさせて。</t>
+          <t xml:space="preserve">社長、私の貢献、ちゃんと見てくれてる？ 確かめさせて。</t>
         </is>
       </c>
     </row>
@@ -4457,7 +4457,7 @@
       </c>
       <c r="F129" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとう社長、嬉しい。ちゃんと届いてたんだね。</t>
+          <t xml:space="preserve">届いていたのね、その気持ち。……ありがとう、社長。</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="F131" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そう、別ルートね。それも嬉しい、ありがとう。</t>
+          <t xml:space="preserve">……ふふ、そちらの筋から来たの。悪くないわ、感謝しておく。</t>
         </is>
       </c>
     </row>
@@ -4585,7 +4585,7 @@
       </c>
       <c r="F133" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そう。じゃあ、覚えておくね。</t>
+          <t xml:space="preserve">……そう。その言葉、覚えておくわ。</t>
         </is>
       </c>
     </row>
@@ -4617,7 +4617,7 @@
       </c>
       <c r="F134" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そう。それも悪くないかもね。ありがとう。</t>
+          <t xml:space="preserve">……なるほど。そういう手もあるのね。悪くないじゃない。</t>
         </is>
       </c>
     </row>
@@ -4649,7 +4649,7 @@
       </c>
       <c r="F135" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとう社長、嬉しい。みんなにも伝えるね。</t>
+          <t xml:space="preserve">感謝するわ、社長。この話、皆にも下ろしておく。</t>
         </is>
       </c>
     </row>
@@ -4681,7 +4681,7 @@
       </c>
       <c r="F136" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そう。わかった、また話そうね。</t>
+          <t xml:space="preserve">……そう。続きはまた、いずれ。</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="F137" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ふぅん、お金じゃないんだ。まあ、それも嬉しいよ。</t>
+          <t xml:space="preserve">……ふぅん、金銭じゃないのね。まあ、そういうのも嫌いじゃないわ。</t>
         </is>
       </c>
     </row>
@@ -4745,7 +4745,7 @@
       </c>
       <c r="F138" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとう社長、嬉しい。ちゃんと見ててくれたんだね。</t>
+          <t xml:space="preserve">見ていてくれたのね。……こういうの、効くじゃない。</t>
         </is>
       </c>
     </row>
@@ -4809,7 +4809,7 @@
       </c>
       <c r="F140" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そう、別の形ね。それも嬉しい、ありがとう。</t>
+          <t xml:space="preserve">……別の形、ね。それはそれで悪くないわ。感謝する。</t>
         </is>
       </c>
     </row>
@@ -4841,7 +4841,7 @@
       </c>
       <c r="F141" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そう、次は声かけるね。ごめんなさい。</t>
+          <t xml:space="preserve">……そう。次は先に一声かけるわ。悪かったわね。</t>
         </is>
       </c>
     </row>
@@ -4905,7 +4905,7 @@
       </c>
       <c r="F143" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そう、気をつけるね。</t>
+          <t xml:space="preserve">……そう。心に留めておくわ。</t>
         </is>
       </c>
     </row>
@@ -4969,7 +4969,7 @@
       </c>
       <c r="F145" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そう、線を引くね。客はノッてたんだけど。</t>
+          <t xml:space="preserve">……線ね。引くわ。客は乗っていたのだけれど。</t>
         </is>
       </c>
     </row>
@@ -5033,7 +5033,7 @@
       </c>
       <c r="F147" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ごめん、社長。明日から、ちゃんと出るね。</t>
+          <t xml:space="preserve">……悪かったわ、社長。明日からはきちんと顔を出す。</t>
         </is>
       </c>
     </row>
@@ -5129,7 +5129,7 @@
       </c>
       <c r="F150" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとう、社長。ちょっと休むね。</t>
+          <t xml:space="preserve">……ありがとう。少しだけ、身体を休めておくわ。</t>
         </is>
       </c>
     </row>
@@ -5161,7 +5161,7 @@
       </c>
       <c r="F151" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…大丈夫、まだ平気だよ。</t>
+          <t xml:space="preserve">……平気よ。まだ倒れる気はないの。</t>
         </is>
       </c>
     </row>
@@ -5225,7 +5225,7 @@
       </c>
       <c r="F153" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そう。私から皆に話すね。</t>
+          <t xml:space="preserve">……そう。皆へは私の口から通しておくわ。</t>
         </is>
       </c>
     </row>
@@ -5321,7 +5321,7 @@
       </c>
       <c r="F156" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そう。気をつけるね。</t>
+          <t xml:space="preserve">……了解。次から気を配るわ。</t>
         </is>
       </c>
     </row>
@@ -5417,7 +5417,7 @@
       </c>
       <c r="F159" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そうね、緩めるね。怪我させたくないし。</t>
+          <t xml:space="preserve">……そうね、加減はするわ。壊してしまっては意味がないもの。</t>
         </is>
       </c>
     </row>
@@ -5449,7 +5449,7 @@
       </c>
       <c r="F160" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとう、社長。このまま続けるね。</t>
+          <t xml:space="preserve">……感謝するわ、社長。このまま突き進ませてもらう。</t>
         </is>
       </c>
     </row>
@@ -5840,7 +5840,7 @@
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.seductive.bold[1]</t>
+          <t xml:space="preserve">AWARD_LINES.autumnWarChampion.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5855,7 +5855,7 @@
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.seductive.bold[1]</t>
+          <t xml:space="preserve">autumnWarChampion.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr" s="2">
@@ -5865,14 +5865,14 @@
       </c>
       <c r="F173" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全力を引き出してくれた相手に感謝。…次はもっと激しくいくわよ？</t>
+          <t xml:space="preserve">対抗戦の主役は私たちよ。忘れないでね。</t>
         </is>
       </c>
     </row>
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.seductive.bold[1]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -5887,7 +5887,7 @@
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.seductive.bold[1]</t>
+          <t xml:space="preserve">bestMatch.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E174" t="inlineStr" s="2">
@@ -5897,14 +5897,14 @@
       </c>
       <c r="F174" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頂点からの景色は最高よ。…あなたには見せてあげないけど</t>
+          <t xml:space="preserve">全力を引き出してくれた相手に感謝。…次はもっと激しくいくわよ？</t>
         </is>
       </c>
     </row>
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.seductive.bold[1]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -5919,7 +5919,7 @@
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.seductive.bold[1]</t>
+          <t xml:space="preserve">champion.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E175" t="inlineStr" s="2">
@@ -5929,14 +5929,14 @@
       </c>
       <c r="F175" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高の舞台で、最高の人生だった。…最後まで美しかったでしょう？</t>
+          <t xml:space="preserve">頂点からの景色は最高よ。…あなたには見せてあげないけど</t>
         </is>
       </c>
     </row>
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.seductive.bold[1]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -5951,7 +5951,7 @@
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.seductive.bold[1]</t>
+          <t xml:space="preserve">hallOfFame.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
@@ -5961,14 +5961,14 @@
       </c>
       <c r="F176" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一番になるべくしてなった。当然でしょう？ …でも、まだ満足してないわ</t>
+          <t xml:space="preserve">最高の舞台で、最高の人生だった。…最後まで美しかったでしょう？</t>
         </is>
       </c>
     </row>
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.seductive.bold[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -5983,7 +5983,7 @@
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.seductive.bold[1]</t>
+          <t xml:space="preserve">mvp.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
@@ -5993,14 +5993,14 @@
       </c>
       <c r="F177" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">嬉しい？ ええ、嬉しいわ。でもこの程度で満足する女じゃないの</t>
+          <t xml:space="preserve">一番になるべくしてなった。当然でしょう？ …でも、まだ満足してないわ</t>
         </is>
       </c>
     </row>
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.seductive.bold[1]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -6010,12 +6010,12 @@
       </c>
       <c r="C178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.bold[1]</t>
+          <t xml:space="preserve">rookie.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr" s="2">
@@ -6025,14 +6025,14 @@
       </c>
       <c r="F178" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ドームで…本気の私、見せてあげる</t>
+          <t xml:space="preserve">嬉しい？ ええ、嬉しいわ。でもこの程度で満足する女じゃないの</t>
         </is>
       </c>
     </row>
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.seductive.bold[2]</t>
+          <t xml:space="preserve">AWARD_LINES.springTagChampion.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -6042,12 +6042,12 @@
       </c>
       <c r="C179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.bold[2]</t>
+          <t xml:space="preserve">springTagChampion.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr" s="2">
@@ -6057,14 +6057,14 @@
       </c>
       <c r="F179" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この大舞台、たっぷり熱くしてあげるわよ</t>
+          <t xml:space="preserve">相棒との舞台は最上級よ。次も目を離さないで。</t>
         </is>
       </c>
     </row>
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.seductive.bold[3]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -6079,7 +6079,7 @@
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.bold[3]</t>
+          <t xml:space="preserve">seductive.bold[1]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
@@ -6089,14 +6089,14 @@
       </c>
       <c r="F180" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うふふ、今夜は容赦しないわよ</t>
+          <t xml:space="preserve">ドームで…本気の私、見せてあげる</t>
         </is>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.seductive.bold[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -6106,12 +6106,12 @@
       </c>
       <c r="C181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.bold[1]</t>
+          <t xml:space="preserve">seductive.bold[2]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
@@ -6121,14 +6121,14 @@
       </c>
       <c r="F181" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">満員…最高の演出になったわね</t>
+          <t xml:space="preserve">この大舞台、たっぷり熱くしてあげるわよ</t>
         </is>
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.seductive.bold[2]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.seductive.bold[3]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -6138,12 +6138,12 @@
       </c>
       <c r="C182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.bold[2]</t>
+          <t xml:space="preserve">seductive.bold[3]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
@@ -6153,14 +6153,14 @@
       </c>
       <c r="F182" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この熱量、また必ず味わいたい</t>
+          <t xml:space="preserve">うふふ、今夜は容赦しないわよ</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.seductive.bold[3]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6175,7 +6175,7 @@
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.bold[3]</t>
+          <t xml:space="preserve">seductive.bold[1]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
@@ -6185,14 +6185,14 @@
       </c>
       <c r="F183" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うふふ、皆様を虜にしてやったわ</t>
+          <t xml:space="preserve">満員…最高の演出になったわね</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.seductive.bold[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6202,29 +6202,29 @@
       </c>
       <c r="C184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.seductive.bold[1]</t>
+          <t xml:space="preserve">seductive.bold[2]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ足りないわ。もっと強くなれる気がするの</t>
+          <t xml:space="preserve">この熱量、また必ず味わいたい</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.seductive.bold[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.seductive.bold[3]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6234,29 +6234,29 @@
       </c>
       <c r="C185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.seductive.bold[1]</t>
+          <t xml:space="preserve">seductive.bold[3]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仲間がいるって、いいものね</t>
+          <t xml:space="preserve">うふふ、皆様を虜にしてあげたわ</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.seductive.bold[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.seductive.bold[1]</t>
+          <t xml:space="preserve">N1.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
@@ -6281,14 +6281,14 @@
       </c>
       <c r="F186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この程度で止まるつもりはないわ</t>
+          <t xml:space="preserve">まだ足りないわ。もっと強くなれる気がするの</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.seductive.bold[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6303,7 +6303,7 @@
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.seductive.bold[1]</t>
+          <t xml:space="preserve">N2.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
@@ -6313,14 +6313,14 @@
       </c>
       <c r="F187" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この人気、活かさない手はないわね</t>
+          <t xml:space="preserve">仲間がいるって、いいものね</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.seductive.bold[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.seductive.bold[1]</t>
+          <t xml:space="preserve">N3.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
@@ -6345,14 +6345,14 @@
       </c>
       <c r="F188" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ここにいて、私の夢は叶うのかしら</t>
+          <t xml:space="preserve">この程度で止まるつもりはないわ</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.seductive.bold[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6367,7 +6367,7 @@
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_warning.seductive.bold[1]</t>
+          <t xml:space="preserve">N4.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
@@ -6377,14 +6377,14 @@
       </c>
       <c r="F189" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…このままでいいのかなって、ふと思うの</t>
+          <t xml:space="preserve">この人気、活かさない手はないわね</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.seductive.bold[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6394,29 +6394,29 @@
       </c>
       <c r="C190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.seductive.bold[1]</t>
+          <t xml:space="preserve">N5_low.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F190" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">嬉しいわ。実力で返させてもらうわね</t>
+          <t xml:space="preserve">…ここにいて、私の夢は叶うのかしら</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.seductive.bold[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6426,29 +6426,29 @@
       </c>
       <c r="C191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.seductive.bold[1]</t>
+          <t xml:space="preserve">N5_warning.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F191" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">帰る頃には一回り強くなってるわよ</t>
+          <t xml:space="preserve">…このままでいいのかしらって、ふと思うの</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.seductive.bold[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6463,7 +6463,7 @@
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage_high_trust.seductive.bold[1]</t>
+          <t xml:space="preserve">bonus.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
@@ -6473,14 +6473,14 @@
       </c>
       <c r="F192" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あなたが信じてくれるなら…絶対応えるわ</t>
+          <t xml:space="preserve">嬉しいわ。実力で返させてもらうわね</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.seductive.bold[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6495,7 +6495,7 @@
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.seductive.bold[1]</t>
+          <t xml:space="preserve">camp.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
@@ -6505,14 +6505,14 @@
       </c>
       <c r="F193" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">止まるつもりはないわ。見ていてね</t>
+          <t xml:space="preserve">帰る頃には一回り強くなってるわよ</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.seductive.bold[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6527,7 +6527,7 @@
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faction_decree.seductive.bold[1]</t>
+          <t xml:space="preserve">encourage_high_trust.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
@@ -6537,14 +6537,14 @@
       </c>
       <c r="F194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いいわ、畳みましょう。……でも、覚えておいて</t>
+          <t xml:space="preserve">あなたが信じてくれるなら…絶対応えるわ</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.seductive.bold[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6559,7 +6559,7 @@
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.seductive.bold[1]</t>
+          <t xml:space="preserve">encourage.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
@@ -6569,14 +6569,14 @@
       </c>
       <c r="F195" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">注目される場って好きよ。任せて</t>
+          <t xml:space="preserve">止まるつもりはないわ。見ていてね</t>
         </is>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.seductive.bold[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6591,7 +6591,7 @@
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.seductive.bold[1]</t>
+          <t xml:space="preserve">faction_decree.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
@@ -6601,14 +6601,14 @@
       </c>
       <c r="F196" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい雰囲気ね。チームが成長してる証拠だわ</t>
+          <t xml:space="preserve">いいわ、畳みましょう。……でも、覚えておいて</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.seductive.bold[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6623,7 +6623,7 @@
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.seductive.bold[1]</t>
+          <t xml:space="preserve">media.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
@@ -6633,14 +6633,14 @@
       </c>
       <c r="F197" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">リフレッシュしてくるわ。戻ったらもっと輝くから</t>
+          <t xml:space="preserve">注目される場って好きよ。任せて</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.seductive.bold[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6655,7 +6655,7 @@
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">special_treatment.seductive.bold[1]</t>
+          <t xml:space="preserve">party.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
@@ -6665,14 +6665,14 @@
       </c>
       <c r="F198" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">早く戻りたいの…待っていてね</t>
+          <t xml:space="preserve">いい雰囲気ね。チームが成長してる証拠だわ</t>
         </is>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.seductive.bold[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6687,7 +6687,7 @@
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.seductive.bold[1]</t>
+          <t xml:space="preserve">refresh_leave.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
@@ -6697,14 +6697,14 @@
       </c>
       <c r="F199" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この環境、無駄にしないわ。見ていてね</t>
+          <t xml:space="preserve">リフレッシュしてくるわ。戻ったらもっと輝くから</t>
         </is>
       </c>
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.seductive.bold[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6714,12 +6714,12 @@
       </c>
       <c r="C200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.seductive.bold[1]</t>
+          <t xml:space="preserve">special_treatment.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
@@ -6729,14 +6729,14 @@
       </c>
       <c r="F200" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">注目される場は好きよ。もちろんやるわ</t>
+          <t xml:space="preserve">早く戻りたいの…待っていてね</t>
         </is>
       </c>
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.seductive.bold[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6746,12 +6746,12 @@
       </c>
       <c r="C201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.seductive.bold[1]</t>
+          <t xml:space="preserve">trainer.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
@@ -6761,14 +6761,14 @@
       </c>
       <c r="F201" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">他所からいい話が来てるの。正直、迷ってるわ</t>
+          <t xml:space="preserve">この環境、無駄にしないわ。見ていてね</t>
         </is>
       </c>
     </row>
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.seductive.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6783,7 +6783,7 @@
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.seductive.bold[1]</t>
+          <t xml:space="preserve">E1.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
@@ -6793,14 +6793,14 @@
       </c>
       <c r="F202" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">練習？ 出してもくれないのに、意味があるのかしら</t>
+          <t xml:space="preserve">注目される場は好きよ。もちろんやるわ</t>
         </is>
       </c>
     </row>
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.seductive.bold[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6815,7 +6815,7 @@
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.seductive.bold[2]</t>
+          <t xml:space="preserve">E6.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
@@ -6825,14 +6825,14 @@
       </c>
       <c r="F203" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">リングに上がれないなら、やっても同じでしょう？</t>
+          <t xml:space="preserve">他所からいい話が来てるの。正直、迷ってるわ</t>
         </is>
       </c>
     </row>
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.seductive.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6847,7 +6847,7 @@
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_grumble.seductive.bold[1]</t>
+          <t xml:space="preserve">S_boycott.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
@@ -6857,14 +6857,14 @@
       </c>
       <c r="F204" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（「わたしたち、ずいぶん軽く見られてるのね」と笑みを崩さずに言い放っている）</t>
+          <t xml:space="preserve">練習？ 出してもくれないのに、意味があるのかしら</t>
         </is>
       </c>
     </row>
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.seductive.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6879,7 +6879,7 @@
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_sns.seductive.bold[1]</t>
+          <t xml:space="preserve">S_boycott.seductive.bold[2]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
@@ -6889,14 +6889,14 @@
       </c>
       <c r="F205" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（SNSに「このまま終わるつもりはないの。楽しみにしてて」と投稿）</t>
+          <t xml:space="preserve">リングに上がれないなら、やっても同じでしょう？</t>
         </is>
       </c>
     </row>
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.seductive.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6911,7 +6911,7 @@
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.seductive.bold[1]</t>
+          <t xml:space="preserve">S_grumble.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
@@ -6921,14 +6921,14 @@
       </c>
       <c r="F206" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ベルトが欲しいの。組んでもらえる？</t>
+          <t xml:space="preserve">（「私たち、ずいぶん軽く見られてるのね」と笑みを崩さずに言い放っている）</t>
         </is>
       </c>
     </row>
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.seductive.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6943,7 +6943,7 @@
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.seductive.bold[1]</t>
+          <t xml:space="preserve">S_sns.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
@@ -6953,14 +6953,14 @@
       </c>
       <c r="F207" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの人と決着をつけたいの。組んでもらえる？</t>
+          <t xml:space="preserve">（SNSに「このまま終わるつもりはないの。楽しみにしてて」と投稿）</t>
         </is>
       </c>
     </row>
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.seductive.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -6975,7 +6975,7 @@
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.seductive.bold[1]</t>
+          <t xml:space="preserve">S1.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
@@ -6985,14 +6985,14 @@
       </c>
       <c r="F208" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…体が限界なの。少し休ませて</t>
+          <t xml:space="preserve">ベルトが欲しいの。組んでもらえる？</t>
         </is>
       </c>
     </row>
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.seductive.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -7007,7 +7007,7 @@
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.seductive.bold[1]</t>
+          <t xml:space="preserve">S2.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
@@ -7017,14 +7017,14 @@
       </c>
       <c r="F209" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このままじゃ我慢の限界よ。考え直してもらえない？</t>
+          <t xml:space="preserve">あの人と決着をつけたいの。組んでもらえる？</t>
         </is>
       </c>
     </row>
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.seductive.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -7039,7 +7039,7 @@
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_silent.seductive.bold[1]</t>
+          <t xml:space="preserve">S3.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
@@ -7049,14 +7049,14 @@
       </c>
       <c r="F210" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…………（笑みは崩さないまま、指先だけが強く握られている）</t>
+          <t xml:space="preserve">…体が限界なの。少し休ませて</t>
         </is>
       </c>
     </row>
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.seductive.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7071,7 +7071,7 @@
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.seductive.bold[1]</t>
+          <t xml:space="preserve">S4_direct.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
@@ -7081,14 +7081,14 @@
       </c>
       <c r="F211" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もっと強くなりたいの。特訓させてもらえる？</t>
+          <t xml:space="preserve">このままじゃ我慢の限界よ。考え直してもらえない？</t>
         </is>
       </c>
     </row>
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.seductive.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7103,7 +7103,7 @@
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.seductive.bold[1]</t>
+          <t xml:space="preserve">S4_silent.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
@@ -7113,14 +7113,14 @@
       </c>
       <c r="F212" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">後輩の面倒、見させてもらえるかしら？</t>
+          <t xml:space="preserve">…………（笑みは崩さないまま、指先だけが強く握られている）</t>
         </is>
       </c>
     </row>
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.seductive.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7130,12 +7130,12 @@
       </c>
       <c r="C213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.seductive.bold[1]</t>
+          <t xml:space="preserve">S5.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
@@ -7145,14 +7145,14 @@
       </c>
       <c r="F213" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんなところで止まるつもりはないわ…すぐ戻る</t>
+          <t xml:space="preserve">もっと強くなりたいの。特訓させてもらえる？</t>
         </is>
       </c>
     </row>
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.seductive.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="C214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.seductive.bold[1]</t>
+          <t xml:space="preserve">S6.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
@@ -7177,14 +7177,14 @@
       </c>
       <c r="F214" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの人の態度、もう我慢できないの</t>
+          <t xml:space="preserve">後輩の面倒、見させてもらえるかしら？</t>
         </is>
       </c>
     </row>
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.seductive.bold[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7199,7 +7199,7 @@
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.seductive.bold[1]</t>
+          <t xml:space="preserve">B1.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
@@ -7209,14 +7209,14 @@
       </c>
       <c r="F215" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">黙ってるつもりはないわ。向こうが悪いんだから</t>
+          <t xml:space="preserve">こんなところで止まるつもりはないわ…すぐ戻る</t>
         </is>
       </c>
     </row>
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.seductive.bold[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.seductive.bold[1]</t>
+          <t xml:space="preserve">B2_fighter1.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
@@ -7241,14 +7241,14 @@
       </c>
       <c r="F216" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私とブランドの組み合わせ…最高じゃない♡</t>
+          <t xml:space="preserve">あの人の態度、もう我慢できないの</t>
         </is>
       </c>
     </row>
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.seductive.bold[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7263,7 +7263,7 @@
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.seductive.bold[1]</t>
+          <t xml:space="preserve">B2_fighter2.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
@@ -7273,14 +7273,14 @@
       </c>
       <c r="F217" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全国に私を見てもらえるのね。楽しみだわ♡</t>
+          <t xml:space="preserve">黙ってるつもりはないわ。向こうが悪いんだから</t>
         </is>
       </c>
     </row>
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.seductive.bold[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7295,7 +7295,7 @@
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.seductive.bold[1]</t>
+          <t xml:space="preserve">B4_brand.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
@@ -7305,14 +7305,14 @@
       </c>
       <c r="F218" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ファンを喜ばせるのは得意よ。任せて♡</t>
+          <t xml:space="preserve">私とブランドの組み合わせ…最高じゃない</t>
         </is>
       </c>
     </row>
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.seductive.bold[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7327,7 +7327,7 @@
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.seductive.bold[1]</t>
+          <t xml:space="preserve">B4_cm.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
@@ -7337,14 +7337,14 @@
       </c>
       <c r="F219" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ランウェイ、私のためにあるようなものよ♡</t>
+          <t xml:space="preserve">全国に私を見てもらえるのね。楽しみだわ</t>
         </is>
       </c>
     </row>
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.seductive.bold[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7359,7 +7359,7 @@
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.seductive.bold[1]</t>
+          <t xml:space="preserve">B4_fan.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
@@ -7369,14 +7369,14 @@
       </c>
       <c r="F220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私の本気の魅力、たっぷり撮ってもらうわ♡</t>
+          <t xml:space="preserve">ファンを喜ばせるのは得意よ。任せて</t>
         </is>
       </c>
     </row>
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.seductive.bold[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.seductive.bold[1]</t>
+          <t xml:space="preserve">B4_fashion.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
@@ -7401,14 +7401,14 @@
       </c>
       <c r="F221" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">バラエティでも私のペースで話すわ♡</t>
+          <t xml:space="preserve">ランウェイ、私のためにあるようなものよ</t>
         </is>
       </c>
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.seductive.bold[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7423,7 +7423,7 @@
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.seductive.bold[1]</t>
+          <t xml:space="preserve">B4_gravure.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
@@ -7433,14 +7433,14 @@
       </c>
       <c r="F222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全国に見てもらえるのね。楽しみだわ</t>
+          <t xml:space="preserve">私の本気の魅力、たっぷり撮ってもらうわ</t>
         </is>
       </c>
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.seductive.bold[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7450,29 +7450,29 @@
       </c>
       <c r="C223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.bold[1]</t>
+          <t xml:space="preserve">B4_variety.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F223" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私を選んで。後悔はさせないわ</t>
+          <t xml:space="preserve">バラエティでも私のペースで話すわ</t>
         </is>
       </c>
     </row>
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.seductive.bold[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7482,29 +7482,29 @@
       </c>
       <c r="C224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.bold[1]</t>
+          <t xml:space="preserve">B4.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F224" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオン、獲りに来たの。覚悟してて</t>
+          <t xml:space="preserve">全国に見てもらえるのね。楽しみだわ</t>
         </is>
       </c>
     </row>
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.seductive.bold[2]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7514,12 +7514,12 @@
       </c>
       <c r="C225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.bold[2]</t>
+          <t xml:space="preserve">seductive.bold[1]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
@@ -7529,14 +7529,14 @@
       </c>
       <c r="F225" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この団体、私が盛り上げてあげる</t>
+          <t xml:space="preserve">私を選んで。後悔はさせないわ</t>
         </is>
       </c>
     </row>
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.seductive.bold[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7546,7 +7546,7 @@
       </c>
       <c r="C226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D226" t="inlineStr" s="12">
@@ -7561,14 +7561,14 @@
       </c>
       <c r="F226" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">てっぺん獲りに来たの。一緒に頂点に立ちましょう</t>
+          <t xml:space="preserve">チャンピオン、獲りに来たの。覚悟してて</t>
         </is>
       </c>
     </row>
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.seductive.bold[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7578,12 +7578,12 @@
       </c>
       <c r="C227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.bold[1]</t>
+          <t xml:space="preserve">seductive.bold[2]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
@@ -7593,14 +7593,14 @@
       </c>
       <c r="F227" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頂点まで一直線よ。見ていてね</t>
+          <t xml:space="preserve">この団体、私が盛り上げてあげる</t>
         </is>
       </c>
     </row>
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.seductive.bold[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7610,7 +7610,7 @@
       </c>
       <c r="C228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D228" t="inlineStr" s="12">
@@ -7625,14 +7625,14 @@
       </c>
       <c r="F228" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんなことで止まると思ってる？ 甘いわ</t>
+          <t xml:space="preserve">てっぺん獲りに来たの。一緒に頂点に立ちましょう</t>
         </is>
       </c>
     </row>
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.seductive.bold[2]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7642,12 +7642,12 @@
       </c>
       <c r="C229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.bold[2]</t>
+          <t xml:space="preserve">seductive.bold[1]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
@@ -7657,14 +7657,14 @@
       </c>
       <c r="F229" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">すぐ戻るわ。覚悟してなさい</t>
+          <t xml:space="preserve">頂点まで一直線よ。見ていてね</t>
         </is>
       </c>
     </row>
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.seductive.bold[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7674,12 +7674,12 @@
       </c>
       <c r="C230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.seductive.bold[1]</t>
+          <t xml:space="preserve">seductive.bold[1]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
@@ -7689,14 +7689,14 @@
       </c>
       <c r="F230" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私を選んで。後悔はさせないわ</t>
+          <t xml:space="preserve">こんなことで止まると思ってる？ 甘いわ</t>
         </is>
       </c>
     </row>
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.seductive.bold[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7706,12 +7706,12 @@
       </c>
       <c r="C231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.seductive.bold[1]</t>
+          <t xml:space="preserve">seductive.bold[2]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
@@ -7721,14 +7721,14 @@
       </c>
       <c r="F231" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオン、獲りに来たの。覚悟してて</t>
+          <t xml:space="preserve">すぐ戻るわ。覚悟してなさい</t>
         </is>
       </c>
     </row>
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.seductive.bold[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7743,7 +7743,7 @@
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.seductive.bold[2]</t>
+          <t xml:space="preserve">draftInterest.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
@@ -7753,14 +7753,14 @@
       </c>
       <c r="F232" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この団体、私が盛り上げてあげる</t>
+          <t xml:space="preserve">私を選んで。後悔はさせないわ</t>
         </is>
       </c>
     </row>
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.seductive.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7775,7 +7775,7 @@
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.seductive.bold[1]</t>
+          <t xml:space="preserve">draftJoin.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
@@ -7785,14 +7785,14 @@
       </c>
       <c r="F233" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">拾った目利きは正解よ。…すぐに分かるわ</t>
+          <t xml:space="preserve">チャンピオン、獲りに来たの。覚悟してて</t>
         </is>
       </c>
     </row>
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.seductive.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7807,7 +7807,7 @@
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.seductive.bold[1]</t>
+          <t xml:space="preserve">draftJoin.seductive.bold[2]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
@@ -7817,14 +7817,14 @@
       </c>
       <c r="F234" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">てっぺん獲りに来たの。一緒に頂点に立ちましょう</t>
+          <t xml:space="preserve">この団体、私が盛り上げてあげる</t>
         </is>
       </c>
     </row>
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.seductive.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7839,7 +7839,7 @@
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.seductive.bold[1]</t>
+          <t xml:space="preserve">faGreeting.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
@@ -7849,14 +7849,14 @@
       </c>
       <c r="F235" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頂点まで一直線よ。見ていてね</t>
+          <t xml:space="preserve">拾った目利きは正解よ。…すぐに分かるわ</t>
         </is>
       </c>
     </row>
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.seductive.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7871,7 +7871,7 @@
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.seductive.bold[1]</t>
+          <t xml:space="preserve">faSigning.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
@@ -7881,14 +7881,14 @@
       </c>
       <c r="F236" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんなことで止まると思ってる？ 甘いわ</t>
+          <t xml:space="preserve">てっぺん獲りに来たの。一緒に頂点に立ちましょう</t>
         </is>
       </c>
     </row>
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.seductive.bold[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -7903,7 +7903,7 @@
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.seductive.bold[2]</t>
+          <t xml:space="preserve">faWelcome.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
@@ -7913,14 +7913,14 @@
       </c>
       <c r="F237" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">すぐ戻るわ。覚悟してなさい</t>
+          <t xml:space="preserve">頂点まで一直線よ。見ていてね</t>
         </is>
       </c>
     </row>
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.seductive.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -7935,7 +7935,7 @@
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.seductive.bold[1]</t>
+          <t xml:space="preserve">injury.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
@@ -7945,14 +7945,14 @@
       </c>
       <c r="F238" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しいわ…でも、いつか必ず戻ってくる</t>
+          <t xml:space="preserve">こんなことで止まると思ってる？ 甘いわ</t>
         </is>
       </c>
     </row>
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.seductive.bold[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -7967,7 +7967,7 @@
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.seductive.bold[2]</t>
+          <t xml:space="preserve">injury.seductive.bold[2]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
@@ -7977,14 +7977,14 @@
       </c>
       <c r="F239" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この借り、いつか返しに来るから</t>
+          <t xml:space="preserve">すぐ戻るわ。覚悟してなさい</t>
         </is>
       </c>
     </row>
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.seductive.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -7999,7 +7999,7 @@
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.seductive.bold[1]</t>
+          <t xml:space="preserve">release.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
@@ -8009,14 +8009,14 @@
       </c>
       <c r="F240" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">レンタルでも全力よ。見ていてね</t>
+          <t xml:space="preserve">悔しいわ…でも、いつか必ず戻ってくる</t>
         </is>
       </c>
     </row>
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.seductive.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -8031,7 +8031,7 @@
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.seductive.bold[1]</t>
+          <t xml:space="preserve">release.seductive.bold[2]</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
@@ -8041,14 +8041,14 @@
       </c>
       <c r="F241" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたしに声をかけた責任は、取ってちょうだいね</t>
+          <t xml:space="preserve">この借り、いつか返しに来るから</t>
         </is>
       </c>
     </row>
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.seductive.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8063,7 +8063,7 @@
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.seductive.bold[1]</t>
+          <t xml:space="preserve">rentalGreeting.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
@@ -8073,14 +8073,14 @@
       </c>
       <c r="F242" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…今日は認めるわ。でもこの借り、必ず返す</t>
+          <t xml:space="preserve">レンタルでも全力よ。見ていてね</t>
         </is>
       </c>
     </row>
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.seductive.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -8095,7 +8095,7 @@
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.seductive.bold[1]</t>
+          <t xml:space="preserve">scoutGreeting.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E243" t="inlineStr" s="2">
@@ -8105,14 +8105,14 @@
       </c>
       <c r="F243" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ誰も私を超えられないわね。当然でしょう</t>
+          <t xml:space="preserve">私に声をかけた責任は、取ってちょうだいね</t>
         </is>
       </c>
     </row>
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.seductive.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8127,7 +8127,7 @@
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.seductive.bold[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
@@ -8137,14 +8137,14 @@
       </c>
       <c r="F244" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…覚えておきなさい。すぐに返してもらうわ</t>
+          <t xml:space="preserve">…今日は認めるわ。でもこの借り、必ず返す</t>
         </is>
       </c>
     </row>
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.seductive.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8159,7 +8159,7 @@
       </c>
       <c r="D245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.seductive.bold[1]</t>
+          <t xml:space="preserve">titleDefense.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
@@ -8169,14 +8169,14 @@
       </c>
       <c r="F245" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">これが始まりよ。このベルトで時代を作る</t>
+          <t xml:space="preserve">まだ誰も私を超えられないわね。当然でしょう</t>
         </is>
       </c>
     </row>
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.seductive.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8186,12 +8186,12 @@
       </c>
       <c r="C246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.bold[1]</t>
+          <t xml:space="preserve">titleLoss.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E246" t="inlineStr" s="2">
@@ -8201,14 +8201,14 @@
       </c>
       <c r="F246" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しいわ…でも、いつか必ず戻ってくる</t>
+          <t xml:space="preserve">…覚えておきなさい。すぐに返してもらうわ</t>
         </is>
       </c>
     </row>
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.seductive.bold[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8218,12 +8218,12 @@
       </c>
       <c r="C247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.bold[2]</t>
+          <t xml:space="preserve">titleWin.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E247" t="inlineStr" s="2">
@@ -8233,14 +8233,14 @@
       </c>
       <c r="F247" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この借り、いつか返しに来るから</t>
+          <t xml:space="preserve">これが始まりよ。このベルトで時代を作る</t>
         </is>
       </c>
     </row>
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.seductive.bold[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8250,7 +8250,7 @@
       </c>
       <c r="C248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D248" t="inlineStr" s="12">
@@ -8265,14 +8265,14 @@
       </c>
       <c r="F248" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">レンタルでも全力よ。見ていてね</t>
+          <t xml:space="preserve">悔しいわ…でも、いつか必ず戻ってくる</t>
         </is>
       </c>
     </row>
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.seductive.bold[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8282,12 +8282,12 @@
       </c>
       <c r="C249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.bold[1]</t>
+          <t xml:space="preserve">seductive.bold[2]</t>
         </is>
       </c>
       <c r="E249" t="inlineStr" s="2">
@@ -8297,14 +8297,14 @@
       </c>
       <c r="F249" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…今日は認めるわ。でもこの借り、必ず返す</t>
+          <t xml:space="preserve">この借り、いつか返しに来るから</t>
         </is>
       </c>
     </row>
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.seductive.bold[1]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8314,7 +8314,7 @@
       </c>
       <c r="C250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D250" t="inlineStr" s="12">
@@ -8329,14 +8329,14 @@
       </c>
       <c r="F250" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ誰も私を超えられないわね。当然でしょう</t>
+          <t xml:space="preserve">レンタルでも全力よ。見ていてね</t>
         </is>
       </c>
     </row>
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.seductive.bold[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8346,7 +8346,7 @@
       </c>
       <c r="C251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D251" t="inlineStr" s="12">
@@ -8361,14 +8361,14 @@
       </c>
       <c r="F251" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…覚えておきなさい。すぐに返してもらうわ</t>
+          <t xml:space="preserve">…今日は認めるわ。でもこの借り、必ず返す</t>
         </is>
       </c>
     </row>
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.seductive.bold[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="C252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D252" t="inlineStr" s="12">
@@ -8393,14 +8393,14 @@
       </c>
       <c r="F252" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">これが始まりよ。このベルトで時代を作る</t>
+          <t xml:space="preserve">まだ誰も私を超えられないわね。当然でしょう</t>
         </is>
       </c>
     </row>
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.bold.seductive[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8410,29 +8410,29 @@
       </c>
       <c r="C253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.bold.seductive[1]</t>
+          <t xml:space="preserve">seductive.bold[1]</t>
         </is>
       </c>
       <c r="E253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F253" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">合わないわ。どうしても合わないの</t>
+          <t xml:space="preserve">…覚えておきなさい。すぐに返してもらうわ</t>
         </is>
       </c>
     </row>
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.bold.seductive[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8442,29 +8442,29 @@
       </c>
       <c r="C254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.bold.seductive[2]</t>
+          <t xml:space="preserve">seductive.bold[1]</t>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F254" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">これ以上は無理ね。それだけよ</t>
+          <t xml:space="preserve">これが始まりよ。このベルトで時代を作る</t>
         </is>
       </c>
     </row>
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.bold.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8479,7 +8479,7 @@
       </c>
       <c r="D255" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.bold.seductive[1]</t>
+          <t xml:space="preserve">bond_39_down.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E255" t="inlineStr" s="2">
@@ -8489,14 +8489,14 @@
       </c>
       <c r="F255" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">壁を作ってない？ 気に入らないわ</t>
+          <t xml:space="preserve">合わないわ。どうしても合わないの</t>
         </is>
       </c>
     </row>
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.bold.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.bold.seductive[2]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="D256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.bold.seductive[2]</t>
+          <t xml:space="preserve">bond_39_down.bold.seductive[2]</t>
         </is>
       </c>
       <c r="E256" t="inlineStr" s="2">
@@ -8521,14 +8521,14 @@
       </c>
       <c r="F256" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">前はもっと話してくれたのに。…どうしたのかしら</t>
+          <t xml:space="preserve">これ以上は無理ね。それだけよ</t>
         </is>
       </c>
     </row>
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.bold.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8543,7 +8543,7 @@
       </c>
       <c r="D257" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.bold.seductive[1]</t>
+          <t xml:space="preserve">bond_59_down.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E257" t="inlineStr" s="2">
@@ -8553,14 +8553,14 @@
       </c>
       <c r="F257" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">気に入ったわ。なかなか味のある人ね</t>
+          <t xml:space="preserve">壁を作ってない？ 気に入らないわ</t>
         </is>
       </c>
     </row>
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.bold.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.bold.seductive[2]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8575,7 +8575,7 @@
       </c>
       <c r="D258" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.bold.seductive[1]</t>
+          <t xml:space="preserve">bond_59_down.bold.seductive[2]</t>
         </is>
       </c>
       <c r="E258" t="inlineStr" s="2">
@@ -8585,14 +8585,14 @@
       </c>
       <c r="F258" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高のコンビネーションよ、私たち</t>
+          <t xml:space="preserve">前はもっと話してくれたのに。…どうしたのかしら</t>
         </is>
       </c>
     </row>
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.bold.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8607,7 +8607,7 @@
       </c>
       <c r="D259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.bold.seductive[1]</t>
+          <t xml:space="preserve">bond_60_up.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E259" t="inlineStr" s="2">
@@ -8617,14 +8617,14 @@
       </c>
       <c r="F259" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……もう終わったことよ</t>
+          <t xml:space="preserve">気に入ったわ。なかなか味のある人ね</t>
         </is>
       </c>
     </row>
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.bold.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8639,7 +8639,7 @@
       </c>
       <c r="D260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.bold.seductive[2]</t>
+          <t xml:space="preserve">bond_80_up.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E260" t="inlineStr" s="2">
@@ -8649,14 +8649,14 @@
       </c>
       <c r="F260" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決着はついたわ。次に進むの</t>
+          <t xml:space="preserve">最高のコンビネーションよ、私たち</t>
         </is>
       </c>
     </row>
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.bold.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8671,7 +8671,7 @@
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.bold.seductive[1]</t>
+          <t xml:space="preserve">rivalry_29_down.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
@@ -8681,14 +8681,14 @@
       </c>
       <c r="F261" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">なかなかの逸材ね。ふふ、楽しみ</t>
+          <t xml:space="preserve">……もう終わったことよ</t>
         </is>
       </c>
     </row>
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.bold.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.bold.seductive[2]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8703,7 +8703,7 @@
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.bold.seductive[1]</t>
+          <t xml:space="preserve">rivalry_29_down.bold.seductive[2]</t>
         </is>
       </c>
       <c r="E262" t="inlineStr" s="2">
@@ -8713,14 +8713,14 @@
       </c>
       <c r="F262" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全力を出せる相手。最高の敵ね、ふふ</t>
+          <t xml:space="preserve">決着はついたわ。次に進むの</t>
         </is>
       </c>
     </row>
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.bold.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8735,7 +8735,7 @@
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.bold.seductive[2]</t>
+          <t xml:space="preserve">rivalry_30_up.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E263" t="inlineStr" s="2">
@@ -8745,14 +8745,14 @@
       </c>
       <c r="F263" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">超える。それが今の私の全てよ</t>
+          <t xml:space="preserve">なかなかの逸材ね。ふふ、楽しみ</t>
         </is>
       </c>
     </row>
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.bold.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8767,7 +8767,7 @@
       </c>
       <c r="D264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.bold.seductive[1]</t>
+          <t xml:space="preserve">rivalry_50_up.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E264" t="inlineStr" s="2">
@@ -8777,14 +8777,14 @@
       </c>
       <c r="F264" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの人がいたから強くなれたの。感謝してる…でも負けないわ</t>
+          <t xml:space="preserve">全力を出せる相手。最高の敵ね、ふふ</t>
         </is>
       </c>
     </row>
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.bold.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.bold.seductive[2]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8799,7 +8799,7 @@
       </c>
       <c r="D265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.bold.seductive[2]</t>
+          <t xml:space="preserve">rivalry_50_up.bold.seductive[2]</t>
         </is>
       </c>
       <c r="E265" t="inlineStr" s="2">
@@ -8809,14 +8809,14 @@
       </c>
       <c r="F265" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この戦いに終わりはない。…望むところね</t>
+          <t xml:space="preserve">超える。それが今の私の全てよ</t>
         </is>
       </c>
     </row>
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.bold.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="D266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.bold.seductive[1]</t>
+          <t xml:space="preserve">rivalry_70_up.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E266" t="inlineStr" s="2">
@@ -8841,14 +8841,14 @@
       </c>
       <c r="F266" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここが最高の場所。私がもっと強くしてみせるわ</t>
+          <t xml:space="preserve">あの人がいたから強くなれたの。感謝してる…でも負けないわ</t>
         </is>
       </c>
     </row>
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.bold.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.bold.seductive[2]</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -8863,7 +8863,7 @@
       </c>
       <c r="D267" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.bold.seductive[2]</t>
+          <t xml:space="preserve">rivalry_70_up.bold.seductive[2]</t>
         </is>
       </c>
       <c r="E267" t="inlineStr" s="2">
@@ -8873,14 +8873,14 @@
       </c>
       <c r="F267" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この団体を背負っていく覚悟はできてるの</t>
+          <t xml:space="preserve">この戦いに終わりはない。…望むところね</t>
         </is>
       </c>
     </row>
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.bold.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -8895,7 +8895,7 @@
       </c>
       <c r="D268" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.bold.seductive[1]</t>
+          <t xml:space="preserve">trust_above_75.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E268" t="inlineStr" s="2">
@@ -8905,14 +8905,14 @@
       </c>
       <c r="F268" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふざけないで。私の価値がわからないなら、もう付き合いきれないわ</t>
+          <t xml:space="preserve">ここが最高の場所。私がもっと強くしてみせるわ</t>
         </is>
       </c>
     </row>
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.bold.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.bold.seductive[2]</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -8927,7 +8927,7 @@
       </c>
       <c r="D269" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.bold.seductive[2]</t>
+          <t xml:space="preserve">trust_above_75.bold.seductive[2]</t>
         </is>
       </c>
       <c r="E269" t="inlineStr" s="2">
@@ -8937,14 +8937,14 @@
       </c>
       <c r="F269" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この扱い、許すつもりはないの。忘れないことね</t>
+          <t xml:space="preserve">この団体を背負っていく覚悟はできてるの</t>
         </is>
       </c>
     </row>
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.bold.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -8959,7 +8959,7 @@
       </c>
       <c r="D270" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.bold.seductive[1]</t>
+          <t xml:space="preserve">trust_below_20.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E270" t="inlineStr" s="2">
@@ -8969,14 +8969,14 @@
       </c>
       <c r="F270" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この扱いは何かしら。私の実力、わかってるの？</t>
+          <t xml:space="preserve">ふざけないで。私の価値がわからないなら、もう付き合いきれないわ</t>
         </is>
       </c>
     </row>
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.bold.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.bold.seductive[2]</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -8991,7 +8991,7 @@
       </c>
       <c r="D271" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.bold.seductive[2]</t>
+          <t xml:space="preserve">trust_below_20.bold.seductive[2]</t>
         </is>
       </c>
       <c r="E271" t="inlineStr" s="2">
@@ -9001,14 +9001,14 @@
       </c>
       <c r="F271" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここにいていいのか…考え直す時期かもね</t>
+          <t xml:space="preserve">この扱い、許すつもりはないの。忘れないことね</t>
         </is>
       </c>
     </row>
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.seductive.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -9018,12 +9018,12 @@
       </c>
       <c r="C272" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D272" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.bold[1]</t>
+          <t xml:space="preserve">trust_below_35.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E272" t="inlineStr" s="2">
@@ -9033,14 +9033,14 @@
       </c>
       <c r="F272" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、あの輝きは一時的だったみたいね。でもいい夢だったわ</t>
+          <t xml:space="preserve">この扱いは何かしら。私の実力、わかってるの？</t>
         </is>
       </c>
     </row>
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.seductive.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.bold.seductive[2]</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -9050,29 +9050,29 @@
       </c>
       <c r="C273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.seductive.bold[1]</t>
+          <t xml:space="preserve">trust_below_35.bold.seductive[2]</t>
         </is>
       </c>
       <c r="E273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F273" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">満身創痍の私、悪くないでしょ? この傷ごと、最後を飾るわ</t>
+          <t xml:space="preserve">ここにいていいのか…考え直す時期かもね</t>
         </is>
       </c>
     </row>
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.seductive.bold[2]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -9082,29 +9082,29 @@
       </c>
       <c r="C274" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.seductive.bold[2]</t>
+          <t xml:space="preserve">seductive.bold[1]</t>
         </is>
       </c>
       <c r="E274" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F274" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで残ったんだもの。一番いいところ、見せてあげる</t>
+          <t xml:space="preserve">ふふ、あの輝きも一度きり……なんて言うと思った？すぐに取り戻してみせるわ。</t>
         </is>
       </c>
     </row>
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.seductive.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -9119,7 +9119,7 @@
       </c>
       <c r="D275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.seductive.bold[1]</t>
+          <t xml:space="preserve">preFinal.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E275" t="inlineStr" s="2">
@@ -9129,14 +9129,14 @@
       </c>
       <c r="F275" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">相手は誰? 何人来ても…最後まで残るのは、こっちよ</t>
+          <t xml:space="preserve">満身創痍の私、悪くないでしょ？ この傷ごと、最後を飾るわ</t>
         </is>
       </c>
     </row>
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.seductive.bold[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -9151,7 +9151,7 @@
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.seductive.bold[2]</t>
+          <t xml:space="preserve">preFinal.seductive.bold[2]</t>
         </is>
       </c>
       <c r="E276" t="inlineStr" s="2">
@@ -9161,14 +9161,14 @@
       </c>
       <c r="F276" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もっと骨のあるのを出してきて。全部相手にしてあげる</t>
+          <t xml:space="preserve">ここまで残ったんだもの。一番いいところ、見せてあげる</t>
         </is>
       </c>
     </row>
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.seductive.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -9183,7 +9183,7 @@
       </c>
       <c r="D277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.seductive.bold[1]</t>
+          <t xml:space="preserve">preMatch.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E277" t="inlineStr" s="2">
@@ -9193,14 +9193,14 @@
       </c>
       <c r="F277" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人、落としたわ。…でも、まだ足りないの。次、早く出してよ</t>
+          <t xml:space="preserve">相手は誰？ 何人来ても…最後まで残るのは、こっちよ</t>
         </is>
       </c>
     </row>
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.seductive.bold[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -9215,7 +9215,7 @@
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.seductive.bold[2]</t>
+          <t xml:space="preserve">preMatch.seductive.bold[2]</t>
         </is>
       </c>
       <c r="E278" t="inlineStr" s="2">
@@ -9225,14 +9225,14 @@
       </c>
       <c r="F278" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ立ってるの、見える? 次の子、こっちにいらっしゃい。全部相手にしてあげる</t>
+          <t xml:space="preserve">もっと骨のあるのを出してきて。全部相手にしてあげる</t>
         </is>
       </c>
     </row>
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.seductive.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="C279" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.seductive.bold[1]</t>
+          <t xml:space="preserve">survivor.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E279" t="inlineStr" s="2">
@@ -9257,14 +9257,14 @@
       </c>
       <c r="F279" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この三人が最強だった。美しい勝利でしょ？</t>
+          <t xml:space="preserve">一人、落としたわ。…でも、まだ足りないの。次、早く出してよ</t>
         </is>
       </c>
     </row>
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.seductive.bold[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -9274,12 +9274,12 @@
       </c>
       <c r="C280" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D280" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.seductive.bold[2]</t>
+          <t xml:space="preserve">survivor.seductive.bold[2]</t>
         </is>
       </c>
       <c r="E280" t="inlineStr" s="2">
@@ -9289,14 +9289,14 @@
       </c>
       <c r="F280" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仲間が繋いでくれた勝ちを、最後に飾ったの。良いチームだったわ</t>
+          <t xml:space="preserve">まだ立ってるの、見える？ 次の子、こっちにいらっしゃい。全部相手にしてあげる</t>
         </is>
       </c>
     </row>
     <row r="281" ht="40" customHeight="1">
       <c r="A281" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.seductive.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -9311,7 +9311,7 @@
       </c>
       <c r="D281" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.seductive.bold[1]</t>
+          <t xml:space="preserve">champion.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E281" t="inlineStr" s="2">
@@ -9321,14 +9321,14 @@
       </c>
       <c r="F281" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">賞はもらっておくわ。でも次は……もっと大きなものを奪いに行くから</t>
+          <t xml:space="preserve">この三人が最強だった。美しい勝利でしょ？</t>
         </is>
       </c>
     </row>
     <row r="282" ht="40" customHeight="1">
       <c r="A282" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.seductive.bold[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -9343,7 +9343,7 @@
       </c>
       <c r="D282" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.seductive.bold[2]</t>
+          <t xml:space="preserve">champion.seductive.bold[2]</t>
         </is>
       </c>
       <c r="E282" t="inlineStr" s="2">
@@ -9353,14 +9353,14 @@
       </c>
       <c r="F282" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この程度じゃ満たされない。次は全部、こっちのものにするわ</t>
+          <t xml:space="preserve">仲間が繋いでくれた勝ちを、最後に飾ったの。良いチームだったわ</t>
         </is>
       </c>
     </row>
     <row r="283" ht="40" customHeight="1">
       <c r="A283" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.seductive.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -9375,7 +9375,7 @@
       </c>
       <c r="D283" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.seductive.bold[1]</t>
+          <t xml:space="preserve">defiant.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E283" t="inlineStr" s="2">
@@ -9385,14 +9385,14 @@
       </c>
       <c r="F283" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何人でもいいわよ？ 最後にこの場所に立つのは、いつだって私だもの</t>
+          <t xml:space="preserve">賞はもらっておくわ。でも次は……もっと大きなものを奪いに行くから</t>
         </is>
       </c>
     </row>
     <row r="284" ht="40" customHeight="1">
       <c r="A284" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.seductive.bold[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -9407,7 +9407,7 @@
       </c>
       <c r="D284" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.seductive.bold[2]</t>
+          <t xml:space="preserve">defiant.seductive.bold[2]</t>
         </is>
       </c>
       <c r="E284" t="inlineStr" s="2">
@@ -9417,14 +9417,14 @@
       </c>
       <c r="F284" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全員倒してきたの。まだ物足りないくらい</t>
+          <t xml:space="preserve">この程度じゃ満たされない。次は全部、こっちのものにするわ</t>
         </is>
       </c>
     </row>
     <row r="285" ht="40" customHeight="1">
       <c r="A285" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.seductive.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
@@ -9434,12 +9434,12 @@
       </c>
       <c r="C285" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D285" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.seductive.bold[1]</t>
+          <t xml:space="preserve">gauntlet.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E285" t="inlineStr" s="2">
@@ -9449,14 +9449,14 @@
       </c>
       <c r="F285" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、優勝しちゃったわ。当然だけどね</t>
+          <t xml:space="preserve">何人でもいいわよ？ 最後にこの場所に立つのは、いつだって私だもの</t>
         </is>
       </c>
     </row>
     <row r="286" ht="40" customHeight="1">
       <c r="A286" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.seductive.bold[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
@@ -9466,12 +9466,12 @@
       </c>
       <c r="C286" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D286" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.seductive.bold[2]</t>
+          <t xml:space="preserve">gauntlet.seductive.bold[2]</t>
         </is>
       </c>
       <c r="E286" t="inlineStr" s="2">
@@ -9481,14 +9481,14 @@
       </c>
       <c r="F286" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたしが一番。それが証明されたわね</t>
+          <t xml:space="preserve">全員倒してきたの。まだ物足りないくらい</t>
         </is>
       </c>
     </row>
     <row r="287" ht="40" customHeight="1">
       <c r="A287" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.seductive.bold[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
@@ -9503,7 +9503,7 @@
       </c>
       <c r="D287" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.seductive.bold[1]</t>
+          <t xml:space="preserve">champion.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E287" t="inlineStr" s="2">
@@ -9513,14 +9513,14 @@
       </c>
       <c r="F287" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悔しいわ。でも、わたしはここで終わらない</t>
+          <t xml:space="preserve">あら、優勝しちゃったわ。当然だけどね</t>
         </is>
       </c>
     </row>
     <row r="288" ht="40" customHeight="1">
       <c r="A288" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.seductive.bold[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
@@ -9535,7 +9535,7 @@
       </c>
       <c r="D288" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.seductive.bold[2]</t>
+          <t xml:space="preserve">champion.seductive.bold[2]</t>
         </is>
       </c>
       <c r="E288" t="inlineStr" s="2">
@@ -9545,14 +9545,14 @@
       </c>
       <c r="F288" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次は必ず勝つわ</t>
+          <t xml:space="preserve">私が一番。それが証明されたわね</t>
         </is>
       </c>
     </row>
     <row r="289" ht="40" customHeight="1">
       <c r="A289" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.seductive.bold[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
@@ -9567,7 +9567,7 @@
       </c>
       <c r="D289" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.seductive.bold[1]</t>
+          <t xml:space="preserve">postLose.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E289" t="inlineStr" s="2">
@@ -9577,14 +9577,14 @@
       </c>
       <c r="F289" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、もう終わり？ 物足りないわね</t>
+          <t xml:space="preserve">…悔しいわ。でも、私はここで終わらない</t>
         </is>
       </c>
     </row>
     <row r="290" ht="40" customHeight="1">
       <c r="A290" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.seductive.bold[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="2">
@@ -9599,7 +9599,7 @@
       </c>
       <c r="D290" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.seductive.bold[2]</t>
+          <t xml:space="preserve">postLose.seductive.bold[2]</t>
         </is>
       </c>
       <c r="E290" t="inlineStr" s="2">
@@ -9609,14 +9609,14 @@
       </c>
       <c r="F290" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、予定通りよ。次の相手が楽しみ</t>
+          <t xml:space="preserve">次は必ず勝つわ</t>
         </is>
       </c>
     </row>
     <row r="291" ht="40" customHeight="1">
       <c r="A291" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.seductive.bold[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="2">
@@ -9631,7 +9631,7 @@
       </c>
       <c r="D291" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.seductive.bold[1]</t>
+          <t xml:space="preserve">postMatchWin.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E291" t="inlineStr" s="2">
@@ -9641,14 +9641,14 @@
       </c>
       <c r="F291" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ足りないわね。もっと上に行くわ</t>
+          <t xml:space="preserve">あら、もう終わり？ 物足りないわね</t>
         </is>
       </c>
     </row>
     <row r="292" ht="40" customHeight="1">
       <c r="A292" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.seductive.bold[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="2">
@@ -9663,7 +9663,7 @@
       </c>
       <c r="D292" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.seductive.bold[2]</t>
+          <t xml:space="preserve">postMatchWin.seductive.bold[2]</t>
         </is>
       </c>
       <c r="E292" t="inlineStr" s="2">
@@ -9673,14 +9673,14 @@
       </c>
       <c r="F292" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい舞台だったわ。でも、わたしはもっと上を目指す</t>
+          <t xml:space="preserve">ふふ、予定通りよ。次の相手が楽しみ</t>
         </is>
       </c>
     </row>
     <row r="293" ht="40" customHeight="1">
       <c r="A293" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.seductive.bold[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="2">
@@ -9695,7 +9695,7 @@
       </c>
       <c r="D293" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.seductive.bold[1]</t>
+          <t xml:space="preserve">postWin.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E293" t="inlineStr" s="2">
@@ -9705,14 +9705,14 @@
       </c>
       <c r="F293" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、最後のお相手ね。たっぷり楽しませてあげるわ</t>
+          <t xml:space="preserve">まだ足りないわね。もっと上に行くわ</t>
         </is>
       </c>
     </row>
     <row r="294" ht="40" customHeight="1">
       <c r="A294" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.seductive.bold[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B294" t="inlineStr" s="2">
@@ -9727,7 +9727,7 @@
       </c>
       <c r="D294" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.seductive.bold[2]</t>
+          <t xml:space="preserve">postWin.seductive.bold[2]</t>
         </is>
       </c>
       <c r="E294" t="inlineStr" s="2">
@@ -9737,14 +9737,14 @@
       </c>
       <c r="F294" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">優勝はわたしのもの。決まっていることよ</t>
+          <t xml:space="preserve">いい舞台だったわ。でも、私はもっと上を目指す</t>
         </is>
       </c>
     </row>
     <row r="295" ht="40" customHeight="1">
       <c r="A295" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.seductive.bold[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B295" t="inlineStr" s="2">
@@ -9759,7 +9759,7 @@
       </c>
       <c r="D295" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.seductive.bold[1]</t>
+          <t xml:space="preserve">preFinal.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E295" t="inlineStr" s="2">
@@ -9769,14 +9769,14 @@
       </c>
       <c r="F295" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、可愛い相手ね。すぐ終わらせてあげるわ</t>
+          <t xml:space="preserve">あら、最後のお相手ね。たっぷり楽しませてあげるわ</t>
         </is>
       </c>
     </row>
     <row r="296" ht="40" customHeight="1">
       <c r="A296" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.seductive.bold[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B296" t="inlineStr" s="2">
@@ -9791,7 +9791,7 @@
       </c>
       <c r="D296" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.seductive.bold[2]</t>
+          <t xml:space="preserve">preFinal.seductive.bold[2]</t>
         </is>
       </c>
       <c r="E296" t="inlineStr" s="2">
@@ -9801,14 +9801,14 @@
       </c>
       <c r="F296" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたしに勝てるつもり？ 甘いわね</t>
+          <t xml:space="preserve">優勝は私のもの。決まっていることよ</t>
         </is>
       </c>
     </row>
     <row r="297" ht="40" customHeight="1">
       <c r="A297" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.seductive.bold[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B297" t="inlineStr" s="2">
@@ -9823,7 +9823,7 @@
       </c>
       <c r="D297" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.seductive.bold[1]</t>
+          <t xml:space="preserve">preMatch.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E297" t="inlineStr" s="2">
@@ -9833,14 +9833,14 @@
       </c>
       <c r="F297" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、指名してくれたの？ 嬉しいわ</t>
+          <t xml:space="preserve">あら、可愛い相手ね。すぐ終わらせてあげるわ</t>
         </is>
       </c>
     </row>
     <row r="298" ht="40" customHeight="1">
       <c r="A298" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.seductive.bold[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B298" t="inlineStr" s="2">
@@ -9855,7 +9855,7 @@
       </c>
       <c r="D298" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.seductive.bold[2]</t>
+          <t xml:space="preserve">preMatch.seductive.bold[2]</t>
         </is>
       </c>
       <c r="E298" t="inlineStr" s="2">
@@ -9865,14 +9865,14 @@
       </c>
       <c r="F298" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたしの舞台が増えるのね。楽しみ</t>
+          <t xml:space="preserve">私に勝てるつもり？ 甘いわね</t>
         </is>
       </c>
     </row>
     <row r="299" ht="40" customHeight="1">
       <c r="A299" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.seductive.bold[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B299" t="inlineStr" s="2">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="C299" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D299" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.bold[1]</t>
+          <t xml:space="preserve">summon.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E299" t="inlineStr" s="2">
@@ -9897,14 +9897,14 @@
       </c>
       <c r="F299" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">容赦しないわよ。覚悟してね</t>
+          <t xml:space="preserve">あら、指名してくれたの？ 嬉しいわ</t>
         </is>
       </c>
     </row>
     <row r="300" ht="40" customHeight="1">
       <c r="A300" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.seductive.bold[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B300" t="inlineStr" s="2">
@@ -9914,12 +9914,12 @@
       </c>
       <c r="C300" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D300" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.bold[1]</t>
+          <t xml:space="preserve">summon.seductive.bold[2]</t>
         </is>
       </c>
       <c r="E300" t="inlineStr" s="2">
@@ -9929,14 +9929,14 @@
       </c>
       <c r="F300" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ずっと待ってたのよ、この瞬間を……!ふふ、最高の気分ね</t>
+          <t xml:space="preserve">私の舞台が増えるのね。楽しみ</t>
         </is>
       </c>
     </row>
     <row r="301" ht="40" customHeight="1">
       <c r="A301" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.seductive.bold[1]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B301" t="inlineStr" s="2">
@@ -9946,7 +9946,7 @@
       </c>
       <c r="C301" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D301" t="inlineStr" s="12">
@@ -9961,14 +9961,14 @@
       </c>
       <c r="F301" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら…随分と自信がおありのようね。壊してあげるわ</t>
+          <t xml:space="preserve">容赦しないわよ。覚悟してね</t>
         </is>
       </c>
     </row>
     <row r="302" ht="40" customHeight="1">
       <c r="A302" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.seductive.bold[2]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B302" t="inlineStr" s="2">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="C302" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D302" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.bold[2]</t>
+          <t xml:space="preserve">seductive.bold[1]</t>
         </is>
       </c>
       <c r="E302" t="inlineStr" s="2">
@@ -9993,14 +9993,14 @@
       </c>
       <c r="F302" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">可哀想だけど…手加減はしないわよ</t>
+          <t xml:space="preserve">ずっと待ってたのよ、この瞬間を……！ふふ、最高の気分ね</t>
         </is>
       </c>
     </row>
     <row r="303" ht="40" customHeight="1">
       <c r="A303" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.seductive.bold[1]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B303" t="inlineStr" s="2">
@@ -10010,7 +10010,7 @@
       </c>
       <c r="C303" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D303" t="inlineStr" s="12">
@@ -10025,14 +10025,14 @@
       </c>
       <c r="F303" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、残念。もっと遊びたかったのに</t>
+          <t xml:space="preserve">あら…随分と自信がおありのようね。壊してあげるわ</t>
         </is>
       </c>
     </row>
     <row r="304" ht="40" customHeight="1">
       <c r="A304" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.seductive.bold[2]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B304" t="inlineStr" s="2">
@@ -10042,7 +10042,7 @@
       </c>
       <c r="C304" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D304" t="inlineStr" s="12">
@@ -10057,14 +10057,14 @@
       </c>
       <c r="F304" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">逃げちゃうの？ …つまらない団体ね</t>
+          <t xml:space="preserve">可哀想だけど…手加減はしないわよ</t>
         </is>
       </c>
     </row>
     <row r="305" ht="40" customHeight="1">
       <c r="A305" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.seductive.bold[1]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B305" t="inlineStr" s="2">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="C305" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D305" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.seductive.bold[1]</t>
+          <t xml:space="preserve">seductive.bold[1]</t>
         </is>
       </c>
       <c r="E305" t="inlineStr" s="2">
@@ -10089,14 +10089,14 @@
       </c>
       <c r="F305" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら…やられちゃったわ。……許さないけど</t>
+          <t xml:space="preserve">あら、残念。もっと遊びたかったのに</t>
         </is>
       </c>
     </row>
     <row r="306" ht="40" customHeight="1">
       <c r="A306" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.seductive.bold[2]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B306" t="inlineStr" s="2">
@@ -10106,12 +10106,12 @@
       </c>
       <c r="C306" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D306" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.seductive.bold[2]</t>
+          <t xml:space="preserve">seductive.bold[2]</t>
         </is>
       </c>
       <c r="E306" t="inlineStr" s="2">
@@ -10121,14 +10121,14 @@
       </c>
       <c r="F306" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日は譲ってあげるわ。次は…ないけどね</t>
+          <t xml:space="preserve">逃げちゃうの？ …つまらない団体ね</t>
         </is>
       </c>
     </row>
     <row r="307" ht="40" customHeight="1">
       <c r="A307" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.seductive.bold[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B307" t="inlineStr" s="2">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="D307" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.seductive.bold[1]</t>
+          <t xml:space="preserve">result_lose.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E307" t="inlineStr" s="2">
@@ -10153,14 +10153,14 @@
       </c>
       <c r="F307" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、もう終わり？ もっと楽しみたかったのに</t>
+          <t xml:space="preserve">あら…やられちゃったわ。……許さないけど</t>
         </is>
       </c>
     </row>
     <row r="308" ht="40" customHeight="1">
       <c r="A308" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.seductive.bold[2]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B308" t="inlineStr" s="2">
@@ -10175,7 +10175,7 @@
       </c>
       <c r="D308" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.seductive.bold[2]</t>
+          <t xml:space="preserve">result_lose.seductive.bold[2]</t>
         </is>
       </c>
       <c r="E308" t="inlineStr" s="2">
@@ -10185,14 +10185,14 @@
       </c>
       <c r="F308" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">予想通りの結果ね。つまらないわ</t>
+          <t xml:space="preserve">今日は譲ってあげるわ。次は…ないけどね</t>
         </is>
       </c>
     </row>
     <row r="309" ht="40" customHeight="1">
       <c r="A309" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.seductive.bold[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B309" t="inlineStr" s="2">
@@ -10202,12 +10202,12 @@
       </c>
       <c r="C309" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D309" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.bold[1]</t>
+          <t xml:space="preserve">result_win.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E309" t="inlineStr" s="2">
@@ -10217,14 +10217,14 @@
       </c>
       <c r="F309" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">当然よ。うちの団体を甘く見ないことね</t>
+          <t xml:space="preserve">あら、もう終わり？ もっと楽しみたかったのに</t>
         </is>
       </c>
     </row>
     <row r="310" ht="40" customHeight="1">
       <c r="A310" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.seductive.bold[2]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B310" t="inlineStr" s="2">
@@ -10234,12 +10234,12 @@
       </c>
       <c r="C310" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D310" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.bold[2]</t>
+          <t xml:space="preserve">result_win.seductive.bold[2]</t>
         </is>
       </c>
       <c r="E310" t="inlineStr" s="2">
@@ -10249,14 +10249,14 @@
       </c>
       <c r="F310" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ物足りないわね。もっと強い相手はいないの？</t>
+          <t xml:space="preserve">予想通りの結果ね。つまらないわ</t>
         </is>
       </c>
     </row>
     <row r="311" ht="40" customHeight="1">
       <c r="A311" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.seductive.bold[3]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B311" t="inlineStr" s="2">
@@ -10271,7 +10271,7 @@
       </c>
       <c r="D311" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.bold[3]</t>
+          <t xml:space="preserve">seductive.bold[1]</t>
         </is>
       </c>
       <c r="E311" t="inlineStr" s="2">
@@ -10281,14 +10281,14 @@
       </c>
       <c r="F311" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">当然の結果よ。うちを甘く見ないことね</t>
+          <t xml:space="preserve">当然よ。うちの団体を甘く見ないことね</t>
         </is>
       </c>
     </row>
     <row r="312" ht="40" customHeight="1">
       <c r="A312" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.seductive.bold[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B312" t="inlineStr" s="2">
@@ -10298,29 +10298,29 @@
       </c>
       <c r="C312" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D312" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.seductive.bold[1]</t>
+          <t xml:space="preserve">seductive.bold[2]</t>
         </is>
       </c>
       <c r="E312" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F312" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頂点に立ったわ。でもまだ先があるみたいね</t>
+          <t xml:space="preserve">まだ物足りないわね。もっと強い相手はいないの？</t>
         </is>
       </c>
     </row>
     <row r="313" ht="40" customHeight="1">
       <c r="A313" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.seductive.bold[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.seductive.bold[3]</t>
         </is>
       </c>
       <c r="B313" t="inlineStr" s="2">
@@ -10330,59 +10330,123 @@
       </c>
       <c r="C313" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D313" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.bold[1]</t>
+          <t xml:space="preserve">seductive.bold[3]</t>
         </is>
       </c>
       <c r="E313" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F313" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">拾った目利きは正解よ。…すぐに分かるわ</t>
+          <t xml:space="preserve">当然の結果よ。うちを甘く見ないことね</t>
         </is>
       </c>
     </row>
     <row r="314" ht="40" customHeight="1">
       <c r="A314" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">ENDING_LINES.fighter.seductive.bold[1]</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ENDING_LINES</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">fighter.seductive.bold[1]</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">頂点に立ったわ。でもまだ先があるみたいね</t>
+        </is>
+      </c>
+    </row>
+    <row r="315" ht="40" customHeight="1">
+      <c r="A315" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.seductive.bold[1]</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">seductive.bold[1]</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">拾った目利きは正解よ。…すぐに分かるわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="316" ht="40" customHeight="1">
+      <c r="A316" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES.seductive.bold[1]</t>
         </is>
       </c>
-      <c r="B314" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C314" t="inlineStr" s="2">
+      <c r="B316" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
-      <c r="D314" t="inlineStr" s="12">
+      <c r="D316" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">seductive.bold[1]</t>
         </is>
       </c>
-      <c r="E314" t="inlineStr" s="2">
+      <c r="E316" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
-      <c r="F314" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">わたしに声をかけた責任は、取ってちょうだいね</t>
+      <c r="F316" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">私に声をかけた責任は、取ってちょうだいね</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H314"/>
+  <autoFilter ref="A1:H316"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/蠱惑×強気.xlsx
+++ b/セリフ編集/キャラタイプ別/蠱惑×強気.xlsx
@@ -306,7 +306,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H316"/>
+  <dimension ref="A1:H323"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -3788,7 +3788,7 @@
     <row r="109" ht="40" customHeight="1">
       <c r="A109" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.seductive.bold[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_accept.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B109" t="inlineStr" s="2">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="D109" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_accept.seductive.bold[1]</t>
+          <t xml:space="preserve">decline_accept.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E109" t="inlineStr" s="2">
@@ -3813,14 +3813,14 @@
       </c>
       <c r="F109" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、分かってくれるじゃない 期待しててね。</t>
+          <t xml:space="preserve">決まりね。……この額で残る意味、あなたにも分からせてあげる。</t>
         </is>
       </c>
     </row>
     <row r="110" ht="40" customHeight="1">
       <c r="A110" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.seductive.bold[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_hold.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B110" t="inlineStr" s="2">
@@ -3835,7 +3835,7 @@
       </c>
       <c r="D110" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_accept.seductive.bold[1]</t>
+          <t xml:space="preserve">decline_hold.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E110" t="inlineStr" s="2">
@@ -3845,14 +3845,14 @@
       </c>
       <c r="F110" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……まあ、少しは考えてくれたのね。次はもっと期待してるわよ</t>
+          <t xml:space="preserve">……下げないですって？　……ずるいわね、そのやり方。借りたままじゃ、いられなくなる。</t>
         </is>
       </c>
     </row>
     <row r="111" ht="40" customHeight="1">
       <c r="A111" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.seductive.bold[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_open.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B111" t="inlineStr" s="2">
@@ -3867,7 +3867,7 @@
       </c>
       <c r="D111" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_refuse.seductive.bold[1]</t>
+          <t xml:space="preserve">decline_open.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E111" t="inlineStr" s="2">
@@ -3877,14 +3877,14 @@
       </c>
       <c r="F111" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ふうん。まあいいわ。でもね、次はないからね？</t>
+          <t xml:space="preserve">下がるのね。……その分は預けておくわ。取り返しに来るから、そのつもりで。</t>
         </is>
       </c>
     </row>
     <row r="112" ht="40" customHeight="1">
       <c r="A112" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.seductive.bold[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_strict.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B112" t="inlineStr" s="2">
@@ -3899,7 +3899,7 @@
       </c>
       <c r="D112" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.seductive.bold[1]</t>
+          <t xml:space="preserve">decline_strict.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E112" t="inlineStr" s="2">
@@ -3909,14 +3909,14 @@
       </c>
       <c r="F112" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ねえ社長。{tenure}もうちょっと私のこと大事にしてくれてもいいんじゃない？ {record}</t>
+          <t xml:space="preserve">……全部きっちり、ね。……いいわ。この冷たさ、そっくり返すから。</t>
         </is>
       </c>
     </row>
     <row r="113" ht="40" customHeight="1">
       <c r="A113" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.seductive.bold[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_voluntary_accept.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B113" t="inlineStr" s="2">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="D113" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_refuse.seductive.bold[1]</t>
+          <t xml:space="preserve">decline_voluntary_accept.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E113" t="inlineStr" s="2">
@@ -3941,14 +3941,14 @@
       </c>
       <c r="F113" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ふうん。まあいいけど、我慢にも限度があるからね？</t>
+          <t xml:space="preserve">潔くていいわね、あなたも。……安く見られたままでいる気はないけれど、今年はね。</t>
         </is>
       </c>
     </row>
     <row r="114" ht="40" customHeight="1">
       <c r="A114" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.seductive.bold[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_voluntary_hold.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B114" t="inlineStr" s="2">
@@ -3963,7 +3963,7 @@
       </c>
       <c r="D114" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.seductive.bold[1]</t>
+          <t xml:space="preserve">decline_voluntary_hold.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E114" t="inlineStr" s="2">
@@ -3973,14 +3973,14 @@
       </c>
       <c r="F114" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、もう無理よ。お世話になりました……って言いたいところだけど、正直そんな気にもなれないの。</t>
+          <t xml:space="preserve">……聞いてなかったの？　下げていいと言ったのに。……なら、見合う女に戻るだけ。</t>
         </is>
       </c>
     </row>
     <row r="115" ht="40" customHeight="1">
       <c r="A115" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.seductive.bold[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_voluntary_open.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B115" t="inlineStr" s="2">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="D115" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.seductive.bold[2]</t>
+          <t xml:space="preserve">decline_voluntary_open.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E115" t="inlineStr" s="2">
@@ -4005,14 +4005,14 @@
       </c>
       <c r="F115" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう決めたの。これ以上ここにいる理由がないもの。……じゃあね。</t>
+          <t xml:space="preserve">言っておくわ。今の私に、去年の値はつかない。……下げなさい。恥はかきたくないの。</t>
         </is>
       </c>
     </row>
     <row r="116" ht="40" customHeight="1">
       <c r="A116" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.seductive.bold[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B116" t="inlineStr" s="2">
@@ -4027,7 +4027,7 @@
       </c>
       <c r="D116" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_listen.seductive.bold[1]</t>
+          <t xml:space="preserve">raise_accept.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E116" t="inlineStr" s="2">
@@ -4037,14 +4037,14 @@
       </c>
       <c r="F116" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……聞いてくれるの。{record}正直ね、もっと大きな舞台が見たいの。</t>
+          <t xml:space="preserve">ふふ、分かってくれるじゃない 期待しててね。</t>
         </is>
       </c>
     </row>
     <row r="117" ht="40" customHeight="1">
       <c r="A117" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.seductive.bold[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B117" t="inlineStr" s="2">
@@ -4059,7 +4059,7 @@
       </c>
       <c r="D117" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.seductive.bold[1]</t>
+          <t xml:space="preserve">raise_negotiate_accept.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E117" t="inlineStr" s="2">
@@ -4069,14 +4069,14 @@
       </c>
       <c r="F117" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長。{tenure}もう決めたの。…ここを出るわ。</t>
+          <t xml:space="preserve">……まあ、少しは考えてくれたのね。次はもっと期待してるわよ</t>
         </is>
       </c>
     </row>
     <row r="118" ht="40" customHeight="1">
       <c r="A118" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.seductive.bold[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B118" t="inlineStr" s="2">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="D118" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_release.seductive.bold[1]</t>
+          <t xml:space="preserve">raise_negotiate_refuse.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E118" t="inlineStr" s="2">
@@ -4101,14 +4101,14 @@
       </c>
       <c r="F118" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ふふ、予想通りね。{rivalry}じゃあね、社長。</t>
+          <t xml:space="preserve">……ふうん。まあいいわ。でもね、次はないからね？</t>
         </is>
       </c>
     </row>
     <row r="119" ht="40" customHeight="1">
       <c r="A119" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.seductive.bold[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B119" t="inlineStr" s="2">
@@ -4123,7 +4123,7 @@
       </c>
       <c r="D119" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_fail.seductive.bold[1]</t>
+          <t xml:space="preserve">raise_open.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E119" t="inlineStr" s="2">
@@ -4133,14 +4133,14 @@
       </c>
       <c r="F119" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……悪いけど、もう決めたの。…引き止めても無駄よ。</t>
+          <t xml:space="preserve">ねえ社長。{tenure}もうちょっと私のこと大事にしてくれてもいいんじゃない？ {record}</t>
         </is>
       </c>
     </row>
     <row r="120" ht="40" customHeight="1">
       <c r="A120" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.seductive.bold[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B120" t="inlineStr" s="2">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="D120" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_success.seductive.bold[1]</t>
+          <t xml:space="preserve">raise_refuse.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E120" t="inlineStr" s="2">
@@ -4165,370 +4165,370 @@
       </c>
       <c r="F120" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……仕方ないわね。そこまで言うなら、もう少しだけ付き合ってあげる。</t>
+          <t xml:space="preserve">……ふうん。まあいいけど、我慢にも限度があるからね？</t>
         </is>
       </c>
     </row>
     <row r="121" ht="40" customHeight="1">
       <c r="A121" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.seductive.bold[1]</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">sudden_departure.seductive.bold[1]</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">社長、もう無理よ。お世話になりました……って言いたいところだけど、正直そんな気にもなれないの。</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="40" customHeight="1">
+      <c r="A122" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.seductive.bold[2]</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">sudden_departure.seductive.bold[2]</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">もう決めたの。これ以上ここにいる理由がないもの。……じゃあね。</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="40" customHeight="1">
+      <c r="A123" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.seductive.bold[1]</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_listen.seductive.bold[1]</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……聞いてくれるの。{record}正直ね、もっと大きな舞台が見たいの。</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="40" customHeight="1">
+      <c r="A124" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.seductive.bold[1]</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_open.seductive.bold[1]</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">社長。{tenure}もう決めたの。…ここを出るわ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="40" customHeight="1">
+      <c r="A125" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.seductive.bold[1]</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_release.seductive.bold[1]</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……ふふ、予想通りね。{rivalry}じゃあね、社長。</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="40" customHeight="1">
+      <c r="A126" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.seductive.bold[1]</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_retain_fail.seductive.bold[1]</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……悪いけど、もう決めたの。…引き止めても無駄よ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="40" customHeight="1">
+      <c r="A127" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.seductive.bold[1]</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_retain_success.seductive.bold[1]</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……仕方ないわね。そこまで言うなら、もう少しだけ付き合ってあげる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="40" customHeight="1">
+      <c r="A128" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">NEGOTIATE_LINES.blocked.seductive.bold[1]</t>
         </is>
       </c>
-      <c r="B121" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr" s="2">
+      <c r="B128" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr" s="12">
+      <c r="D128" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">blocked.seductive.bold[1]</t>
         </is>
       </c>
-      <c r="E121" t="inlineStr" s="2">
+      <c r="E128" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F121" t="inlineStr" s="3">
+      <c r="F128" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">ふふ…買いかぶってくれてありがとう。
 でも今の仲間を裏切るつもりは毛頭ないわ</t>
         </is>
       </c>
     </row>
-    <row r="122" ht="40" customHeight="1">
-      <c r="A122" t="inlineStr" s="15">
+    <row r="129" ht="40" customHeight="1">
+      <c r="A129" t="inlineStr" s="15">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES.fail.seductive.bold[1]</t>
         </is>
       </c>
-      <c r="B122" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr" s="2">
+      <c r="B129" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr" s="12">
+      <c r="D129" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">fail.seductive.bold[1]</t>
         </is>
       </c>
-      <c r="E122" t="inlineStr" s="2">
+      <c r="E129" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F122" t="inlineStr" s="3">
+      <c r="F129" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">ここが私の居場所なの。
 出直してきて</t>
         </is>
       </c>
     </row>
-    <row r="123" ht="40" customHeight="1">
-      <c r="A123" t="inlineStr" s="15">
+    <row r="130" ht="40" customHeight="1">
+      <c r="A130" t="inlineStr" s="15">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES.start.seductive.bold[1]</t>
         </is>
       </c>
-      <c r="B123" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr" s="2">
+      <c r="B130" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr" s="12">
+      <c r="D130" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">start.seductive.bold[1]</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr" s="2">
+      <c r="E130" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F123" t="inlineStr" s="3">
+      <c r="F130" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">私を引き抜こうだなんて…
 ふふ、面白い度胸してるわね</t>
         </is>
       </c>
     </row>
-    <row r="124" ht="40" customHeight="1">
-      <c r="A124" t="inlineStr" s="15">
+    <row r="131" ht="40" customHeight="1">
+      <c r="A131" t="inlineStr" s="15">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES.success.seductive.bold[1]</t>
         </is>
       </c>
-      <c r="B124" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr" s="2">
+      <c r="B131" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr" s="12">
+      <c r="D131" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">success.seductive.bold[1]</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr" s="2">
+      <c r="E131" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F124" t="inlineStr" s="3">
+      <c r="F131" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">認めてあげるわ。
 格の違いを見せてあげる</t>
         </is>
       </c>
     </row>
-    <row r="125" ht="40" customHeight="1">
-      <c r="A125" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_ABSTRACT.seductive.bold[1]</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_ABSTRACT.seductive.bold[1]</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">社長、私たちのこと、もう少し気にかけて。寂しくなっちゃうから。</t>
-        </is>
-      </c>
-    </row>
-    <row r="126" ht="40" customHeight="1">
-      <c r="A126" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MAIN.seductive.bold[1]</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_MAIN.seductive.bold[1]</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">社長、次のメイン、私に任せてくれない？ 必ず客を沸かすから。</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="40" customHeight="1">
-      <c r="A127" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MONEY.seductive.bold[1]</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_MONEY.seductive.bold[1]</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">社長、私たちの給料の話、ちょっと聞いてくれない？</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" ht="40" customHeight="1">
-      <c r="A128" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_RECOGNITION.seductive.bold[1]</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_RECOGNITION.seductive.bold[1]</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">社長、私の貢献、ちゃんと見てくれてる？ 確かめさせて。</t>
-        </is>
-      </c>
-    </row>
-    <row r="129" ht="40" customHeight="1">
-      <c r="A129" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.A.seductive.bold[1]</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.A.seductive.bold[1]</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">届いていたのね、その気持ち。……ありがとう、社長。</t>
-        </is>
-      </c>
-    </row>
-    <row r="130" ht="40" customHeight="1">
-      <c r="A130" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.B.seductive.bold[1]</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.B.seductive.bold[1]</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">…そう。じゃあ、忘れて。</t>
-        </is>
-      </c>
-    </row>
-    <row r="131" ht="40" customHeight="1">
-      <c r="A131" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.C.seductive.bold[1]</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.C.seductive.bold[1]</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">……ふふ、そちらの筋から来たの。悪くないわ、感謝しておく。</t>
-        </is>
-      </c>
-    </row>
     <row r="132" ht="40" customHeight="1">
       <c r="A132" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.A.seductive.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_ABSTRACT.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B132" t="inlineStr" s="2">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="D132" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.A.seductive.bold[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_ABSTRACT.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E132" t="inlineStr" s="2">
@@ -4553,14 +4553,14 @@
       </c>
       <c r="F132" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとう、社長。期待してて、ちゃんと魅せるから。</t>
+          <t xml:space="preserve">社長、私たちのこと、もう少し気にかけて。寂しくなっちゃうから。</t>
         </is>
       </c>
     </row>
     <row r="133" ht="40" customHeight="1">
       <c r="A133" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.B.seductive.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MAIN.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B133" t="inlineStr" s="2">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="D133" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.B.seductive.bold[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_MAIN.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E133" t="inlineStr" s="2">
@@ -4585,14 +4585,14 @@
       </c>
       <c r="F133" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……そう。その言葉、覚えておくわ。</t>
+          <t xml:space="preserve">社長、次のメイン、私に任せてくれない？ 必ず客を沸かすから。</t>
         </is>
       </c>
     </row>
     <row r="134" ht="40" customHeight="1">
       <c r="A134" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.C.seductive.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MONEY.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B134" t="inlineStr" s="2">
@@ -4607,7 +4607,7 @@
       </c>
       <c r="D134" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.C.seductive.bold[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_MONEY.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E134" t="inlineStr" s="2">
@@ -4617,14 +4617,14 @@
       </c>
       <c r="F134" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……なるほど。そういう手もあるのね。悪くないじゃない。</t>
+          <t xml:space="preserve">社長、私たちの給料の話、ちょっと聞いてくれない？</t>
         </is>
       </c>
     </row>
     <row r="135" ht="40" customHeight="1">
       <c r="A135" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.A.seductive.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_RECOGNITION.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B135" t="inlineStr" s="2">
@@ -4639,7 +4639,7 @@
       </c>
       <c r="D135" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.A.seductive.bold[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_RECOGNITION.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E135" t="inlineStr" s="2">
@@ -4649,14 +4649,14 @@
       </c>
       <c r="F135" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">感謝するわ、社長。この話、皆にも下ろしておく。</t>
+          <t xml:space="preserve">社長、私の貢献、ちゃんと見てくれてる？ 確かめさせて。</t>
         </is>
       </c>
     </row>
     <row r="136" ht="40" customHeight="1">
       <c r="A136" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.B.seductive.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.A.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B136" t="inlineStr" s="2">
@@ -4671,7 +4671,7 @@
       </c>
       <c r="D136" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.B.seductive.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.A.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E136" t="inlineStr" s="2">
@@ -4681,14 +4681,14 @@
       </c>
       <c r="F136" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……そう。続きはまた、いずれ。</t>
+          <t xml:space="preserve">届いていたのね、その気持ち。……ありがとう、社長。</t>
         </is>
       </c>
     </row>
     <row r="137" ht="40" customHeight="1">
       <c r="A137" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.C.seductive.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.B.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B137" t="inlineStr" s="2">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="D137" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.C.seductive.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.B.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E137" t="inlineStr" s="2">
@@ -4713,14 +4713,14 @@
       </c>
       <c r="F137" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ふぅん、金銭じゃないのね。まあ、そういうのも嫌いじゃないわ。</t>
+          <t xml:space="preserve">…そう。じゃあ、忘れて。</t>
         </is>
       </c>
     </row>
     <row r="138" ht="40" customHeight="1">
       <c r="A138" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.A.seductive.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.C.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B138" t="inlineStr" s="2">
@@ -4735,7 +4735,7 @@
       </c>
       <c r="D138" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.A.seductive.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.C.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E138" t="inlineStr" s="2">
@@ -4745,14 +4745,14 @@
       </c>
       <c r="F138" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">見ていてくれたのね。……こういうの、効くじゃない。</t>
+          <t xml:space="preserve">……ふふ、そちらの筋から来たの。悪くないわ、感謝しておく。</t>
         </is>
       </c>
     </row>
     <row r="139" ht="40" customHeight="1">
       <c r="A139" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.B.seductive.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.A.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B139" t="inlineStr" s="2">
@@ -4767,7 +4767,7 @@
       </c>
       <c r="D139" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.B.seductive.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.A.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E139" t="inlineStr" s="2">
@@ -4777,14 +4777,14 @@
       </c>
       <c r="F139" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そう。じゃあ忘れて。</t>
+          <t xml:space="preserve">ありがとう、社長。期待してて、ちゃんと魅せるから。</t>
         </is>
       </c>
     </row>
     <row r="140" ht="40" customHeight="1">
       <c r="A140" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.C.seductive.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.B.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B140" t="inlineStr" s="2">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="D140" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.C.seductive.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.B.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E140" t="inlineStr" s="2">
@@ -4809,14 +4809,14 @@
       </c>
       <c r="F140" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……別の形、ね。それはそれで悪くないわ。感謝する。</t>
+          <t xml:space="preserve">……そう。その言葉、覚えておくわ。</t>
         </is>
       </c>
     </row>
     <row r="141" ht="40" customHeight="1">
       <c r="A141" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.A.seductive.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.C.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B141" t="inlineStr" s="2">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="D141" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.A.seductive.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.C.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E141" t="inlineStr" s="2">
@@ -4841,14 +4841,14 @@
       </c>
       <c r="F141" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……そう。次は先に一声かけるわ。悪かったわね。</t>
+          <t xml:space="preserve">……なるほど。そういう手もあるのね。悪くないじゃない。</t>
         </is>
       </c>
     </row>
     <row r="142" ht="40" customHeight="1">
       <c r="A142" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.B.seductive.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.A.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B142" t="inlineStr" s="2">
@@ -4863,7 +4863,7 @@
       </c>
       <c r="D142" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.B.seductive.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.A.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E142" t="inlineStr" s="2">
@@ -4873,14 +4873,14 @@
       </c>
       <c r="F142" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとう。仲間内の付き合いも、大事だからね。</t>
+          <t xml:space="preserve">感謝するわ、社長。この話、皆にも下ろしておく。</t>
         </is>
       </c>
     </row>
     <row r="143" ht="40" customHeight="1">
       <c r="A143" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.A.seductive.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.B.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B143" t="inlineStr" s="2">
@@ -4895,7 +4895,7 @@
       </c>
       <c r="D143" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.A.seductive.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.B.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E143" t="inlineStr" s="2">
@@ -4905,14 +4905,14 @@
       </c>
       <c r="F143" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……そう。心に留めておくわ。</t>
+          <t xml:space="preserve">……そう。続きはまた、いずれ。</t>
         </is>
       </c>
     </row>
     <row r="144" ht="40" customHeight="1">
       <c r="A144" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.B.seductive.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.C.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B144" t="inlineStr" s="2">
@@ -4927,7 +4927,7 @@
       </c>
       <c r="D144" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.B.seductive.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.C.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E144" t="inlineStr" s="2">
@@ -4937,14 +4937,14 @@
       </c>
       <c r="F144" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとう、社長。</t>
+          <t xml:space="preserve">……ふぅん、金銭じゃないのね。まあ、そういうのも嫌いじゃないわ。</t>
         </is>
       </c>
     </row>
     <row r="145" ht="40" customHeight="1">
       <c r="A145" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.A.seductive.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.A.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B145" t="inlineStr" s="2">
@@ -4959,7 +4959,7 @@
       </c>
       <c r="D145" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.A.seductive.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.A.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E145" t="inlineStr" s="2">
@@ -4969,14 +4969,14 @@
       </c>
       <c r="F145" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……線ね。引くわ。客は乗っていたのだけれど。</t>
+          <t xml:space="preserve">見ていてくれたのね。……こういうの、効くじゃない。</t>
         </is>
       </c>
     </row>
     <row r="146" ht="40" customHeight="1">
       <c r="A146" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.B.seductive.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.B.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B146" t="inlineStr" s="2">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="D146" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.B.seductive.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.B.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E146" t="inlineStr" s="2">
@@ -5001,14 +5001,14 @@
       </c>
       <c r="F146" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとう、社長。これも仕事だからね。</t>
+          <t xml:space="preserve">…そう。じゃあ忘れて。</t>
         </is>
       </c>
     </row>
     <row r="147" ht="40" customHeight="1">
       <c r="A147" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.A.seductive.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.C.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B147" t="inlineStr" s="2">
@@ -5023,7 +5023,7 @@
       </c>
       <c r="D147" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.A.seductive.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.C.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E147" t="inlineStr" s="2">
@@ -5033,14 +5033,14 @@
       </c>
       <c r="F147" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……悪かったわ、社長。明日からはきちんと顔を出す。</t>
+          <t xml:space="preserve">……別の形、ね。それはそれで悪くないわ。感謝する。</t>
         </is>
       </c>
     </row>
     <row r="148" ht="40" customHeight="1">
       <c r="A148" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.B.seductive.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.A.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B148" t="inlineStr" s="2">
@@ -5055,7 +5055,7 @@
       </c>
       <c r="D148" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.B.seductive.bold[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.A.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E148" t="inlineStr" s="2">
@@ -5065,14 +5065,14 @@
       </c>
       <c r="F148" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとう、社長。お返しは、ちゃんとするから。</t>
+          <t xml:space="preserve">……そう。次は先に一声かけるわ。悪かったわね。</t>
         </is>
       </c>
     </row>
     <row r="149" ht="40" customHeight="1">
       <c r="A149" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.C.seductive.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.B.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B149" t="inlineStr" s="2">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="D149" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.C.seductive.bold[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.B.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E149" t="inlineStr" s="2">
@@ -5097,14 +5097,14 @@
       </c>
       <c r="F149" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そう、メンバー優先ね。ありがとう。</t>
+          <t xml:space="preserve">…ありがとう。仲間内の付き合いも、大事だからね。</t>
         </is>
       </c>
     </row>
     <row r="150" ht="40" customHeight="1">
       <c r="A150" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.A.seductive.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.A.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B150" t="inlineStr" s="2">
@@ -5119,7 +5119,7 @@
       </c>
       <c r="D150" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.A.seductive.bold[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.A.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E150" t="inlineStr" s="2">
@@ -5129,14 +5129,14 @@
       </c>
       <c r="F150" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ありがとう。少しだけ、身体を休めておくわ。</t>
+          <t xml:space="preserve">……そう。心に留めておくわ。</t>
         </is>
       </c>
     </row>
     <row r="151" ht="40" customHeight="1">
       <c r="A151" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.B.seductive.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.B.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="2">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="D151" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.B.seductive.bold[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.B.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E151" t="inlineStr" s="2">
@@ -5161,14 +5161,14 @@
       </c>
       <c r="F151" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……平気よ。まだ倒れる気はないの。</t>
+          <t xml:space="preserve">…ありがとう、社長。</t>
         </is>
       </c>
     </row>
     <row r="152" ht="40" customHeight="1">
       <c r="A152" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.C.seductive.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.A.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B152" t="inlineStr" s="2">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="D152" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.C.seductive.bold[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.A.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E152" t="inlineStr" s="2">
@@ -5193,14 +5193,14 @@
       </c>
       <c r="F152" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そう、メンバーケアね。私も助かる、ありがとう。</t>
+          <t xml:space="preserve">……線ね。引くわ。客は乗っていたのだけれど。</t>
         </is>
       </c>
     </row>
     <row r="153" ht="40" customHeight="1">
       <c r="A153" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.A.seductive.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.B.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="2">
@@ -5215,7 +5215,7 @@
       </c>
       <c r="D153" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.A.seductive.bold[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.B.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E153" t="inlineStr" s="2">
@@ -5225,14 +5225,14 @@
       </c>
       <c r="F153" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……そう。皆へは私の口から通しておくわ。</t>
+          <t xml:space="preserve">…ありがとう、社長。これも仕事だからね。</t>
         </is>
       </c>
     </row>
     <row r="154" ht="40" customHeight="1">
       <c r="A154" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.B.seductive.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.A.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B154" t="inlineStr" s="2">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="D154" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.B.seductive.bold[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.A.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E154" t="inlineStr" s="2">
@@ -5257,14 +5257,14 @@
       </c>
       <c r="F154" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとう、社長。穏便にね。</t>
+          <t xml:space="preserve">……悪かったわ、社長。明日からはきちんと顔を出す。</t>
         </is>
       </c>
     </row>
     <row r="155" ht="40" customHeight="1">
       <c r="A155" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.C.seductive.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.B.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="2">
@@ -5279,7 +5279,7 @@
       </c>
       <c r="D155" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.C.seductive.bold[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.B.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E155" t="inlineStr" s="2">
@@ -5289,14 +5289,14 @@
       </c>
       <c r="F155" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そう、下の子のケアね。ありがとう。</t>
+          <t xml:space="preserve">…ありがとう、社長。お返しは、ちゃんとするから。</t>
         </is>
       </c>
     </row>
     <row r="156" ht="40" customHeight="1">
       <c r="A156" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.A.seductive.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.C.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="2">
@@ -5311,7 +5311,7 @@
       </c>
       <c r="D156" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.A.seductive.bold[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.C.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E156" t="inlineStr" s="2">
@@ -5321,14 +5321,14 @@
       </c>
       <c r="F156" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……了解。次から気を配るわ。</t>
+          <t xml:space="preserve">…そう、メンバー優先ね。ありがとう。</t>
         </is>
       </c>
     </row>
     <row r="157" ht="40" customHeight="1">
       <c r="A157" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.B.seductive.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.A.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="2">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="D157" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.B.seductive.bold[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.A.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E157" t="inlineStr" s="2">
@@ -5353,14 +5353,14 @@
       </c>
       <c r="F157" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（小さく息を吐いて、視線を逸らした）</t>
+          <t xml:space="preserve">……ありがとう。少しだけ、身体を休めておくわ。</t>
         </is>
       </c>
     </row>
     <row r="158" ht="40" customHeight="1">
       <c r="A158" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.C.seductive.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.B.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B158" t="inlineStr" s="2">
@@ -5375,7 +5375,7 @@
       </c>
       <c r="D158" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.C.seductive.bold[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.B.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E158" t="inlineStr" s="2">
@@ -5385,14 +5385,14 @@
       </c>
       <c r="F158" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そう、別ルートね。ありがとう。</t>
+          <t xml:space="preserve">……平気よ。まだ倒れる気はないの。</t>
         </is>
       </c>
     </row>
     <row r="159" ht="40" customHeight="1">
       <c r="A159" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.A.seductive.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.C.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="2">
@@ -5407,7 +5407,7 @@
       </c>
       <c r="D159" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.A.seductive.bold[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.C.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E159" t="inlineStr" s="2">
@@ -5417,14 +5417,14 @@
       </c>
       <c r="F159" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……そうね、加減はするわ。壊してしまっては意味がないもの。</t>
+          <t xml:space="preserve">…そう、メンバーケアね。私も助かる、ありがとう。</t>
         </is>
       </c>
     </row>
     <row r="160" ht="40" customHeight="1">
       <c r="A160" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.B.seductive.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.A.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="2">
@@ -5439,7 +5439,7 @@
       </c>
       <c r="D160" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.B.seductive.bold[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.A.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E160" t="inlineStr" s="2">
@@ -5449,14 +5449,14 @@
       </c>
       <c r="F160" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……感謝するわ、社長。このまま突き進ませてもらう。</t>
+          <t xml:space="preserve">……そう。皆へは私の口から通しておくわ。</t>
         </is>
       </c>
     </row>
     <row r="161" ht="40" customHeight="1">
       <c r="A161" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.C.seductive.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.B.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
@@ -5471,7 +5471,7 @@
       </c>
       <c r="D161" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.C.seductive.bold[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.B.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E161" t="inlineStr" s="2">
@@ -5481,14 +5481,14 @@
       </c>
       <c r="F161" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そう、子たち優先ね。ありがとう。</t>
+          <t xml:space="preserve">…ありがとう、社長。穏便にね。</t>
         </is>
       </c>
     </row>
     <row r="162" ht="40" customHeight="1">
       <c r="A162" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES.bold.attack.seductive</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.C.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="C162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D162" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.attack.seductive</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.C.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E162" t="inlineStr" s="2">
@@ -5513,14 +5513,14 @@
       </c>
       <c r="F162" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう、隣には立てないわ</t>
+          <t xml:space="preserve">…そう、下の子のケアね。ありがとう。</t>
         </is>
       </c>
     </row>
     <row r="163" ht="40" customHeight="1">
       <c r="A163" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES.bold.defend.seductive</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.A.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
@@ -5530,12 +5530,12 @@
       </c>
       <c r="C163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D163" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.defend.seductive</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.A.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E163" t="inlineStr" s="2">
@@ -5545,14 +5545,14 @@
       </c>
       <c r="F163" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">上等よ。受けて立つわ</t>
+          <t xml:space="preserve">……了解。次から気を配るわ。</t>
         </is>
       </c>
     </row>
     <row r="164" ht="40" customHeight="1">
       <c r="A164" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES.seductive.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.B.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
@@ -5562,29 +5562,29 @@
       </c>
       <c r="C164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D164" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.bold[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.B.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F164" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">当然よ。まだまだこんなものじゃないわ</t>
+          <t xml:space="preserve">（小さく息を吐いて、視線を逸らした）</t>
         </is>
       </c>
     </row>
     <row r="165" ht="40" customHeight="1">
       <c r="A165" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES.seductive.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.C.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
@@ -5594,29 +5594,29 @@
       </c>
       <c r="C165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D165" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.bold[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.C.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F165" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう少し…あと少しで何かが掴めそうなの</t>
+          <t xml:space="preserve">…そう、別ルートね。ありがとう。</t>
         </is>
       </c>
     </row>
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES.seductive.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.A.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -5626,29 +5626,29 @@
       </c>
       <c r="C166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.bold[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.A.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F166" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">燃えないの…何をしても、火がつかないわ</t>
+          <t xml:space="preserve">……そうね、加減はするわ。壊してしまっては意味がないもの。</t>
         </is>
       </c>
     </row>
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.seductive.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.B.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -5658,29 +5658,29 @@
       </c>
       <c r="C167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.bold[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.B.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F167" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">目が覚めたわ。ここで終わるなんて、つまらないもの</t>
+          <t xml:space="preserve">……感謝するわ、社長。このまま突き進ませてもらう。</t>
         </is>
       </c>
     </row>
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES.seductive.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.C.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
@@ -5690,29 +5690,29 @@
       </c>
       <c r="C168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.bold[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.C.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F168" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お待たせ。ここからが本番よ</t>
+          <t xml:space="preserve">…そう、子たち優先ね。ありがとう。</t>
         </is>
       </c>
     </row>
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.defeat.seductive.bold[1]</t>
+          <t xml:space="preserve">FACTION_F02_LINES.bold.attack.seductive</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -5722,29 +5722,29 @@
       </c>
       <c r="C169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
         </is>
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defeat.seductive.bold[1]</t>
+          <t xml:space="preserve">bold.attack.seductive</t>
         </is>
       </c>
       <c r="E169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F169" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら…おかしいわね、こんなはずじゃ</t>
+          <t xml:space="preserve">もう、隣には立てないわ</t>
         </is>
       </c>
     </row>
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.seductive.bold[1]</t>
+          <t xml:space="preserve">FACTION_F02_LINES.bold.defend.seductive</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
@@ -5754,29 +5754,29 @@
       </c>
       <c r="C170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
         </is>
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_moderate_recovery.seductive.bold[1]</t>
+          <t xml:space="preserve">bold.defend.seductive</t>
         </is>
       </c>
       <c r="E170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F170" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">治ったはずなのに…おかしいわね</t>
+          <t xml:space="preserve">上等よ。受けて立つわ</t>
         </is>
       </c>
     </row>
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.seductive.bold[1]</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="C171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
         </is>
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_severe_recovery.seductive.bold[1]</t>
+          <t xml:space="preserve">seductive.bold[1]</t>
         </is>
       </c>
       <c r="E171" t="inlineStr" s="2">
@@ -5801,14 +5801,14 @@
       </c>
       <c r="F171" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私が…怯えてる？ 嘘でしょう</t>
+          <t xml:space="preserve">当然よ。まだまだこんなものじゃないわ</t>
         </is>
       </c>
     </row>
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.seductive.bold[1]</t>
+          <t xml:space="preserve">BT_HINT_LINES.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="C172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">BT_HINT_LINES</t>
         </is>
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">penalty_end.seductive.bold[1]</t>
+          <t xml:space="preserve">seductive.bold[1]</t>
         </is>
       </c>
       <c r="E172" t="inlineStr" s="2">
@@ -5833,14 +5833,14 @@
       </c>
       <c r="F172" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">体は万全なのに…気持ちがついてこないの</t>
+          <t xml:space="preserve">もう少し…あと少しで何かが掴めそうなの</t>
         </is>
       </c>
     </row>
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.autumnWarChampion.seductive.bold[1]</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5850,29 +5850,29 @@
       </c>
       <c r="C173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
         </is>
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">autumnWarChampion.seductive.bold[1]</t>
+          <t xml:space="preserve">seductive.bold[1]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F173" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">対抗戦の主役は私たちよ。忘れないでね。</t>
+          <t xml:space="preserve">燃えないの…何をしても、火がつかないわ</t>
         </is>
       </c>
     </row>
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.seductive.bold[1]</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -5882,29 +5882,29 @@
       </c>
       <c r="C174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
         </is>
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.seductive.bold[1]</t>
+          <t xml:space="preserve">seductive.bold[1]</t>
         </is>
       </c>
       <c r="E174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F174" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全力を引き出してくれた相手に感謝。…次はもっと激しくいくわよ？</t>
+          <t xml:space="preserve">目が覚めたわ。ここで終わるなんて、つまらないもの</t>
         </is>
       </c>
     </row>
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.seductive.bold[1]</t>
+          <t xml:space="preserve">SLUMP_END_LINES.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -5914,29 +5914,29 @@
       </c>
       <c r="C175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_END_LINES</t>
         </is>
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.seductive.bold[1]</t>
+          <t xml:space="preserve">seductive.bold[1]</t>
         </is>
       </c>
       <c r="E175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F175" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頂点からの景色は最高よ。…あなたには見せてあげないけど</t>
+          <t xml:space="preserve">お待たせ。ここからが本番よ</t>
         </is>
       </c>
     </row>
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.seductive.bold[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.defeat.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -5946,29 +5946,29 @@
       </c>
       <c r="C176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.seductive.bold[1]</t>
+          <t xml:space="preserve">defeat.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F176" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高の舞台で、最高の人生だった。…最後まで美しかったでしょう？</t>
+          <t xml:space="preserve">あら…おかしいわね、こんなはずじゃ</t>
         </is>
       </c>
     </row>
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.seductive.bold[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -5978,29 +5978,29 @@
       </c>
       <c r="C177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.seductive.bold[1]</t>
+          <t xml:space="preserve">injury_moderate_recovery.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F177" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一番になるべくしてなった。当然でしょう？ …でも、まだ満足してないわ</t>
+          <t xml:space="preserve">治ったはずなのに…おかしいわね</t>
         </is>
       </c>
     </row>
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.seductive.bold[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -6010,29 +6010,29 @@
       </c>
       <c r="C178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.seductive.bold[1]</t>
+          <t xml:space="preserve">injury_severe_recovery.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F178" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">嬉しい？ ええ、嬉しいわ。でもこの程度で満足する女じゃないの</t>
+          <t xml:space="preserve">私が…怯えてる？ 嘘でしょう</t>
         </is>
       </c>
     </row>
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.springTagChampion.seductive.bold[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -6042,29 +6042,29 @@
       </c>
       <c r="C179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">springTagChampion.seductive.bold[1]</t>
+          <t xml:space="preserve">penalty_end.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F179" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">相棒との舞台は最上級よ。次も目を離さないで。</t>
+          <t xml:space="preserve">体は万全なのに…気持ちがついてこないの</t>
         </is>
       </c>
     </row>
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.seductive.bold[1]</t>
+          <t xml:space="preserve">AWARD_LINES.autumnWarChampion.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -6074,12 +6074,12 @@
       </c>
       <c r="C180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.bold[1]</t>
+          <t xml:space="preserve">autumnWarChampion.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
@@ -6089,14 +6089,14 @@
       </c>
       <c r="F180" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ドームで…本気の私、見せてあげる</t>
+          <t xml:space="preserve">対抗戦の主役は私たちよ。忘れないでね。</t>
         </is>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.seductive.bold[2]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -6106,12 +6106,12 @@
       </c>
       <c r="C181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.bold[2]</t>
+          <t xml:space="preserve">bestMatch.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
@@ -6121,14 +6121,14 @@
       </c>
       <c r="F181" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この大舞台、たっぷり熱くしてあげるわよ</t>
+          <t xml:space="preserve">全力を引き出してくれた相手に感謝。…次はもっと激しくいくわよ？</t>
         </is>
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.seductive.bold[3]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -6138,12 +6138,12 @@
       </c>
       <c r="C182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.bold[3]</t>
+          <t xml:space="preserve">champion.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
@@ -6153,14 +6153,14 @@
       </c>
       <c r="F182" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うふふ、今夜は容赦しないわよ</t>
+          <t xml:space="preserve">頂点からの景色は最高よ。…あなたには見せてあげないけど</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.seductive.bold[1]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6170,12 +6170,12 @@
       </c>
       <c r="C183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.bold[1]</t>
+          <t xml:space="preserve">hallOfFame.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
@@ -6185,14 +6185,14 @@
       </c>
       <c r="F183" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">満員…最高の演出になったわね</t>
+          <t xml:space="preserve">最高の舞台で、最高の人生だった。…最後まで美しかったでしょう？</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.seductive.bold[2]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6202,12 +6202,12 @@
       </c>
       <c r="C184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.bold[2]</t>
+          <t xml:space="preserve">mvp.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
@@ -6217,14 +6217,14 @@
       </c>
       <c r="F184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この熱量、また必ず味わいたい</t>
+          <t xml:space="preserve">一番になるべくしてなった。当然でしょう？ …でも、まだ満足してないわ</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.seductive.bold[3]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6234,12 +6234,12 @@
       </c>
       <c r="C185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.bold[3]</t>
+          <t xml:space="preserve">rookie.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
@@ -6249,14 +6249,14 @@
       </c>
       <c r="F185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うふふ、皆様を虜にしてあげたわ</t>
+          <t xml:space="preserve">嬉しい？ ええ、嬉しいわ。でもこの程度で満足する女じゃないの</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.seductive.bold[1]</t>
+          <t xml:space="preserve">AWARD_LINES.springTagChampion.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6266,29 +6266,29 @@
       </c>
       <c r="C186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.seductive.bold[1]</t>
+          <t xml:space="preserve">springTagChampion.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ足りないわ。もっと強くなれる気がするの</t>
+          <t xml:space="preserve">相棒との舞台は最上級よ。次も目を離さないで。</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.seductive.bold[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6298,29 +6298,29 @@
       </c>
       <c r="C187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.seductive.bold[1]</t>
+          <t xml:space="preserve">seductive.bold[1]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F187" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仲間がいるって、いいものね</t>
+          <t xml:space="preserve">ドームで…本気の私、見せてあげる</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.seductive.bold[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6330,29 +6330,29 @@
       </c>
       <c r="C188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.seductive.bold[1]</t>
+          <t xml:space="preserve">seductive.bold[2]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F188" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この程度で止まるつもりはないわ</t>
+          <t xml:space="preserve">この大舞台、たっぷり熱くしてあげるわよ</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.seductive.bold[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.seductive.bold[3]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6362,29 +6362,29 @@
       </c>
       <c r="C189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.seductive.bold[1]</t>
+          <t xml:space="preserve">seductive.bold[3]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F189" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この人気、活かさない手はないわね</t>
+          <t xml:space="preserve">うふふ、今夜は容赦しないわよ</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.seductive.bold[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6394,29 +6394,29 @@
       </c>
       <c r="C190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.seductive.bold[1]</t>
+          <t xml:space="preserve">seductive.bold[1]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F190" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ここにいて、私の夢は叶うのかしら</t>
+          <t xml:space="preserve">満員…最高の演出になったわね</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.seductive.bold[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6426,29 +6426,29 @@
       </c>
       <c r="C191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_warning.seductive.bold[1]</t>
+          <t xml:space="preserve">seductive.bold[2]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F191" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…このままでいいのかしらって、ふと思うの</t>
+          <t xml:space="preserve">この熱量、また必ず味わいたい</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.seductive.bold[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.seductive.bold[3]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6458,29 +6458,29 @@
       </c>
       <c r="C192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.seductive.bold[1]</t>
+          <t xml:space="preserve">seductive.bold[3]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F192" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">嬉しいわ。実力で返させてもらうわね</t>
+          <t xml:space="preserve">うふふ、皆様を虜にしてあげたわ</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.seductive.bold[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6490,29 +6490,29 @@
       </c>
       <c r="C193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.seductive.bold[1]</t>
+          <t xml:space="preserve">N1.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F193" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">帰る頃には一回り強くなってるわよ</t>
+          <t xml:space="preserve">まだ足りないわ。もっと強くなれる気がするの</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.seductive.bold[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6522,29 +6522,29 @@
       </c>
       <c r="C194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage_high_trust.seductive.bold[1]</t>
+          <t xml:space="preserve">N2.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あなたが信じてくれるなら…絶対応えるわ</t>
+          <t xml:space="preserve">仲間がいるって、いいものね</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.seductive.bold[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6554,29 +6554,29 @@
       </c>
       <c r="C195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.seductive.bold[1]</t>
+          <t xml:space="preserve">N3.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F195" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">止まるつもりはないわ。見ていてね</t>
+          <t xml:space="preserve">この程度で止まるつもりはないわ</t>
         </is>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.seductive.bold[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6586,29 +6586,29 @@
       </c>
       <c r="C196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faction_decree.seductive.bold[1]</t>
+          <t xml:space="preserve">N4.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F196" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いいわ、畳みましょう。……でも、覚えておいて</t>
+          <t xml:space="preserve">この人気、活かさない手はないわね</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.seductive.bold[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6618,29 +6618,29 @@
       </c>
       <c r="C197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.seductive.bold[1]</t>
+          <t xml:space="preserve">N5_low.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F197" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">注目される場って好きよ。任せて</t>
+          <t xml:space="preserve">…ここにいて、私の夢は叶うのかしら</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.seductive.bold[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6650,29 +6650,29 @@
       </c>
       <c r="C198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.seductive.bold[1]</t>
+          <t xml:space="preserve">N5_warning.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F198" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい雰囲気ね。チームが成長してる証拠だわ</t>
+          <t xml:space="preserve">…このままでいいのかしらって、ふと思うの</t>
         </is>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.seductive.bold[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6687,7 +6687,7 @@
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.seductive.bold[1]</t>
+          <t xml:space="preserve">bonus.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
@@ -6697,14 +6697,14 @@
       </c>
       <c r="F199" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">リフレッシュしてくるわ。戻ったらもっと輝くから</t>
+          <t xml:space="preserve">嬉しいわ。実力で返させてもらうわね</t>
         </is>
       </c>
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.seductive.bold[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6719,7 +6719,7 @@
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">special_treatment.seductive.bold[1]</t>
+          <t xml:space="preserve">camp.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
@@ -6729,14 +6729,14 @@
       </c>
       <c r="F200" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">早く戻りたいの…待っていてね</t>
+          <t xml:space="preserve">帰る頃には一回り強くなってるわよ</t>
         </is>
       </c>
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.seductive.bold[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.seductive.bold[1]</t>
+          <t xml:space="preserve">encourage_high_trust.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
@@ -6761,14 +6761,14 @@
       </c>
       <c r="F201" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この環境、無駄にしないわ。見ていてね</t>
+          <t xml:space="preserve">あなたが信じてくれるなら…絶対応えるわ</t>
         </is>
       </c>
     </row>
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.seductive.bold[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6778,12 +6778,12 @@
       </c>
       <c r="C202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.seductive.bold[1]</t>
+          <t xml:space="preserve">encourage.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
@@ -6793,14 +6793,14 @@
       </c>
       <c r="F202" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">注目される場は好きよ。もちろんやるわ</t>
+          <t xml:space="preserve">止まるつもりはないわ。見ていてね</t>
         </is>
       </c>
     </row>
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.seductive.bold[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="C203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.seductive.bold[1]</t>
+          <t xml:space="preserve">faction_decree.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
@@ -6825,14 +6825,14 @@
       </c>
       <c r="F203" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">他所からいい話が来てるの。正直、迷ってるわ</t>
+          <t xml:space="preserve">いいわ、畳みましょう。……でも、覚えておいて</t>
         </is>
       </c>
     </row>
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.seductive.bold[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6842,12 +6842,12 @@
       </c>
       <c r="C204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.seductive.bold[1]</t>
+          <t xml:space="preserve">media.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
@@ -6857,14 +6857,14 @@
       </c>
       <c r="F204" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">練習？ 出してもくれないのに、意味があるのかしら</t>
+          <t xml:space="preserve">注目される場って好きよ。任せて</t>
         </is>
       </c>
     </row>
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.seductive.bold[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="C205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.seductive.bold[2]</t>
+          <t xml:space="preserve">party.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
@@ -6889,14 +6889,14 @@
       </c>
       <c r="F205" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">リングに上がれないなら、やっても同じでしょう？</t>
+          <t xml:space="preserve">いい雰囲気ね。チームが成長してる証拠だわ</t>
         </is>
       </c>
     </row>
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.seductive.bold[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6906,12 +6906,12 @@
       </c>
       <c r="C206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_grumble.seductive.bold[1]</t>
+          <t xml:space="preserve">refresh_leave.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
@@ -6921,14 +6921,14 @@
       </c>
       <c r="F206" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（「私たち、ずいぶん軽く見られてるのね」と笑みを崩さずに言い放っている）</t>
+          <t xml:space="preserve">リフレッシュしてくるわ。戻ったらもっと輝くから</t>
         </is>
       </c>
     </row>
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.seductive.bold[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6938,12 +6938,12 @@
       </c>
       <c r="C207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_sns.seductive.bold[1]</t>
+          <t xml:space="preserve">special_treatment.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
@@ -6953,14 +6953,14 @@
       </c>
       <c r="F207" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（SNSに「このまま終わるつもりはないの。楽しみにしてて」と投稿）</t>
+          <t xml:space="preserve">早く戻りたいの…待っていてね</t>
         </is>
       </c>
     </row>
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.seductive.bold[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -6970,12 +6970,12 @@
       </c>
       <c r="C208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.seductive.bold[1]</t>
+          <t xml:space="preserve">trainer.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
@@ -6985,14 +6985,14 @@
       </c>
       <c r="F208" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ベルトが欲しいの。組んでもらえる？</t>
+          <t xml:space="preserve">この環境、無駄にしないわ。見ていてね</t>
         </is>
       </c>
     </row>
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.seductive.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -7007,7 +7007,7 @@
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.seductive.bold[1]</t>
+          <t xml:space="preserve">E1.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
@@ -7017,14 +7017,14 @@
       </c>
       <c r="F209" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの人と決着をつけたいの。組んでもらえる？</t>
+          <t xml:space="preserve">注目される場は好きよ。もちろんやるわ</t>
         </is>
       </c>
     </row>
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.seductive.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -7039,7 +7039,7 @@
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.seductive.bold[1]</t>
+          <t xml:space="preserve">E6.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
@@ -7049,14 +7049,14 @@
       </c>
       <c r="F210" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…体が限界なの。少し休ませて</t>
+          <t xml:space="preserve">他所からいい話が来てるの。正直、迷ってるわ</t>
         </is>
       </c>
     </row>
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.seductive.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7071,7 +7071,7 @@
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.seductive.bold[1]</t>
+          <t xml:space="preserve">S_boycott.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
@@ -7081,14 +7081,14 @@
       </c>
       <c r="F211" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このままじゃ我慢の限界よ。考え直してもらえない？</t>
+          <t xml:space="preserve">練習？ 出してもくれないのに、意味があるのかしら</t>
         </is>
       </c>
     </row>
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.seductive.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7103,7 +7103,7 @@
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_silent.seductive.bold[1]</t>
+          <t xml:space="preserve">S_boycott.seductive.bold[2]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
@@ -7113,14 +7113,14 @@
       </c>
       <c r="F212" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…………（笑みは崩さないまま、指先だけが強く握られている）</t>
+          <t xml:space="preserve">リングに上がれないなら、やっても同じでしょう？</t>
         </is>
       </c>
     </row>
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.seductive.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7135,7 +7135,7 @@
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.seductive.bold[1]</t>
+          <t xml:space="preserve">S_grumble.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
@@ -7145,14 +7145,14 @@
       </c>
       <c r="F213" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もっと強くなりたいの。特訓させてもらえる？</t>
+          <t xml:space="preserve">（「私たち、ずいぶん軽く見られてるのね」と笑みを崩さずに言い放っている）</t>
         </is>
       </c>
     </row>
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.seductive.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7167,7 +7167,7 @@
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.seductive.bold[1]</t>
+          <t xml:space="preserve">S_sns.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
@@ -7177,14 +7177,14 @@
       </c>
       <c r="F214" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">後輩の面倒、見させてもらえるかしら？</t>
+          <t xml:space="preserve">（SNSに「このまま終わるつもりはないの。楽しみにしてて」と投稿）</t>
         </is>
       </c>
     </row>
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.seductive.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="C215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.seductive.bold[1]</t>
+          <t xml:space="preserve">S1.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
@@ -7209,14 +7209,14 @@
       </c>
       <c r="F215" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんなところで止まるつもりはないわ…すぐ戻る</t>
+          <t xml:space="preserve">ベルトが欲しいの。組んでもらえる？</t>
         </is>
       </c>
     </row>
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.seductive.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7226,12 +7226,12 @@
       </c>
       <c r="C216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.seductive.bold[1]</t>
+          <t xml:space="preserve">S2.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
@@ -7241,14 +7241,14 @@
       </c>
       <c r="F216" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの人の態度、もう我慢できないの</t>
+          <t xml:space="preserve">あの人と決着をつけたいの。組んでもらえる？</t>
         </is>
       </c>
     </row>
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.seductive.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7258,12 +7258,12 @@
       </c>
       <c r="C217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.seductive.bold[1]</t>
+          <t xml:space="preserve">S3.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
@@ -7273,14 +7273,14 @@
       </c>
       <c r="F217" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">黙ってるつもりはないわ。向こうが悪いんだから</t>
+          <t xml:space="preserve">…体が限界なの。少し休ませて</t>
         </is>
       </c>
     </row>
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.seductive.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7290,12 +7290,12 @@
       </c>
       <c r="C218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.seductive.bold[1]</t>
+          <t xml:space="preserve">S4_direct.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
@@ -7305,14 +7305,14 @@
       </c>
       <c r="F218" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私とブランドの組み合わせ…最高じゃない</t>
+          <t xml:space="preserve">このままじゃ我慢の限界よ。考え直してもらえない？</t>
         </is>
       </c>
     </row>
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.seductive.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7322,12 +7322,12 @@
       </c>
       <c r="C219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.seductive.bold[1]</t>
+          <t xml:space="preserve">S4_silent.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
@@ -7337,14 +7337,14 @@
       </c>
       <c r="F219" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全国に私を見てもらえるのね。楽しみだわ</t>
+          <t xml:space="preserve">…………（笑みは崩さないまま、指先だけが強く握られている）</t>
         </is>
       </c>
     </row>
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.seductive.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7354,12 +7354,12 @@
       </c>
       <c r="C220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.seductive.bold[1]</t>
+          <t xml:space="preserve">S5.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
@@ -7369,14 +7369,14 @@
       </c>
       <c r="F220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ファンを喜ばせるのは得意よ。任せて</t>
+          <t xml:space="preserve">もっと強くなりたいの。特訓させてもらえる？</t>
         </is>
       </c>
     </row>
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.seductive.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="C221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.seductive.bold[1]</t>
+          <t xml:space="preserve">S6.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
@@ -7401,14 +7401,14 @@
       </c>
       <c r="F221" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ランウェイ、私のためにあるようなものよ</t>
+          <t xml:space="preserve">後輩の面倒、見させてもらえるかしら？</t>
         </is>
       </c>
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.seductive.bold[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7423,7 +7423,7 @@
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.seductive.bold[1]</t>
+          <t xml:space="preserve">B1.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
@@ -7433,14 +7433,14 @@
       </c>
       <c r="F222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私の本気の魅力、たっぷり撮ってもらうわ</t>
+          <t xml:space="preserve">こんなところで止まるつもりはないわ…すぐ戻る</t>
         </is>
       </c>
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.seductive.bold[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7455,7 +7455,7 @@
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.seductive.bold[1]</t>
+          <t xml:space="preserve">B2_fighter1.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
@@ -7465,14 +7465,14 @@
       </c>
       <c r="F223" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">バラエティでも私のペースで話すわ</t>
+          <t xml:space="preserve">あの人の態度、もう我慢できないの</t>
         </is>
       </c>
     </row>
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.seductive.bold[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7487,7 +7487,7 @@
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.seductive.bold[1]</t>
+          <t xml:space="preserve">B2_fighter2.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
@@ -7497,14 +7497,14 @@
       </c>
       <c r="F224" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全国に見てもらえるのね。楽しみだわ</t>
+          <t xml:space="preserve">黙ってるつもりはないわ。向こうが悪いんだから</t>
         </is>
       </c>
     </row>
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.seductive.bold[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7514,29 +7514,29 @@
       </c>
       <c r="C225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.bold[1]</t>
+          <t xml:space="preserve">B4_brand.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F225" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私を選んで。後悔はさせないわ</t>
+          <t xml:space="preserve">私とブランドの組み合わせ…最高じゃない</t>
         </is>
       </c>
     </row>
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.seductive.bold[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7546,29 +7546,29 @@
       </c>
       <c r="C226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.bold[1]</t>
+          <t xml:space="preserve">B4_cm.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F226" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオン、獲りに来たの。覚悟してて</t>
+          <t xml:space="preserve">全国に私を見てもらえるのね。楽しみだわ</t>
         </is>
       </c>
     </row>
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.seductive.bold[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7578,29 +7578,29 @@
       </c>
       <c r="C227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.bold[2]</t>
+          <t xml:space="preserve">B4_fan.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F227" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この団体、私が盛り上げてあげる</t>
+          <t xml:space="preserve">ファンを喜ばせるのは得意よ。任せて</t>
         </is>
       </c>
     </row>
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.seductive.bold[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7610,29 +7610,29 @@
       </c>
       <c r="C228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.bold[1]</t>
+          <t xml:space="preserve">B4_fashion.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F228" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">てっぺん獲りに来たの。一緒に頂点に立ちましょう</t>
+          <t xml:space="preserve">ランウェイ、私のためにあるようなものよ</t>
         </is>
       </c>
     </row>
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.seductive.bold[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7642,29 +7642,29 @@
       </c>
       <c r="C229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.bold[1]</t>
+          <t xml:space="preserve">B4_gravure.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F229" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頂点まで一直線よ。見ていてね</t>
+          <t xml:space="preserve">私の本気の魅力、たっぷり撮ってもらうわ</t>
         </is>
       </c>
     </row>
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.seductive.bold[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7674,29 +7674,29 @@
       </c>
       <c r="C230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.bold[1]</t>
+          <t xml:space="preserve">B4_variety.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F230" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんなことで止まると思ってる？ 甘いわ</t>
+          <t xml:space="preserve">バラエティでも私のペースで話すわ</t>
         </is>
       </c>
     </row>
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.seductive.bold[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7706,29 +7706,29 @@
       </c>
       <c r="C231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.bold[2]</t>
+          <t xml:space="preserve">B4.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F231" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">すぐ戻るわ。覚悟してなさい</t>
+          <t xml:space="preserve">全国に見てもらえるのね。楽しみだわ</t>
         </is>
       </c>
     </row>
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.seductive.bold[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="C232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.seductive.bold[1]</t>
+          <t xml:space="preserve">seductive.bold[1]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
@@ -7760,7 +7760,7 @@
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.seductive.bold[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="C233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.seductive.bold[1]</t>
+          <t xml:space="preserve">seductive.bold[1]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
@@ -7792,7 +7792,7 @@
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.seductive.bold[2]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7802,12 +7802,12 @@
       </c>
       <c r="C234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.seductive.bold[2]</t>
+          <t xml:space="preserve">seductive.bold[2]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
@@ -7824,7 +7824,7 @@
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.seductive.bold[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7834,12 +7834,12 @@
       </c>
       <c r="C235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.seductive.bold[1]</t>
+          <t xml:space="preserve">seductive.bold[1]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
@@ -7849,14 +7849,14 @@
       </c>
       <c r="F235" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">拾った目利きは正解よ。…すぐに分かるわ</t>
+          <t xml:space="preserve">てっぺん獲りに来たの。一緒に頂点に立ちましょう</t>
         </is>
       </c>
     </row>
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.seductive.bold[1]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="C236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.seductive.bold[1]</t>
+          <t xml:space="preserve">seductive.bold[1]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
@@ -7881,14 +7881,14 @@
       </c>
       <c r="F236" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">てっぺん獲りに来たの。一緒に頂点に立ちましょう</t>
+          <t xml:space="preserve">頂点まで一直線よ。見ていてね</t>
         </is>
       </c>
     </row>
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.seductive.bold[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -7898,12 +7898,12 @@
       </c>
       <c r="C237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.seductive.bold[1]</t>
+          <t xml:space="preserve">seductive.bold[1]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
@@ -7913,14 +7913,14 @@
       </c>
       <c r="F237" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頂点まで一直線よ。見ていてね</t>
+          <t xml:space="preserve">こんなことで止まると思ってる？ 甘いわ</t>
         </is>
       </c>
     </row>
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.seductive.bold[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -7930,12 +7930,12 @@
       </c>
       <c r="C238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.seductive.bold[1]</t>
+          <t xml:space="preserve">seductive.bold[2]</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
@@ -7945,14 +7945,14 @@
       </c>
       <c r="F238" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんなことで止まると思ってる？ 甘いわ</t>
+          <t xml:space="preserve">すぐ戻るわ。覚悟してなさい</t>
         </is>
       </c>
     </row>
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.seductive.bold[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -7967,7 +7967,7 @@
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.seductive.bold[2]</t>
+          <t xml:space="preserve">draftInterest.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
@@ -7977,14 +7977,14 @@
       </c>
       <c r="F239" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">すぐ戻るわ。覚悟してなさい</t>
+          <t xml:space="preserve">私を選んで。後悔はさせないわ</t>
         </is>
       </c>
     </row>
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.seductive.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -7999,7 +7999,7 @@
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.seductive.bold[1]</t>
+          <t xml:space="preserve">draftJoin.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
@@ -8009,14 +8009,14 @@
       </c>
       <c r="F240" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しいわ…でも、いつか必ず戻ってくる</t>
+          <t xml:space="preserve">チャンピオン、獲りに来たの。覚悟してて</t>
         </is>
       </c>
     </row>
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.seductive.bold[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -8031,7 +8031,7 @@
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.seductive.bold[2]</t>
+          <t xml:space="preserve">draftJoin.seductive.bold[2]</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
@@ -8041,14 +8041,14 @@
       </c>
       <c r="F241" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この借り、いつか返しに来るから</t>
+          <t xml:space="preserve">この団体、私が盛り上げてあげる</t>
         </is>
       </c>
     </row>
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.seductive.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8063,7 +8063,7 @@
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.seductive.bold[1]</t>
+          <t xml:space="preserve">faGreeting.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
@@ -8073,14 +8073,14 @@
       </c>
       <c r="F242" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">レンタルでも全力よ。見ていてね</t>
+          <t xml:space="preserve">拾った目利きは正解よ。…すぐに分かるわ</t>
         </is>
       </c>
     </row>
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.seductive.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -8095,7 +8095,7 @@
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.seductive.bold[1]</t>
+          <t xml:space="preserve">faSigning.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E243" t="inlineStr" s="2">
@@ -8105,14 +8105,14 @@
       </c>
       <c r="F243" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私に声をかけた責任は、取ってちょうだいね</t>
+          <t xml:space="preserve">てっぺん獲りに来たの。一緒に頂点に立ちましょう</t>
         </is>
       </c>
     </row>
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.seductive.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8127,7 +8127,7 @@
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.seductive.bold[1]</t>
+          <t xml:space="preserve">faWelcome.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
@@ -8137,14 +8137,14 @@
       </c>
       <c r="F244" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…今日は認めるわ。でもこの借り、必ず返す</t>
+          <t xml:space="preserve">頂点まで一直線よ。見ていてね</t>
         </is>
       </c>
     </row>
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.seductive.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8159,7 +8159,7 @@
       </c>
       <c r="D245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.seductive.bold[1]</t>
+          <t xml:space="preserve">injury.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
@@ -8169,14 +8169,14 @@
       </c>
       <c r="F245" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ誰も私を超えられないわね。当然でしょう</t>
+          <t xml:space="preserve">こんなことで止まると思ってる？ 甘いわ</t>
         </is>
       </c>
     </row>
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.seductive.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8191,7 +8191,7 @@
       </c>
       <c r="D246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.seductive.bold[1]</t>
+          <t xml:space="preserve">injury.seductive.bold[2]</t>
         </is>
       </c>
       <c r="E246" t="inlineStr" s="2">
@@ -8201,14 +8201,14 @@
       </c>
       <c r="F246" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…覚えておきなさい。すぐに返してもらうわ</t>
+          <t xml:space="preserve">すぐ戻るわ。覚悟してなさい</t>
         </is>
       </c>
     </row>
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.seductive.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8223,7 +8223,7 @@
       </c>
       <c r="D247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.seductive.bold[1]</t>
+          <t xml:space="preserve">release.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E247" t="inlineStr" s="2">
@@ -8233,14 +8233,14 @@
       </c>
       <c r="F247" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">これが始まりよ。このベルトで時代を作る</t>
+          <t xml:space="preserve">悔しいわ…でも、いつか必ず戻ってくる</t>
         </is>
       </c>
     </row>
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.seductive.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8250,12 +8250,12 @@
       </c>
       <c r="C248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.bold[1]</t>
+          <t xml:space="preserve">release.seductive.bold[2]</t>
         </is>
       </c>
       <c r="E248" t="inlineStr" s="2">
@@ -8265,14 +8265,14 @@
       </c>
       <c r="F248" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しいわ…でも、いつか必ず戻ってくる</t>
+          <t xml:space="preserve">この借り、いつか返しに来るから</t>
         </is>
       </c>
     </row>
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.seductive.bold[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8282,12 +8282,12 @@
       </c>
       <c r="C249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.bold[2]</t>
+          <t xml:space="preserve">rentalGreeting.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E249" t="inlineStr" s="2">
@@ -8297,14 +8297,14 @@
       </c>
       <c r="F249" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この借り、いつか返しに来るから</t>
+          <t xml:space="preserve">レンタルでも全力よ。見ていてね</t>
         </is>
       </c>
     </row>
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.seductive.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8314,12 +8314,12 @@
       </c>
       <c r="C250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.bold[1]</t>
+          <t xml:space="preserve">scoutGreeting.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E250" t="inlineStr" s="2">
@@ -8329,14 +8329,14 @@
       </c>
       <c r="F250" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">レンタルでも全力よ。見ていてね</t>
+          <t xml:space="preserve">私に声をかけた責任は、取ってちょうだいね</t>
         </is>
       </c>
     </row>
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.seductive.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8346,12 +8346,12 @@
       </c>
       <c r="C251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.bold[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E251" t="inlineStr" s="2">
@@ -8368,7 +8368,7 @@
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.seductive.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8378,12 +8378,12 @@
       </c>
       <c r="C252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.bold[1]</t>
+          <t xml:space="preserve">titleDefense.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E252" t="inlineStr" s="2">
@@ -8400,7 +8400,7 @@
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.seductive.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8410,12 +8410,12 @@
       </c>
       <c r="C253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.bold[1]</t>
+          <t xml:space="preserve">titleLoss.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E253" t="inlineStr" s="2">
@@ -8432,7 +8432,7 @@
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.seductive.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8442,12 +8442,12 @@
       </c>
       <c r="C254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.bold[1]</t>
+          <t xml:space="preserve">titleWin.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="2">
@@ -8464,7 +8464,7 @@
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.bold.seductive[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8474,29 +8474,29 @@
       </c>
       <c r="C255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D255" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.bold.seductive[1]</t>
+          <t xml:space="preserve">seductive.bold[1]</t>
         </is>
       </c>
       <c r="E255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F255" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">合わないわ。どうしても合わないの</t>
+          <t xml:space="preserve">悔しいわ…でも、いつか必ず戻ってくる</t>
         </is>
       </c>
     </row>
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.bold.seductive[2]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8506,29 +8506,29 @@
       </c>
       <c r="C256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.bold.seductive[2]</t>
+          <t xml:space="preserve">seductive.bold[2]</t>
         </is>
       </c>
       <c r="E256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F256" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">これ以上は無理ね。それだけよ</t>
+          <t xml:space="preserve">この借り、いつか返しに来るから</t>
         </is>
       </c>
     </row>
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.bold.seductive[1]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8538,29 +8538,29 @@
       </c>
       <c r="C257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D257" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.bold.seductive[1]</t>
+          <t xml:space="preserve">seductive.bold[1]</t>
         </is>
       </c>
       <c r="E257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F257" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">壁を作ってない？ 気に入らないわ</t>
+          <t xml:space="preserve">レンタルでも全力よ。見ていてね</t>
         </is>
       </c>
     </row>
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.bold.seductive[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8570,29 +8570,29 @@
       </c>
       <c r="C258" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D258" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.bold.seductive[2]</t>
+          <t xml:space="preserve">seductive.bold[1]</t>
         </is>
       </c>
       <c r="E258" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F258" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">前はもっと話してくれたのに。…どうしたのかしら</t>
+          <t xml:space="preserve">…今日は認めるわ。でもこの借り、必ず返す</t>
         </is>
       </c>
     </row>
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.bold.seductive[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8602,29 +8602,29 @@
       </c>
       <c r="C259" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.bold.seductive[1]</t>
+          <t xml:space="preserve">seductive.bold[1]</t>
         </is>
       </c>
       <c r="E259" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F259" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">気に入ったわ。なかなか味のある人ね</t>
+          <t xml:space="preserve">まだ誰も私を超えられないわね。当然でしょう</t>
         </is>
       </c>
     </row>
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.bold.seductive[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8634,29 +8634,29 @@
       </c>
       <c r="C260" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.bold.seductive[1]</t>
+          <t xml:space="preserve">seductive.bold[1]</t>
         </is>
       </c>
       <c r="E260" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F260" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高のコンビネーションよ、私たち</t>
+          <t xml:space="preserve">…覚えておきなさい。すぐに返してもらうわ</t>
         </is>
       </c>
     </row>
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.bold.seductive[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8666,29 +8666,29 @@
       </c>
       <c r="C261" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.bold.seductive[1]</t>
+          <t xml:space="preserve">seductive.bold[1]</t>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F261" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……もう終わったことよ</t>
+          <t xml:space="preserve">これが始まりよ。このベルトで時代を作る</t>
         </is>
       </c>
     </row>
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.bold.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8703,7 +8703,7 @@
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.bold.seductive[2]</t>
+          <t xml:space="preserve">bond_39_down.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E262" t="inlineStr" s="2">
@@ -8713,14 +8713,14 @@
       </c>
       <c r="F262" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決着はついたわ。次に進むの</t>
+          <t xml:space="preserve">合わないわ。どうしても合わないの</t>
         </is>
       </c>
     </row>
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.bold.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.bold.seductive[2]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8735,7 +8735,7 @@
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.bold.seductive[1]</t>
+          <t xml:space="preserve">bond_39_down.bold.seductive[2]</t>
         </is>
       </c>
       <c r="E263" t="inlineStr" s="2">
@@ -8745,14 +8745,14 @@
       </c>
       <c r="F263" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">なかなかの逸材ね。ふふ、楽しみ</t>
+          <t xml:space="preserve">これ以上は無理ね。それだけよ</t>
         </is>
       </c>
     </row>
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.bold.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8767,7 +8767,7 @@
       </c>
       <c r="D264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.bold.seductive[1]</t>
+          <t xml:space="preserve">bond_59_down.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E264" t="inlineStr" s="2">
@@ -8777,14 +8777,14 @@
       </c>
       <c r="F264" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全力を出せる相手。最高の敵ね、ふふ</t>
+          <t xml:space="preserve">壁を作ってない？ 気に入らないわ</t>
         </is>
       </c>
     </row>
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.bold.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.bold.seductive[2]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8799,7 +8799,7 @@
       </c>
       <c r="D265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.bold.seductive[2]</t>
+          <t xml:space="preserve">bond_59_down.bold.seductive[2]</t>
         </is>
       </c>
       <c r="E265" t="inlineStr" s="2">
@@ -8809,14 +8809,14 @@
       </c>
       <c r="F265" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">超える。それが今の私の全てよ</t>
+          <t xml:space="preserve">前はもっと話してくれたのに。…どうしたのかしら</t>
         </is>
       </c>
     </row>
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.bold.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="D266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.bold.seductive[1]</t>
+          <t xml:space="preserve">bond_60_up.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E266" t="inlineStr" s="2">
@@ -8841,14 +8841,14 @@
       </c>
       <c r="F266" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの人がいたから強くなれたの。感謝してる…でも負けないわ</t>
+          <t xml:space="preserve">気に入ったわ。なかなか味のある人ね</t>
         </is>
       </c>
     </row>
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.bold.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -8863,7 +8863,7 @@
       </c>
       <c r="D267" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.bold.seductive[2]</t>
+          <t xml:space="preserve">bond_80_up.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E267" t="inlineStr" s="2">
@@ -8873,14 +8873,14 @@
       </c>
       <c r="F267" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この戦いに終わりはない。…望むところね</t>
+          <t xml:space="preserve">最高のコンビネーションよ、私たち</t>
         </is>
       </c>
     </row>
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.bold.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -8895,7 +8895,7 @@
       </c>
       <c r="D268" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.bold.seductive[1]</t>
+          <t xml:space="preserve">rivalry_29_down.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E268" t="inlineStr" s="2">
@@ -8905,14 +8905,14 @@
       </c>
       <c r="F268" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここが最高の場所。私がもっと強くしてみせるわ</t>
+          <t xml:space="preserve">……もう終わったことよ</t>
         </is>
       </c>
     </row>
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.bold.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.bold.seductive[2]</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -8927,7 +8927,7 @@
       </c>
       <c r="D269" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.bold.seductive[2]</t>
+          <t xml:space="preserve">rivalry_29_down.bold.seductive[2]</t>
         </is>
       </c>
       <c r="E269" t="inlineStr" s="2">
@@ -8937,14 +8937,14 @@
       </c>
       <c r="F269" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この団体を背負っていく覚悟はできてるの</t>
+          <t xml:space="preserve">決着はついたわ。次に進むの</t>
         </is>
       </c>
     </row>
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.bold.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -8959,7 +8959,7 @@
       </c>
       <c r="D270" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.bold.seductive[1]</t>
+          <t xml:space="preserve">rivalry_30_up.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E270" t="inlineStr" s="2">
@@ -8969,14 +8969,14 @@
       </c>
       <c r="F270" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふざけないで。私の価値がわからないなら、もう付き合いきれないわ</t>
+          <t xml:space="preserve">なかなかの逸材ね。ふふ、楽しみ</t>
         </is>
       </c>
     </row>
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.bold.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -8991,7 +8991,7 @@
       </c>
       <c r="D271" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.bold.seductive[2]</t>
+          <t xml:space="preserve">rivalry_50_up.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E271" t="inlineStr" s="2">
@@ -9001,14 +9001,14 @@
       </c>
       <c r="F271" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この扱い、許すつもりはないの。忘れないことね</t>
+          <t xml:space="preserve">全力を出せる相手。最高の敵ね、ふふ</t>
         </is>
       </c>
     </row>
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.bold.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.bold.seductive[2]</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -9023,7 +9023,7 @@
       </c>
       <c r="D272" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.bold.seductive[1]</t>
+          <t xml:space="preserve">rivalry_50_up.bold.seductive[2]</t>
         </is>
       </c>
       <c r="E272" t="inlineStr" s="2">
@@ -9033,14 +9033,14 @@
       </c>
       <c r="F272" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この扱いは何かしら。私の実力、わかってるの？</t>
+          <t xml:space="preserve">超える。それが今の私の全てよ</t>
         </is>
       </c>
     </row>
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.bold.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -9055,7 +9055,7 @@
       </c>
       <c r="D273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.bold.seductive[2]</t>
+          <t xml:space="preserve">rivalry_70_up.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E273" t="inlineStr" s="2">
@@ -9065,14 +9065,14 @@
       </c>
       <c r="F273" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここにいていいのか…考え直す時期かもね</t>
+          <t xml:space="preserve">あの人がいたから強くなれたの。感謝してる…でも負けないわ</t>
         </is>
       </c>
     </row>
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.seductive.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.bold.seductive[2]</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="C274" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.bold[1]</t>
+          <t xml:space="preserve">rivalry_70_up.bold.seductive[2]</t>
         </is>
       </c>
       <c r="E274" t="inlineStr" s="2">
@@ -9097,14 +9097,14 @@
       </c>
       <c r="F274" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、あの輝きも一度きり……なんて言うと思った？すぐに取り戻してみせるわ。</t>
+          <t xml:space="preserve">この戦いに終わりはない。…望むところね</t>
         </is>
       </c>
     </row>
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.seductive.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -9114,29 +9114,29 @@
       </c>
       <c r="C275" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.seductive.bold[1]</t>
+          <t xml:space="preserve">trust_above_75.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E275" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F275" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">満身創痍の私、悪くないでしょ？ この傷ごと、最後を飾るわ</t>
+          <t xml:space="preserve">ここが最高の場所。私がもっと強くしてみせるわ</t>
         </is>
       </c>
     </row>
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.seductive.bold[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.bold.seductive[2]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -9146,29 +9146,29 @@
       </c>
       <c r="C276" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.seductive.bold[2]</t>
+          <t xml:space="preserve">trust_above_75.bold.seductive[2]</t>
         </is>
       </c>
       <c r="E276" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F276" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで残ったんだもの。一番いいところ、見せてあげる</t>
+          <t xml:space="preserve">この団体を背負っていく覚悟はできてるの</t>
         </is>
       </c>
     </row>
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.seductive.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -9178,29 +9178,29 @@
       </c>
       <c r="C277" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.seductive.bold[1]</t>
+          <t xml:space="preserve">trust_below_20.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E277" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F277" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">相手は誰？ 何人来ても…最後まで残るのは、こっちよ</t>
+          <t xml:space="preserve">ふざけないで。私の価値がわからないなら、もう付き合いきれないわ</t>
         </is>
       </c>
     </row>
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.seductive.bold[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.bold.seductive[2]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -9210,29 +9210,29 @@
       </c>
       <c r="C278" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.seductive.bold[2]</t>
+          <t xml:space="preserve">trust_below_20.bold.seductive[2]</t>
         </is>
       </c>
       <c r="E278" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F278" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もっと骨のあるのを出してきて。全部相手にしてあげる</t>
+          <t xml:space="preserve">この扱い、許すつもりはないの。忘れないことね</t>
         </is>
       </c>
     </row>
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.seductive.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.bold.seductive[1]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -9242,29 +9242,29 @@
       </c>
       <c r="C279" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.seductive.bold[1]</t>
+          <t xml:space="preserve">trust_below_35.bold.seductive[1]</t>
         </is>
       </c>
       <c r="E279" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F279" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人、落としたわ。…でも、まだ足りないの。次、早く出してよ</t>
+          <t xml:space="preserve">この扱いは何かしら。私の実力、わかってるの？</t>
         </is>
       </c>
     </row>
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.seductive.bold[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.bold.seductive[2]</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -9274,29 +9274,29 @@
       </c>
       <c r="C280" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D280" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.seductive.bold[2]</t>
+          <t xml:space="preserve">trust_below_35.bold.seductive[2]</t>
         </is>
       </c>
       <c r="E280" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F280" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ立ってるの、見える？ 次の子、こっちにいらっしゃい。全部相手にしてあげる</t>
+          <t xml:space="preserve">ここにいていいのか…考え直す時期かもね</t>
         </is>
       </c>
     </row>
     <row r="281" ht="40" customHeight="1">
       <c r="A281" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.seductive.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -9306,29 +9306,29 @@
       </c>
       <c r="C281" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D281" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.seductive.bold[1]</t>
+          <t xml:space="preserve">seductive.bold[1]</t>
         </is>
       </c>
       <c r="E281" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F281" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この三人が最強だった。美しい勝利でしょ？</t>
+          <t xml:space="preserve">ふふ、あの輝きも一度きり……なんて言うと思った？すぐに取り戻してみせるわ。</t>
         </is>
       </c>
     </row>
     <row r="282" ht="40" customHeight="1">
       <c r="A282" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.seductive.bold[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -9338,12 +9338,12 @@
       </c>
       <c r="C282" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D282" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.seductive.bold[2]</t>
+          <t xml:space="preserve">preFinal.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E282" t="inlineStr" s="2">
@@ -9353,14 +9353,14 @@
       </c>
       <c r="F282" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仲間が繋いでくれた勝ちを、最後に飾ったの。良いチームだったわ</t>
+          <t xml:space="preserve">満身創痍の私、悪くないでしょ？ この傷ごと、最後を飾るわ</t>
         </is>
       </c>
     </row>
     <row r="283" ht="40" customHeight="1">
       <c r="A283" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.seductive.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -9370,12 +9370,12 @@
       </c>
       <c r="C283" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D283" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.seductive.bold[1]</t>
+          <t xml:space="preserve">preFinal.seductive.bold[2]</t>
         </is>
       </c>
       <c r="E283" t="inlineStr" s="2">
@@ -9385,14 +9385,14 @@
       </c>
       <c r="F283" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">賞はもらっておくわ。でも次は……もっと大きなものを奪いに行くから</t>
+          <t xml:space="preserve">ここまで残ったんだもの。一番いいところ、見せてあげる</t>
         </is>
       </c>
     </row>
     <row r="284" ht="40" customHeight="1">
       <c r="A284" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.seductive.bold[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -9402,12 +9402,12 @@
       </c>
       <c r="C284" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D284" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.seductive.bold[2]</t>
+          <t xml:space="preserve">preMatch.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E284" t="inlineStr" s="2">
@@ -9417,14 +9417,14 @@
       </c>
       <c r="F284" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この程度じゃ満たされない。次は全部、こっちのものにするわ</t>
+          <t xml:space="preserve">相手は誰？ 何人来ても…最後まで残るのは、こっちよ</t>
         </is>
       </c>
     </row>
     <row r="285" ht="40" customHeight="1">
       <c r="A285" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.seductive.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
@@ -9434,12 +9434,12 @@
       </c>
       <c r="C285" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D285" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.seductive.bold[1]</t>
+          <t xml:space="preserve">preMatch.seductive.bold[2]</t>
         </is>
       </c>
       <c r="E285" t="inlineStr" s="2">
@@ -9449,14 +9449,14 @@
       </c>
       <c r="F285" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何人でもいいわよ？ 最後にこの場所に立つのは、いつだって私だもの</t>
+          <t xml:space="preserve">もっと骨のあるのを出してきて。全部相手にしてあげる</t>
         </is>
       </c>
     </row>
     <row r="286" ht="40" customHeight="1">
       <c r="A286" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.seductive.bold[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
@@ -9466,12 +9466,12 @@
       </c>
       <c r="C286" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D286" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.seductive.bold[2]</t>
+          <t xml:space="preserve">survivor.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E286" t="inlineStr" s="2">
@@ -9481,14 +9481,14 @@
       </c>
       <c r="F286" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全員倒してきたの。まだ物足りないくらい</t>
+          <t xml:space="preserve">一人、落としたわ。…でも、まだ足りないの。次、早く出してよ</t>
         </is>
       </c>
     </row>
     <row r="287" ht="40" customHeight="1">
       <c r="A287" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.seductive.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C287" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D287" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.seductive.bold[1]</t>
+          <t xml:space="preserve">survivor.seductive.bold[2]</t>
         </is>
       </c>
       <c r="E287" t="inlineStr" s="2">
@@ -9513,14 +9513,14 @@
       </c>
       <c r="F287" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、優勝しちゃったわ。当然だけどね</t>
+          <t xml:space="preserve">まだ立ってるの、見える？ 次の子、こっちにいらっしゃい。全部相手にしてあげる</t>
         </is>
       </c>
     </row>
     <row r="288" ht="40" customHeight="1">
       <c r="A288" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.seductive.bold[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
@@ -9530,12 +9530,12 @@
       </c>
       <c r="C288" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D288" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.seductive.bold[2]</t>
+          <t xml:space="preserve">champion.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E288" t="inlineStr" s="2">
@@ -9545,14 +9545,14 @@
       </c>
       <c r="F288" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私が一番。それが証明されたわね</t>
+          <t xml:space="preserve">この三人が最強だった。美しい勝利でしょ？</t>
         </is>
       </c>
     </row>
     <row r="289" ht="40" customHeight="1">
       <c r="A289" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.seductive.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
@@ -9562,12 +9562,12 @@
       </c>
       <c r="C289" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D289" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.seductive.bold[1]</t>
+          <t xml:space="preserve">champion.seductive.bold[2]</t>
         </is>
       </c>
       <c r="E289" t="inlineStr" s="2">
@@ -9577,14 +9577,14 @@
       </c>
       <c r="F289" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悔しいわ。でも、私はここで終わらない</t>
+          <t xml:space="preserve">仲間が繋いでくれた勝ちを、最後に飾ったの。良いチームだったわ</t>
         </is>
       </c>
     </row>
     <row r="290" ht="40" customHeight="1">
       <c r="A290" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.seductive.bold[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="2">
@@ -9594,12 +9594,12 @@
       </c>
       <c r="C290" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D290" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.seductive.bold[2]</t>
+          <t xml:space="preserve">defiant.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E290" t="inlineStr" s="2">
@@ -9609,14 +9609,14 @@
       </c>
       <c r="F290" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次は必ず勝つわ</t>
+          <t xml:space="preserve">賞はもらっておくわ。でも次は……もっと大きなものを奪いに行くから</t>
         </is>
       </c>
     </row>
     <row r="291" ht="40" customHeight="1">
       <c r="A291" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.seductive.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="2">
@@ -9626,12 +9626,12 @@
       </c>
       <c r="C291" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D291" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.seductive.bold[1]</t>
+          <t xml:space="preserve">defiant.seductive.bold[2]</t>
         </is>
       </c>
       <c r="E291" t="inlineStr" s="2">
@@ -9641,14 +9641,14 @@
       </c>
       <c r="F291" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、もう終わり？ 物足りないわね</t>
+          <t xml:space="preserve">この程度じゃ満たされない。次は全部、こっちのものにするわ</t>
         </is>
       </c>
     </row>
     <row r="292" ht="40" customHeight="1">
       <c r="A292" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.seductive.bold[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="2">
@@ -9658,12 +9658,12 @@
       </c>
       <c r="C292" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D292" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.seductive.bold[2]</t>
+          <t xml:space="preserve">gauntlet.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E292" t="inlineStr" s="2">
@@ -9673,14 +9673,14 @@
       </c>
       <c r="F292" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、予定通りよ。次の相手が楽しみ</t>
+          <t xml:space="preserve">何人でもいいわよ？ 最後にこの場所に立つのは、いつだって私だもの</t>
         </is>
       </c>
     </row>
     <row r="293" ht="40" customHeight="1">
       <c r="A293" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.seductive.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="2">
@@ -9690,12 +9690,12 @@
       </c>
       <c r="C293" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D293" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.seductive.bold[1]</t>
+          <t xml:space="preserve">gauntlet.seductive.bold[2]</t>
         </is>
       </c>
       <c r="E293" t="inlineStr" s="2">
@@ -9705,14 +9705,14 @@
       </c>
       <c r="F293" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ足りないわね。もっと上に行くわ</t>
+          <t xml:space="preserve">全員倒してきたの。まだ物足りないくらい</t>
         </is>
       </c>
     </row>
     <row r="294" ht="40" customHeight="1">
       <c r="A294" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.seductive.bold[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B294" t="inlineStr" s="2">
@@ -9727,7 +9727,7 @@
       </c>
       <c r="D294" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.seductive.bold[2]</t>
+          <t xml:space="preserve">champion.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E294" t="inlineStr" s="2">
@@ -9737,14 +9737,14 @@
       </c>
       <c r="F294" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい舞台だったわ。でも、私はもっと上を目指す</t>
+          <t xml:space="preserve">あら、優勝しちゃったわ。当然だけどね</t>
         </is>
       </c>
     </row>
     <row r="295" ht="40" customHeight="1">
       <c r="A295" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.seductive.bold[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B295" t="inlineStr" s="2">
@@ -9759,7 +9759,7 @@
       </c>
       <c r="D295" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.seductive.bold[1]</t>
+          <t xml:space="preserve">champion.seductive.bold[2]</t>
         </is>
       </c>
       <c r="E295" t="inlineStr" s="2">
@@ -9769,14 +9769,14 @@
       </c>
       <c r="F295" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、最後のお相手ね。たっぷり楽しませてあげるわ</t>
+          <t xml:space="preserve">私が一番。それが証明されたわね</t>
         </is>
       </c>
     </row>
     <row r="296" ht="40" customHeight="1">
       <c r="A296" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.seductive.bold[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B296" t="inlineStr" s="2">
@@ -9791,7 +9791,7 @@
       </c>
       <c r="D296" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.seductive.bold[2]</t>
+          <t xml:space="preserve">postLose.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E296" t="inlineStr" s="2">
@@ -9801,14 +9801,14 @@
       </c>
       <c r="F296" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">優勝は私のもの。決まっていることよ</t>
+          <t xml:space="preserve">…悔しいわ。でも、私はここで終わらない</t>
         </is>
       </c>
     </row>
     <row r="297" ht="40" customHeight="1">
       <c r="A297" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.seductive.bold[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B297" t="inlineStr" s="2">
@@ -9823,7 +9823,7 @@
       </c>
       <c r="D297" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.seductive.bold[1]</t>
+          <t xml:space="preserve">postLose.seductive.bold[2]</t>
         </is>
       </c>
       <c r="E297" t="inlineStr" s="2">
@@ -9833,14 +9833,14 @@
       </c>
       <c r="F297" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、可愛い相手ね。すぐ終わらせてあげるわ</t>
+          <t xml:space="preserve">次は必ず勝つわ</t>
         </is>
       </c>
     </row>
     <row r="298" ht="40" customHeight="1">
       <c r="A298" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.seductive.bold[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B298" t="inlineStr" s="2">
@@ -9855,7 +9855,7 @@
       </c>
       <c r="D298" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.seductive.bold[2]</t>
+          <t xml:space="preserve">postMatchWin.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E298" t="inlineStr" s="2">
@@ -9865,14 +9865,14 @@
       </c>
       <c r="F298" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私に勝てるつもり？ 甘いわね</t>
+          <t xml:space="preserve">あら、もう終わり？ 物足りないわね</t>
         </is>
       </c>
     </row>
     <row r="299" ht="40" customHeight="1">
       <c r="A299" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.seductive.bold[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B299" t="inlineStr" s="2">
@@ -9887,7 +9887,7 @@
       </c>
       <c r="D299" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.seductive.bold[1]</t>
+          <t xml:space="preserve">postMatchWin.seductive.bold[2]</t>
         </is>
       </c>
       <c r="E299" t="inlineStr" s="2">
@@ -9897,14 +9897,14 @@
       </c>
       <c r="F299" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、指名してくれたの？ 嬉しいわ</t>
+          <t xml:space="preserve">ふふ、予定通りよ。次の相手が楽しみ</t>
         </is>
       </c>
     </row>
     <row r="300" ht="40" customHeight="1">
       <c r="A300" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.seductive.bold[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B300" t="inlineStr" s="2">
@@ -9919,7 +9919,7 @@
       </c>
       <c r="D300" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.seductive.bold[2]</t>
+          <t xml:space="preserve">postWin.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E300" t="inlineStr" s="2">
@@ -9929,14 +9929,14 @@
       </c>
       <c r="F300" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私の舞台が増えるのね。楽しみ</t>
+          <t xml:space="preserve">まだ足りないわね。もっと上に行くわ</t>
         </is>
       </c>
     </row>
     <row r="301" ht="40" customHeight="1">
       <c r="A301" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.seductive.bold[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B301" t="inlineStr" s="2">
@@ -9946,12 +9946,12 @@
       </c>
       <c r="C301" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D301" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.bold[1]</t>
+          <t xml:space="preserve">postWin.seductive.bold[2]</t>
         </is>
       </c>
       <c r="E301" t="inlineStr" s="2">
@@ -9961,14 +9961,14 @@
       </c>
       <c r="F301" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">容赦しないわよ。覚悟してね</t>
+          <t xml:space="preserve">いい舞台だったわ。でも、私はもっと上を目指す</t>
         </is>
       </c>
     </row>
     <row r="302" ht="40" customHeight="1">
       <c r="A302" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.seductive.bold[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B302" t="inlineStr" s="2">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="C302" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D302" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.bold[1]</t>
+          <t xml:space="preserve">preFinal.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E302" t="inlineStr" s="2">
@@ -9993,14 +9993,14 @@
       </c>
       <c r="F302" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ずっと待ってたのよ、この瞬間を……！ふふ、最高の気分ね</t>
+          <t xml:space="preserve">あら、最後のお相手ね。たっぷり楽しませてあげるわ</t>
         </is>
       </c>
     </row>
     <row r="303" ht="40" customHeight="1">
       <c r="A303" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.seductive.bold[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B303" t="inlineStr" s="2">
@@ -10010,12 +10010,12 @@
       </c>
       <c r="C303" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D303" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.bold[1]</t>
+          <t xml:space="preserve">preFinal.seductive.bold[2]</t>
         </is>
       </c>
       <c r="E303" t="inlineStr" s="2">
@@ -10025,14 +10025,14 @@
       </c>
       <c r="F303" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら…随分と自信がおありのようね。壊してあげるわ</t>
+          <t xml:space="preserve">優勝は私のもの。決まっていることよ</t>
         </is>
       </c>
     </row>
     <row r="304" ht="40" customHeight="1">
       <c r="A304" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.seductive.bold[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B304" t="inlineStr" s="2">
@@ -10042,12 +10042,12 @@
       </c>
       <c r="C304" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D304" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.bold[2]</t>
+          <t xml:space="preserve">preMatch.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E304" t="inlineStr" s="2">
@@ -10057,14 +10057,14 @@
       </c>
       <c r="F304" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">可哀想だけど…手加減はしないわよ</t>
+          <t xml:space="preserve">あら、可愛い相手ね。すぐ終わらせてあげるわ</t>
         </is>
       </c>
     </row>
     <row r="305" ht="40" customHeight="1">
       <c r="A305" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.seductive.bold[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B305" t="inlineStr" s="2">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="C305" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D305" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.bold[1]</t>
+          <t xml:space="preserve">preMatch.seductive.bold[2]</t>
         </is>
       </c>
       <c r="E305" t="inlineStr" s="2">
@@ -10089,14 +10089,14 @@
       </c>
       <c r="F305" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、残念。もっと遊びたかったのに</t>
+          <t xml:space="preserve">私に勝てるつもり？ 甘いわね</t>
         </is>
       </c>
     </row>
     <row r="306" ht="40" customHeight="1">
       <c r="A306" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.seductive.bold[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B306" t="inlineStr" s="2">
@@ -10106,12 +10106,12 @@
       </c>
       <c r="C306" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D306" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.bold[2]</t>
+          <t xml:space="preserve">summon.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E306" t="inlineStr" s="2">
@@ -10121,14 +10121,14 @@
       </c>
       <c r="F306" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">逃げちゃうの？ …つまらない団体ね</t>
+          <t xml:space="preserve">あら、指名してくれたの？ 嬉しいわ</t>
         </is>
       </c>
     </row>
     <row r="307" ht="40" customHeight="1">
       <c r="A307" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.seductive.bold[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B307" t="inlineStr" s="2">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="C307" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D307" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.seductive.bold[1]</t>
+          <t xml:space="preserve">summon.seductive.bold[2]</t>
         </is>
       </c>
       <c r="E307" t="inlineStr" s="2">
@@ -10153,14 +10153,14 @@
       </c>
       <c r="F307" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら…やられちゃったわ。……許さないけど</t>
+          <t xml:space="preserve">私の舞台が増えるのね。楽しみ</t>
         </is>
       </c>
     </row>
     <row r="308" ht="40" customHeight="1">
       <c r="A308" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.seductive.bold[2]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B308" t="inlineStr" s="2">
@@ -10170,12 +10170,12 @@
       </c>
       <c r="C308" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D308" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.seductive.bold[2]</t>
+          <t xml:space="preserve">seductive.bold[1]</t>
         </is>
       </c>
       <c r="E308" t="inlineStr" s="2">
@@ -10185,14 +10185,14 @@
       </c>
       <c r="F308" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日は譲ってあげるわ。次は…ないけどね</t>
+          <t xml:space="preserve">容赦しないわよ。覚悟してね</t>
         </is>
       </c>
     </row>
     <row r="309" ht="40" customHeight="1">
       <c r="A309" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.seductive.bold[1]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B309" t="inlineStr" s="2">
@@ -10202,12 +10202,12 @@
       </c>
       <c r="C309" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D309" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.seductive.bold[1]</t>
+          <t xml:space="preserve">seductive.bold[1]</t>
         </is>
       </c>
       <c r="E309" t="inlineStr" s="2">
@@ -10217,14 +10217,14 @@
       </c>
       <c r="F309" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、もう終わり？ もっと楽しみたかったのに</t>
+          <t xml:space="preserve">ずっと待ってたのよ、この瞬間を……！ふふ、最高の気分ね</t>
         </is>
       </c>
     </row>
     <row r="310" ht="40" customHeight="1">
       <c r="A310" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.seductive.bold[2]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B310" t="inlineStr" s="2">
@@ -10234,12 +10234,12 @@
       </c>
       <c r="C310" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D310" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.seductive.bold[2]</t>
+          <t xml:space="preserve">seductive.bold[1]</t>
         </is>
       </c>
       <c r="E310" t="inlineStr" s="2">
@@ -10249,14 +10249,14 @@
       </c>
       <c r="F310" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">予想通りの結果ね。つまらないわ</t>
+          <t xml:space="preserve">あら…随分と自信がおありのようね。壊してあげるわ</t>
         </is>
       </c>
     </row>
     <row r="311" ht="40" customHeight="1">
       <c r="A311" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.seductive.bold[1]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B311" t="inlineStr" s="2">
@@ -10266,12 +10266,12 @@
       </c>
       <c r="C311" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D311" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.bold[1]</t>
+          <t xml:space="preserve">seductive.bold[2]</t>
         </is>
       </c>
       <c r="E311" t="inlineStr" s="2">
@@ -10281,14 +10281,14 @@
       </c>
       <c r="F311" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">当然よ。うちの団体を甘く見ないことね</t>
+          <t xml:space="preserve">可哀想だけど…手加減はしないわよ</t>
         </is>
       </c>
     </row>
     <row r="312" ht="40" customHeight="1">
       <c r="A312" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.seductive.bold[2]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B312" t="inlineStr" s="2">
@@ -10298,12 +10298,12 @@
       </c>
       <c r="C312" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D312" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.bold[2]</t>
+          <t xml:space="preserve">seductive.bold[1]</t>
         </is>
       </c>
       <c r="E312" t="inlineStr" s="2">
@@ -10313,14 +10313,14 @@
       </c>
       <c r="F312" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ物足りないわね。もっと強い相手はいないの？</t>
+          <t xml:space="preserve">あら、残念。もっと遊びたかったのに</t>
         </is>
       </c>
     </row>
     <row r="313" ht="40" customHeight="1">
       <c r="A313" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.seductive.bold[3]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B313" t="inlineStr" s="2">
@@ -10330,12 +10330,12 @@
       </c>
       <c r="C313" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D313" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.bold[3]</t>
+          <t xml:space="preserve">seductive.bold[2]</t>
         </is>
       </c>
       <c r="E313" t="inlineStr" s="2">
@@ -10345,14 +10345,14 @@
       </c>
       <c r="F313" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">当然の結果よ。うちを甘く見ないことね</t>
+          <t xml:space="preserve">逃げちゃうの？ …つまらない団体ね</t>
         </is>
       </c>
     </row>
     <row r="314" ht="40" customHeight="1">
       <c r="A314" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.seductive.bold[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B314" t="inlineStr" s="2">
@@ -10362,29 +10362,29 @@
       </c>
       <c r="C314" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D314" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.seductive.bold[1]</t>
+          <t xml:space="preserve">result_lose.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E314" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F314" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頂点に立ったわ。でもまだ先があるみたいね</t>
+          <t xml:space="preserve">あら…やられちゃったわ。……許さないけど</t>
         </is>
       </c>
     </row>
     <row r="315" ht="40" customHeight="1">
       <c r="A315" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.seductive.bold[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B315" t="inlineStr" s="2">
@@ -10394,59 +10394,283 @@
       </c>
       <c r="C315" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D315" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.bold[1]</t>
+          <t xml:space="preserve">result_lose.seductive.bold[2]</t>
         </is>
       </c>
       <c r="E315" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F315" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">拾った目利きは正解よ。…すぐに分かるわ</t>
+          <t xml:space="preserve">今日は譲ってあげるわ。次は…ないけどね</t>
         </is>
       </c>
     </row>
     <row r="316" ht="40" customHeight="1">
       <c r="A316" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.seductive.bold[1]</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_win.seductive.bold[1]</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あら、もう終わり？ もっと楽しみたかったのに</t>
+        </is>
+      </c>
+    </row>
+    <row r="317" ht="40" customHeight="1">
+      <c r="A317" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.seductive.bold[2]</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_win.seductive.bold[2]</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">予想通りの結果ね。つまらないわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="318" ht="40" customHeight="1">
+      <c r="A318" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.seductive.bold[1]</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">seductive.bold[1]</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">当然よ。うちの団体を甘く見ないことね</t>
+        </is>
+      </c>
+    </row>
+    <row r="319" ht="40" customHeight="1">
+      <c r="A319" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.seductive.bold[2]</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">seductive.bold[2]</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">まだ物足りないわね。もっと強い相手はいないの？</t>
+        </is>
+      </c>
+    </row>
+    <row r="320" ht="40" customHeight="1">
+      <c r="A320" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.seductive.bold[3]</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">seductive.bold[3]</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">当然の結果よ。うちを甘く見ないことね</t>
+        </is>
+      </c>
+    </row>
+    <row r="321" ht="40" customHeight="1">
+      <c r="A321" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">ENDING_LINES.fighter.seductive.bold[1]</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ENDING_LINES</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">fighter.seductive.bold[1]</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">頂点に立ったわ。でもまだ先があるみたいね</t>
+        </is>
+      </c>
+    </row>
+    <row r="322" ht="40" customHeight="1">
+      <c r="A322" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.seductive.bold[1]</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">seductive.bold[1]</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">拾った目利きは正解よ。…すぐに分かるわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="323" ht="40" customHeight="1">
+      <c r="A323" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES.seductive.bold[1]</t>
         </is>
       </c>
-      <c r="B316" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C316" t="inlineStr" s="2">
+      <c r="B323" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
-      <c r="D316" t="inlineStr" s="12">
+      <c r="D323" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">seductive.bold[1]</t>
         </is>
       </c>
-      <c r="E316" t="inlineStr" s="2">
+      <c r="E323" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
-      <c r="F316" t="inlineStr" s="3">
+      <c r="F323" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">私に声をかけた責任は、取ってちょうだいね</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H316"/>
+  <autoFilter ref="A1:H323"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/蠱惑×強気.xlsx
+++ b/セリフ編集/キャラタイプ別/蠱惑×強気.xlsx
@@ -306,7 +306,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H316"/>
+  <dimension ref="A1:H320"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -9072,7 +9072,7 @@
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.seductive.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="C274" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.bold[1]</t>
+          <t xml:space="preserve">GL-01.goodLoss.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E274" t="inlineStr" s="2">
@@ -9097,14 +9097,14 @@
       </c>
       <c r="F274" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、あの輝きも一度きり……なんて言うと思った？すぐに取り戻してみせるわ。</t>
+          <t xml:space="preserve">ふふ……これは、これで、悪くないわね</t>
         </is>
       </c>
     </row>
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.seductive.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -9114,29 +9114,29 @@
       </c>
       <c r="C275" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.seductive.bold[1]</t>
+          <t xml:space="preserve">GL-01.greatWin.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E275" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F275" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">満身創痍の私、悪くないでしょ？ この傷ごと、最後を飾るわ</t>
+          <t xml:space="preserve">ふふ……最高の、夜ね</t>
         </is>
       </c>
     </row>
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.seductive.bold[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -9146,29 +9146,29 @@
       </c>
       <c r="C276" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.seductive.bold[2]</t>
+          <t xml:space="preserve">GL-01.loss.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E276" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F276" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで残ったんだもの。一番いいところ、見せてあげる</t>
+          <t xml:space="preserve">ふ……まだ、足りなかった、みたいね</t>
         </is>
       </c>
     </row>
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.seductive.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -9178,29 +9178,29 @@
       </c>
       <c r="C277" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.seductive.bold[1]</t>
+          <t xml:space="preserve">GL-01.win.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E277" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F277" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">相手は誰？ 何人来ても…最後まで残るのは、こっちよ</t>
+          <t xml:space="preserve">ふ……いい試合、だったわ</t>
         </is>
       </c>
     </row>
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.seductive.bold[2]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -9210,29 +9210,29 @@
       </c>
       <c r="C278" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.seductive.bold[2]</t>
+          <t xml:space="preserve">seductive.bold[1]</t>
         </is>
       </c>
       <c r="E278" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F278" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もっと骨のあるのを出してきて。全部相手にしてあげる</t>
+          <t xml:space="preserve">ふふ、あの輝きも一度きり……なんて言うと思った？すぐに取り戻してみせるわ。</t>
         </is>
       </c>
     </row>
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.seductive.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -9247,7 +9247,7 @@
       </c>
       <c r="D279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.seductive.bold[1]</t>
+          <t xml:space="preserve">preFinal.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E279" t="inlineStr" s="2">
@@ -9257,14 +9257,14 @@
       </c>
       <c r="F279" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人、落としたわ。…でも、まだ足りないの。次、早く出してよ</t>
+          <t xml:space="preserve">満身創痍の私、悪くないでしょ？ この傷ごと、最後を飾るわ</t>
         </is>
       </c>
     </row>
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.seductive.bold[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -9279,7 +9279,7 @@
       </c>
       <c r="D280" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.seductive.bold[2]</t>
+          <t xml:space="preserve">preFinal.seductive.bold[2]</t>
         </is>
       </c>
       <c r="E280" t="inlineStr" s="2">
@@ -9289,14 +9289,14 @@
       </c>
       <c r="F280" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ立ってるの、見える？ 次の子、こっちにいらっしゃい。全部相手にしてあげる</t>
+          <t xml:space="preserve">ここまで残ったんだもの。一番いいところ、見せてあげる</t>
         </is>
       </c>
     </row>
     <row r="281" ht="40" customHeight="1">
       <c r="A281" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.seductive.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -9306,12 +9306,12 @@
       </c>
       <c r="C281" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D281" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.seductive.bold[1]</t>
+          <t xml:space="preserve">preMatch.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E281" t="inlineStr" s="2">
@@ -9321,14 +9321,14 @@
       </c>
       <c r="F281" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この三人が最強だった。美しい勝利でしょ？</t>
+          <t xml:space="preserve">相手は誰？ 何人来ても…最後まで残るのは、こっちよ</t>
         </is>
       </c>
     </row>
     <row r="282" ht="40" customHeight="1">
       <c r="A282" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.seductive.bold[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -9338,12 +9338,12 @@
       </c>
       <c r="C282" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D282" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.seductive.bold[2]</t>
+          <t xml:space="preserve">preMatch.seductive.bold[2]</t>
         </is>
       </c>
       <c r="E282" t="inlineStr" s="2">
@@ -9353,14 +9353,14 @@
       </c>
       <c r="F282" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仲間が繋いでくれた勝ちを、最後に飾ったの。良いチームだったわ</t>
+          <t xml:space="preserve">もっと骨のあるのを出してきて。全部相手にしてあげる</t>
         </is>
       </c>
     </row>
     <row r="283" ht="40" customHeight="1">
       <c r="A283" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.seductive.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -9370,12 +9370,12 @@
       </c>
       <c r="C283" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D283" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.seductive.bold[1]</t>
+          <t xml:space="preserve">survivor.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E283" t="inlineStr" s="2">
@@ -9385,14 +9385,14 @@
       </c>
       <c r="F283" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">賞はもらっておくわ。でも次は……もっと大きなものを奪いに行くから</t>
+          <t xml:space="preserve">一人、落としたわ。…でも、まだ足りないの。次、早く出してよ</t>
         </is>
       </c>
     </row>
     <row r="284" ht="40" customHeight="1">
       <c r="A284" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.seductive.bold[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -9402,12 +9402,12 @@
       </c>
       <c r="C284" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D284" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.seductive.bold[2]</t>
+          <t xml:space="preserve">survivor.seductive.bold[2]</t>
         </is>
       </c>
       <c r="E284" t="inlineStr" s="2">
@@ -9417,14 +9417,14 @@
       </c>
       <c r="F284" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この程度じゃ満たされない。次は全部、こっちのものにするわ</t>
+          <t xml:space="preserve">まだ立ってるの、見える？ 次の子、こっちにいらっしゃい。全部相手にしてあげる</t>
         </is>
       </c>
     </row>
     <row r="285" ht="40" customHeight="1">
       <c r="A285" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.seductive.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
@@ -9439,7 +9439,7 @@
       </c>
       <c r="D285" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.seductive.bold[1]</t>
+          <t xml:space="preserve">champion.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E285" t="inlineStr" s="2">
@@ -9449,14 +9449,14 @@
       </c>
       <c r="F285" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何人でもいいわよ？ 最後にこの場所に立つのは、いつだって私だもの</t>
+          <t xml:space="preserve">この三人が最強だった。美しい勝利でしょ？</t>
         </is>
       </c>
     </row>
     <row r="286" ht="40" customHeight="1">
       <c r="A286" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.seductive.bold[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
@@ -9471,7 +9471,7 @@
       </c>
       <c r="D286" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.seductive.bold[2]</t>
+          <t xml:space="preserve">champion.seductive.bold[2]</t>
         </is>
       </c>
       <c r="E286" t="inlineStr" s="2">
@@ -9481,14 +9481,14 @@
       </c>
       <c r="F286" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全員倒してきたの。まだ物足りないくらい</t>
+          <t xml:space="preserve">仲間が繋いでくれた勝ちを、最後に飾ったの。良いチームだったわ</t>
         </is>
       </c>
     </row>
     <row r="287" ht="40" customHeight="1">
       <c r="A287" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.seductive.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C287" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D287" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.seductive.bold[1]</t>
+          <t xml:space="preserve">defiant.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E287" t="inlineStr" s="2">
@@ -9513,14 +9513,14 @@
       </c>
       <c r="F287" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、優勝しちゃったわ。当然だけどね</t>
+          <t xml:space="preserve">賞はもらっておくわ。でも次は……もっと大きなものを奪いに行くから</t>
         </is>
       </c>
     </row>
     <row r="288" ht="40" customHeight="1">
       <c r="A288" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.seductive.bold[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
@@ -9530,12 +9530,12 @@
       </c>
       <c r="C288" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D288" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.seductive.bold[2]</t>
+          <t xml:space="preserve">defiant.seductive.bold[2]</t>
         </is>
       </c>
       <c r="E288" t="inlineStr" s="2">
@@ -9545,14 +9545,14 @@
       </c>
       <c r="F288" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私が一番。それが証明されたわね</t>
+          <t xml:space="preserve">この程度じゃ満たされない。次は全部、こっちのものにするわ</t>
         </is>
       </c>
     </row>
     <row r="289" ht="40" customHeight="1">
       <c r="A289" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.seductive.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
@@ -9562,12 +9562,12 @@
       </c>
       <c r="C289" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D289" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.seductive.bold[1]</t>
+          <t xml:space="preserve">gauntlet.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E289" t="inlineStr" s="2">
@@ -9577,14 +9577,14 @@
       </c>
       <c r="F289" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悔しいわ。でも、私はここで終わらない</t>
+          <t xml:space="preserve">何人でもいいわよ？ 最後にこの場所に立つのは、いつだって私だもの</t>
         </is>
       </c>
     </row>
     <row r="290" ht="40" customHeight="1">
       <c r="A290" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.seductive.bold[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="2">
@@ -9594,12 +9594,12 @@
       </c>
       <c r="C290" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D290" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.seductive.bold[2]</t>
+          <t xml:space="preserve">gauntlet.seductive.bold[2]</t>
         </is>
       </c>
       <c r="E290" t="inlineStr" s="2">
@@ -9609,14 +9609,14 @@
       </c>
       <c r="F290" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次は必ず勝つわ</t>
+          <t xml:space="preserve">全員倒してきたの。まだ物足りないくらい</t>
         </is>
       </c>
     </row>
     <row r="291" ht="40" customHeight="1">
       <c r="A291" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.seductive.bold[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="2">
@@ -9631,7 +9631,7 @@
       </c>
       <c r="D291" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.seductive.bold[1]</t>
+          <t xml:space="preserve">champion.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E291" t="inlineStr" s="2">
@@ -9641,14 +9641,14 @@
       </c>
       <c r="F291" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、もう終わり？ 物足りないわね</t>
+          <t xml:space="preserve">あら、優勝しちゃったわ。当然だけどね</t>
         </is>
       </c>
     </row>
     <row r="292" ht="40" customHeight="1">
       <c r="A292" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.seductive.bold[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="2">
@@ -9663,7 +9663,7 @@
       </c>
       <c r="D292" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.seductive.bold[2]</t>
+          <t xml:space="preserve">champion.seductive.bold[2]</t>
         </is>
       </c>
       <c r="E292" t="inlineStr" s="2">
@@ -9673,14 +9673,14 @@
       </c>
       <c r="F292" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、予定通りよ。次の相手が楽しみ</t>
+          <t xml:space="preserve">私が一番。それが証明されたわね</t>
         </is>
       </c>
     </row>
     <row r="293" ht="40" customHeight="1">
       <c r="A293" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.seductive.bold[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="2">
@@ -9695,7 +9695,7 @@
       </c>
       <c r="D293" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.seductive.bold[1]</t>
+          <t xml:space="preserve">postLose.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E293" t="inlineStr" s="2">
@@ -9705,14 +9705,14 @@
       </c>
       <c r="F293" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ足りないわね。もっと上に行くわ</t>
+          <t xml:space="preserve">…悔しいわ。でも、私はここで終わらない</t>
         </is>
       </c>
     </row>
     <row r="294" ht="40" customHeight="1">
       <c r="A294" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.seductive.bold[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B294" t="inlineStr" s="2">
@@ -9727,7 +9727,7 @@
       </c>
       <c r="D294" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.seductive.bold[2]</t>
+          <t xml:space="preserve">postLose.seductive.bold[2]</t>
         </is>
       </c>
       <c r="E294" t="inlineStr" s="2">
@@ -9737,14 +9737,14 @@
       </c>
       <c r="F294" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい舞台だったわ。でも、私はもっと上を目指す</t>
+          <t xml:space="preserve">次は必ず勝つわ</t>
         </is>
       </c>
     </row>
     <row r="295" ht="40" customHeight="1">
       <c r="A295" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.seductive.bold[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B295" t="inlineStr" s="2">
@@ -9759,7 +9759,7 @@
       </c>
       <c r="D295" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.seductive.bold[1]</t>
+          <t xml:space="preserve">postMatchWin.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E295" t="inlineStr" s="2">
@@ -9769,14 +9769,14 @@
       </c>
       <c r="F295" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、最後のお相手ね。たっぷり楽しませてあげるわ</t>
+          <t xml:space="preserve">あら、もう終わり？ 物足りないわね</t>
         </is>
       </c>
     </row>
     <row r="296" ht="40" customHeight="1">
       <c r="A296" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.seductive.bold[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B296" t="inlineStr" s="2">
@@ -9791,7 +9791,7 @@
       </c>
       <c r="D296" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.seductive.bold[2]</t>
+          <t xml:space="preserve">postMatchWin.seductive.bold[2]</t>
         </is>
       </c>
       <c r="E296" t="inlineStr" s="2">
@@ -9801,14 +9801,14 @@
       </c>
       <c r="F296" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">優勝は私のもの。決まっていることよ</t>
+          <t xml:space="preserve">ふふ、予定通りよ。次の相手が楽しみ</t>
         </is>
       </c>
     </row>
     <row r="297" ht="40" customHeight="1">
       <c r="A297" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.seductive.bold[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B297" t="inlineStr" s="2">
@@ -9823,7 +9823,7 @@
       </c>
       <c r="D297" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.seductive.bold[1]</t>
+          <t xml:space="preserve">postWin.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E297" t="inlineStr" s="2">
@@ -9833,14 +9833,14 @@
       </c>
       <c r="F297" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、可愛い相手ね。すぐ終わらせてあげるわ</t>
+          <t xml:space="preserve">まだ足りないわね。もっと上に行くわ</t>
         </is>
       </c>
     </row>
     <row r="298" ht="40" customHeight="1">
       <c r="A298" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.seductive.bold[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B298" t="inlineStr" s="2">
@@ -9855,7 +9855,7 @@
       </c>
       <c r="D298" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.seductive.bold[2]</t>
+          <t xml:space="preserve">postWin.seductive.bold[2]</t>
         </is>
       </c>
       <c r="E298" t="inlineStr" s="2">
@@ -9865,14 +9865,14 @@
       </c>
       <c r="F298" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私に勝てるつもり？ 甘いわね</t>
+          <t xml:space="preserve">いい舞台だったわ。でも、私はもっと上を目指す</t>
         </is>
       </c>
     </row>
     <row r="299" ht="40" customHeight="1">
       <c r="A299" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.seductive.bold[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B299" t="inlineStr" s="2">
@@ -9887,7 +9887,7 @@
       </c>
       <c r="D299" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.seductive.bold[1]</t>
+          <t xml:space="preserve">preFinal.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E299" t="inlineStr" s="2">
@@ -9897,14 +9897,14 @@
       </c>
       <c r="F299" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、指名してくれたの？ 嬉しいわ</t>
+          <t xml:space="preserve">あら、最後のお相手ね。たっぷり楽しませてあげるわ</t>
         </is>
       </c>
     </row>
     <row r="300" ht="40" customHeight="1">
       <c r="A300" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.seductive.bold[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B300" t="inlineStr" s="2">
@@ -9919,7 +9919,7 @@
       </c>
       <c r="D300" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.seductive.bold[2]</t>
+          <t xml:space="preserve">preFinal.seductive.bold[2]</t>
         </is>
       </c>
       <c r="E300" t="inlineStr" s="2">
@@ -9929,14 +9929,14 @@
       </c>
       <c r="F300" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私の舞台が増えるのね。楽しみ</t>
+          <t xml:space="preserve">優勝は私のもの。決まっていることよ</t>
         </is>
       </c>
     </row>
     <row r="301" ht="40" customHeight="1">
       <c r="A301" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.seductive.bold[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B301" t="inlineStr" s="2">
@@ -9946,12 +9946,12 @@
       </c>
       <c r="C301" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D301" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.bold[1]</t>
+          <t xml:space="preserve">preMatch.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E301" t="inlineStr" s="2">
@@ -9961,14 +9961,14 @@
       </c>
       <c r="F301" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">容赦しないわよ。覚悟してね</t>
+          <t xml:space="preserve">あら、可愛い相手ね。すぐ終わらせてあげるわ</t>
         </is>
       </c>
     </row>
     <row r="302" ht="40" customHeight="1">
       <c r="A302" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.seductive.bold[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B302" t="inlineStr" s="2">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="C302" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D302" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.bold[1]</t>
+          <t xml:space="preserve">preMatch.seductive.bold[2]</t>
         </is>
       </c>
       <c r="E302" t="inlineStr" s="2">
@@ -9993,14 +9993,14 @@
       </c>
       <c r="F302" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ずっと待ってたのよ、この瞬間を……！ふふ、最高の気分ね</t>
+          <t xml:space="preserve">私に勝てるつもり？ 甘いわね</t>
         </is>
       </c>
     </row>
     <row r="303" ht="40" customHeight="1">
       <c r="A303" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.seductive.bold[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B303" t="inlineStr" s="2">
@@ -10010,12 +10010,12 @@
       </c>
       <c r="C303" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D303" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.bold[1]</t>
+          <t xml:space="preserve">summon.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E303" t="inlineStr" s="2">
@@ -10025,14 +10025,14 @@
       </c>
       <c r="F303" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら…随分と自信がおありのようね。壊してあげるわ</t>
+          <t xml:space="preserve">あら、指名してくれたの？ 嬉しいわ</t>
         </is>
       </c>
     </row>
     <row r="304" ht="40" customHeight="1">
       <c r="A304" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.seductive.bold[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B304" t="inlineStr" s="2">
@@ -10042,12 +10042,12 @@
       </c>
       <c r="C304" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D304" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.bold[2]</t>
+          <t xml:space="preserve">summon.seductive.bold[2]</t>
         </is>
       </c>
       <c r="E304" t="inlineStr" s="2">
@@ -10057,14 +10057,14 @@
       </c>
       <c r="F304" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">可哀想だけど…手加減はしないわよ</t>
+          <t xml:space="preserve">私の舞台が増えるのね。楽しみ</t>
         </is>
       </c>
     </row>
     <row r="305" ht="40" customHeight="1">
       <c r="A305" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.seductive.bold[1]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B305" t="inlineStr" s="2">
@@ -10074,7 +10074,7 @@
       </c>
       <c r="C305" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D305" t="inlineStr" s="12">
@@ -10089,14 +10089,14 @@
       </c>
       <c r="F305" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、残念。もっと遊びたかったのに</t>
+          <t xml:space="preserve">容赦しないわよ。覚悟してね</t>
         </is>
       </c>
     </row>
     <row r="306" ht="40" customHeight="1">
       <c r="A306" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.seductive.bold[2]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B306" t="inlineStr" s="2">
@@ -10106,12 +10106,12 @@
       </c>
       <c r="C306" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D306" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.bold[2]</t>
+          <t xml:space="preserve">seductive.bold[1]</t>
         </is>
       </c>
       <c r="E306" t="inlineStr" s="2">
@@ -10121,14 +10121,14 @@
       </c>
       <c r="F306" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">逃げちゃうの？ …つまらない団体ね</t>
+          <t xml:space="preserve">ずっと待ってたのよ、この瞬間を……！ふふ、最高の気分ね</t>
         </is>
       </c>
     </row>
     <row r="307" ht="40" customHeight="1">
       <c r="A307" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.seductive.bold[1]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B307" t="inlineStr" s="2">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="C307" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D307" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.seductive.bold[1]</t>
+          <t xml:space="preserve">seductive.bold[1]</t>
         </is>
       </c>
       <c r="E307" t="inlineStr" s="2">
@@ -10153,14 +10153,14 @@
       </c>
       <c r="F307" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら…やられちゃったわ。……許さないけど</t>
+          <t xml:space="preserve">あら…随分と自信がおありのようね。壊してあげるわ</t>
         </is>
       </c>
     </row>
     <row r="308" ht="40" customHeight="1">
       <c r="A308" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.seductive.bold[2]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B308" t="inlineStr" s="2">
@@ -10170,12 +10170,12 @@
       </c>
       <c r="C308" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D308" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.seductive.bold[2]</t>
+          <t xml:space="preserve">seductive.bold[2]</t>
         </is>
       </c>
       <c r="E308" t="inlineStr" s="2">
@@ -10185,14 +10185,14 @@
       </c>
       <c r="F308" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日は譲ってあげるわ。次は…ないけどね</t>
+          <t xml:space="preserve">可哀想だけど…手加減はしないわよ</t>
         </is>
       </c>
     </row>
     <row r="309" ht="40" customHeight="1">
       <c r="A309" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.seductive.bold[1]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B309" t="inlineStr" s="2">
@@ -10202,12 +10202,12 @@
       </c>
       <c r="C309" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D309" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.seductive.bold[1]</t>
+          <t xml:space="preserve">seductive.bold[1]</t>
         </is>
       </c>
       <c r="E309" t="inlineStr" s="2">
@@ -10217,14 +10217,14 @@
       </c>
       <c r="F309" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、もう終わり？ もっと楽しみたかったのに</t>
+          <t xml:space="preserve">あら、残念。もっと遊びたかったのに</t>
         </is>
       </c>
     </row>
     <row r="310" ht="40" customHeight="1">
       <c r="A310" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.seductive.bold[2]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B310" t="inlineStr" s="2">
@@ -10234,12 +10234,12 @@
       </c>
       <c r="C310" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D310" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.seductive.bold[2]</t>
+          <t xml:space="preserve">seductive.bold[2]</t>
         </is>
       </c>
       <c r="E310" t="inlineStr" s="2">
@@ -10249,14 +10249,14 @@
       </c>
       <c r="F310" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">予想通りの結果ね。つまらないわ</t>
+          <t xml:space="preserve">逃げちゃうの？ …つまらない団体ね</t>
         </is>
       </c>
     </row>
     <row r="311" ht="40" customHeight="1">
       <c r="A311" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.seductive.bold[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B311" t="inlineStr" s="2">
@@ -10266,12 +10266,12 @@
       </c>
       <c r="C311" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D311" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.bold[1]</t>
+          <t xml:space="preserve">result_lose.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E311" t="inlineStr" s="2">
@@ -10281,14 +10281,14 @@
       </c>
       <c r="F311" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">当然よ。うちの団体を甘く見ないことね</t>
+          <t xml:space="preserve">あら…やられちゃったわ。……許さないけど</t>
         </is>
       </c>
     </row>
     <row r="312" ht="40" customHeight="1">
       <c r="A312" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.seductive.bold[2]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B312" t="inlineStr" s="2">
@@ -10298,12 +10298,12 @@
       </c>
       <c r="C312" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D312" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.bold[2]</t>
+          <t xml:space="preserve">result_lose.seductive.bold[2]</t>
         </is>
       </c>
       <c r="E312" t="inlineStr" s="2">
@@ -10313,14 +10313,14 @@
       </c>
       <c r="F312" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ物足りないわね。もっと強い相手はいないの？</t>
+          <t xml:space="preserve">今日は譲ってあげるわ。次は…ないけどね</t>
         </is>
       </c>
     </row>
     <row r="313" ht="40" customHeight="1">
       <c r="A313" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.seductive.bold[3]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B313" t="inlineStr" s="2">
@@ -10330,12 +10330,12 @@
       </c>
       <c r="C313" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D313" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.bold[3]</t>
+          <t xml:space="preserve">result_win.seductive.bold[1]</t>
         </is>
       </c>
       <c r="E313" t="inlineStr" s="2">
@@ -10345,14 +10345,14 @@
       </c>
       <c r="F313" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">当然の結果よ。うちを甘く見ないことね</t>
+          <t xml:space="preserve">あら、もう終わり？ もっと楽しみたかったのに</t>
         </is>
       </c>
     </row>
     <row r="314" ht="40" customHeight="1">
       <c r="A314" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.seductive.bold[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.seductive.bold[2]</t>
         </is>
       </c>
       <c r="B314" t="inlineStr" s="2">
@@ -10362,29 +10362,29 @@
       </c>
       <c r="C314" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D314" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.seductive.bold[1]</t>
+          <t xml:space="preserve">result_win.seductive.bold[2]</t>
         </is>
       </c>
       <c r="E314" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F314" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頂点に立ったわ。でもまだ先があるみたいね</t>
+          <t xml:space="preserve">予想通りの結果ね。つまらないわ</t>
         </is>
       </c>
     </row>
     <row r="315" ht="40" customHeight="1">
       <c r="A315" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.seductive.bold[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.seductive.bold[1]</t>
         </is>
       </c>
       <c r="B315" t="inlineStr" s="2">
@@ -10394,7 +10394,7 @@
       </c>
       <c r="C315" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D315" t="inlineStr" s="12">
@@ -10404,49 +10404,177 @@
       </c>
       <c r="E315" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F315" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">拾った目利きは正解よ。…すぐに分かるわ</t>
+          <t xml:space="preserve">当然よ。うちの団体を甘く見ないことね</t>
         </is>
       </c>
     </row>
     <row r="316" ht="40" customHeight="1">
       <c r="A316" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.seductive.bold[2]</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">seductive.bold[2]</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">まだ物足りないわね。もっと強い相手はいないの？</t>
+        </is>
+      </c>
+    </row>
+    <row r="317" ht="40" customHeight="1">
+      <c r="A317" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.seductive.bold[3]</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">seductive.bold[3]</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">当然の結果よ。うちを甘く見ないことね</t>
+        </is>
+      </c>
+    </row>
+    <row r="318" ht="40" customHeight="1">
+      <c r="A318" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">ENDING_LINES.fighter.seductive.bold[1]</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ENDING_LINES</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">fighter.seductive.bold[1]</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">頂点に立ったわ。でもまだ先があるみたいね</t>
+        </is>
+      </c>
+    </row>
+    <row r="319" ht="40" customHeight="1">
+      <c r="A319" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.seductive.bold[1]</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">seductive.bold[1]</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">拾った目利きは正解よ。…すぐに分かるわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="320" ht="40" customHeight="1">
+      <c r="A320" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES.seductive.bold[1]</t>
         </is>
       </c>
-      <c r="B316" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C316" t="inlineStr" s="2">
+      <c r="B320" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
-      <c r="D316" t="inlineStr" s="12">
+      <c r="D320" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">seductive.bold[1]</t>
         </is>
       </c>
-      <c r="E316" t="inlineStr" s="2">
+      <c r="E320" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
-      <c r="F316" t="inlineStr" s="3">
+      <c r="F320" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">私に声をかけた責任は、取ってちょうだいね</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H316"/>
+  <autoFilter ref="A1:H320"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/蠱惑×強気.xlsx
+++ b/セリフ編集/キャラタイプ別/蠱惑×強気.xlsx
@@ -2245,7 +2245,7 @@
       </c>
       <c r="F60" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、{org}のあの女、私にやらせて。</t>
+          <t xml:space="preserve">社長、あの団体、私たち三人にやらせて。</t>
         </is>
       </c>
     </row>
@@ -2277,7 +2277,7 @@
       </c>
       <c r="F61" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">気に入らない女がいるの。……そいつと、やらせてほしいのよ。</t>
+          <t xml:space="preserve">気に入らない連中がいるの。……三人で、やらせてほしいのよ。</t>
         </is>
       </c>
     </row>
@@ -2309,7 +2309,7 @@
       </c>
       <c r="F62" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">身の程を教えてあげたい相手がいるの。組んでくれる？</t>
+          <t xml:space="preserve">身の程を教えてあげたい団体があるの。三人で組んでくれる？</t>
         </is>
       </c>
     </row>
